--- a/Sources/Event_scrapper_-_Website_completed.xlsx
+++ b/Sources/Event_scrapper_-_Website_completed.xlsx
@@ -3,11 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="India" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="USA" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UK" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -8893,7 +8894,7 @@
         </is>
       </c>
     </row>
-    <row r="188">
+    <row r="188" ht="28.8" customHeight="1">
       <c r="A188" t="n">
         <v>187</v>
       </c>
@@ -9953,4 +9954,2857 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D187"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="4.88671875" customWidth="1" min="1" max="1"/>
+    <col width="31.6640625" customWidth="1" min="2" max="3"/>
+    <col width="31.21875" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Organisation / Website</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Event Page</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Chartered Institute of Taxation (CIOT)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28.8" customHeight="1">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Association of Taxation Technicians (ATT)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28.8" customHeight="1">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Chartered Institute of Payroll Professionals (CIPP)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Tax / Payroll</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ICAEW</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Accounting / Finance / Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ACCA UK</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Accounting / Finance / Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ICAS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Accounting / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AAT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Accounting / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CIPFA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Public Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28.8" customHeight="1">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Association of Corporate Treasurers (ACT)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Finance / Treasury</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CISI</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Finance / Investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CFA UK</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Investment / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pensions UK</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Pensions / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>The Investment Association</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Investment / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>UKSIF</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Finance / ESG</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28.8" customHeight="1">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Institute of Internal Auditors UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Audit / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28.8" customHeight="1">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Chartered Governance Institute UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Governance / Legal / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Investor Relations Society</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Tax / Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>The Law Society of England &amp; Wales</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bar Council of England &amp; Wales</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CILEX</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Law Society of Scotland</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Law Society of Northern Ireland</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28.8" customHeight="1">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Chartered Institute of Arbitrators (CIArb)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Legal / Arbitration</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BIICL</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>International Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Employment Lawyers Association</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Employment Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Insolvency Lawyers' Association</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Legal / Insolvency</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Insolvency / Finance / Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Association of Costs Lawyers</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Civil Mediation Council</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Legal / ADR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Family Law Bar Association</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Chancery Bar Association</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Legal / Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>COMBAR</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Commercial Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>TECBAR</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28.8" customHeight="1">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Chartered Institute of Credit Management</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Credit / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Association of Corporate Counsel</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Legal / Corporate</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CIMA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Accounting / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Institute of Financial Accountants</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Accounting / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Chartered Management Institute</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Management / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Pensions Management Institute</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Pensions / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Personal Finance Society</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Financial Planning</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Society of Pension Professionals</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Pensions / Legal / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ICAEW Tax Faculty</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>VAT Practitioners Group</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>VAT / Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>British Academy of Forensic Sciences</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Legal / Forensics</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28.8" customHeight="1">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Association of Tax Technicians Scotland</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28.8" customHeight="1">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Chartered Institute of Securities &amp; Investment</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Finance / Investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28.8" customHeight="1">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Institute of Chartered Accountants in England &amp; Wales</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Accounting / Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28.8" customHeight="1">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Institute of Chartered Accountants of Scotland</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Accounting / Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28.8" customHeight="1">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Association of International Accountants</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Accounting / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Finance &amp; Leasing Association (FLA)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Finance / Leasing</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="28.8" customHeight="1">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Institute of Legal Finance &amp; Management (ILFM)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Legal Finance / Compliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Institute for Fiscal Studies (IFS)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Tax / Public Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28.8" customHeight="1">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>International Fiscal Association UK Branch</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>International Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Finance Innovation Lab</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Finance / Financial Innovation</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="28.8" customHeight="1">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Association for Financial Markets in Europe (AFME)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>London Institute of Banking &amp; Finance</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Finance / Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Financial Markets Standards Board</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Financial Markets / Regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="28.8" customHeight="1">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>International Securities Lending Association (ISLA)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Securities / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="28.8" customHeight="1">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Association of Corporate Counsel Europe</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Corporate Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Environmental Law Association</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Environmental Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="28.8" customHeight="1">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Planning and Environmental Bar Association</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Planning / Environmental Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Administrative Law Bar Association</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Public / Administrative Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>British Maritime Law Association</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Maritime Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Society of Construction Law UK</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Construction Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Society for Computers and Law</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Technology / Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="28.8" customHeight="1">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>British Intellectual Property Lawyers' Association</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Intellectual Property Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>IP Federation</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Intellectual Property</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="28.8" customHeight="1">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Licensing Executives Society Britain &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>IP / Commercial Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Competition Law Association</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Competition Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="28.8" customHeight="1">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Financial Services Lawyers Association</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Financial Services Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Insolvency Practitioners Association</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Insolvency / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="28.8" customHeight="1">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Turnaround Management Association UK</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Restructuring / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="28.8" customHeight="1">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Credit Services Association</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Credit / Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Institute of Risk Management</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Risk / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>International Compliance Association</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Compliance / Financial Crime</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Compliance Institute UK</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Compliance / Regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Association of Business Professionals</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Business / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Association of Corporate Counsel UK</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Corporate Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Institute of Chartered Accountants in Ireland</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Accounting / Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="28.8" customHeight="1">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Association of Chartered Certified Accountants Ireland</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Accounting / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="28.8" customHeight="1">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Tax Research LLP / Tax Research Network</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="28.8" customHeight="1">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Chartered Institute of Payroll Professionals Scotland</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Payroll / Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="28.8" customHeight="1">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Association of Corporate Services Providers</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Corporate / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="28.8" customHeight="1">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Society of Trust and Estate Practitioners Scotland</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Tax / Legal / Private Client</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="28.8" customHeight="1">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Association of Taxation Technicians Northern Ireland</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="28.8" customHeight="1">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Northern Ireland Chamber of Commerce</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Business / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="28.8" customHeight="1">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Scottish Financial Enterprise</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Scottish Property Federation</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Property / Finance / Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Scottish Arbitration Centre</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Arbitration / Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Scottish Young Lawyers' Association</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Scottish Planning and Environmental Law</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Planning / Environmental Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="28.8" customHeight="1">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>UK Environmental Law Association Scotland</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Environmental Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="28.8" customHeight="1">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>British Insurance Law Association</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Insurance Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Association of Pension Lawyers</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Pensions / Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Pensions Research Accountants Group</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Pensions / Accounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="28.8" customHeight="1">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Institute of Chartered Accountants of England and Wales, Insolvency Community</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Insolvency / Accounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Association of Corporate Treasurers Ireland</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Finance / Treasury</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="28.8" customHeight="1">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>British Academy of Management</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Business / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="43.2" customHeight="1">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>British Accounting &amp; Finance Association</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Accounting / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="28.8" customHeight="1">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>European Finance Association</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Finance / Economics</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Royal Economic Society</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Economics / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="28.8" customHeight="1">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Society of Business Economists</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Economics / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>UK Economic Regulators Network</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Regulation / Economics</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>UK Parliament Treasury Committee</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Tax / Public Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>National Audit Office</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Public Finance / Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Public Accounts Committee</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Public Finance / Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Institute for Government</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Public Policy / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Resolution Foundation</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Economics / Public Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Tax Justice UK</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Tax / Public Policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Chartered Institute of Public Finance and Accountancy Network</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Public Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Public Finance by CIPFA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Public Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>UK Tax Research LLP</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="28.8" customHeight="1">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>TaxPayers' Alliance</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Tax / Public Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Association of Accounting Technicians Northern Ireland</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Accounting / Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Chartered Accountants Benevolent Association</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Accounting / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>British Accounting &amp; Finance Association Northern Region</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Accounting / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="28.8" customHeight="1">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>British Institute of Energy Economics</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Energy / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="28.8" customHeight="1">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Energy UK</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Energy / Regulation / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="28.8" customHeight="1">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>UK Steel</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Industry / Finance / Regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>British Retail Consortium</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Business / Tax / Regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>British Property Federation</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Property / Finance / Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Royal Institution of Chartered Surveyors</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Property / Finance / Regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Association of Property Lenders</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Property Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Commercial Finance Association UK</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Commercial Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="28.8" customHeight="1">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>UK Finance and Leasing Association</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Asset Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>British Venture Capital Association</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Investment / Private Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>UK Private Equity &amp; Venture Capital Association</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Investment / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Venture Capital Association UK</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Venture Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>British Private Equity &amp; Venture Capital Association</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Private Equity / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="28.8" customHeight="1">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Association of Investment Companies</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Investment / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>UK Society of Investment Professionals</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Investment / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="28.8" customHeight="1">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Alternative Investment Management Association</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Alternative Investment / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Hedge Fund Standards Board</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Investment / Regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="28.8" customHeight="1">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Institutional Investors Group on Climate Change</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Investment / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="28.8" customHeight="1">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>UK Shareholders' Association</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Investment / Corporate Governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Quoted Companies Alliance</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Corporate Finance / Governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="28.8" customHeight="1">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Association of Financial Mutuals</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Financial Services / Regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Building Societies Association</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Finance / Regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Association of Financial Markets in Europe</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Capital Markets / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>International Capital Market Association</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Capital Markets / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>International Securities Association</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Securities / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="28.8" customHeight="1">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>International Securities Lending Association</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Securities / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="28.8" customHeight="1">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>London Bullion Market Association</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Financial Markets / Commodities</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>London Metal Exchange</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Financial Markets / Commodities</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="28.8" customHeight="1">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Futures Industry Association</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Derivatives / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Association of Legal Compliance &amp; Accounts (ALCA)</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Legal Finance / Compliance / VAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Institute of Chartered Accountants of India UK Chapter</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Accounting / Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Association of Certified Fraud Examiners UK Chapter</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Fraud / Finance / Compliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="28.8" customHeight="1">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Fraud Advisory Panel</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Fraud / Financial Crime</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="28.8" customHeight="1">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>UK Finance Institute of Financial Services</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Finance / Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="28.8" customHeight="1">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Chartered Institute for Securities &amp; Investment Wales</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Investment / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>CFA Society United Kingdom</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Investment / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="28.8" customHeight="1">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Society of Financial Advisers</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Financial Advice / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="28.8" customHeight="1">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Personal Finance Society Scotland</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Financial Planning</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Society of Mortgage Professionals</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Finance / Mortgages</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="28.8" customHeight="1">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Association of Short Term Lenders</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Property Finance / Lending</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Association of Bridging Professionals</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Property Finance / Lending</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>British Business Bank</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Business Finance / Investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="28.8" customHeight="1">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>UK Business Angels Association</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Investment / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="28.8" customHeight="1">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>UK Crowdfunding Association</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Finance / Investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="28.8" customHeight="1">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Pensions and Lifetime Savings Association</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Pensions / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Association of Consulting Actuaries</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Actuarial / Pensions / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Institute and Faculty of Actuaries</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Actuarial / Finance / Risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Association of Corporate Treasurers</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Treasury / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>British Institute of International and Comparative Law</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>International Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="28.8" customHeight="1">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Immigration Law Practitioners' Association</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Property Litigation Association</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Property Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Intellectual Property Lawyers' Association</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Intellectual Property Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Society of Professional Accountants (SPA)</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Accounting / Tax / Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="28.8" customHeight="1">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Association of Charity Independent Examiners (ACIE)</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Accounting / Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Worshipful Company of Tax Advisers</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="28.8" customHeight="1">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Association of Legal Compliance &amp; Accounts</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Legal Finance / Compliance / VAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="28.8" customHeight="1">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Institute of Legal Finance &amp; Management</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Legal Finance / Accounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Institute of Actuaries</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Actuarial / Finance / Risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Association of Certified Fraud Examiners UK</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Fraud / Finance / Compliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Finance &amp; Leasing Association</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Finance / Credit / Regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Institute of Financial Markets</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Association for Financial Markets in Europe</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Capital Markets / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>International Swaps and Derivatives Association</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Derivatives / Financial Regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Global Legal Post</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>International Bar Association</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>International Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="28.8" customHeight="1">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Institute of Economic Affairs</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Economics / Public Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Institute for Fiscal Studies</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Tax / Public Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Association of Independent Examiners</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Audit / Accounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Institute of Government &amp; Public Policy</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Public Policy / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="28.8" customHeight="1"/>
+    <row r="193" ht="28.8" customHeight="1"/>
+    <row r="196" ht="28.8" customHeight="1"/>
+    <row r="200" ht="28.8" customHeight="1"/>
+    <row r="201" ht="28.8" customHeight="1"/>
+    <row r="202" ht="28.8" customHeight="1"/>
+    <row r="203" ht="28.8" customHeight="1"/>
+    <row r="205" ht="28.8" customHeight="1"/>
+    <row r="206" ht="28.8" customHeight="1"/>
+    <row r="207" ht="28.8" customHeight="1"/>
+    <row r="208" ht="28.8" customHeight="1"/>
+    <row r="211" ht="28.8" customHeight="1"/>
+    <row r="214" ht="28.8" customHeight="1"/>
+    <row r="217" ht="28.8" customHeight="1"/>
+    <row r="218" ht="28.8" customHeight="1"/>
+    <row r="219" ht="28.8" customHeight="1"/>
+    <row r="224" ht="28.8" customHeight="1"/>
+    <row r="227" ht="28.8" customHeight="1"/>
+    <row r="237" ht="28.8" customHeight="1"/>
+    <row r="238" ht="28.8" customHeight="1"/>
+    <row r="250" ht="28.8" customHeight="1"/>
+    <row r="251" ht="28.8" customHeight="1"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Sources/Event_scrapper_-_Website_completed.xlsx
+++ b/Sources/Event_scrapper_-_Website_completed.xlsx
@@ -10006,6 +10006,11 @@
           <t>Tax</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.tax.org.uk/events</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="28.8" customHeight="1">
       <c r="A3" t="n">
@@ -10021,6 +10026,11 @@
           <t>Tax</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.att.org.uk/events</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="28.8" customHeight="1">
       <c r="A4" t="n">
@@ -10036,6 +10046,11 @@
           <t>Tax / Payroll</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.cipp.org.uk/events.html</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -10051,6 +10066,11 @@
           <t>Accounting / Finance / Tax</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.icaew.com/learning-and-development/events</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -10066,6 +10086,11 @@
           <t>Accounting / Finance / Tax</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.accaglobal.com/learning-and-events.html</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -10081,6 +10106,11 @@
           <t>Accounting / Finance</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.icas.com/news-insights-events/upcoming-events</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -10096,6 +10126,11 @@
           <t>Accounting / Finance</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.aat.org.uk/events/search</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -10111,6 +10146,11 @@
           <t>Public Finance</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.cipfa.org/training/cipfa-conferences</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="28.8" customHeight="1">
       <c r="A10" t="n">
@@ -10126,6 +10166,11 @@
           <t>Finance / Treasury</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.treasurers.org/events</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -10141,6 +10186,11 @@
           <t>Finance / Investment</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.cisi.org/cisiweb2/shop/events</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -10156,6 +10206,11 @@
           <t>Investment / Finance</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.cfauk.org/events/events-listing</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -10171,6 +10226,11 @@
           <t>Pensions / Finance</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.plsa.co.uk/Events</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -10186,6 +10246,11 @@
           <t>Investment / Finance</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.theia.org/events-training</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -10201,6 +10266,11 @@
           <t>Finance / ESG</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://uksif.org/category/events/</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="28.8" customHeight="1">
       <c r="A16" t="n">
@@ -10231,6 +10301,11 @@
           <t>Governance / Legal / Finance</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.cgi.org.uk/events/</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10246,6 +10321,11 @@
           <t>Finance</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://irsociety.org.uk/events</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10261,6 +10341,11 @@
           <t>Tax / Legal</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.step.org/events</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -10276,6 +10361,11 @@
           <t>Legal</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.lawsociety.org.uk/events</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -10291,6 +10381,11 @@
           <t>Legal</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.barcouncil.org.uk/training-events/calendar.html</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -10306,6 +10401,11 @@
           <t>Legal</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.cilex.org.uk/membership/events.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -10321,6 +10421,11 @@
           <t>Legal</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.lawscot.org.uk/news-and-events/events/</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -10336,6 +10441,11 @@
           <t>Legal</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://lawsoc-ni.org/about-the-law-society/news-events/events</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="28.8" customHeight="1">
       <c r="A25" t="n">
@@ -10351,6 +10461,11 @@
           <t>Legal / Arbitration</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.ciarb.org/events/</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -10366,6 +10481,11 @@
           <t>International Law</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.biicl.org/events</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -10381,6 +10501,11 @@
           <t>Employment Law</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.elaweb.org.uk/future-events</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -10396,6 +10521,11 @@
           <t>Legal / Insolvency</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.ilauk.com/news-events/upcoming-events</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -10411,6 +10541,11 @@
           <t>Insolvency / Finance / Legal</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.r3.org.uk/events-training/</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -10426,6 +10561,11 @@
           <t>Legal</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://associationofcostslawyers.co.uk/events/</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -10441,6 +10581,11 @@
           <t>Legal / ADR</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://civilmediation.org/news-events/</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -10456,6 +10601,11 @@
           <t>Legal</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.flba.co.uk/events/</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -10471,6 +10621,11 @@
           <t>Legal / Tax</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.chba.org.uk/for-members/library/seminars</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -10486,6 +10641,11 @@
           <t>Commercial Law</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.combar.com/news-and-events/events/</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -10501,6 +10661,11 @@
           <t>Legal</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://tecbar.org/events/</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="28.8" customHeight="1">
       <c r="A36" t="n">
@@ -10516,6 +10681,11 @@
           <t>Credit / Finance</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.cicm.com/cicm-events/</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -10531,6 +10701,11 @@
           <t>Legal / Corporate</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.acc.com/education-events</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -10546,6 +10721,11 @@
           <t>Accounting / Finance</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.aicpa-cima.com/cpe-learning/event</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -10561,6 +10741,11 @@
           <t>Accounting / Finance</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.ifa.org.uk/cpd</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -10576,6 +10761,11 @@
           <t>Management / Finance</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.managers.org.uk/community/events/</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -10591,6 +10781,11 @@
           <t>Pensions / Finance</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.pensions-pmi.org.uk/events/</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -10606,6 +10801,11 @@
           <t>Financial Planning</t>
         </is>
       </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://events.thepfs.org/</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -10621,6 +10821,11 @@
           <t>Pensions / Legal / Finance</t>
         </is>
       </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://the-spp.co.uk/events/upcoming-events/</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -10636,6 +10841,11 @@
           <t>Tax</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.icaew.com/en/technical/tax/tax-faculty/tax-faculty-events</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -10651,6 +10861,11 @@
           <t>VAT / Tax</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://vpgweb.com/</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -10666,6 +10881,11 @@
           <t>Legal / Forensics</t>
         </is>
       </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.bafs.org.uk/events/past-events.php</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="28.8" customHeight="1">
       <c r="A47" t="n">
@@ -10681,6 +10901,11 @@
           <t>Tax</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.att.org.uk/edinburgh</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="28.8" customHeight="1">
       <c r="A48" t="n">
@@ -10696,6 +10921,11 @@
           <t>Finance / Investment</t>
         </is>
       </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.cisi.org/events</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="28.8" customHeight="1">
       <c r="A49" t="n">
@@ -10711,6 +10941,11 @@
           <t>Accounting / Tax</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.icaew.com/events-support</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="28.8" customHeight="1">
       <c r="A50" t="n">
@@ -10741,6 +10976,11 @@
           <t>Accounting / Finance</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.aiaworldwide.com/cpd/events/</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -10756,6 +10996,11 @@
           <t>Finance / Leasing</t>
         </is>
       </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://fla.org.uk/events/</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="28.8" customHeight="1">
       <c r="A53" t="n">
@@ -10771,6 +11016,11 @@
           <t>Legal Finance / Compliance</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.ilfm.org.uk/site/training-and-events/</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -10786,6 +11036,11 @@
           <t>Tax / Public Finance</t>
         </is>
       </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://ifs.org.uk/events</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="28.8" customHeight="1">
       <c r="A55" t="n">
@@ -10801,6 +11056,11 @@
           <t>International Tax</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://ifa-uk.org/events/</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -10816,6 +11076,11 @@
           <t>Finance / Financial Innovation</t>
         </is>
       </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://financeinnovationlab.org/events/</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="28.8" customHeight="1">
       <c r="A57" t="n">
@@ -10831,6 +11096,11 @@
           <t>Financial Markets</t>
         </is>
       </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.afme.eu/events</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -10861,6 +11131,11 @@
           <t>Financial Markets / Regulation</t>
         </is>
       </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://fmsb.com/events/</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="28.8" customHeight="1">
       <c r="A60" t="n">
@@ -10876,6 +11151,11 @@
           <t>Securities / Finance</t>
         </is>
       </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://www.islaemea.org/isla-events/</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="28.8" customHeight="1">
       <c r="A61" t="n">
@@ -10891,6 +11171,11 @@
           <t>Corporate Legal</t>
         </is>
       </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://www.acc.com/chapters-networks/chapters/europe/events-europe</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -10906,6 +11191,11 @@
           <t>Environmental Law</t>
         </is>
       </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.ukela.org/UKELA/UKELA/Events/Annual-Conference.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="28.8" customHeight="1">
       <c r="A63" t="n">
@@ -10921,6 +11211,11 @@
           <t>Planning / Environmental Law</t>
         </is>
       </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://peba.org.uk/news-events/</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -10936,6 +11231,11 @@
           <t>Public / Administrative Law</t>
         </is>
       </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://adminlaw.org.uk/events/</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -10966,6 +11266,11 @@
           <t>Construction Law</t>
         </is>
       </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.scl.org.uk/events</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -10981,6 +11286,11 @@
           <t>Technology / Legal</t>
         </is>
       </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.scl.org/events/event/</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="28.8" customHeight="1">
       <c r="A68" t="n">
@@ -11026,6 +11336,11 @@
           <t>IP / Commercial Law</t>
         </is>
       </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://les-bi.org/events-calendar/</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -11041,6 +11356,11 @@
           <t>Competition Law</t>
         </is>
       </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://competitionlawassociation.org.uk/events/</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="28.8" customHeight="1">
       <c r="A72" t="n">
@@ -11056,6 +11376,11 @@
           <t>Financial Services Law</t>
         </is>
       </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://fsla.org.uk/category/events/</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -11071,6 +11396,11 @@
           <t>Insolvency / Finance</t>
         </is>
       </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://insolvency-practitioners.org.uk/calendar-of-events/</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="28.8" customHeight="1">
       <c r="A74" t="n">
@@ -11086,6 +11416,11 @@
           <t>Restructuring / Finance</t>
         </is>
       </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://tma-uk.org/events/</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="28.8" customHeight="1">
       <c r="A75" t="n">
@@ -11101,6 +11436,11 @@
           <t>Credit / Financial Services</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://www.csa-uk.com/page/events</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -11116,6 +11456,11 @@
           <t>Risk / Finance</t>
         </is>
       </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://www.theirm.org/events/</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -11131,6 +11476,11 @@
           <t>Compliance / Financial Crime</t>
         </is>
       </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://www.int-comp.org/events/</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -11191,6 +11541,11 @@
           <t>Accounting / Tax</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://www.charteredaccountants.ie/professional-development/cpd-courses-and-networking-events</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="28.8" customHeight="1">
       <c r="A82" t="n">
@@ -11206,6 +11561,11 @@
           <t>Accounting / Finance</t>
         </is>
       </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://www.accaglobal.com/learning-and-events.html</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="28.8" customHeight="1">
       <c r="A83" t="n">
@@ -11221,6 +11581,11 @@
           <t>Tax</t>
         </is>
       </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://taxresearch.network/event/trn-26-london-registration/</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="28.8" customHeight="1">
       <c r="A84" t="n">
@@ -11266,6 +11631,11 @@
           <t>Tax / Legal / Private Client</t>
         </is>
       </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://www.step.org/branches/step-scotland</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="28.8" customHeight="1">
       <c r="A87" t="n">
@@ -11281,6 +11651,11 @@
           <t>Tax</t>
         </is>
       </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://www.att.org.uk/northern-ireland</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="28.8" customHeight="1">
       <c r="A88" t="n">
@@ -11296,6 +11671,11 @@
           <t>Business / Finance</t>
         </is>
       </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://www.northernirelandchamber.com/event/festival-of-business-2026/</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="28.8" customHeight="1">
       <c r="A89" t="n">
@@ -11311,6 +11691,11 @@
           <t>Financial Services</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://www.sfe.org.uk/events</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11326,6 +11711,11 @@
           <t>Property / Finance / Legal</t>
         </is>
       </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://scottishpropertyfederation.org.uk/events</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11341,6 +11731,11 @@
           <t>Arbitration / Legal</t>
         </is>
       </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://scottisharbitrationcentre.org/category/events-training/</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11356,6 +11751,11 @@
           <t>Legal</t>
         </is>
       </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.co.uk/o/scottish-young-lawyers-association-1867524801</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11386,6 +11786,11 @@
           <t>Environmental Law</t>
         </is>
       </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://www.ukela.org/UKELA/UKELA/Events/Annual-Conference.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="28.8" customHeight="1">
       <c r="A95" t="n">
@@ -11401,6 +11806,11 @@
           <t>Insurance Law</t>
         </is>
       </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://bila.org.uk/events/upcoming-events/</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11416,6 +11826,11 @@
           <t>Pensions / Legal</t>
         </is>
       </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>http://apl-live.aptsolutions.net/calendar.php?id=5</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11446,6 +11861,11 @@
           <t>Insolvency / Accounting</t>
         </is>
       </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://www.icaew.com/groups-and-networks/communities/restructuring-and-insolvency/restructuring-and-insolvency-community/events</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11461,6 +11881,11 @@
           <t>Finance / Treasury</t>
         </is>
       </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://treasurers.ie/events</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="28.8" customHeight="1">
       <c r="A100" t="n">
@@ -11476,6 +11901,11 @@
           <t>Business / Finance</t>
         </is>
       </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.bam.ac.uk/events-landing.html</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="43.2" customHeight="1">
       <c r="A101" t="n">
@@ -11491,6 +11921,11 @@
           <t>Accounting / Finance</t>
         </is>
       </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://www.bafa.ac.uk/events/upcoming-events.html</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="28.8" customHeight="1">
       <c r="A102" t="n">
@@ -11506,6 +11941,11 @@
           <t>Finance / Economics</t>
         </is>
       </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://www.efa-finance.org/efa-annual-meeting/</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11521,6 +11961,11 @@
           <t>Economics / Finance</t>
         </is>
       </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://res.org.uk/event-listing/res-2026-annual-conference/</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="28.8" customHeight="1">
       <c r="A104" t="n">
@@ -11536,6 +11981,11 @@
           <t>Economics / Finance</t>
         </is>
       </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://spe.org.uk/whats-on/events/</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11551,6 +12001,11 @@
           <t>Regulation / Economics</t>
         </is>
       </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://ukrn.org.uk/events/</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11566,6 +12021,11 @@
           <t>Tax / Public Finance</t>
         </is>
       </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://committees.parliament.uk/committee/158/treasury-committee/events/</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11596,6 +12056,11 @@
           <t>Public Finance / Audit</t>
         </is>
       </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://committees.parliament.uk/committee/127/public-accounts-committee/events/</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11611,6 +12076,11 @@
           <t>Public Policy / Finance</t>
         </is>
       </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://www.instituteforgovernment.org.uk/our-events</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11626,6 +12096,11 @@
           <t>Economics / Public Finance</t>
         </is>
       </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://www.resolutionfoundation.org/events/</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11656,6 +12131,11 @@
           <t>Public Finance</t>
         </is>
       </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://www.cipfa.org/training</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11671,6 +12151,11 @@
           <t>Public Finance</t>
         </is>
       </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://publicfinancelive.org/</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11701,6 +12186,11 @@
           <t>Tax / Public Finance</t>
         </is>
       </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://www.taxpayersalliance.com/events</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11731,6 +12221,11 @@
           <t>Accounting / Finance</t>
         </is>
       </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://www.caba.org.uk/online-events-feedback-and-outcomes.html</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -11761,6 +12256,11 @@
           <t>Energy / Finance</t>
         </is>
       </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://www.biee.org/</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="28.8" customHeight="1">
       <c r="A120" t="n">
@@ -11776,6 +12276,11 @@
           <t>Energy / Regulation / Finance</t>
         </is>
       </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>https://www.energy-uk.org.uk/events/</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="28.8" customHeight="1">
       <c r="A121" t="n">
@@ -11791,6 +12296,11 @@
           <t>Industry / Finance / Regulation</t>
         </is>
       </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://www.makeuk.org/news-and-events/events</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -11806,6 +12316,11 @@
           <t>Business / Tax / Regulation</t>
         </is>
       </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>https://brc.org.uk/news-and-events/events/</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -11821,6 +12336,11 @@
           <t>Property / Finance / Tax</t>
         </is>
       </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>https://bpf.org.uk/events/</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -11851,6 +12371,11 @@
           <t>Property Finance</t>
         </is>
       </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://the-apl.com/events/</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12331,6 +12856,11 @@
           <t>Finance / Mortgages</t>
         </is>
       </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>https://www.smp.org.uk/events/</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="28.8" customHeight="1">
       <c r="A158" t="n">
@@ -12346,6 +12876,11 @@
           <t>Property Finance / Lending</t>
         </is>
       </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>https://www.tickettailor.com/events/bdla</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -12376,6 +12911,11 @@
           <t>Business Finance / Investment</t>
         </is>
       </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>https://www.british-business-bank.co.uk/news-and-events/events</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="28.8" customHeight="1">
       <c r="A161" t="n">
@@ -12391,6 +12931,11 @@
           <t>Investment / Finance</t>
         </is>
       </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>https://ukbaa.org.uk/events/</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="28.8" customHeight="1">
       <c r="A162" t="n">
@@ -12421,6 +12966,11 @@
           <t>Pensions / Finance</t>
         </is>
       </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>https://www.pensionsuk.org.uk/Events</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -12436,6 +12986,11 @@
           <t>Actuarial / Pensions / Finance</t>
         </is>
       </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>https://aca.org.uk/events-dates/</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -12451,6 +13006,11 @@
           <t>Actuarial / Finance / Risk</t>
         </is>
       </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>https://www.actuaries.org.uk/learn-and-develop/events-calendar/events-save-date</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -12466,6 +13026,11 @@
           <t>Treasury / Finance</t>
         </is>
       </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>https://www.treasurers.org/events</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -12481,6 +13046,11 @@
           <t>International Law</t>
         </is>
       </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>https://www.biicl.org/events</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="28.8" customHeight="1">
       <c r="A168" t="n">
@@ -12496,6 +13066,11 @@
           <t>Legal</t>
         </is>
       </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>https://ilpa.org.uk/training-and-events-calendar/</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -12511,6 +13086,11 @@
           <t>Property Law</t>
         </is>
       </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>https://www.pla.org.uk/events</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -12541,6 +13121,11 @@
           <t>Accounting / Tax / Audit</t>
         </is>
       </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>https://spa.org.uk/webinars/</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="28.8" customHeight="1">
       <c r="A172" t="n">
@@ -12556,6 +13141,11 @@
           <t>Accounting / Audit</t>
         </is>
       </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>https://www.acie.org.uk/events</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -12571,6 +13161,11 @@
           <t>Tax</t>
         </is>
       </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>https://www.taxadvisers.org.uk/future-events/</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="28.8" customHeight="1">
       <c r="A174" t="n">
@@ -12586,6 +13181,11 @@
           <t>Legal Finance / Compliance / VAT</t>
         </is>
       </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>https://alca.org.uk/events/</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="28.8" customHeight="1">
       <c r="A175" t="n">
@@ -12601,6 +13201,11 @@
           <t>Legal Finance / Accounting</t>
         </is>
       </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>https://www.ilfm.org.uk/site/training-and-events/</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -12631,6 +13236,11 @@
           <t>Fraud / Finance / Compliance</t>
         </is>
       </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>https://acfeuk.co.uk/http-acfeuk-co-uk-events/</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -12646,6 +13256,11 @@
           <t>Finance / Credit / Regulation</t>
         </is>
       </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>https://fla.org.uk/events-and-training/events/</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -12676,6 +13291,11 @@
           <t>Capital Markets / Finance</t>
         </is>
       </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>https://www.afme.eu/events</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -12691,6 +13311,11 @@
           <t>Derivatives / Financial Regulation</t>
         </is>
       </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>https://www.isda.org/events</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -12721,6 +13346,11 @@
           <t>International Legal</t>
         </is>
       </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>https://www.ibanet.org/conferences</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="28.8" customHeight="1">
       <c r="A184" t="n">
@@ -12736,6 +13366,11 @@
           <t>Economics / Public Finance</t>
         </is>
       </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>https://iea.org.uk/events/</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -12749,6 +13384,11 @@
       <c r="C185" t="inlineStr">
         <is>
           <t>Tax / Public Finance</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>https://ifs.org.uk/events</t>
         </is>
       </c>
     </row>

--- a/Sources/Event_scrapper_-_Website_completed.xlsx
+++ b/Sources/Event_scrapper_-_Website_completed.xlsx
@@ -10286,6 +10286,11 @@
           <t>Audit / Finance</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://charterediia.org/events-calendar/</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="28.8" customHeight="1">
       <c r="A17" t="n">
@@ -10843,7 +10848,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.icaew.com/en/technical/tax/tax-faculty/tax-faculty-events</t>
+          <t>https://www.icaew.com/technical/tax/tax-faculty/tax-faculty-events</t>
         </is>
       </c>
     </row>

--- a/Sources/Event_scrapper_-_Website_completed.xlsx
+++ b/Sources/Event_scrapper_-_Website_completed.xlsx
@@ -3,12 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="India" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="USA" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UK" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SG" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UAE" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AUS" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -11216,7 +11219,7 @@
           <t>Planning / Environmental Law</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="10" t="inlineStr">
         <is>
           <t>https://peba.org.uk/news-events/</t>
         </is>
@@ -13450,6 +13453,8036 @@
     <row r="250" ht="28.8" customHeight="1"/>
     <row r="251" ht="28.8" customHeight="1"/>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D200"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="7.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="4.77734375" customWidth="1" min="1" max="1"/>
+    <col width="39.21875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="16.5546875" customWidth="1" min="3" max="3"/>
+    <col width="27.77734375" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="8.88671875" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Organisation</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Events Page</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Singapore Chartered Tax Professionals (SCTP)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Events Calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28.8" customHeight="1">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Institute of Singapore Chartered Accountants (ISCA)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Accounting / Finance</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Tax Academy of Singapore</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Events / Seminars &amp; Conferences</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ICAI Singapore Chapter</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Accounting / Tax</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.8" customHeight="1">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ACCA Singapore</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Accounting / Finance</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Events &amp; CPD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Law Society of Singapore</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Legal / Tax</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CPD Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Singapore Academy of Law (SAL)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Singapore Institute of Legal Education (SILE)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Events / CPD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28.8" customHeight="1">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Singapore International Arbitration Centre (SIAC)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Legal / Arbitration</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28.8" customHeight="1">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Singapore International Commercial Court (SICC)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Legal / Commercial Law</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28.8" customHeight="1">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Singapore Corporate Counsel Association (SCCA)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28.8" customHeight="1">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Singapore Institute of Directors (SID)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Governance / Finance</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="43.2" customHeight="1">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Singapore Association of the Institute of Chartered Secretaries and Administrators (SAICSA)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Governance / Corporate</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28.8" customHeight="1">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CFA Society Singapore</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Finance / Investment</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28.8" customHeight="1">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Investment Management Association of Singapore (IMAS)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Investment / Finance</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28.8" customHeight="1">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Securities Investors Association (Singapore) (SIAS)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Investment / Finance</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28.8" customHeight="1">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Singapore Venture &amp; Private Capital Association (SVCA)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Private Capital / Finance</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Singapore FinTech Association (SFA)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>FinTech / Finance</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Association of Banks in Singapore (ABS)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Banking / Finance</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Singapore Actuarial Society (SAS)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Finance / Actuarial</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28.8" customHeight="1">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Singapore Insurance Institute (SII)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Insurance / Finance</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28.8" customHeight="1">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Financial Planning Association of Singapore (FPAS)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Financial Planning</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28.8" customHeight="1">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Accounting and Corporate Regulatory Authority (ACRA)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Accounting / Regulation</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Event Highlights</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Inland Revenue Authority of Singapore (IRAS)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Events &amp; Seminars</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28.8" customHeight="1">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Monetary Authority of Singapore (MAS)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Finance / Regulation</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Intellectual Property Office of Singapore (IPOS)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>IP / Legal</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28.8" customHeight="1">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ministry of Finance Singapore (MOF)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Tax / Finance / Policy</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Events &amp; Announcements</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Singapore Business Federation (SBF)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Business / Finance</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="43.2" customHeight="1">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Singapore International Chamber of Commerce (SICC)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Business / Professional Services</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28.8" customHeight="1">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Singapore Chinese Chamber of Commerce &amp; Industry (SCCCI)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Business / Finance</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28.8" customHeight="1">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Association of Small &amp; Medium Enterprises (ASME)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Business / Finance</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Singapore Manufacturing Federation (SMF)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Business / Finance</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Singapore Logistics Association (SLA)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Business / Trade</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28.8" customHeight="1">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Enterprise Singapore</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Business / Investment</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28.8" customHeight="1">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Singapore Economic Development Board (EDB)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Investment / Business</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28.8" customHeight="1">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>STEP Singapore</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Tax / Private Wealth</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28.8" customHeight="1">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>International Fiscal Association (IFA) Singapore Branch</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>International Tax</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28.8" customHeight="1">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Singapore Tax Academy Research Initiative (STARI)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>International Tax</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>STARI Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28.8" customHeight="1">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Institute of Valuers and Appraisers, Singapore (IVAS)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Valuation / Finance</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28.8" customHeight="1">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Singapore Chamber of Maritime Arbitration (SCMA)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Legal / Arbitration</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28.8" customHeight="1">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Singapore Mediation Centre (SMC)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Legal / Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28.8" customHeight="1">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Singapore International Chamber of Commerce Arbitration / Legal community</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Legal / Arbitration</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SICC / SICC Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28.8" customHeight="1">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Singapore Computer Society (SCS)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Technology / Professional</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28.8" customHeight="1">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Singapore Institute of Management (SIM)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Professional / Finance</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28.8" customHeight="1">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Singapore Human Resources Institute (SHRI)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Professional / Employment Law</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28.8" customHeight="1">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Marketing Institute of Singapore (MIS)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Professional / Business</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28.8" customHeight="1">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Singapore Institute of Purchasing &amp; Materials Management (SIPMM)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Business / Management</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28.8" customHeight="1">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Singapore Management University – Centre for Commercial Law Studies</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Commercial / Legal</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28.8" customHeight="1">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Singapore Management University – Yong Pung How School of Law</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28.8" customHeight="1">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Singapore Management University – Centre for AI &amp; Data Governance</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Legal / Regulation / Finance</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="28.8" customHeight="1">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Association of Corporate Treasurers Singapore (ACTS)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Treasury / Finance</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="28.8" customHeight="1">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Risk and Insurance Management Association of Singapore (RIMAS)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Risk Management</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Events / Calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28.8" customHeight="1">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Institute of Internal Auditors Singapore (IIA Singapore)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Internal Audit / Governance</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28.8" customHeight="1">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ISACA Singapore Chapter</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>IT Audit / Governance / Risk</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Chapter Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="28.8" customHeight="1">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ISC2 Singapore Chapter</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Cybersecurity / Risk / Governance</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Singapore Institute of Arbitrators (SIArb)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Legal / Arbitration</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Events &amp; Courses</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28.8" customHeight="1">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Chartered Institute of Arbitrators Singapore Branch</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Legal / Arbitration</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="28.8" customHeight="1">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Association of Corporate Counsel Singapore (ACC Singapore)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Legal / Corporate Counsel</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="28.8" customHeight="1">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Financial Women's Association of Singapore (FWA)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="43.2" customHeight="1">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CAIA Singapore Chapter</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Alternative Investments / Finance</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Singapore Chapter Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="28.8" customHeight="1">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>International Swaps and Derivatives Association (ISDA)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Derivatives / Finance / Legal</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Singapore Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="28.8" customHeight="1">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>TRACE International</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Anti-Bribery / Compliance / Legal</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="28.8" customHeight="1">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Association of Governance, Risk &amp; Compliance (AGRC)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Governance / Risk / Compliance</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Events Calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="28.8" customHeight="1">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>International Association of Privacy Professionals (IAPP)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Privacy / Legal / Compliance</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="28.8" customHeight="1">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>International Compliance Association (ICA)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Compliance / Financial Crime</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="43.2" customHeight="1">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Association of Certified Fraud Examiners Singapore Chapter</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Fraud / Compliance / Finance</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="28.8" customHeight="1">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Association of Certified Anti-Money Laundering Specialists (ACAMS) Singapore</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AML / Compliance / Finance</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="43.2" customHeight="1">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Asian Corporate Governance Association (ACGA)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Corporate Governance / Investment</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Events Calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="28.8" customHeight="1">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>REIT Association of Singapore (REITAS)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Investment / Real Estate Finance</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Upcoming Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Singapore FinTech Association</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>FinTech / Finance</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Institute of Banking and Finance Singapore (IBF)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Banking / Finance</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="28.8" customHeight="1">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Association of Alternative Investment Management (AIMA) Singapore</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Alternative Investments</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Singapore Events / Forum</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="28.8" customHeight="1">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Institute of Risk Management (IRM) Singapore network</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Risk Management</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="28.8" customHeight="1">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Association of Corporate Treasurers (ACT)</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Treasury / Finance</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Upcoming Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>International Chamber of Commerce (ICC) Singapore / Asia-Pacific arbitration community</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Legal / Arbitration</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ICC Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="28.8" customHeight="1">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>International Bar Association (IBA)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>International Fiscal Association</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>International Tax</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Society of Trust and Estate Practitioners (STEP) Singapore</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Tax / Trusts / Wealth</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>STEP Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="28.8" customHeight="1">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>International Tax Review</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>International Tax</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>International Bar Association Tax Committee</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Tax / Legal</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>IBA Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>International Association of Young Lawyers (AIJA)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="28.8" customHeight="1">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Inter-Pacific Bar Association (IPBA)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Legal / Business Law</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="28.8" customHeight="1">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>International Association of Lawyers (UIA)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>International Association for Contract &amp; Commercial Management (WorldCC)</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Commercial / Legal</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="28.8" customHeight="1">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Chartered Institute of Procurement &amp; Supply Singapore community (CIPS)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Procurement / Finance</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="28.8" customHeight="1">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Institute of Supply Management Singapore community</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Procurement / Business</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="28.8" customHeight="1">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Association for Financial Professionals (AFP) Singapore community</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Treasury / Finance</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="28.8" customHeight="1">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Global Association of Risk Professionals (GARP) Singapore</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Risk / Finance</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="28.8" customHeight="1">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>PRMIA Singapore Chapter</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Risk / Finance</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Global Association of Compliance Professionals (GACP)</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Compliance / Governance</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="28.8" customHeight="1">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Association of Certified Financial Crime Specialists (ACFCS)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Financial Crime / Compliance</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="28.8" customHeight="1">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>International Association of Insurance Supervisors (IAIS)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Insurance / Regulation</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="28.8" customHeight="1">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>International Organization of Securities Commissions (IOSCO)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Securities / Regulation</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Meetings &amp; Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="28.8" customHeight="1">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>International Association of Insurance Professionals</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Insurance / Finance</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="28.8" customHeight="1">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Global Reporting Initiative (GRI)</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Reporting / Finance / ESG</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="28.8" customHeight="1">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>International Integrated Reporting Council / IFRS Foundation community</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Reporting / Finance</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="28.8" customHeight="1">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Sustainability Accounting Standards Board / IFRS Sustainability community</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Finance / Reporting</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>IFRS Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="28.8" customHeight="1">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>World Economic Forum Singapore community</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Economics / Finance / Business</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="28.8" customHeight="1">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>United Nations Commission on International Trade Law (UNCITRAL)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>International Law / Trade</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="28.8" customHeight="1">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Fund Finance Association</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Fund Finance / Legal / Finance</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://fundfinanceassociation.com/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="28.8" customHeight="1">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>International Legal Finance Association (ILFA)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Legal Finance / Litigation Finance</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LITFINCON Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="28.8" customHeight="1">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Thomson Reuters</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Legal / Tax / Risk</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Singapore Events &amp; Webinars</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Centre for Commercial Law in Asia (CCLA), SMU</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Commercial Law</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="28.8" customHeight="1">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Centre for AI &amp; Data Governance, SMU</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Legal / Regulation / Governance</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="28.8" customHeight="1">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Centre for Cross-Border Commercial Law in Asia, SMU</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Commercial Law</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="28.8" customHeight="1">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Asian Law and Economics Association (AsLEA)</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Law / Economics</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Annual Conference</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Singapore Management University, Yong Pung How School of Law</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="28.8" customHeight="1">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SMU Centre for AI &amp; Data Governance</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>AI / Legal / Regulation</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="28.8" customHeight="1">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Singapore Management University, Institute of Innovation &amp; Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Finance / Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="28.8" customHeight="1">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Singapore Management University, Sim Kee Boon Institute for Financial Economics</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Finance / Economics</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="28.8" customHeight="1">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Singapore Management University, Centre for Sustainable Finance</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Sustainable Finance</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="28.8" customHeight="1">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>NUS Centre for Banking &amp; Finance</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Banking / Finance</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>NUS Centre for International Law</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>International Law</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>NUS Law</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>NUS Business School</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Finance / Business</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>NUS Risk Management Institute</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Risk / Finance</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>NUS Institute of Real Estate and Urban Studies</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Real Estate / Finance</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="28.8" customHeight="1">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>NUS Sustainable and Green Finance Institute</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Sustainable Finance</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="28.8" customHeight="1">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Nanyang Business School</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Finance / Business</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>NTU Centre for Applied Financial Studies</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>NTU Centre for Banking &amp; Finance</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Banking / Finance</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Singapore University of Social Sciences, School of Business</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Finance / Business</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="28.8" customHeight="1">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Singapore University of Technology and Design, Business &amp; Law programmes</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Business / Legal</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="28.8" customHeight="1">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Singapore Institute of Technology, Business / Professional Education</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Business / Finance</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="28.8" customHeight="1">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Singapore Centre for Environmental Life Sciences Engineering, NUS</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Governance / Regulation</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="28.8" customHeight="1">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Centre for Maritime Law, NUS</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Maritime / Commercial Law</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="28.8" customHeight="1">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>EW Barker Centre for Law &amp; Business, NUS</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Commercial Law / Business</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="28.8" customHeight="1">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Asian Law Institute (ASLI), NUS</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Asian / International Law</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="28.8" customHeight="1">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Centre for Asian Legal Studies, NUS</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Centre for Banking &amp; Finance Law, NUS</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Banking / Finance / Legal</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="28.8" customHeight="1">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Centre for International Law, NUS Investment Law &amp; Policy</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>International Investment Law</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="28.8" customHeight="1">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Singapore Green Finance Centre</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Sustainable Finance</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="28.8" customHeight="1">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Asian Institute of Digital Finance (AIDF), NUS</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Digital Finance / FinTech</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="28.8" customHeight="1">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>NUS FinTech Lab</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>FinTech / Finance</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Singapore Data Science Consortium</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Data / Finance / Risk</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="28.8" customHeight="1">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Singapore Centre for 4th Industrial Revolution</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Technology / Regulation</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="28.8" customHeight="1">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Singapore International Energy Week</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Energy / Finance / Policy</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="28.8" customHeight="1">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Singapore International Transport Congress &amp; Exhibition</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Infrastructure / Finance / Policy</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="28.8" customHeight="1">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Singapore Maritime Week</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Maritime / Finance / Legal</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="28.8" customHeight="1">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Singapore International Commercial Court Alumni Association</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="28.8" customHeight="1">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Singapore Chamber of Maritime Arbitration</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Maritime Arbitration / Legal</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="28.8" customHeight="1">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Singapore Institute of Arbitrators</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Arbitration / Legal</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Singapore International Mediation Institute</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Mediation / Legal</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Singapore International Dispute Resolution Academy</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Dispute Resolution / Legal</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="28.8" customHeight="1">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Singapore Mediation Centre</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Mediation / Legal</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Singapore Chamber of Maritime Arbitration Young Practitioners Group</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Arbitration / Legal</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="28.8" customHeight="1">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Singapore Institute of Legal Education</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Legal Education</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Events / CPD</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Singapore Corporate Counsel Association</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Corporate Legal</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Financial Services Institute of Australasia Singapore community</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Finance / Financial Services</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="28.8" customHeight="1">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Singapore Chamber of Commerce &amp; Industry Malaysia-Singapore Business Council</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Business / Finance</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="28.8" customHeight="1">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Singapore Contractors Association Limited (SCAL)</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Business / Finance</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="28.8" customHeight="1">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Singapore Furniture Industries Council</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Business / Trade</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Singapore Retailers Association</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Business / Finance</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Singapore Hotel Association</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Business / Finance</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Singapore Shipping Association</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Maritime / Finance / Legal</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="28.8" customHeight="1">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Singapore Maritime Institute</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Maritime / Finance / Policy</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="28.8" customHeight="1">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Singapore Chamber of Maritime Arbitration Young Practitioners</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Maritime / Arbitration</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="28.8" customHeight="1">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Singapore Maritime Foundation</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Maritime / Business</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="28.8" customHeight="1">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Singapore Shipping Association Young Executives Group</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Maritime / Business</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="28.8" customHeight="1">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Singapore International Foundation</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>International / Business</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="28.8" customHeight="1">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Singapore Cooperation Programme</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>International / Finance / Policy</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Courses &amp; Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="28.8" customHeight="1">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Singapore Economic Society</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Economics / Finance</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="28.8" customHeight="1">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Economic Society of Singapore Young Economists Network</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Economics / Finance</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="28.8" customHeight="1">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Singapore Statistical Society</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Statistics / Economics</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="28.8" customHeight="1">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Singapore National Employers Federation</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Business / Employment / Policy</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="43.2" customHeight="1">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Singapore Human Resources Institute</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Employment / Business Law</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="28.8" customHeight="1">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Tripartite Alliance for Dispute Management</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Employment / Legal</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Tripartite Alliance for Fair and Progressive Employment Practices</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Employment / Regulation</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="28.8" customHeight="1">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Workplace Fairness Institute Singapore</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Employment / Legal</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Singapore Institute of Human Resource Professionals</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>HR / Employment</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="28.8" customHeight="1">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Singapore Professional Centre</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Professional / Business</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="28.8" customHeight="1">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Singapore Institute of Management</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Business / Professional Education</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="43.2" customHeight="1">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Singapore Business and Professional Women’s Association</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Business / Finance</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="28.8" customHeight="1">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Financial Women’s Association of Singapore</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Women in Finance Asia</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Women in Payments Asia</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Payments / Finance</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="28.8" customHeight="1">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Singapore Payments Network</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Payments / Finance</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="28.8" customHeight="1">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Emerging Payments Association Asia</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Payments / FinTech</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="28.8" customHeight="1">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Singapore FinTech Festival</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>FinTech / Finance</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Singapore Week of Innovation and Technology</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Technology / Finance</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="28.8" customHeight="1">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Singapore International Cyber Week</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Cybersecurity / Risk</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="28.8" customHeight="1">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Association of Information Security Professionals</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Cybersecurity / Risk</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="28.8" customHeight="1">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Singapore Computer Society</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Technology / Professional</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="28.8" customHeight="1">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Singapore IT Federation</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Technology / Business</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="28.8" customHeight="1">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Asia Cloud Computing Association</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Technology / Finance</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="28.8" customHeight="1">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>SGTech</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Technology / Business</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="28.8" customHeight="1">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Singapore Digital Chamber of Commerce</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Digital Business / Finance</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="28.8" customHeight="1">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Singapore Blockchain Association</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Blockchain / Finance</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="28.8" customHeight="1">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Blockchain Association Singapore</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Blockchain / Finance</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="28.8" customHeight="1">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>ACCESS Singapore</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Digital Assets / Finance</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="28.8" customHeight="1">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>FinTech Association of Singapore Women in FinTech</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>FinTech / Finance</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="28.8" customHeight="1">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Singapore FinTech Association Payments Committee</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Payments / Finance</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="28.8" customHeight="1">
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Singapore FinTech Association RegTech Committee</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Regulation / FinTech</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="28.8" customHeight="1">
+      <c r="A195" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Singapore FinTech Association InsurTech Committee</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Insurance / FinTech</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="28.8" customHeight="1">
+      <c r="A196" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Singapore FinTech Association WealthTech Committee</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Wealth / Finance</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="28.8" customHeight="1">
+      <c r="A197" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Singapore FinTech Association Blockchain Committee</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Blockchain / Finance</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="28.8" customHeight="1">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Singapore FinTech Association AI Committee</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>AI / Finance</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Singapore FinTech Association Sustainable Finance Committee</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Sustainable Finance</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="28.8" customHeight="1">
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Singapore FinTech Association Cybersecurity Committee</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Cybersecurity / Finance</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="28.8" customHeight="1"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D89"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="34" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="3.88671875" customWidth="1" min="1" max="1"/>
+    <col width="42" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="26.88671875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="18.6640625" bestFit="1" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Organisation</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Events Page</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28.8" customHeight="1">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Federal Tax Authority</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28.8" customHeight="1">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Taxation Society UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Tax / Compliance</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Events &amp; Conferences</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28.8" customHeight="1">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ICAI Dubai UAE Chapter</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Accounting / Tax / Finance</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="57.6" customHeight="1">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Emirates Association for Accountants &amp; Auditors</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Accounting / Audit</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Training &amp; Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.8" customHeight="1">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PICPA Dubai</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Accounting / Finance</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28.8" customHeight="1">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IMA Middle East</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Accounting / Finance</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="43.2" customHeight="1">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>UAE Internal Auditors Association</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Internal Audit / Risk</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Events Calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28.8" customHeight="1">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CFA Society Emirates</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Finance / Investment</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28.8" customHeight="1">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ISACA UAE Chapter</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>IT Audit / Risk / Compliance</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Events Calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28.8" customHeight="1">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai Business Women Council</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Business / Finance</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Events Calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28.8" customHeight="1">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai Chambers</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Business / Trade / Finance</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28.8" customHeight="1">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Abu Dhabi Chamber</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Business / Trade / Finance</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="43.2" customHeight="1">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sharjah Chamber of Commerce &amp; Industry</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Business / Trade</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28.8" customHeight="1">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ICC UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Trade / Finance / Arbitration</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Events &amp; Trainings</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28.8" customHeight="1">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>UAE Singapore Business Council</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Business / Trade / Finance</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="43.2" customHeight="1">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Netherlands Business Council UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Business / Trade / Finance</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Events Listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28.8" customHeight="1">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Finnish Business Council UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Business / Finance / Trade</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28.8" customHeight="1">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Austrian Business Council UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Business / Trade / Finance</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="43.2" customHeight="1">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>U.S.-U.A.E. Business Council</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Business / Investment / Finance</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Upcoming Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28.8" customHeight="1">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Emirates Institute of Finance</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Banking / Finance</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28.8" customHeight="1">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>UAE Banks Federation</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Banking / Finance</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="43.2" customHeight="1">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Emirates Lawyers &amp; Legal Association</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Legal / Judicial</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28.8" customHeight="1">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DIFC Academy</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Legal / Finance / Compliance</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28.8" customHeight="1">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai International Arbitration Centre</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Arbitration / Legal</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28.8" customHeight="1">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Abu Dhabi Global Market</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Finance / Legal / Regulation</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28.8" customHeight="1">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Dubai Financial Services Authority</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Financial Regulation</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="43.2" customHeight="1">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Securities &amp; Commodities Authority UAE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Securities / Finance</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28.8" customHeight="1">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ministry of Finance UAE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Tax / Finance</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Events &amp; Activities</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28.8" customHeight="1">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Dubai World Trade Centre</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Business / Finance / Trade</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28.8" customHeight="1">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Dubai Business Events</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Business / Finance / Trade</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Events Calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28.8" customHeight="1">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>British Chamber of Commerce Dubai</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Business / Finance / Trade</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="43.2" customHeight="1">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Canadian Business Council Dubai</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Business / Finance / Trade</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Upcoming Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="43.2" customHeight="1">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Australian Business Council Dubai</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Business / Finance / Trade</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28.8" customHeight="1">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Spanish Business Council UAE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Business / Trade / Investment</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28.8" customHeight="1">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Swiss Business Council UAE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Business / Finance / Trade</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28.8" customHeight="1">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Belgian Business Council UAE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Business / Finance / Trade</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="43.2" customHeight="1">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>South African Business Council UAE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Business / Trade / Finance</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28.8" customHeight="1">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Bulgarian Business Council in Dubai</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Business / Trade / Finance</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28.8" customHeight="1">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Acamind Academy</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Accounting / Finance / Tax</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="43.2" customHeight="1">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Association of Corporate Treasurers</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Treasury / Finance</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="43.2" customHeight="1">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Association of Governance, Risk &amp; Compliance</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Governance / Risk / Compliance</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Events Calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28.8" customHeight="1">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LexisNexis Middle East</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Legal / Compliance</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Training &amp; Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28.8" customHeight="1">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Law House</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Legal / Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28.8" customHeight="1">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>UCL</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Legal / Arbitration</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28.8" customHeight="1">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Tax Experts Club UAE</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Tax / Finance / Compliance</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="43.2" customHeight="1">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>UAE Financial Markets Association</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Finance / Capital Markets</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28.8" customHeight="1">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CFA Institute Middle East</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Finance / Investment</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="43.2" customHeight="1">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Chartered Institute for Securities &amp; Investment UAE</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Finance / Investment</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="43.2" customHeight="1">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Global Association of Risk Professionals</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Risk / Finance</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Institute of Risk Management UAE</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Risk / Compliance / Finance</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Association of Practising Accountants UAE (AOPA)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Accounting / Audit</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="28.8" customHeight="1">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Emirates Association for Accountants &amp; Auditors (EAAA)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Accounting / Audit</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Training &amp; Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28.8" customHeight="1">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Global Association of Risk Professionals – UAE Chapter</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Risk / Finance</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>UAE Chapter Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Association of Certified Fraud Examiners (ACFE)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Fraud / Audit / Compliance</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Events Calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Sri Lankan Bankers Association UAE</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Banking / Finance</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ADGM Academy</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Finance / Banking / Law</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Ajman Chamber of Commerce &amp; Industry</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Business / Trade</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Exhibitions &amp; Conferences</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Ras Al Khaimah Chamber of Commerce &amp; Industry</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Business / Trade</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Fujairah Chamber of Commerce &amp; Industry</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Business / Trade</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Umm Al Quwain Chamber of Commerce &amp; Industry</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Business / Trade</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Irish Business Network Dubai</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Business / Trade</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Swedish Business Council UAE</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Business / Trade / Compliance</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Belgian Business Council Dubai</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Business / Trade / Finance</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Singapore Business Council UAE</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Business / Trade / Investment</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Dubai International Arbitration Centre – DIAC</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Arbitration / Legal</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Abu Dhabi Judicial Department</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Legal / Judicial</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Dubai Legal Affairs Department</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Legal / Regulation</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Emirates Legal Network</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Legal / Compliance</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CMS Middle East</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Legal / Tax / Compliance</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Thomson Reuters Middle East &amp; North Africa</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Tax / Legal / Risk</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Events &amp; Webinars</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Baker Tilly UAE</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Audit / Tax / Advisory</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Grant Thornton UAE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Audit / Tax / Advisory</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Crowe UAE</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Audit / Tax / Risk / Advisory</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Deloitte Middle East</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Audit / Tax / Advisory</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>BDO UAE</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Audit / Tax / Advisory</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>KPMG Lower Gulf</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Audit / Tax / Advisory</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PwC Middle East</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Audit / Tax / Advisory</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>EY Middle East</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Audit / Tax / Advisory</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Institute of Internal Auditors – UAE</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Internal Audit / Risk</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Chartered Institute for Securities &amp; Investment (CISI) – UAE</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Finance / Investment</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Global Ethical Finance Initiative</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Finance / Islamic Finance</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Our Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Dubai Stock Brokers &amp; Investment Services Group</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Investment / Capital Markets</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Upcoming Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Abu Dhabi Global Market Academy</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Finance / Banking / Legal</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Ministry of Industry &amp; Advanced Technology UAE</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Business / Industry / Trade</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>RAK Chamber – Business &amp; Investment Community</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Business / Investment</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Association of Practising Accountants UAE – CPD</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Accounting / Finance</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>AOPA Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Abu Dhabi Chamber of Commerce &amp; Industry – Business Community</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Business / Tax / Trade</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="28.8" customHeight="1">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Ajman Chamber – Exhibitions &amp; Conferences</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Business / Trade / Investment</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Exhibitions &amp; Conferences</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="28.8" customHeight="1"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D108"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="5.77734375" customWidth="1" min="1" max="1"/>
+    <col width="35" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="16.6640625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="18.6640625" bestFit="1" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Organisation</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Events Page</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>The Tax Institute</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28.8" customHeight="1">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CPA Australia</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Accounting &amp; Finance</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Conferences &amp; Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28.8" customHeight="1">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Chartered Accountants Australia and New Zealand (CA ANZ)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Institute of Public Accountants (IPA)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Events &amp; CPD</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.8" customHeight="1">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Institute of Financial Professionals Australia (IFPA)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Tax, Accounting &amp; Finance</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>International Fiscal Association Australia</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>International Tax</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Events Calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28.8" customHeight="1">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Association of Taxation and Management Accountants (ATMA)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Tax &amp; Accounting</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28.8" customHeight="1">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Financial Advice Association Australia (FAAA)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Advice</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28.8" customHeight="1">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SMSF Association</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Superannuation &amp; Finance</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28.8" customHeight="1">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Australian Institute of Superannuation Trustees (AIST)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Superannuation</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28.8" customHeight="1">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Australian Financial Markets Association (AFMA)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Australian Banking Association (ABA)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Banking &amp; Finance</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Financial Services Council</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28.8" customHeight="1">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Governance Institute of Australia</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Governance, Risk &amp; Compliance</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28.8" customHeight="1">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Australian Restructuring Insolvency &amp; Turnaround Association (ARITA)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Insolvency &amp; Restructuring</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Law Council of Australia</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Law Society of New South Wales</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Law Institute of Victoria</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Queensland Law Society</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Law Society of South Australia</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Law Society of Western Australia</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Law Society of Tasmania</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Law Society Northern Territory</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Commercial Law Association of Australia</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Commercial Law</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Australian Academy of Law</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Events &amp; Videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Asian Australian Lawyers Association</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28.8" customHeight="1">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Australian Corporate Lawyers Association (ACC Australia)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Corporate Legal</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28.8" customHeight="1">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Australian Institute of Company Directors (AICD)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Corporate Governance</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28.8" customHeight="1">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Australian Institute of Credit Management (AICM)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Credit &amp; Finance</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Financial Counselling Australia</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28.8" customHeight="1">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Association of Financial Professionals Australia</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Treasury &amp; Finance</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Australian Risk Policy Institute (ARPI)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Risk &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28.8" customHeight="1">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Risk Management Institute of Australasia (RMIA)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Risk Management</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28.8" customHeight="1">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Australian Institute of Management</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Business &amp; Management</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28.8" customHeight="1">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Australian Institute of Management WA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Business &amp; Management</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28.8" customHeight="1">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Australian Institute of Quantity Surveyors (AIQS)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Finance &amp; Property</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Property Council of Australia</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Property &amp; Finance</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Australian Property Institute (API)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Property &amp; Finance</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Australian Payroll Association</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Payroll &amp; Tax</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28.8" customHeight="1">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>The Association for Payroll Specialists (TAPS)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Payroll &amp; Tax</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28.8" customHeight="1">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Australian Association of National Advertisers (AANA)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Business &amp; Regulation</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28.8" customHeight="1">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Australian Institute of Company Directors NSW Division</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Corporate Governance</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28.8" customHeight="1">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Australian Business Lawyers &amp; Advisors</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Business &amp; Employment Law</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28.8" customHeight="1">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Thomson Reuters Australia</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tax, Legal &amp; Finance</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Events &amp; Webinars</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28.8" customHeight="1">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Television Education Network (TVED)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Legal, Tax &amp; Accounting CPD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28.8" customHeight="1">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Legalwise Seminars</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Legal &amp; Accounting CPD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Leo Cussen Centre for Law</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>College of Law Australia</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28.8" customHeight="1">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Australian Institute of Company Directors Queensland</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Corporate Governance</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28.8" customHeight="1">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Australian Institute of Company Directors Victoria</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Corporate Governance</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Corporate Tax Association of Australia</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Corporate Tax</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="28.8" customHeight="1">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Australian Bookkeepers Network</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Bookkeeping &amp; Accounting</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28.8" customHeight="1">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Institute of Certified Bookkeepers</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Bookkeeping &amp; Accounting</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28.8" customHeight="1">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Association of Accounting Technicians Australia</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="28.8" customHeight="1">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Australian Association of Graduate Employers</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Professional &amp; Business</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Australian Financial Complaints Authority</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28.8" customHeight="1">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Australian Securities and Investments Commission</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Financial Regulation</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="28.8" customHeight="1">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Australian Prudential Regulation Authority</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Financial Regulation</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Australian Taxation Office</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="28.8" customHeight="1">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Australian Accounting Standards Board</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Accounting Standards</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Auditing and Assurance Standards Board</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Auditing</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Financial Reporting Council</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Financial Reporting</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="28.8" customHeight="1">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Australian Competition and Consumer Commission</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Competition &amp; Regulation</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Australian Competition Tribunal</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Competition Law</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Information &amp; Proceedings</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Australian Institute of Company Directors</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="28.8" customHeight="1">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Australian Compliance Institute</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Compliance &amp; Risk</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Risk Management Institute of Australasia</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Risk Management</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Australian Risk Policy Institute</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Risk &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Australian Institute of Internal Auditors</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Internal Audit</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Institute of Risk Management Australia</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Risk Management</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Australian Institute of Credit Management</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Credit &amp; Finance</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Australian Restructuring Insolvency &amp; Turnaround Association</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Insolvency</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="28.8" customHeight="1">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Australian Institute of Credit Union Management</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Credit &amp; Banking</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="28.8" customHeight="1">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Australian Finance Industry Association</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Australian Financial Markets Association</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Australian Banking Association</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Customer Owned Banking Association</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Australian Securitisation Forum</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Australian Private Equity &amp; Venture Capital Association</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Private Equity &amp; Venture Capital</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Alternative Investment Management Association Australia</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Alternative Investments</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="28.8" customHeight="1">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Australian Investment Council</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Investment &amp; Private Capital</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="28.8" customHeight="1">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Financial Advice Association Australia</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Financial Advice</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="28.8" customHeight="1">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Association of Financial Advisers</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Financial Advice</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Financial Planning Association of Australia</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Financial Planning</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Association of Superannuation Funds of Australia</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Superannuation</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="28.8" customHeight="1">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Australian Institute of Superannuation Trustees</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Superannuation</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Australian Institute of Family Law Arbitrators and Mediators</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Family Law</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="28.8" customHeight="1">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Australian Lawyers Alliance</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="28.8" customHeight="1">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Australian Bar Association</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="28.8" customHeight="1">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Australian Corporate Lawyers Association</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Corporate Law</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="28.8" customHeight="1">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>CFA Society Australia</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Investment &amp; Finance</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Energy &amp; Resources Law Association</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Energy &amp; Resources Law</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>FinTech Australia</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>FinTech &amp; Finance</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Events Calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Mortgage &amp; Finance Association of Australia (MFAA)</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Finance &amp; Mortgage</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Banking &amp; Financial Services Law Association</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Banking &amp; Financial Law</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Events / Conference</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Australian Financial Industry Association (AFIA)</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>FinPro</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Local Government Finance</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Australian Law Librarians' Association</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Legal Information</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Conference / Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Victorian Society for Computers and the Law</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Legal Technology</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Charity Law Association of Australia and New Zealand</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Charity &amp; Nonprofit Law</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="28.8" customHeight="1">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Australian Pro Bono Centre</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Legal / Pro Bono</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Events &amp; Conferences</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="28.8" customHeight="1">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Sunshine Coast Law Association</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Television Education Network</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Legal, Tax &amp; Accounting CPD</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="28.8" customHeight="1">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Institute of Financial Professionals Australia</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Tax, Accounting &amp; Finance</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="28.8" customHeight="1">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Accounting and Finance Association of Australia and New Zealand</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Accounting &amp; Finance</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="28.8" customHeight="1">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Association for Payroll Specialists</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Payroll &amp; Tax</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="28.8" customHeight="1">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Australian Property Institute</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Property &amp; Finance</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="28.8" customHeight="1"/>
+    <row r="111" ht="28.8" customHeight="1"/>
+    <row r="112" ht="28.8" customHeight="1"/>
+    <row r="118" ht="43.2" customHeight="1"/>
+    <row r="119" ht="28.8" customHeight="1"/>
+    <row r="125" ht="28.8" customHeight="1"/>
+    <row r="130" ht="28.8" customHeight="1"/>
+    <row r="131" ht="28.8" customHeight="1"/>
+    <row r="133" ht="28.8" customHeight="1"/>
+    <row r="138" ht="43.2" customHeight="1"/>
+    <row r="139" ht="28.8" customHeight="1"/>
+    <row r="140" ht="28.8" customHeight="1"/>
+    <row r="141" ht="28.8" customHeight="1"/>
+    <row r="143" ht="28.8" customHeight="1"/>
+    <row r="144" ht="28.8" customHeight="1"/>
+    <row r="145" ht="28.8" customHeight="1"/>
+    <row r="147" ht="28.8" customHeight="1"/>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Sources/Event_scrapper_-_Website_completed.xlsx
+++ b/Sources/Event_scrapper_-_Website_completed.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="India" sheetId="1" state="visible" r:id="rId1"/>
@@ -13467,16 +13467,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D200"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="7.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="4.77734375" customWidth="1" min="1" max="1"/>
-    <col width="39.21875" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="16.5546875" customWidth="1" min="3" max="3"/>
-    <col width="27.77734375" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="8.88671875" customWidth="1" min="8" max="8"/>
+    <col width="8.6640625" customWidth="1" min="1" max="1"/>
+    <col width="17.6640625" customWidth="1" min="2" max="2"/>
+    <col width="17.21875" customWidth="1" min="3" max="3"/>
+    <col width="29.88671875" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28.8" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>#</t>
@@ -13498,7 +13497,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="100.8" customHeight="1">
       <c r="A2" t="n">
         <v>1</v>
       </c>
@@ -13514,11 +13513,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Events Calendar</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28.8" customHeight="1">
+          <t>https://sctp.org.sg/events/Tax-Professionals?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="115.2" customHeight="1">
       <c r="A3" t="n">
         <v>2</v>
       </c>
@@ -13534,11 +13533,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>https://www.isca.org.sg/member-support/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="72" customHeight="1">
       <c r="A4" t="n">
         <v>3</v>
       </c>
@@ -13554,11 +13553,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Events / Seminars &amp; Conferences</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>https://www.taxacademy.sg/seminars-and-conferences/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="43.2" customHeight="1">
       <c r="A5" t="n">
         <v>4</v>
       </c>
@@ -13574,11 +13573,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28.8" customHeight="1">
+          <t>https://icai.org.sg/events/recent-events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="43.2" customHeight="1">
       <c r="A6" t="n">
         <v>5</v>
       </c>
@@ -13594,11 +13593,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Events &amp; CPD</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+          <t>https://www.accaglobal.com/sg/en/member/cpd/events.html?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="57.6" customHeight="1">
       <c r="A7" t="n">
         <v>6</v>
       </c>
@@ -13614,11 +13613,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CPD Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+          <t>https://www.lawsociety.org.sg/cpd-events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="72" customHeight="1">
       <c r="A8" t="n">
         <v>7</v>
       </c>
@@ -13634,11 +13633,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>https://www.sal.org.sg/Events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="72" customHeight="1">
       <c r="A9" t="n">
         <v>8</v>
       </c>
@@ -13654,11 +13653,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Events / CPD</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28.8" customHeight="1">
+          <t>https://www.sile.edu.sg/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="100.8" customHeight="1">
       <c r="A10" t="n">
         <v>9</v>
       </c>
@@ -13674,11 +13673,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28.8" customHeight="1">
+          <t>https://siac.org.sg/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="100.8" customHeight="1">
       <c r="A11" t="n">
         <v>10</v>
       </c>
@@ -13694,11 +13693,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28.8" customHeight="1">
+          <t>https://www.sicc.gov.sg/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="100.8" customHeight="1">
       <c r="A12" t="n">
         <v>11</v>
       </c>
@@ -13714,11 +13713,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28.8" customHeight="1">
+          <t>https://www.scca.org.sg/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="72" customHeight="1">
       <c r="A13" t="n">
         <v>12</v>
       </c>
@@ -13734,11 +13733,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="43.2" customHeight="1">
+          <t>https://www.sid.org.sg/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="187.2" customHeight="1">
       <c r="A14" t="n">
         <v>13</v>
       </c>
@@ -13754,11 +13753,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28.8" customHeight="1">
+          <t>https://saicsa.org.sg/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="57.6" customHeight="1">
       <c r="A15" t="n">
         <v>14</v>
       </c>
@@ -13774,11 +13773,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28.8" customHeight="1">
+          <t>https://www.cfasocietysingapore.org/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="115.2" customHeight="1">
       <c r="A16" t="n">
         <v>15</v>
       </c>
@@ -13794,11 +13793,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28.8" customHeight="1">
+          <t>https://imas.org.sg/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="100.8" customHeight="1">
       <c r="A17" t="n">
         <v>16</v>
       </c>
@@ -13814,11 +13813,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28.8" customHeight="1">
+          <t>https://sias.org.sg/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="86.40000000000001" customHeight="1">
       <c r="A18" t="n">
         <v>17</v>
       </c>
@@ -13834,11 +13833,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
+          <t>https://svca.org.sg/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="57.6" customHeight="1">
       <c r="A19" t="n">
         <v>18</v>
       </c>
@@ -13854,11 +13853,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
+          <t>https://singaporefintech.org/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="72" customHeight="1">
       <c r="A20" t="n">
         <v>19</v>
       </c>
@@ -13874,11 +13873,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+          <t>https://www.abs.org.sg/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="72" customHeight="1">
       <c r="A21" t="n">
         <v>20</v>
       </c>
@@ -13894,11 +13893,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28.8" customHeight="1">
+          <t>https://www.actuaries.org.sg/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="72" customHeight="1">
       <c r="A22" t="n">
         <v>21</v>
       </c>
@@ -13914,11 +13913,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28.8" customHeight="1">
+          <t>https://www.sii.org.sg/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="86.40000000000001" customHeight="1">
       <c r="A23" t="n">
         <v>22</v>
       </c>
@@ -13934,11 +13933,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28.8" customHeight="1">
+          <t>https://www.fpas.org.sg/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="115.2" customHeight="1">
       <c r="A24" t="n">
         <v>23</v>
       </c>
@@ -13954,11 +13953,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Event Highlights</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
+          <t>https://www.acra.gov.sg/news-events/event-highlights/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="86.40000000000001" customHeight="1">
       <c r="A25" t="n">
         <v>24</v>
       </c>
@@ -13974,11 +13973,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Events &amp; Seminars</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28.8" customHeight="1">
+          <t>https://www.iras.gov.sg/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="72" customHeight="1">
       <c r="A26" t="n">
         <v>25</v>
       </c>
@@ -13994,11 +13993,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+          <t>https://www.mas.gov.sg/news/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="86.40000000000001" customHeight="1">
       <c r="A27" t="n">
         <v>26</v>
       </c>
@@ -14014,11 +14013,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="28.8" customHeight="1">
+          <t>https://www.ipos.gov.sg/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="72" customHeight="1">
       <c r="A28" t="n">
         <v>27</v>
       </c>
@@ -14034,11 +14033,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Events &amp; Announcements</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
+          <t>https://www.mof.gov.sg/news-publications/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="72" customHeight="1">
       <c r="A29" t="n">
         <v>28</v>
       </c>
@@ -14054,11 +14053,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="43.2" customHeight="1">
+          <t>https://www.sbf.org.sg/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="115.2" customHeight="1">
       <c r="A30" t="n">
         <v>29</v>
       </c>
@@ -14074,11 +14073,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28.8" customHeight="1">
+          <t>https://sicc.com.sg/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="115.2" customHeight="1">
       <c r="A31" t="n">
         <v>30</v>
       </c>
@@ -14094,11 +14093,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28.8" customHeight="1">
+          <t>https://www.sccci.org.sg/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="86.40000000000001" customHeight="1">
       <c r="A32" t="n">
         <v>31</v>
       </c>
@@ -14114,11 +14113,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
+          <t>https://asme.org.sg/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="86.40000000000001" customHeight="1">
       <c r="A33" t="n">
         <v>32</v>
       </c>
@@ -14134,11 +14133,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
+          <t>https://www.smfederation.org.sg/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="72" customHeight="1">
       <c r="A34" t="n">
         <v>33</v>
       </c>
@@ -14154,11 +14153,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="28.8" customHeight="1">
+          <t>https://www.sla.org.sg/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="57.6" customHeight="1">
       <c r="A35" t="n">
         <v>34</v>
       </c>
@@ -14174,11 +14173,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="28.8" customHeight="1">
+          <t>https://www.enterprisesg.gov.sg/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="115.2" customHeight="1">
       <c r="A36" t="n">
         <v>35</v>
       </c>
@@ -14194,11 +14193,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="28.8" customHeight="1">
+          <t>https://www.edb.gov.sg/en/events.html?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="43.2" customHeight="1">
       <c r="A37" t="n">
         <v>36</v>
       </c>
@@ -14214,11 +14213,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="28.8" customHeight="1">
+          <t>https://www.step.org/singapore/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="86.40000000000001" customHeight="1">
       <c r="A38" t="n">
         <v>37</v>
       </c>
@@ -14234,11 +14233,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28.8" customHeight="1">
+          <t>https://www.ifa.nl/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="86.40000000000001" customHeight="1">
       <c r="A39" t="n">
         <v>38</v>
       </c>
@@ -14254,11 +14253,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>STARI Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="28.8" customHeight="1">
+          <t>https://www.taxacademy.sg/stari/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="115.2" customHeight="1">
       <c r="A40" t="n">
         <v>39</v>
       </c>
@@ -14274,11 +14273,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28.8" customHeight="1">
+          <t>https://www.ivass.org.sg/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="100.8" customHeight="1">
       <c r="A41" t="n">
         <v>40</v>
       </c>
@@ -14294,11 +14293,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="28.8" customHeight="1">
+          <t>https://scma.org.sg/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="72" customHeight="1">
       <c r="A42" t="n">
         <v>41</v>
       </c>
@@ -14314,11 +14313,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="28.8" customHeight="1">
+          <t>https://www.smc.org.sg/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="172.8" customHeight="1">
       <c r="A43" t="n">
         <v>42</v>
       </c>
@@ -14334,11 +14333,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SICC / SICC Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="28.8" customHeight="1">
+          <t>https://sicc.gov.sg/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="72" customHeight="1">
       <c r="A44" t="n">
         <v>43</v>
       </c>
@@ -14354,11 +14353,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="28.8" customHeight="1">
+          <t>https://www.scs.org.sg/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="72" customHeight="1">
       <c r="A45" t="n">
         <v>44</v>
       </c>
@@ -14374,11 +14373,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="28.8" customHeight="1">
+          <t>https://www.sim.edu.sg/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="72" customHeight="1">
       <c r="A46" t="n">
         <v>45</v>
       </c>
@@ -14394,11 +14393,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="28.8" customHeight="1">
+          <t>https://www.shri.org.sg/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="72" customHeight="1">
       <c r="A47" t="n">
         <v>46</v>
       </c>
@@ -14414,11 +14413,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="28.8" customHeight="1">
+          <t>https://mis.org.sg/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="129.6" customHeight="1">
       <c r="A48" t="n">
         <v>47</v>
       </c>
@@ -14434,11 +14433,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="28.8" customHeight="1">
+          <t>https://www.sipmm.edu.sg/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="144" customHeight="1">
       <c r="A49" t="n">
         <v>48</v>
       </c>
@@ -14454,11 +14453,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="28.8" customHeight="1">
+          <t>https://ccls.smu.edu.sg/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="144" customHeight="1">
       <c r="A50" t="n">
         <v>49</v>
       </c>
@@ -14474,11 +14473,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="28.8" customHeight="1">
+          <t>https://law.smu.edu.sg/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="72" customHeight="1">
       <c r="A51" t="n">
         <v>50</v>
       </c>
@@ -14494,11 +14493,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="28.8" customHeight="1">
+          <t>https://caidg.smu.edu.sg/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="57.6" customHeight="1">
       <c r="A52" t="n">
         <v>51</v>
       </c>
@@ -14514,11 +14513,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="28.8" customHeight="1">
+          <t>https://act.org.sg/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="57.6" customHeight="1">
       <c r="A53" t="n">
         <v>52</v>
       </c>
@@ -14534,11 +14533,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Events / Calendar</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="28.8" customHeight="1">
+          <t>https://www.rimas.org.sg/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="43.2" customHeight="1">
       <c r="A54" t="n">
         <v>53</v>
       </c>
@@ -14554,7 +14553,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://iia.org.sg/Home?utm_source=chatgpt.com</t>
         </is>
       </c>
     </row>
@@ -14574,7 +14573,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Chapter Events</t>
+          <t>https://engage.isaca.org/singaporechapter/events?utm_source=chatgpt.com</t>
         </is>
       </c>
     </row>
@@ -14594,11 +14593,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
+          <t>https://www.isc2chapter.sg/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="28.8" customHeight="1">
       <c r="A57" t="n">
         <v>56</v>
       </c>
@@ -14614,11 +14613,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Events &amp; Courses</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="28.8" customHeight="1">
+          <t>https://siarb.org.sg/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="43.2" customHeight="1">
       <c r="A58" t="n">
         <v>57</v>
       </c>
@@ -14634,11 +14633,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="28.8" customHeight="1">
+          <t>https://ciarbsingapore.wildapricot.org/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="57.6" customHeight="1">
       <c r="A59" t="n">
         <v>58</v>
       </c>
@@ -14654,11 +14653,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="28.8" customHeight="1">
+          <t>https://www.acc.com/webview/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="43.2" customHeight="1">
       <c r="A60" t="n">
         <v>59</v>
       </c>
@@ -14674,7 +14673,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://www.fwasg.org/events/Default.aspx?utm_source=chatgpt.com</t>
         </is>
       </c>
     </row>
@@ -14694,11 +14693,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Singapore Chapter Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="28.8" customHeight="1">
+          <t>https://caia.org/chapter-locations/caia-chapter-singapore/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="43.2" customHeight="1">
       <c r="A62" t="n">
         <v>61</v>
       </c>
@@ -14714,7 +14713,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Singapore Events</t>
+          <t>https://www.isda.org/location/singapore/?utm_source=chatgpt.com</t>
         </is>
       </c>
     </row>
@@ -14734,11 +14733,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="28.8" customHeight="1">
+          <t>https://www.traceinternational.org/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="43.2" customHeight="1">
       <c r="A64" t="n">
         <v>63</v>
       </c>
@@ -14754,11 +14753,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Events Calendar</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="28.8" customHeight="1">
+          <t>https://members.agrc.org/events/event_list.asp?group=258545&amp;show=&amp;utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="57.6" customHeight="1">
       <c r="A65" t="n">
         <v>64</v>
       </c>
@@ -14774,11 +14773,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="28.8" customHeight="1">
+          <t>https://iapp.org/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="43.2" customHeight="1">
       <c r="A66" t="n">
         <v>65</v>
       </c>
@@ -14794,11 +14793,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="43.2" customHeight="1">
+          <t>https://www.int-comp.org/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="57.6" customHeight="1">
       <c r="A67" t="n">
         <v>66</v>
       </c>
@@ -14814,11 +14813,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="28.8" customHeight="1">
+          <t>https://www.acfe.com/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="72" customHeight="1">
       <c r="A68" t="n">
         <v>67</v>
       </c>
@@ -14834,7 +14833,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://www.acams.org/en/events?utm_source=chatgpt.com</t>
         </is>
       </c>
     </row>
@@ -14854,7 +14853,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Events Calendar</t>
+          <t>https://www.acga-asia.org/events.php?utm_source=chatgpt.com</t>
         </is>
       </c>
     </row>
@@ -14874,11 +14873,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Upcoming Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
+          <t>https://www.reitas.sg/events/upcoming-events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="28.8" customHeight="1">
       <c r="A71" t="n">
         <v>70</v>
       </c>
@@ -14894,11 +14893,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
+          <t>https://singaporefintech.org/event/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="43.2" customHeight="1">
       <c r="A72" t="n">
         <v>71</v>
       </c>
@@ -14914,11 +14913,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="28.8" customHeight="1">
+          <t>https://www.ibf.org.sg/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="43.2" customHeight="1">
       <c r="A73" t="n">
         <v>72</v>
       </c>
@@ -14934,11 +14933,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Singapore Events / Forum</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="28.8" customHeight="1">
+          <t>https://www.aima.org/events/aima-conferences-information/aima-singapore-forum.html?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="72" customHeight="1">
       <c r="A74" t="n">
         <v>73</v>
       </c>
@@ -14954,11 +14953,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="28.8" customHeight="1">
+          <t>https://www.theirm.org/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="43.2" customHeight="1">
       <c r="A75" t="n">
         <v>74</v>
       </c>
@@ -14974,11 +14973,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Upcoming Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
+          <t>https://www.treasurers.org/events-and-networking/upcoming-events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="43.2" customHeight="1">
       <c r="A76" t="n">
         <v>75</v>
       </c>
@@ -14994,11 +14993,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ICC Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="28.8" customHeight="1">
+          <t>https://events2go.iccwbo.org/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="86.40000000000001" customHeight="1">
       <c r="A77" t="n">
         <v>76</v>
       </c>
@@ -15014,11 +15013,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
+          <t>https://www.ibanet.org/conferences-events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="28.8" customHeight="1">
       <c r="A78" t="n">
         <v>77</v>
       </c>
@@ -15034,11 +15033,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
+          <t>https://www.ifa.nl/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="28.8" customHeight="1">
       <c r="A79" t="n">
         <v>78</v>
       </c>
@@ -15054,11 +15053,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>STEP Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="28.8" customHeight="1">
+          <t>https://www.step.org/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="43.2" customHeight="1">
       <c r="A80" t="n">
         <v>79</v>
       </c>
@@ -15074,11 +15073,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
+          <t>https://www.internationaltaxreview.com/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="28.8" customHeight="1">
       <c r="A81" t="n">
         <v>80</v>
       </c>
@@ -15094,11 +15093,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>IBA Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
+          <t>https://www.ibanet.org/conferences-events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="43.2" customHeight="1">
       <c r="A82" t="n">
         <v>81</v>
       </c>
@@ -15114,11 +15113,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="28.8" customHeight="1">
+          <t>https://www.aija.org/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="43.2" customHeight="1">
       <c r="A83" t="n">
         <v>82</v>
       </c>
@@ -15134,7 +15133,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://www.ipba.org/events/?utm_source=chatgpt.com</t>
         </is>
       </c>
     </row>
@@ -15154,11 +15153,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
+          <t>https://www.uianet.org/en/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="43.2" customHeight="1">
       <c r="A85" t="n">
         <v>84</v>
       </c>
@@ -15174,11 +15173,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="28.8" customHeight="1">
+          <t>https://www.worldcc.com/Events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="86.40000000000001" customHeight="1">
       <c r="A86" t="n">
         <v>85</v>
       </c>
@@ -15194,11 +15193,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="28.8" customHeight="1">
+          <t>https://www.cips.org/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="57.6" customHeight="1">
       <c r="A87" t="n">
         <v>86</v>
       </c>
@@ -15214,11 +15213,11 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="28.8" customHeight="1">
+          <t>https://www.ismworld.org/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="57.6" customHeight="1">
       <c r="A88" t="n">
         <v>87</v>
       </c>
@@ -15234,11 +15233,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="28.8" customHeight="1">
+          <t>https://www.afponline.org/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="72" customHeight="1">
       <c r="A89" t="n">
         <v>88</v>
       </c>
@@ -15254,11 +15253,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="28.8" customHeight="1">
+          <t>https://www.garp.org/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="43.2" customHeight="1">
       <c r="A90" t="n">
         <v>89</v>
       </c>
@@ -15274,11 +15273,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
+          <t>https://www.prmia.org/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="28.8" customHeight="1">
       <c r="A91" t="n">
         <v>90</v>
       </c>
@@ -15294,11 +15293,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="28.8" customHeight="1">
+          <t>https://www.gacp.org/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="57.6" customHeight="1">
       <c r="A92" t="n">
         <v>91</v>
       </c>
@@ -15314,11 +15313,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="28.8" customHeight="1">
+          <t>https://www.acfcs.org/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="57.6" customHeight="1">
       <c r="A93" t="n">
         <v>92</v>
       </c>
@@ -15334,11 +15333,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="28.8" customHeight="1">
+          <t>https://www.iais.org/activities-meetings/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="57.6" customHeight="1">
       <c r="A94" t="n">
         <v>93</v>
       </c>
@@ -15354,11 +15353,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Meetings &amp; Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="28.8" customHeight="1">
+          <t>https://www.iosco.org/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="72" customHeight="1">
       <c r="A95" t="n">
         <v>94</v>
       </c>
@@ -15374,11 +15373,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="28.8" customHeight="1">
+          <t>https://www.internationalinsuranceprofessionals.org/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="57.6" customHeight="1">
       <c r="A96" t="n">
         <v>95</v>
       </c>
@@ -15394,7 +15393,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://www.globalreporting.org/events/?utm_source=chatgpt.com</t>
         </is>
       </c>
     </row>
@@ -15414,11 +15413,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="28.8" customHeight="1">
+          <t>https://www.ifrs.org/news-and-events/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="72" customHeight="1">
       <c r="A98" t="n">
         <v>97</v>
       </c>
@@ -15434,11 +15433,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>IFRS Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="28.8" customHeight="1">
+          <t>https://www.ifrs.org/news-and-events/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="72" customHeight="1">
       <c r="A99" t="n">
         <v>98</v>
       </c>
@@ -15454,11 +15453,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="28.8" customHeight="1">
+          <t>https://www.weforum.org/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="43.2" customHeight="1">
       <c r="A100" t="n">
         <v>99</v>
       </c>
@@ -15474,11 +15473,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="28.8" customHeight="1">
+          <t>https://uncitral.un.org/en/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="57.6" customHeight="1">
       <c r="A101" t="n">
         <v>100</v>
       </c>
@@ -15494,7 +15493,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://fundfinanceassociation.com/events/</t>
+          <t>https://fundfinanceassociation.com/events/apac/11-04-26-asia-pacific-symposium/</t>
         </is>
       </c>
     </row>
@@ -15514,11 +15513,11 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LITFINCON Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="28.8" customHeight="1">
+          <t>https://litfincon.com/asia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="43.2" customHeight="1">
       <c r="A103" t="n">
         <v>102</v>
       </c>
@@ -15534,7 +15533,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Singapore Events &amp; Webinars</t>
+          <t>https://www.thomsonreuters.com.sg/en-sg/events.html</t>
         </is>
       </c>
     </row>
@@ -15554,11 +15553,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="28.8" customHeight="1">
+          <t>https://ccla.smu.edu.sg/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="43.2" customHeight="1">
       <c r="A105" t="n">
         <v>104</v>
       </c>
@@ -15574,7 +15573,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://caidg.smu.edu.sg/events</t>
         </is>
       </c>
     </row>
@@ -15594,11 +15593,11 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="28.8" customHeight="1">
+          <t>https://law.smu.edu.sg/research/centres/centre-cross-border-commercial-law-asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="43.2" customHeight="1">
       <c r="A107" t="n">
         <v>106</v>
       </c>
@@ -15614,11 +15613,11 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Annual Conference</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
+          <t>https://ccla.smu.edu.sg/events/past-events</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="43.2" customHeight="1">
       <c r="A108" t="n">
         <v>107</v>
       </c>
@@ -15634,11 +15633,11 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="28.8" customHeight="1">
+          <t>https://law.smu.edu.sg/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="72" customHeight="1">
       <c r="A109" t="n">
         <v>108</v>
       </c>
@@ -15654,7 +15653,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://caidg.smu.edu.sg/events</t>
         </is>
       </c>
     </row>
@@ -15674,11 +15673,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="28.8" customHeight="1">
+          <t>https://iie.smu.edu.sg/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="72" customHeight="1">
       <c r="A111" t="n">
         <v>110</v>
       </c>
@@ -15694,11 +15693,11 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="28.8" customHeight="1">
+          <t>https://skbi.smu.edu.sg/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="86.40000000000001" customHeight="1">
       <c r="A112" t="n">
         <v>111</v>
       </c>
@@ -15714,11 +15713,11 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="28.8" customHeight="1">
+          <t>https://business.smu.edu.sg/centres/centre-sustainable-finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="72" customHeight="1">
       <c r="A113" t="n">
         <v>112</v>
       </c>
@@ -15734,11 +15733,11 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
+          <t>https://bschool.nus.edu.sg/cbfl/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="28.8" customHeight="1">
       <c r="A114" t="n">
         <v>113</v>
       </c>
@@ -15754,11 +15753,11 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
+          <t>https://cil.nus.edu.sg/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="28.8" customHeight="1">
       <c r="A115" t="n">
         <v>114</v>
       </c>
@@ -15774,7 +15773,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://law.nus.edu.sg/events/</t>
         </is>
       </c>
     </row>
@@ -15794,11 +15793,11 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
+          <t>https://bschool.nus.edu.sg/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="28.8" customHeight="1">
       <c r="A117" t="n">
         <v>116</v>
       </c>
@@ -15814,11 +15813,11 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
+          <t>https://rmi.nus.edu.sg/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="43.2" customHeight="1">
       <c r="A118" t="n">
         <v>117</v>
       </c>
@@ -15834,11 +15833,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="28.8" customHeight="1">
+          <t>https://ireus.nus.edu.sg/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="43.2" customHeight="1">
       <c r="A119" t="n">
         <v>118</v>
       </c>
@@ -15854,11 +15853,11 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="28.8" customHeight="1">
+          <t>https://sfi.nus.edu.sg/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="43.2" customHeight="1">
       <c r="A120" t="n">
         <v>119</v>
       </c>
@@ -15874,11 +15873,11 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
+          <t>https://www.ntu.edu.sg/business/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="28.8" customHeight="1">
       <c r="A121" t="n">
         <v>120</v>
       </c>
@@ -15894,11 +15893,11 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
+          <t>https://www.ntu.edu.sg/business/research/centres/cafs</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="43.2" customHeight="1">
       <c r="A122" t="n">
         <v>121</v>
       </c>
@@ -15914,11 +15913,11 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
+          <t>https://www.ntu.edu.sg/business/research/centres</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="28.8" customHeight="1">
       <c r="A123" t="n">
         <v>122</v>
       </c>
@@ -15934,11 +15933,11 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="28.8" customHeight="1">
+          <t>https://www.suss.edu.sg/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="43.2" customHeight="1">
       <c r="A124" t="n">
         <v>123</v>
       </c>
@@ -15954,11 +15953,11 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="28.8" customHeight="1">
+          <t>https://www.sutd.edu.sg/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="57.6" customHeight="1">
       <c r="A125" t="n">
         <v>124</v>
       </c>
@@ -15974,11 +15973,11 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="28.8" customHeight="1">
+          <t>https://www.singaporetech.edu.sg/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="72" customHeight="1">
       <c r="A126" t="n">
         <v>125</v>
       </c>
@@ -15994,11 +15993,11 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="28.8" customHeight="1">
+          <t>https://scles.nus.edu.sg/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="57.6" customHeight="1">
       <c r="A127" t="n">
         <v>126</v>
       </c>
@@ -16014,7 +16013,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://law.nus.edu.sg/cml/</t>
         </is>
       </c>
     </row>
@@ -16034,11 +16033,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="28.8" customHeight="1">
+          <t>https://law.nus.edu.sg/ewbclb/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="43.2" customHeight="1">
       <c r="A129" t="n">
         <v>128</v>
       </c>
@@ -16054,7 +16053,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://law.nus.edu.sg/asli/</t>
         </is>
       </c>
     </row>
@@ -16074,11 +16073,11 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
+          <t>https://law.nus.edu.sg/cals/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="28.8" customHeight="1">
       <c r="A131" t="n">
         <v>130</v>
       </c>
@@ -16094,7 +16093,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://law.nus.edu.sg/cbfl/</t>
         </is>
       </c>
     </row>
@@ -16114,11 +16113,11 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="28.8" customHeight="1">
+          <t>https://cil.nus.edu.sg/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="57.6" customHeight="1">
       <c r="A133" t="n">
         <v>132</v>
       </c>
@@ -16134,7 +16133,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://www.singaporegreenfinance.sg/events</t>
         </is>
       </c>
     </row>
@@ -16154,11 +16153,11 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="28.8" customHeight="1">
+          <t>https://nus.edu.sg/aidf/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="43.2" customHeight="1">
       <c r="A135" t="n">
         <v>134</v>
       </c>
@@ -16174,7 +16173,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://fintechlab.nus.edu.sg/events/</t>
         </is>
       </c>
     </row>
@@ -16194,7 +16193,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://www.sdsconsortium.sg/events</t>
         </is>
       </c>
     </row>
@@ -16214,11 +16213,11 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="28.8" customHeight="1">
+          <t>https://www.weforum.org/centres/centre-for-the-fourth-industrial-revolution-singapore/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="43.2" customHeight="1">
       <c r="A138" t="n">
         <v>137</v>
       </c>
@@ -16234,11 +16233,11 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="28.8" customHeight="1">
+          <t>https://www.siew.gov.sg/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="43.2" customHeight="1">
       <c r="A139" t="n">
         <v>138</v>
       </c>
@@ -16254,11 +16253,11 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="28.8" customHeight="1">
+          <t>https://www.sitce.org.sg/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="57.6" customHeight="1">
       <c r="A140" t="n">
         <v>139</v>
       </c>
@@ -16274,7 +16273,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://www.smw.sg/</t>
         </is>
       </c>
     </row>
@@ -16294,11 +16293,11 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="28.8" customHeight="1">
+          <t>https://www.sicc.gov.sg/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="57.6" customHeight="1">
       <c r="A142" t="n">
         <v>141</v>
       </c>
@@ -16314,11 +16313,11 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="28.8" customHeight="1">
+          <t>https://scma.org.sg/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="43.2" customHeight="1">
       <c r="A143" t="n">
         <v>142</v>
       </c>
@@ -16334,11 +16333,11 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
+          <t>https://siarb.org.sg/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="28.8" customHeight="1">
       <c r="A144" t="n">
         <v>143</v>
       </c>
@@ -16354,11 +16353,11 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
+          <t>https://simimediators.org/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="43.2" customHeight="1">
       <c r="A145" t="n">
         <v>144</v>
       </c>
@@ -16374,11 +16373,11 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="28.8" customHeight="1">
+          <t>https://sidra.smu.edu.sg/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="57.6" customHeight="1">
       <c r="A146" t="n">
         <v>145</v>
       </c>
@@ -16394,11 +16393,11 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
+          <t>https://www.smc.org.sg/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="28.8" customHeight="1">
       <c r="A147" t="n">
         <v>146</v>
       </c>
@@ -16414,11 +16413,11 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="28.8" customHeight="1">
+          <t>https://scma.org.sg/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="57.6" customHeight="1">
       <c r="A148" t="n">
         <v>147</v>
       </c>
@@ -16434,11 +16433,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Events / CPD</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
+          <t>https://www.sile.edu.sg/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="28.8" customHeight="1">
       <c r="A149" t="n">
         <v>148</v>
       </c>
@@ -16454,11 +16453,11 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
+          <t>https://www.scca.org.sg/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="28.8" customHeight="1">
       <c r="A150" t="n">
         <v>149</v>
       </c>
@@ -16474,11 +16473,11 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="28.8" customHeight="1">
+          <t>https://www.finsia.com/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="72" customHeight="1">
       <c r="A151" t="n">
         <v>150</v>
       </c>
@@ -16494,11 +16493,11 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="28.8" customHeight="1">
+          <t>https://www.sccci.org.sg/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="72" customHeight="1">
       <c r="A152" t="n">
         <v>151</v>
       </c>
@@ -16514,11 +16513,11 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="28.8" customHeight="1">
+          <t>https://www.scal.com.sg/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="57.6" customHeight="1">
       <c r="A153" t="n">
         <v>152</v>
       </c>
@@ -16534,11 +16533,11 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
+          <t>https://www.singaporefurniture.com/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="28.8" customHeight="1">
       <c r="A154" t="n">
         <v>153</v>
       </c>
@@ -16554,11 +16553,11 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
+          <t>https://www.sra.org.sg/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="28.8" customHeight="1">
       <c r="A155" t="n">
         <v>154</v>
       </c>
@@ -16574,11 +16573,11 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
+          <t>https://sha.org.sg/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="28.8" customHeight="1">
       <c r="A156" t="n">
         <v>155</v>
       </c>
@@ -16594,7 +16593,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://www.ssa.org.sg/events/</t>
         </is>
       </c>
     </row>
@@ -16614,7 +16613,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://www.smi-ntu.sg/events/</t>
         </is>
       </c>
     </row>
@@ -16634,11 +16633,11 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="28.8" customHeight="1">
+          <t>https://scma.org.sg/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="57.6" customHeight="1">
       <c r="A159" t="n">
         <v>158</v>
       </c>
@@ -16654,7 +16653,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://www.smf.com.sg/events/</t>
         </is>
       </c>
     </row>
@@ -16674,11 +16673,11 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="28.8" customHeight="1">
+          <t>https://www.ssa.org.sg/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="43.2" customHeight="1">
       <c r="A161" t="n">
         <v>160</v>
       </c>
@@ -16694,11 +16693,11 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="28.8" customHeight="1">
+          <t>https://www.sif.org.sg/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="43.2" customHeight="1">
       <c r="A162" t="n">
         <v>161</v>
       </c>
@@ -16714,11 +16713,11 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Courses &amp; Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="28.8" customHeight="1">
+          <t>https://scp.gov.sg/</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="43.2" customHeight="1">
       <c r="A163" t="n">
         <v>162</v>
       </c>
@@ -16734,7 +16733,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://ses.org.sg/events/</t>
         </is>
       </c>
     </row>
@@ -16754,11 +16753,11 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="28.8" customHeight="1">
+          <t>https://ses.org.sg/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="43.2" customHeight="1">
       <c r="A165" t="n">
         <v>164</v>
       </c>
@@ -16774,7 +16773,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://www.singstat.gov.sg/whats-new/events</t>
         </is>
       </c>
     </row>
@@ -16794,7 +16793,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://snef.org.sg/events/</t>
         </is>
       </c>
     </row>
@@ -16814,7 +16813,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://www.shri.org.sg/events</t>
         </is>
       </c>
     </row>
@@ -16834,11 +16833,11 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
+          <t>https://www.tadm.sg/</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="43.2" customHeight="1">
       <c r="A169" t="n">
         <v>168</v>
       </c>
@@ -16854,11 +16853,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="28.8" customHeight="1">
+          <t>https://www.tafep.sg/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="72" customHeight="1">
       <c r="A170" t="n">
         <v>169</v>
       </c>
@@ -16874,11 +16873,11 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
+          <t>https://www.tafep.sg/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="28.8" customHeight="1">
       <c r="A171" t="n">
         <v>170</v>
       </c>
@@ -16894,11 +16893,11 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="28.8" customHeight="1">
+          <t>https://www.sihrp.org/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="43.2" customHeight="1">
       <c r="A172" t="n">
         <v>171</v>
       </c>
@@ -16914,7 +16913,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://www.spc.org.sg/events</t>
         </is>
       </c>
     </row>
@@ -16934,7 +16933,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://www.sim.edu.sg/events</t>
         </is>
       </c>
     </row>
@@ -16954,11 +16953,11 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="28.8" customHeight="1">
+          <t>https://bpw-singapore.org/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="57.6" customHeight="1">
       <c r="A175" t="n">
         <v>174</v>
       </c>
@@ -16974,11 +16973,11 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
+          <t>https://www.fwasg.org/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="43.2" customHeight="1">
       <c r="A176" t="n">
         <v>175</v>
       </c>
@@ -16994,11 +16993,11 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
+          <t>https://womeninfinanceasia.com/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="28.8" customHeight="1">
       <c r="A177" t="n">
         <v>176</v>
       </c>
@@ -17014,7 +17013,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://womeninpayments.org/events/</t>
         </is>
       </c>
     </row>
@@ -17034,7 +17033,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://www.singaporepayments.org/events</t>
         </is>
       </c>
     </row>
@@ -17054,7 +17053,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://emergingpayments.org/events/</t>
         </is>
       </c>
     </row>
@@ -17074,11 +17073,11 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
+          <t>https://www.singaporefintechfestival.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="28.8" customHeight="1">
       <c r="A181" t="n">
         <v>180</v>
       </c>
@@ -17094,11 +17093,11 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="28.8" customHeight="1">
+          <t>https://www.switchsg.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="43.2" customHeight="1">
       <c r="A182" t="n">
         <v>181</v>
       </c>
@@ -17114,11 +17113,11 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="28.8" customHeight="1">
+          <t>https://www.sicw.gov.sg/</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="43.2" customHeight="1">
       <c r="A183" t="n">
         <v>182</v>
       </c>
@@ -17134,11 +17133,11 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="28.8" customHeight="1">
+          <t>https://www.aisp.sg/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="43.2" customHeight="1">
       <c r="A184" t="n">
         <v>183</v>
       </c>
@@ -17154,7 +17153,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://www.scs.org.sg/events</t>
         </is>
       </c>
     </row>
@@ -17174,7 +17173,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://sitf.org.sg/events/</t>
         </is>
       </c>
     </row>
@@ -17194,11 +17193,11 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="28.8" customHeight="1">
+          <t>https://www.asiacloudcomputing.org/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="43.2" customHeight="1">
       <c r="A187" t="n">
         <v>186</v>
       </c>
@@ -17214,7 +17213,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://www.sgtech.org.sg/events</t>
         </is>
       </c>
     </row>
@@ -17234,11 +17233,11 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="28.8" customHeight="1">
+          <t>https://www.sdcc.sg/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="43.2" customHeight="1">
       <c r="A189" t="n">
         <v>188</v>
       </c>
@@ -17254,11 +17253,11 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="28.8" customHeight="1">
+          <t>https://www.singaporeblockchain.org/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="43.2" customHeight="1">
       <c r="A190" t="n">
         <v>189</v>
       </c>
@@ -17274,11 +17273,11 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="28.8" customHeight="1">
+          <t>https://www.bas.sg/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="43.2" customHeight="1">
       <c r="A191" t="n">
         <v>190</v>
       </c>
@@ -17294,7 +17293,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://www.access.org.sg/events</t>
         </is>
       </c>
     </row>
@@ -17314,11 +17313,11 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="28.8" customHeight="1">
+          <t>https://singaporefintech.org/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="43.2" customHeight="1">
       <c r="A193" t="n">
         <v>192</v>
       </c>
@@ -17334,11 +17333,11 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="28.8" customHeight="1">
+          <t>https://singaporefintech.org/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="57.6" customHeight="1">
       <c r="A194" t="n">
         <v>193</v>
       </c>
@@ -17354,11 +17353,11 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="28.8" customHeight="1">
+          <t>https://singaporefintech.org/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="43.2" customHeight="1">
       <c r="A195" t="n">
         <v>194</v>
       </c>
@@ -17374,11 +17373,11 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="28.8" customHeight="1">
+          <t>https://singaporefintech.org/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="57.6" customHeight="1">
       <c r="A196" t="n">
         <v>195</v>
       </c>
@@ -17394,11 +17393,11 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="197" ht="28.8" customHeight="1">
+          <t>https://singaporefintech.org/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="57.6" customHeight="1">
       <c r="A197" t="n">
         <v>196</v>
       </c>
@@ -17414,11 +17413,11 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="198" ht="28.8" customHeight="1">
+          <t>https://singaporefintech.org/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="57.6" customHeight="1">
       <c r="A198" t="n">
         <v>197</v>
       </c>
@@ -17434,11 +17433,11 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
+          <t>https://singaporefintech.org/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="43.2" customHeight="1">
       <c r="A199" t="n">
         <v>198</v>
       </c>
@@ -17454,11 +17453,11 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" ht="28.8" customHeight="1">
+          <t>https://singaporefintech.org/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="57.6" customHeight="1">
       <c r="A200" t="n">
         <v>199</v>
       </c>
@@ -17474,14 +17473,13 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" ht="28.8" customHeight="1"/>
+          <t>https://singaporefintech.org/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="57.6" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -17491,16 +17489,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D89"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="34" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="3.88671875" customWidth="1" min="1" max="1"/>
-    <col width="42" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="26.88671875" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="18.6640625" bestFit="1" customWidth="1" min="4" max="4"/>
-  </cols>
+  <dimension ref="A1:D135"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28.8" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>#</t>
@@ -17522,7 +17514,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="28.8" customHeight="1">
+    <row r="2" ht="43.2" customHeight="1">
       <c r="A2" t="n">
         <v>1</v>
       </c>
@@ -17538,11 +17530,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28.8" customHeight="1">
+          <t>https://tax.gov.ae/en/media.centre/events.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="43.2" customHeight="1">
       <c r="A3" t="n">
         <v>2</v>
       </c>
@@ -17558,11 +17550,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Events &amp; Conferences</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28.8" customHeight="1">
+          <t>https://taxationsociety.org/events-conferences/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="57.6" customHeight="1">
       <c r="A4" t="n">
         <v>3</v>
       </c>
@@ -17578,11 +17570,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="57.6" customHeight="1">
+          <t>https://www.icaidubai.org/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="86.40000000000001" customHeight="1">
       <c r="A5" t="n">
         <v>4</v>
       </c>
@@ -17598,11 +17590,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Training &amp; Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28.8" customHeight="1">
+          <t>https://aaa4uae.ae/site/en/training-manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="43.2" customHeight="1">
       <c r="A6" t="n">
         <v>5</v>
       </c>
@@ -17618,11 +17610,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28.8" customHeight="1">
+          <t>https://picpadubai.org/events/list/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="43.2" customHeight="1">
       <c r="A7" t="n">
         <v>6</v>
       </c>
@@ -17638,11 +17630,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="43.2" customHeight="1">
+          <t>https://imamiddleast.org/en/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="72" customHeight="1">
       <c r="A8" t="n">
         <v>7</v>
       </c>
@@ -17658,11 +17650,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Events Calendar</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28.8" customHeight="1">
+          <t>https://uaeiaa.org/events-calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="43.2" customHeight="1">
       <c r="A9" t="n">
         <v>8</v>
       </c>
@@ -17678,11 +17670,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28.8" customHeight="1">
+          <t>https://www.cfasociety.org/emirates/events/calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="57.6" customHeight="1">
       <c r="A10" t="n">
         <v>9</v>
       </c>
@@ -17698,11 +17690,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Events Calendar</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28.8" customHeight="1">
+          <t>https://engage.isaca.org/uaechapter/events/calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="57.6" customHeight="1">
       <c r="A11" t="n">
         <v>10</v>
       </c>
@@ -17718,11 +17710,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Events Calendar</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28.8" customHeight="1">
+          <t>https://www.dbwc.ae/event/calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="43.2" customHeight="1">
       <c r="A12" t="n">
         <v>11</v>
       </c>
@@ -17738,11 +17730,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28.8" customHeight="1">
+          <t>https://www.dubaichamber.com/en/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="43.2" customHeight="1">
       <c r="A13" t="n">
         <v>12</v>
       </c>
@@ -17758,11 +17750,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="43.2" customHeight="1">
+          <t>https://www.abudhabichamber.ae/en/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="86.40000000000001" customHeight="1">
       <c r="A14" t="n">
         <v>13</v>
       </c>
@@ -17778,11 +17770,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28.8" customHeight="1">
+          <t>https://www.sharjah.gov.ae/en/media-center/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="57.6" customHeight="1">
       <c r="A15" t="n">
         <v>14</v>
       </c>
@@ -17798,11 +17790,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Events &amp; Trainings</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28.8" customHeight="1">
+          <t>https://iccuae.ae/events-and-trainings/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="72" customHeight="1">
       <c r="A16" t="n">
         <v>15</v>
       </c>
@@ -17818,11 +17810,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="43.2" customHeight="1">
+          <t>https://www.uaesbc.com/event-list</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="72" customHeight="1">
       <c r="A17" t="n">
         <v>16</v>
       </c>
@@ -17838,11 +17830,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Events Listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28.8" customHeight="1">
+          <t>https://www.nlbcuae.com/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="57.6" customHeight="1">
       <c r="A18" t="n">
         <v>17</v>
       </c>
@@ -17858,11 +17850,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28.8" customHeight="1">
+          <t>https://www.fbcuae.fi/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="57.6" customHeight="1">
       <c r="A19" t="n">
         <v>18</v>
       </c>
@@ -17878,11 +17870,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="43.2" customHeight="1">
+          <t>https://austrianbc.ae/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="72" customHeight="1">
       <c r="A20" t="n">
         <v>19</v>
       </c>
@@ -17898,11 +17890,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Upcoming Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28.8" customHeight="1">
+          <t>https://usuaebusiness.org/events_category/upcoming-events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="57.6" customHeight="1">
       <c r="A21" t="n">
         <v>20</v>
       </c>
@@ -17918,11 +17910,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28.8" customHeight="1">
+          <t>https://eif.gov.ae/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="57.6" customHeight="1">
       <c r="A22" t="n">
         <v>21</v>
       </c>
@@ -17938,11 +17930,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="43.2" customHeight="1">
+          <t>https://ubf.ae/en/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="72" customHeight="1">
       <c r="A23" t="n">
         <v>22</v>
       </c>
@@ -17958,11 +17950,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28.8" customHeight="1">
+          <t>https://www.eall.org.ae/en/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="57.6" customHeight="1">
       <c r="A24" t="n">
         <v>23</v>
       </c>
@@ -17978,11 +17970,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28.8" customHeight="1">
+          <t>https://academy.difc.ae/school-of-law?category=Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="72" customHeight="1">
       <c r="A25" t="n">
         <v>24</v>
       </c>
@@ -17998,11 +17990,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28.8" customHeight="1">
+          <t>https://www.diac.com/en/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="57.6" customHeight="1">
       <c r="A26" t="n">
         <v>25</v>
       </c>
@@ -18018,11 +18010,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="28.8" customHeight="1">
+          <t>https://www.adgm.com/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="57.6" customHeight="1">
       <c r="A27" t="n">
         <v>26</v>
       </c>
@@ -18038,11 +18030,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="43.2" customHeight="1">
+          <t>https://www.dfsa.ae/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="86.40000000000001" customHeight="1">
       <c r="A28" t="n">
         <v>27</v>
       </c>
@@ -18058,11 +18050,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="28.8" customHeight="1">
+          <t>https://www.sca.gov.ae/en/media-center/events.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="57.6" customHeight="1">
       <c r="A29" t="n">
         <v>28</v>
       </c>
@@ -18078,11 +18070,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Events &amp; Activities</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28.8" customHeight="1">
+          <t>https://mof.gov.ae/en/media-center/events-and-activities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="57.6" customHeight="1">
       <c r="A30" t="n">
         <v>29</v>
       </c>
@@ -18098,11 +18090,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28.8" customHeight="1">
+          <t>https://www.dwtc.com/en/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="43.2" customHeight="1">
       <c r="A31" t="n">
         <v>30</v>
       </c>
@@ -18118,11 +18110,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Events Calendar</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28.8" customHeight="1">
+          <t>https://www.investindubai.gov.ae/events-calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="72" customHeight="1">
       <c r="A32" t="n">
         <v>31</v>
       </c>
@@ -18138,11 +18130,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="43.2" customHeight="1">
+          <t>https://britishchamberdubai.com/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="57.6" customHeight="1">
       <c r="A33" t="n">
         <v>32</v>
       </c>
@@ -18158,11 +18150,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Upcoming Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="43.2" customHeight="1">
+          <t>https://www.cbc-dubai.com/upcoming-events</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="72" customHeight="1">
       <c r="A34" t="n">
         <v>33</v>
       </c>
@@ -18178,11 +18170,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="28.8" customHeight="1">
+          <t>https://www.abcduae.com/community-and-business-events</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="57.6" customHeight="1">
       <c r="A35" t="n">
         <v>34</v>
       </c>
@@ -18198,11 +18190,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="28.8" customHeight="1">
+          <t>https://www.spanishbusinesscouncil.ae/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="57.6" customHeight="1">
       <c r="A36" t="n">
         <v>35</v>
       </c>
@@ -18218,11 +18210,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="28.8" customHeight="1">
+          <t>https://www.swissbcuae.com/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="57.6" customHeight="1">
       <c r="A37" t="n">
         <v>36</v>
       </c>
@@ -18238,11 +18230,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="43.2" customHeight="1">
+          <t>https://www.bbc-uae.com/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="72" customHeight="1">
       <c r="A38" t="n">
         <v>37</v>
       </c>
@@ -18258,11 +18250,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28.8" customHeight="1">
+          <t>https://sabco-uae.org/event/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="57.6" customHeight="1">
       <c r="A39" t="n">
         <v>38</v>
       </c>
@@ -18278,11 +18270,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="28.8" customHeight="1">
+          <t>https://bgbc.ae/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="57.6" customHeight="1">
       <c r="A40" t="n">
         <v>39</v>
       </c>
@@ -18298,11 +18290,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="43.2" customHeight="1">
+          <t>https://acamind.ae/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="86.40000000000001" customHeight="1">
       <c r="A41" t="n">
         <v>40</v>
       </c>
@@ -18318,11 +18310,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="43.2" customHeight="1">
+          <t>https://www.treasurers.org/events-and-networking/upcoming-events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="86.40000000000001" customHeight="1">
       <c r="A42" t="n">
         <v>41</v>
       </c>
@@ -18338,11 +18330,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Events Calendar</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="28.8" customHeight="1">
+          <t>https://members.agrc.org/events/event_list.asp</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="43.2" customHeight="1">
       <c r="A43" t="n">
         <v>42</v>
       </c>
@@ -18358,11 +18350,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Training &amp; Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="28.8" customHeight="1">
+          <t>https://www.lexis.ae/training-events-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="57.6" customHeight="1">
       <c r="A44" t="n">
         <v>43</v>
       </c>
@@ -18378,11 +18370,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="28.8" customHeight="1">
+          <t>https://lawhouse.ae/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="43.2" customHeight="1">
       <c r="A45" t="n">
         <v>44</v>
       </c>
@@ -18398,11 +18390,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="28.8" customHeight="1">
+          <t>https://ucl.ae/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="57.6" customHeight="1">
       <c r="A46" t="n">
         <v>45</v>
       </c>
@@ -18418,11 +18410,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="43.2" customHeight="1">
+          <t>https://taxexpertsclub.ae/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="72" customHeight="1">
       <c r="A47" t="n">
         <v>46</v>
       </c>
@@ -18438,11 +18430,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="28.8" customHeight="1">
+          <t>https://www.uaefma.org/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="57.6" customHeight="1">
       <c r="A48" t="n">
         <v>47</v>
       </c>
@@ -18458,11 +18450,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="43.2" customHeight="1">
+          <t>https://www.cfainstitute.org/societies/directory/middle-east</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="100.8" customHeight="1">
       <c r="A49" t="n">
         <v>48</v>
       </c>
@@ -18478,11 +18470,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="43.2" customHeight="1">
+          <t>https://www.cisi.org/cisiweb2/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="72" customHeight="1">
       <c r="A50" t="n">
         <v>49</v>
       </c>
@@ -18498,11 +18490,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
+          <t>https://www.garp.org/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="57.6" customHeight="1">
       <c r="A51" t="n">
         <v>50</v>
       </c>
@@ -18518,11 +18510,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
+          <t>https://www.theirm.org/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="100.8" customHeight="1">
       <c r="A52" t="n">
         <v>51</v>
       </c>
@@ -18538,11 +18530,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="28.8" customHeight="1">
+          <t>https://www.aopauae.com/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="100.8" customHeight="1">
       <c r="A53" t="n">
         <v>52</v>
       </c>
@@ -18558,11 +18550,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Training &amp; Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="28.8" customHeight="1">
+          <t>https://mail.aaa4uae.ae/site/en/eaaa?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="100.8" customHeight="1">
       <c r="A54" t="n">
         <v>53</v>
       </c>
@@ -18578,11 +18570,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>UAE Chapter Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
+          <t>https://www.garp.org/membership/chapter/united-arab-emirates?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="86.40000000000001" customHeight="1">
       <c r="A55" t="n">
         <v>54</v>
       </c>
@@ -18598,11 +18590,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Events Calendar</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
+          <t>https://www.acfe.com/calendar?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="72" customHeight="1">
       <c r="A56" t="n">
         <v>55</v>
       </c>
@@ -18618,11 +18610,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
+          <t>https://slba.ae/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="43.2" customHeight="1">
       <c r="A57" t="n">
         <v>56</v>
       </c>
@@ -18638,11 +18630,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
+          <t>https://academy.adgm.com/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="57.6" customHeight="1">
       <c r="A58" t="n">
         <v>57</v>
       </c>
@@ -18658,11 +18650,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Exhibitions &amp; Conferences</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
+          <t>https://ajmanchamber.ae/en/archives/exhibitions-conferences/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="86.40000000000001" customHeight="1">
       <c r="A59" t="n">
         <v>58</v>
       </c>
@@ -18678,11 +18670,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
+          <t>https://rakchamber.ae/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="100.8" customHeight="1">
       <c r="A60" t="n">
         <v>59</v>
       </c>
@@ -18698,11 +18690,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
+          <t>https://www.fujairahchamber.ae/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="86.40000000000001" customHeight="1">
       <c r="A61" t="n">
         <v>60</v>
       </c>
@@ -18718,11 +18710,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
+          <t>https://uaqchamber.ae/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="100.8" customHeight="1">
       <c r="A62" t="n">
         <v>61</v>
       </c>
@@ -18738,11 +18730,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
+          <t>https://www.irishbusinessnetwork.org/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="57.6" customHeight="1">
       <c r="A63" t="n">
         <v>62</v>
       </c>
@@ -18758,11 +18750,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
+          <t>https://www.sbcuae.se/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="57.6" customHeight="1">
       <c r="A64" t="n">
         <v>63</v>
       </c>
@@ -18778,11 +18770,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
+          <t>https://www.bbc-uae.com/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="57.6" customHeight="1">
       <c r="A65" t="n">
         <v>64</v>
       </c>
@@ -18798,11 +18790,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
+          <t>https://www.sbcuae.org/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="57.6" customHeight="1">
       <c r="A66" t="n">
         <v>65</v>
       </c>
@@ -18818,11 +18810,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
+          <t>https://www.diac.com/en/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="72" customHeight="1">
       <c r="A67" t="n">
         <v>66</v>
       </c>
@@ -18838,11 +18830,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
+          <t>https://www.adjd.gov.ae/EN/Pages/Events.aspx?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="57.6" customHeight="1">
       <c r="A68" t="n">
         <v>67</v>
       </c>
@@ -18858,11 +18850,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
+          <t>https://www.dld.gov.ae/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="72" customHeight="1">
       <c r="A69" t="n">
         <v>68</v>
       </c>
@@ -18878,11 +18870,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
+          <t>https://www.emirateslegalnetwork.com/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="72" customHeight="1">
       <c r="A70" t="n">
         <v>69</v>
       </c>
@@ -18898,11 +18890,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
+          <t>https://cms.law/en/are/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="57.6" customHeight="1">
       <c r="A71" t="n">
         <v>70</v>
       </c>
@@ -18918,11 +18910,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Events &amp; Webinars</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
+          <t>https://mena.thomsonreuters.com/en/events.html?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="86.40000000000001" customHeight="1">
       <c r="A72" t="n">
         <v>71</v>
       </c>
@@ -18938,11 +18930,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
+          <t>https://www.bakertilly.ae/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="57.6" customHeight="1">
       <c r="A73" t="n">
         <v>72</v>
       </c>
@@ -18958,11 +18950,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
+          <t>https://www.grantthornton.ae/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="72" customHeight="1">
       <c r="A74" t="n">
         <v>73</v>
       </c>
@@ -18978,11 +18970,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
+          <t>https://www.crowe.com/ae/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="72" customHeight="1">
       <c r="A75" t="n">
         <v>74</v>
       </c>
@@ -18998,11 +18990,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
+          <t>https://www.deloitte.com/middle-east/en/events.html?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="43.2" customHeight="1">
       <c r="A76" t="n">
         <v>75</v>
       </c>
@@ -19018,11 +19010,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
+          <t>https://www.bdo.ae/en-gb/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="57.6" customHeight="1">
       <c r="A77" t="n">
         <v>76</v>
       </c>
@@ -19038,11 +19030,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
+          <t>https://kpmg.com/ae/en/home/events.html?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="57.6" customHeight="1">
       <c r="A78" t="n">
         <v>77</v>
       </c>
@@ -19058,11 +19050,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
+          <t>https://www.pwc.com/m1/en/events.html?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="86.40000000000001" customHeight="1">
       <c r="A79" t="n">
         <v>78</v>
       </c>
@@ -19078,11 +19070,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
+          <t>https://www.ey.com/en_ae/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="43.2" customHeight="1">
       <c r="A80" t="n">
         <v>79</v>
       </c>
@@ -19098,11 +19090,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
+          <t>https://uaeiaa.org/events-calendar?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="43.2" customHeight="1">
       <c r="A81" t="n">
         <v>80</v>
       </c>
@@ -19118,11 +19110,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
+          <t>https://www.cisi.org/cisiweb2/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="43.2" customHeight="1">
       <c r="A82" t="n">
         <v>81</v>
       </c>
@@ -19138,11 +19130,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Our Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
+          <t>https://www.globalethicalfinance.org/our-events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="43.2" customHeight="1">
       <c r="A83" t="n">
         <v>82</v>
       </c>
@@ -19158,11 +19150,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Upcoming Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
+          <t>https://www.dsig.ae/upcoming-events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="43.2" customHeight="1">
       <c r="A84" t="n">
         <v>83</v>
       </c>
@@ -19178,11 +19170,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
+          <t>https://academy.adgm.com/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="43.2" customHeight="1">
       <c r="A85" t="n">
         <v>84</v>
       </c>
@@ -19198,11 +19190,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
+          <t>https://moiat.gov.ae/en/media-center/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="43.2" customHeight="1">
       <c r="A86" t="n">
         <v>85</v>
       </c>
@@ -19218,11 +19210,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
+          <t>https://rakchamber.ae/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="43.2" customHeight="1">
       <c r="A87" t="n">
         <v>86</v>
       </c>
@@ -19238,11 +19230,11 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AOPA Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
+          <t>https://www.aopauae.com/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="72" customHeight="1">
       <c r="A88" t="n">
         <v>87</v>
       </c>
@@ -19258,11 +19250,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="28.8" customHeight="1">
+          <t>https://www.abudhabichamber.ae/en?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="115.2" customHeight="1">
       <c r="A89" t="n">
         <v>88</v>
       </c>
@@ -19278,11 +19270,916 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Exhibitions &amp; Conferences</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="28.8" customHeight="1"/>
+          <t>https://ajmanchamber.ae/en/archives/exhibitions-conferences/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="57.6" customHeight="1">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Sharia Professionals Association</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Islamic Finance / Sharia</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="100.8" customHeight="1">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CMT Association – Dubai Community</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Finance / Investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="86.40000000000001" customHeight="1">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>IMA – Dubai Chapter</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Accounting / Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="86.40000000000001" customHeight="1">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Interarab Cambist Association</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Banking / Financial Markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="72" customHeight="1">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ADNEC Group</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Business / Conferences / Finance</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://www.adnecgroup.ae/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="57.6" customHeight="1">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Abu Dhabi Finance Week</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Finance / Investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="86.40000000000001" customHeight="1">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Abu Dhabi Sustainable Finance Forum</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Sustainable Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="129.6" customHeight="1">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Dubai FinTech Summit</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>FinTech / Finance</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://www.dubaifintechsummit.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="72" customHeight="1">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Dubai Future Finance Week</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Finance / Financial Services</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://www.dubaifuturefinanceweek.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="100.8" customHeight="1">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Dubai International Financial Centre</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Financial Services / Regulation</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://www.difc.com/whats-on/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="144" customHeight="1">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Financial Services Regulatory Authority – ADGM</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Financial Regulation</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.adgm.com/media/announcements</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="100.8" customHeight="1">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ADGM Courts</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Legal / Arbitration</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://www.adgm.com/operating-in-adgm/courts/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="72" customHeight="1">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>DIFC Courts</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Legal / Arbitration</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://www.difccourts.ae/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="86.40000000000001" customHeight="1">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Dubai International Arbitration Centre Academy</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Arbitration / Legal</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://www.diac.com/en/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="72" customHeight="1">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Dubai Arbitration Week</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Arbitration / Legal</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://www.dubaiarbitrationweek.com/calender/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="72" customHeight="1">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Dubai Legal Week</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Legal / Business</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://www.dubailegalweek.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="57.6" customHeight="1">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Emirates Maritime Arbitration Centre</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Arbitration / Legal</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://emac.org.ae/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="72" customHeight="1">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>DIFC-LCIA / Dubai arbitration community</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Arbitration / Legal</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://www.diac.com/en/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="57.6" customHeight="1">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Chartered Institute of Arbitrators – UAE Branch</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Arbitration / Legal</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://www.ciarb.org/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="86.40000000000001" customHeight="1">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>International Bar Association – UAE activities</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://www.ibanet.org/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="43.2" customHeight="1">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>International Association of Young Lawyers – UAE</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://www.iayl.org/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="57.6" customHeight="1">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Society of Construction Law – UAE</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Construction Law / Legal</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://www.scl.org.ae/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="72" customHeight="1">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Dubai Chamber of Commerce – Legal &amp; Business Community</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Business / Legal</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://www.dubaichamber.com/en/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="86.40000000000001" customHeight="1">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Norwegian Business Association Dubai</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Business / Trade</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://nbad.ae/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="43.2" customHeight="1">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Danish Business Association UAE</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Business / Trade</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://dba-uae.com/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="43.2" customHeight="1">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>German Emirati Joint Council for Industry &amp; Commerce</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Business / Trade / Investment</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://vae.ahk.de/en/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="86.40000000000001" customHeight="1">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>French Business Council Dubai &amp; Northern Emirates</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Business / Trade / Investment</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://www.ccifranceuae.com/events.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="43.2" customHeight="1">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Italian Industry &amp; Commerce Office in the UAE</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Business / Trade / Investment</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://www.iicuae.com/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="43.2" customHeight="1">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Turkish Business Council UAE</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Business / Trade / Investment</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://www.turkeybusinesscouncil.ae/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="57.6" customHeight="1">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Indian Business &amp; Professional Council Dubai</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Business / Professional</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://ibpcdubai.com/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="100.8" customHeight="1">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Pakistan Business Council Dubai</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Business / Trade / Finance</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>https://pakistansbc.org/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="86.40000000000001" customHeight="1">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Bangladesh Business Council UAE</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Business / Trade</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://bbcu.ae/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="72" customHeight="1">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Philippine Business Council Dubai &amp; Northern Emirates</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Business / Trade</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>https://pbcdubai.org/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="100.8" customHeight="1">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Korean Business Council UAE</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Business / Trade / Investment</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>https://www.kbcuae.com/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="57.6" customHeight="1">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Japanese Business Council Dubai</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Business / Trade / Investment</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>https://www.jbcuae.com/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="129.6" customHeight="1">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Greek Business Council UAE</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Business / Trade / Investment</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://www.gbcuae.com/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="86.40000000000001" customHeight="1">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Polish Business Council UAE</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Business / Trade / Investment</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>https://pbcu.ae/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="72" customHeight="1">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Czech Business Council Dubai</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Business / Trade / Investment</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>https://www.cbcuae.com/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="72" customHeight="1">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Romanian Business Council UAE</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Business / Trade / Investment</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>https://www.rbcu.ae/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="57.6" customHeight="1">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Lebanese Business Council Dubai</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Business / Trade / Investment</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>https://lbcdubai.com/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="115.2" customHeight="1">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Egyptian Business Council Dubai</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Business / Trade / Investment</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>https://ebcdubai.com/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="86.40000000000001" customHeight="1">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Jordan Business Council UAE</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Business / Trade / Investment</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>https://jbcuae.com/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="86.40000000000001" customHeight="1">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Moroccan Business Council UAE</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Business / Trade / Investment</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>https://mbcuae.org/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="57.6" customHeight="1">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Brazilian Business Council UAE</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Business / Trade / Investment</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>https://www.braziluae.com/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="100.8" customHeight="1">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Mexican Business Council UAE</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Business / Trade / Investment</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>https://www.mexicanbusinesscouncil.com/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="57.6" customHeight="1">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>New Zealand Business Council UAE</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Business / Trade / Investment</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>https://nzbcuae.com/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="72" customHeight="1"/>
+    <row r="137" ht="86.40000000000001" customHeight="1"/>
+    <row r="138" ht="57.6" customHeight="1"/>
+    <row r="139" ht="57.6" customHeight="1"/>
+    <row r="140" ht="57.6" customHeight="1"/>
+    <row r="141" ht="57.6" customHeight="1"/>
+    <row r="142" ht="57.6" customHeight="1"/>
+    <row r="143" ht="72" customHeight="1"/>
+    <row r="144" ht="57.6" customHeight="1"/>
+    <row r="145" ht="57.6" customHeight="1"/>
+    <row r="146" ht="57.6" customHeight="1"/>
+    <row r="147" ht="72" customHeight="1"/>
+    <row r="148" ht="57.6" customHeight="1"/>
+    <row r="149" ht="57.6" customHeight="1"/>
+    <row r="150" ht="72" customHeight="1"/>
+    <row r="151" ht="57.6" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19296,14 +20193,8 @@
   </sheetPr>
   <dimension ref="A1:D108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="5.77734375" customWidth="1" min="1" max="1"/>
-    <col width="35" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="16.6640625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="18.6640625" bestFit="1" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28.8" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>#</t>
@@ -19325,7 +20216,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28.8" customHeight="1">
       <c r="A2" t="n">
         <v>1</v>
       </c>
@@ -19341,11 +20232,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28.8" customHeight="1">
+          <t>https://www.taxinstitute.com.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="43.2" customHeight="1">
       <c r="A3" t="n">
         <v>2</v>
       </c>
@@ -19361,11 +20252,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Conferences &amp; Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28.8" customHeight="1">
+          <t>https://www.cpaaustralia.com.au/professional-development/conferences-and-events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="115.2" customHeight="1">
       <c r="A4" t="n">
         <v>3</v>
       </c>
@@ -19381,11 +20272,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>https://www.charteredaccountants.com.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="57.6" customHeight="1">
       <c r="A5" t="n">
         <v>4</v>
       </c>
@@ -19401,11 +20292,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Events &amp; CPD</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28.8" customHeight="1">
+          <t>https://www.publicaccountants.org.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="100.8" customHeight="1">
       <c r="A6" t="n">
         <v>5</v>
       </c>
@@ -19421,11 +20312,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+          <t>https://ifpa.com.au/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="72" customHeight="1">
       <c r="A7" t="n">
         <v>6</v>
       </c>
@@ -19441,11 +20332,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Events Calendar</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28.8" customHeight="1">
+          <t>https://ifa-australia.com.au/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="129.6" customHeight="1">
       <c r="A8" t="n">
         <v>7</v>
       </c>
@@ -19461,11 +20352,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28.8" customHeight="1">
+          <t>https://www.atma.com.au/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="86.40000000000001" customHeight="1">
       <c r="A9" t="n">
         <v>8</v>
       </c>
@@ -19481,11 +20372,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28.8" customHeight="1">
+          <t>https://faaa.au/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="43.2" customHeight="1">
       <c r="A10" t="n">
         <v>9</v>
       </c>
@@ -19501,11 +20392,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28.8" customHeight="1">
+          <t>https://www.smsfassociation.com/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="100.8" customHeight="1">
       <c r="A11" t="n">
         <v>10</v>
       </c>
@@ -19521,11 +20412,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28.8" customHeight="1">
+          <t>https://www.aist.asn.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="100.8" customHeight="1">
       <c r="A12" t="n">
         <v>11</v>
       </c>
@@ -19541,11 +20432,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
+          <t>https://www.afma.com.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="57.6" customHeight="1">
       <c r="A13" t="n">
         <v>12</v>
       </c>
@@ -19561,11 +20452,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
+          <t>https://www.ausbanking.org.au/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="43.2" customHeight="1">
       <c r="A14" t="n">
         <v>13</v>
       </c>
@@ -19581,11 +20472,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28.8" customHeight="1">
+          <t>https://fsc.org.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="72" customHeight="1">
       <c r="A15" t="n">
         <v>14</v>
       </c>
@@ -19601,11 +20492,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28.8" customHeight="1">
+          <t>https://www.governanceinstitute.com.au/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="158.4" customHeight="1">
       <c r="A16" t="n">
         <v>15</v>
       </c>
@@ -19621,11 +20512,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
+          <t>https://arita.com.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="57.6" customHeight="1">
       <c r="A17" t="n">
         <v>16</v>
       </c>
@@ -19641,11 +20532,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
+          <t>https://lawcouncil.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="72" customHeight="1">
       <c r="A18" t="n">
         <v>17</v>
       </c>
@@ -19661,11 +20552,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
+          <t>https://www.lawsociety.com.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="57.6" customHeight="1">
       <c r="A19" t="n">
         <v>18</v>
       </c>
@@ -19681,11 +20572,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
+          <t>https://www.liv.asn.au/Events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="43.2" customHeight="1">
       <c r="A20" t="n">
         <v>19</v>
       </c>
@@ -19701,11 +20592,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+          <t>https://www.qls.com.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="57.6" customHeight="1">
       <c r="A21" t="n">
         <v>20</v>
       </c>
@@ -19721,11 +20612,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
+          <t>https://www.lawsocietysa.asn.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="57.6" customHeight="1">
       <c r="A22" t="n">
         <v>21</v>
       </c>
@@ -19741,11 +20632,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
+          <t>https://www.lawsocietywa.asn.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="43.2" customHeight="1">
       <c r="A23" t="n">
         <v>22</v>
       </c>
@@ -19761,11 +20652,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
+          <t>https://www.lst.org.au/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="57.6" customHeight="1">
       <c r="A24" t="n">
         <v>23</v>
       </c>
@@ -19781,11 +20672,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
+          <t>https://lawsocietynt.com.au/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="72" customHeight="1">
       <c r="A25" t="n">
         <v>24</v>
       </c>
@@ -19801,11 +20692,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
+          <t>https://www.cla.org.au/Home?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="57.6" customHeight="1">
       <c r="A26" t="n">
         <v>25</v>
       </c>
@@ -19821,11 +20712,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Events &amp; Videos</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+          <t>https://www.academyoflaw.org.au/events-and-videos?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="72" customHeight="1">
       <c r="A27" t="n">
         <v>26</v>
       </c>
@@ -19841,11 +20732,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="28.8" customHeight="1">
+          <t>https://www.aala.org.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="100.8" customHeight="1">
       <c r="A28" t="n">
         <v>27</v>
       </c>
@@ -19861,11 +20752,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="28.8" customHeight="1">
+          <t>https://www.accaustralia.com.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="86.40000000000001" customHeight="1">
       <c r="A29" t="n">
         <v>28</v>
       </c>
@@ -19881,11 +20772,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28.8" customHeight="1">
+          <t>https://www.aicd.com.au/events.html?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="86.40000000000001" customHeight="1">
       <c r="A30" t="n">
         <v>29</v>
       </c>
@@ -19901,11 +20792,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
+          <t>https://www.aicm.com.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="57.6" customHeight="1">
       <c r="A31" t="n">
         <v>30</v>
       </c>
@@ -19921,11 +20812,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28.8" customHeight="1">
+          <t>https://www.financialcounsellingaustralia.org.au/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="86.40000000000001" customHeight="1">
       <c r="A32" t="n">
         <v>31</v>
       </c>
@@ -19941,11 +20832,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
+          <t>https://www.afp.org.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="72" customHeight="1">
       <c r="A33" t="n">
         <v>32</v>
       </c>
@@ -19961,11 +20852,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="28.8" customHeight="1">
+          <t>https://www.arpi.org.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="100.8" customHeight="1">
       <c r="A34" t="n">
         <v>33</v>
       </c>
@@ -19981,11 +20872,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="28.8" customHeight="1">
+          <t>https://www.rmia.org.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="72" customHeight="1">
       <c r="A35" t="n">
         <v>34</v>
       </c>
@@ -20001,11 +20892,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="28.8" customHeight="1">
+          <t>https://www.aim.com.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="72" customHeight="1">
       <c r="A36" t="n">
         <v>35</v>
       </c>
@@ -20021,11 +20912,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="28.8" customHeight="1">
+          <t>https://aimwa.com/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="86.40000000000001" customHeight="1">
       <c r="A37" t="n">
         <v>36</v>
       </c>
@@ -20041,11 +20932,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
+          <t>https://www.aiqs.com.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="57.6" customHeight="1">
       <c r="A38" t="n">
         <v>37</v>
       </c>
@@ -20061,11 +20952,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
+          <t>https://www.propertycouncil.com.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="72" customHeight="1">
       <c r="A39" t="n">
         <v>38</v>
       </c>
@@ -20081,11 +20972,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
+          <t>https://www.api.org.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="57.6" customHeight="1">
       <c r="A40" t="n">
         <v>39</v>
       </c>
@@ -20101,11 +20992,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28.8" customHeight="1">
+          <t>https://www.australianpayrollassociation.com.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="86.40000000000001" customHeight="1">
       <c r="A41" t="n">
         <v>40</v>
       </c>
@@ -20121,11 +21012,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="28.8" customHeight="1">
+          <t>https://taps.associationonline.com.au/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="100.8" customHeight="1">
       <c r="A42" t="n">
         <v>41</v>
       </c>
@@ -20141,11 +21032,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="28.8" customHeight="1">
+          <t>https://aana.com.au/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="100.8" customHeight="1">
       <c r="A43" t="n">
         <v>42</v>
       </c>
@@ -20161,11 +21052,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="28.8" customHeight="1">
+          <t>https://www.aicd.com.au/events.html?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="86.40000000000001" customHeight="1">
       <c r="A44" t="n">
         <v>43</v>
       </c>
@@ -20181,11 +21072,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="28.8" customHeight="1">
+          <t>https://www.abl.com.au/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="43.2" customHeight="1">
       <c r="A45" t="n">
         <v>44</v>
       </c>
@@ -20201,11 +21092,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Events &amp; Webinars</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="28.8" customHeight="1">
+          <t>https://www.thomsonreuters.com.au/en-au/events.html?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="72" customHeight="1">
       <c r="A46" t="n">
         <v>45</v>
       </c>
@@ -20221,11 +21112,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="28.8" customHeight="1">
+          <t>https://www.tved.net.au/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="43.2" customHeight="1">
       <c r="A47" t="n">
         <v>46</v>
       </c>
@@ -20241,11 +21132,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
+          <t>https://legalwiseseminars.com.au/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="57.6" customHeight="1">
       <c r="A48" t="n">
         <v>47</v>
       </c>
@@ -20261,11 +21152,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
+          <t>https://www.leocussen.edu.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="43.2" customHeight="1">
       <c r="A49" t="n">
         <v>48</v>
       </c>
@@ -20281,11 +21172,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="28.8" customHeight="1">
+          <t>https://www.collaw.edu.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="100.8" customHeight="1">
       <c r="A50" t="n">
         <v>49</v>
       </c>
@@ -20301,11 +21192,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="28.8" customHeight="1">
+          <t>https://www.aicd.com.au/events.html?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="86.40000000000001" customHeight="1">
       <c r="A51" t="n">
         <v>50</v>
       </c>
@@ -20321,11 +21212,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
+          <t>https://www.aicd.com.au/events.html?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="28.8" customHeight="1">
       <c r="A52" t="n">
         <v>51</v>
       </c>
@@ -20341,11 +21232,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="28.8" customHeight="1">
+          <t>https://corptax.com.au/upcoming-events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="72" customHeight="1">
       <c r="A53" t="n">
         <v>52</v>
       </c>
@@ -20361,11 +21252,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="28.8" customHeight="1">
+          <t>https://www.aubn.org.au/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="72" customHeight="1">
       <c r="A54" t="n">
         <v>53</v>
       </c>
@@ -20381,11 +21272,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="28.8" customHeight="1">
+          <t>https://www.icb.org.au/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="72" customHeight="1">
       <c r="A55" t="n">
         <v>54</v>
       </c>
@@ -20401,11 +21292,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="28.8" customHeight="1">
+          <t>https://www.aat.org.au/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="100.8" customHeight="1">
       <c r="A56" t="n">
         <v>55</v>
       </c>
@@ -20421,11 +21312,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
+          <t>https://aage.com.au/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="100.8" customHeight="1">
       <c r="A57" t="n">
         <v>56</v>
       </c>
@@ -20441,11 +21332,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="28.8" customHeight="1">
+          <t>https://www.afca.org.au/about-us/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="86.40000000000001" customHeight="1">
       <c r="A58" t="n">
         <v>57</v>
       </c>
@@ -20461,11 +21352,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="28.8" customHeight="1">
+          <t>https://asic.gov.au/about-asic/news-centre/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="115.2" customHeight="1">
       <c r="A59" t="n">
         <v>58</v>
       </c>
@@ -20481,11 +21372,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
+          <t>https://www.apra.gov.au/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="100.8" customHeight="1">
       <c r="A60" t="n">
         <v>59</v>
       </c>
@@ -20501,11 +21392,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="28.8" customHeight="1">
+          <t>https://www.ato.gov.au/about-ato/learn-about-tax-and-the-ato/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="57.6" customHeight="1">
       <c r="A61" t="n">
         <v>60</v>
       </c>
@@ -20521,11 +21412,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
+          <t>https://www.aasb.gov.au/about-aasb/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="86.40000000000001" customHeight="1">
       <c r="A62" t="n">
         <v>61</v>
       </c>
@@ -20541,11 +21432,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
+          <t>https://www.auasb.gov.au/about-auasb/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="86.40000000000001" customHeight="1">
       <c r="A63" t="n">
         <v>62</v>
       </c>
@@ -20561,11 +21452,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="28.8" customHeight="1">
+          <t>https://www.frc.gov.au/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="43.2" customHeight="1">
       <c r="A64" t="n">
         <v>63</v>
       </c>
@@ -20581,11 +21472,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
+          <t>https://www.accc.gov.au/about-us/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="115.2" customHeight="1">
       <c r="A65" t="n">
         <v>64</v>
       </c>
@@ -20601,11 +21492,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Information &amp; Proceedings</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
+          <t>https://www.competitiontribunal.gov.au/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="72" customHeight="1">
       <c r="A66" t="n">
         <v>65</v>
       </c>
@@ -20621,11 +21512,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="28.8" customHeight="1">
+          <t>https://www.aicd.com.au/events.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="72" customHeight="1">
       <c r="A67" t="n">
         <v>66</v>
       </c>
@@ -20641,11 +21532,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
+          <t>https://www.australiancomplianceinstitute.org/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="72" customHeight="1">
       <c r="A68" t="n">
         <v>67</v>
       </c>
@@ -20661,11 +21552,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
+          <t>https://www.rmia.org.au/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="72" customHeight="1">
       <c r="A69" t="n">
         <v>68</v>
       </c>
@@ -20681,11 +21572,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
+          <t>https://www.arpi.org.au/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="100.8" customHeight="1">
       <c r="A70" t="n">
         <v>69</v>
       </c>
@@ -20701,11 +21592,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
+          <t>https://www.iia.org.au/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="57.6" customHeight="1">
       <c r="A71" t="n">
         <v>70</v>
       </c>
@@ -20721,11 +21612,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
+          <t>https://www.irma.org.au/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="72" customHeight="1">
       <c r="A72" t="n">
         <v>71</v>
       </c>
@@ -20741,11 +21632,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
+          <t>https://www.aicm.com.au/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="72" customHeight="1">
       <c r="A73" t="n">
         <v>72</v>
       </c>
@@ -20761,11 +21652,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="28.8" customHeight="1">
+          <t>https://arita.com.au/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="72" customHeight="1">
       <c r="A74" t="n">
         <v>73</v>
       </c>
@@ -20781,11 +21672,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="28.8" customHeight="1">
+          <t>https://www.aicm.com.au/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="144" customHeight="1">
       <c r="A75" t="n">
         <v>74</v>
       </c>
@@ -20801,11 +21692,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
+          <t>https://afia.asn.au/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="86.40000000000001" customHeight="1">
       <c r="A76" t="n">
         <v>75</v>
       </c>
@@ -20821,11 +21712,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
+          <t>https://www.afma.com.au/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="72" customHeight="1">
       <c r="A77" t="n">
         <v>76</v>
       </c>
@@ -20841,11 +21732,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
+          <t>https://www.ausbanking.org.au/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="86.40000000000001" customHeight="1">
       <c r="A78" t="n">
         <v>77</v>
       </c>
@@ -20861,11 +21752,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
+          <t>https://www.customerownedbanking.asn.au/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="43.2" customHeight="1">
       <c r="A79" t="n">
         <v>78</v>
       </c>
@@ -20881,11 +21772,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
+          <t>https://www.aussecuritisation.com.au/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="57.6" customHeight="1">
       <c r="A80" t="n">
         <v>79</v>
       </c>
@@ -20901,11 +21792,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
+          <t>https://www.avca.asn.au/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="72" customHeight="1">
       <c r="A81" t="n">
         <v>80</v>
       </c>
@@ -20921,11 +21812,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="28.8" customHeight="1">
+          <t>https://www.aima.org/events.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="72" customHeight="1">
       <c r="A82" t="n">
         <v>81</v>
       </c>
@@ -20941,11 +21832,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="28.8" customHeight="1">
+          <t>https://investmentcouncil.org.au/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="100.8" customHeight="1">
       <c r="A83" t="n">
         <v>82</v>
       </c>
@@ -20961,11 +21852,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="28.8" customHeight="1">
+          <t>https://faaa.au/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="129.6" customHeight="1">
       <c r="A84" t="n">
         <v>83</v>
       </c>
@@ -20981,11 +21872,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
+          <t>https://faaa.au/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="72" customHeight="1">
       <c r="A85" t="n">
         <v>84</v>
       </c>
@@ -21001,11 +21892,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
+          <t>https://faaa.au/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="72" customHeight="1">
       <c r="A86" t="n">
         <v>85</v>
       </c>
@@ -21021,11 +21912,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="28.8" customHeight="1">
+          <t>https://www.superannuation.asn.au/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="57.6" customHeight="1">
       <c r="A87" t="n">
         <v>86</v>
       </c>
@@ -21041,11 +21932,11 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
+          <t>https://www.aist.asn.au/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="72" customHeight="1">
       <c r="A88" t="n">
         <v>87</v>
       </c>
@@ -21061,11 +21952,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="28.8" customHeight="1">
+          <t>https://aiflam.org.au/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="43.2" customHeight="1">
       <c r="A89" t="n">
         <v>88</v>
       </c>
@@ -21081,11 +21972,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="28.8" customHeight="1">
+          <t>https://lawyersalliance.com.au/Web/Web/Events/Upcoming-Events.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="86.40000000000001" customHeight="1">
       <c r="A90" t="n">
         <v>89</v>
       </c>
@@ -21101,11 +21992,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="28.8" customHeight="1">
+          <t>https://www.austbar.asn.au/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="86.40000000000001" customHeight="1">
       <c r="A91" t="n">
         <v>90</v>
       </c>
@@ -21121,11 +22012,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="28.8" customHeight="1">
+          <t>https://www.accaustralia.com.au/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="86.40000000000001" customHeight="1">
       <c r="A92" t="n">
         <v>91</v>
       </c>
@@ -21141,11 +22032,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
+          <t>https://cfas.org.au/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="115.2" customHeight="1">
       <c r="A93" t="n">
         <v>92</v>
       </c>
@@ -21161,11 +22052,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
+          <t>https://erlaw.org.au/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="43.2" customHeight="1">
       <c r="A94" t="n">
         <v>93</v>
       </c>
@@ -21181,11 +22072,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Events Calendar</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
+          <t>https://www.fintechaustralia.org.au/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="57.6" customHeight="1">
       <c r="A95" t="n">
         <v>94</v>
       </c>
@@ -21201,11 +22092,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
+          <t>https://www.mfaa.com.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="57.6" customHeight="1">
       <c r="A96" t="n">
         <v>95</v>
       </c>
@@ -21221,11 +22112,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Events / Conference</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
+          <t>https://shop.bfsla.org/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="86.40000000000001" customHeight="1">
       <c r="A97" t="n">
         <v>96</v>
       </c>
@@ -21241,11 +22132,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
+          <t>https://www.afia.asn.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="57.6" customHeight="1">
       <c r="A98" t="n">
         <v>97</v>
       </c>
@@ -21261,11 +22152,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
+          <t>https://www.finpro.org.au/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="43.2" customHeight="1">
       <c r="A99" t="n">
         <v>98</v>
       </c>
@@ -21281,11 +22172,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Conference / Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
+          <t>https://pecbookings.eventsair.com/alla2026/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="57.6" customHeight="1">
       <c r="A100" t="n">
         <v>99</v>
       </c>
@@ -21301,11 +22192,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
+          <t>https://www.vscl.org.au/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="57.6" customHeight="1">
       <c r="A101" t="n">
         <v>100</v>
       </c>
@@ -21321,11 +22212,11 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="28.8" customHeight="1">
+          <t>https://www.claanz.org.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="43.2" customHeight="1">
       <c r="A102" t="n">
         <v>101</v>
       </c>
@@ -21341,11 +22232,11 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Events &amp; Conferences</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="28.8" customHeight="1">
+          <t>https://www.probonocentre.org.au/news-media-2/events-and-conferences/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="43.2" customHeight="1">
       <c r="A103" t="n">
         <v>102</v>
       </c>
@@ -21361,11 +22252,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
+          <t>https://www.scla.org.au/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="72" customHeight="1">
       <c r="A104" t="n">
         <v>103</v>
       </c>
@@ -21381,7 +22272,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>https://www.tved.net.au/?utm_source=chatgpt.com</t>
         </is>
       </c>
     </row>
@@ -21401,11 +22292,11 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="28.8" customHeight="1">
+          <t>https://ifpa.com.au/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="100.8" customHeight="1">
       <c r="A106" t="n">
         <v>105</v>
       </c>
@@ -21421,11 +22312,11 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Conference</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="28.8" customHeight="1">
+          <t>https://www.afaanz.org/conference?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="86.40000000000001" customHeight="1">
       <c r="A107" t="n">
         <v>106</v>
       </c>
@@ -21441,11 +22332,11 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="28.8" customHeight="1">
+          <t>https://taps.associationonline.com.au/events/?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="72" customHeight="1">
       <c r="A108" t="n">
         <v>107</v>
       </c>
@@ -21461,27 +22352,54 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="28.8" customHeight="1"/>
-    <row r="111" ht="28.8" customHeight="1"/>
-    <row r="112" ht="28.8" customHeight="1"/>
-    <row r="118" ht="43.2" customHeight="1"/>
-    <row r="119" ht="28.8" customHeight="1"/>
-    <row r="125" ht="28.8" customHeight="1"/>
-    <row r="130" ht="28.8" customHeight="1"/>
-    <row r="131" ht="28.8" customHeight="1"/>
-    <row r="133" ht="28.8" customHeight="1"/>
-    <row r="138" ht="43.2" customHeight="1"/>
-    <row r="139" ht="28.8" customHeight="1"/>
-    <row r="140" ht="28.8" customHeight="1"/>
-    <row r="141" ht="28.8" customHeight="1"/>
-    <row r="143" ht="28.8" customHeight="1"/>
-    <row r="144" ht="28.8" customHeight="1"/>
-    <row r="145" ht="28.8" customHeight="1"/>
-    <row r="147" ht="28.8" customHeight="1"/>
+          <t>https://www.api.org.au/events?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="86.40000000000001" customHeight="1"/>
+    <row r="110" ht="57.6" customHeight="1"/>
+    <row r="111" ht="86.40000000000001" customHeight="1"/>
+    <row r="112" ht="86.40000000000001" customHeight="1"/>
+    <row r="113" ht="100.8" customHeight="1"/>
+    <row r="114" ht="57.6" customHeight="1"/>
+    <row r="115" ht="72" customHeight="1"/>
+    <row r="116" ht="86.40000000000001" customHeight="1"/>
+    <row r="117" ht="43.2" customHeight="1"/>
+    <row r="118" ht="57.6" customHeight="1"/>
+    <row r="119" ht="72" customHeight="1"/>
+    <row r="120" ht="57.6" customHeight="1"/>
+    <row r="121" ht="72" customHeight="1"/>
+    <row r="122" ht="72" customHeight="1"/>
+    <row r="123" ht="72" customHeight="1"/>
+    <row r="124" ht="100.8" customHeight="1"/>
+    <row r="125" ht="57.6" customHeight="1"/>
+    <row r="126" ht="115.2" customHeight="1"/>
+    <row r="127" ht="43.2" customHeight="1"/>
+    <row r="128" ht="57.6" customHeight="1"/>
+    <row r="129" ht="57.6" customHeight="1"/>
+    <row r="130" ht="86.40000000000001" customHeight="1"/>
+    <row r="131" ht="72" customHeight="1"/>
+    <row r="132" ht="100.8" customHeight="1"/>
+    <row r="133" ht="72" customHeight="1"/>
+    <row r="134" ht="86.40000000000001" customHeight="1"/>
+    <row r="135" ht="72" customHeight="1"/>
+    <row r="136" ht="43.2" customHeight="1"/>
+    <row r="137" ht="57.6" customHeight="1"/>
+    <row r="138" ht="72" customHeight="1"/>
+    <row r="139" ht="72" customHeight="1"/>
+    <row r="140" ht="86.40000000000001" customHeight="1"/>
+    <row r="141" ht="86.40000000000001" customHeight="1"/>
+    <row r="142" ht="43.2" customHeight="1"/>
+    <row r="143" ht="72" customHeight="1"/>
+    <row r="144" ht="86.40000000000001" customHeight="1"/>
+    <row r="145" ht="115.2" customHeight="1"/>
+    <row r="146" ht="72" customHeight="1"/>
+    <row r="147" ht="72" customHeight="1"/>
+    <row r="148" ht="100.8" customHeight="1"/>
+    <row r="149" ht="57.6" customHeight="1"/>
+    <row r="150" ht="72" customHeight="1"/>
+    <row r="151" ht="57.6" customHeight="1"/>
+    <row r="152" ht="57.6" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Sources/Event_scrapper_-_Website_completed.xlsx
+++ b/Sources/Event_scrapper_-_Website_completed.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -73,6 +73,10 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -95,7 +99,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -127,6 +131,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -582,7 +594,7 @@
           <t>Tax, Finance, Accounting, Corporate Law</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>https://www.icai.org/committeeevents.shtml</t>
         </is>
@@ -602,7 +614,7 @@
           <t>International Tax</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>https://www.icai.org/category/international-taxation-committee</t>
         </is>
@@ -622,7 +634,7 @@
           <t>GST / Indirect Tax</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>https://idtc.icai.org/upcoming-events.php</t>
         </is>
@@ -642,7 +654,7 @@
           <t>Accounting / Audit / Finance</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>https://daab.icai.org/events</t>
         </is>
@@ -662,7 +674,7 @@
           <t>Finance / Tax / Accounting</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>https://ipd.icai.org/</t>
         </is>
@@ -682,7 +694,7 @@
           <t>Practice / Tax / Finance</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>https://cmp.icai.org/upcoming-events/</t>
         </is>
@@ -702,7 +714,7 @@
           <t>Tax / Finance / Accounting</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>https://bangaloreicai.org/member/events</t>
         </is>
@@ -722,7 +734,7 @@
           <t>Tax / Finance / Accounting</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>https://www.nagpuricai.org/upcoming-events.php</t>
         </is>
@@ -742,7 +754,7 @@
           <t>Tax / Finance / Accounting</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>https://icaigurugram.org/members/events</t>
         </is>
@@ -762,7 +774,7 @@
           <t>Tax / Finance / Accounting</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>https://thiruvananthapuramicai.org/event_type/members-event/</t>
         </is>
@@ -782,7 +794,7 @@
           <t>Corporate Law / Governance / Finance</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>https://www.icsi.edu/events/</t>
         </is>
@@ -802,7 +814,7 @@
           <t>Cost Accounting / Finance / Tax</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>https://icmai.in/ClntAbout/Events</t>
         </is>
@@ -822,7 +834,7 @@
           <t>Valuation / Insolvency / Finance</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>https://www.rvoicmai.in/upcoming-events</t>
         </is>
@@ -842,7 +854,7 @@
           <t>Insolvency / Law / Finance</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>https://www.ipaicmai.in/IPANEW/ForthcomingEvents.aspx</t>
         </is>
@@ -862,7 +874,7 @@
           <t>Corporate Law / Governance / Compliance</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>https://iica.nic.in/</t>
         </is>
@@ -882,7 +894,7 @@
           <t>Insolvency / Bankruptcy / Corporate Law</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>https://www.iiipicai.in/</t>
         </is>
@@ -902,7 +914,7 @@
           <t>Public Finance / Tax / Economics</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>https://www.nipfp.org.in/event-index-page/</t>
         </is>
@@ -922,7 +934,7 @@
           <t>Investment / Finance / Capital Markets</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>https://cfasocietyindia.org/upcomingevents/</t>
         </is>
@@ -942,7 +954,7 @@
           <t>Banking / Finance / Financial Regulation</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>https://www.cafral.org.in/images/Upcoming-Events.aspx</t>
         </is>
@@ -962,7 +974,7 @@
           <t>Banking / Finance</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>https://www.iibf.org.in/training</t>
         </is>
@@ -982,7 +994,7 @@
           <t>Investment Banking / Capital Markets</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>https://aibi.org.in/event.asp</t>
         </is>
@@ -1002,7 +1014,7 @@
           <t>Capital Markets / Finance</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>https://www.nseindia.com/event-gallery</t>
         </is>
@@ -1022,7 +1034,7 @@
           <t>Capital Markets / Investment / Finance</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>https://www.nseacademy.com/coursedatabase/</t>
         </is>
@@ -1042,7 +1054,7 @@
           <t>Banking / Risk / Finance</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>https://iibfm.com/</t>
         </is>
@@ -1062,7 +1074,7 @@
           <t>Financial Advisory / Finance</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>https://afai.in/</t>
         </is>
@@ -1082,7 +1094,7 @@
           <t>Banking / Capital Markets / FinTech / Finance</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>https://ficci.in/event</t>
         </is>
@@ -1102,7 +1114,7 @@
           <t>Finance / Banking / Tax / Business</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>https://www.cii.in/Events.aspx</t>
         </is>
@@ -1122,7 +1134,7 @@
           <t>Finance / Tax / Business / Regulatory</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>https://www.assocham.org/</t>
         </is>
@@ -1142,7 +1154,7 @@
           <t>Finance / Tax / Business / Law</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="14" t="inlineStr">
         <is>
           <t>https://www.phdcci.in/events/</t>
         </is>
@@ -1162,7 +1174,7 @@
           <t>Finance / Tax / Business Law</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>https://www.bombaychamber.com/events/</t>
         </is>
@@ -1182,7 +1194,7 @@
           <t>Legal / Constitutional / Commercial Law</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>https://barindia.in/</t>
         </is>
@@ -1202,7 +1214,7 @@
           <t>Legal / Corporate Law / Policy</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>https://www.indianbarassociation.org/</t>
         </is>
@@ -1222,7 +1234,7 @@
           <t>Legal / Law &amp; Policy</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="15" t="inlineStr">
         <is>
           <t>https://www.indialawyers.org/event</t>
         </is>
@@ -1242,7 +1254,7 @@
           <t>Arbitration / Dispute Resolution</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="13" t="inlineStr">
         <is>
           <t>https://mcia.org.in/</t>
         </is>
@@ -1262,7 +1274,7 @@
           <t>Arbitration / Commercial Disputes</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>https://www.icaindia.co.in/</t>
         </is>
@@ -1282,7 +1294,7 @@
           <t>Arbitration / Mediation</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
         <is>
           <t>https://www.arbitrationindia.com/</t>
         </is>
@@ -1302,7 +1314,7 @@
           <t>International Law</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>https://isilindia.org/</t>
         </is>
@@ -1322,7 +1334,7 @@
           <t>Legal Profession / Corporate Law</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D39" s="15" t="inlineStr">
         <is>
           <t>https://indianlawfirmsassociation.com/events/</t>
         </is>
@@ -1342,7 +1354,7 @@
           <t>Corporate Law / Compliance</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D40" s="15" t="inlineStr">
         <is>
           <t>https://www.ficl.org.in/ficl-events</t>
         </is>
@@ -1362,7 +1374,7 @@
           <t>Insolvency / Corporate Law</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D41" s="15" t="inlineStr">
         <is>
           <t>https://aipe.org.in/events/</t>
         </is>
@@ -1382,7 +1394,7 @@
           <t>Tax / Legal / Finance / Business</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="14" t="inlineStr">
         <is>
           <t>https://www.ifcci.org.in/events</t>
         </is>
@@ -1402,7 +1414,7 @@
           <t>Finance / Tax / Legal / Business</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D43" s="14" t="inlineStr">
         <is>
           <t>https://indo-german.com/</t>
         </is>
@@ -1422,7 +1434,7 @@
           <t>Finance / Tax / Business Law</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>https://www.indoamerican.org/</t>
         </is>
@@ -1442,7 +1454,7 @@
           <t>Finance / Business / Trade Law</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D45" s="15" t="inlineStr">
         <is>
           <t>https://canada-indiabusiness.com/events</t>
         </is>
@@ -1462,7 +1474,7 @@
           <t>Finance / Regulatory / Business</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D46" s="14" t="inlineStr">
         <is>
           <t>https://ebgfederation.in/</t>
         </is>
@@ -1482,7 +1494,7 @@
           <t>Finance / Business / Tax / Regulatory</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D47" s="14" t="inlineStr">
         <is>
           <t>https://www.mcciapune.com/events</t>
         </is>
@@ -1502,7 +1514,7 @@
           <t>Finance / Business / Tax</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D48" s="15" t="inlineStr">
         <is>
           <t>https://www.tamilchamber.org/upcoming-events</t>
         </is>
@@ -1522,7 +1534,7 @@
           <t>Finance / Business / Regulation</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D49" s="13" t="inlineStr">
         <is>
           <t>https://www.bcic.in/</t>
         </is>
@@ -1542,7 +1554,7 @@
           <t>Finance / Business / Tax / Regulation</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D50" s="15" t="inlineStr">
         <is>
           <t>https://delhichamber.ca/event-calendar/</t>
         </is>
@@ -1562,7 +1574,7 @@
           <t>Finance / Management / Business</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D51" s="14" t="inlineStr">
         <is>
           <t>https://hyma.in/</t>
         </is>
@@ -1582,7 +1594,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D52" s="15" t="inlineStr">
         <is>
           <t>https://indiafa.org/conferences/</t>
         </is>
@@ -1602,7 +1614,7 @@
           <t>Capital Markets</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D53" s="15" t="inlineStr">
         <is>
           <t>https://anmi.in/anmi_front/event_platform/public/</t>
         </is>
@@ -1622,7 +1634,7 @@
           <t>Investment / Finance</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D54" s="13" t="inlineStr">
         <is>
           <t>https://www.amfiindia.com/events</t>
         </is>
@@ -1642,7 +1654,7 @@
           <t>Fixed Income / Finance</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D55" s="13" t="inlineStr">
         <is>
           <t>https://www.fimmda.org/</t>
         </is>
@@ -1662,7 +1674,7 @@
           <t>Forex / Banking / Finance</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" s="13" t="inlineStr">
         <is>
           <t>https://www.fedai.org.in/</t>
         </is>
@@ -1702,7 +1714,7 @@
           <t>Financial Planning</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D58" s="13" t="inlineStr">
         <is>
           <t>https://www.fpsbindia.org/</t>
         </is>
@@ -1742,7 +1754,7 @@
           <t>PE / VC / Finance</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D60" s="13" t="inlineStr">
         <is>
           <t>https://ivca.in/events/</t>
         </is>
@@ -1762,7 +1774,7 @@
           <t>Finance / NBFC</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="D61" s="15" t="inlineStr">
         <is>
           <t>https://fla.org.uk/events-and-training/events/</t>
         </is>
@@ -1782,7 +1794,7 @@
           <t>Banking / Finance</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D62" s="13" t="inlineStr">
         <is>
           <t>https://www.iba.org.in/</t>
         </is>
@@ -1802,7 +1814,7 @@
           <t>Banking / Regulation</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D63" s="13" t="inlineStr">
         <is>
           <t>https://www.bcsbi.org.in/</t>
         </is>
@@ -1822,7 +1834,7 @@
           <t>Insurance / Regulation</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D64" s="13" t="inlineStr">
         <is>
           <t>https://www.cioins.co.in/</t>
         </is>
@@ -1842,7 +1854,7 @@
           <t>Insurance / Finance</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D65" s="13" t="inlineStr">
         <is>
           <t>https://www.gicouncil.in/</t>
         </is>
@@ -1862,7 +1874,7 @@
           <t>Insurance / Finance</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D66" s="13" t="inlineStr">
         <is>
           <t>https://www.lifeinscouncil.org/</t>
         </is>
@@ -1882,7 +1894,7 @@
           <t>Financial Crime / Compliance</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr">
+      <c r="D67" s="15" t="inlineStr">
         <is>
           <t>https://www.acfcs.org/upcoming-events</t>
         </is>
@@ -1902,7 +1914,7 @@
           <t>Capital Markets / Finance</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D68" s="13" t="inlineStr">
         <is>
           <t>https://www.indiainx.com/</t>
         </is>
@@ -1922,7 +1934,7 @@
           <t>Capital Markets</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D69" s="13" t="inlineStr">
         <is>
           <t>https://www.msei.in/</t>
         </is>
@@ -1942,7 +1954,7 @@
           <t>Commodities / Finance</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D70" s="13" t="inlineStr">
         <is>
           <t>https://www.mcxindia.com/</t>
         </is>
@@ -1962,7 +1974,7 @@
           <t>Commodities / Finance</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D71" s="13" t="inlineStr">
         <is>
           <t>https://ncdex.com/</t>
         </is>
@@ -1982,7 +1994,7 @@
           <t>Capital Markets / Finance</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D72" s="13" t="inlineStr">
         <is>
           <t>https://www.bseindia.com/</t>
         </is>
@@ -2022,7 +2034,7 @@
           <t>Investment Advisory</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr">
+      <c r="D74" s="15" t="inlineStr">
         <is>
           <t>https://aria.org.in/events-upcoming-past/</t>
         </is>
@@ -2082,7 +2094,7 @@
           <t>Audit / Tax / Accounting</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="D77" s="14" t="inlineStr">
         <is>
           <t>http://www.societyofauditors.org/</t>
         </is>
@@ -2122,7 +2134,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="D79" s="13" t="inlineStr">
         <is>
           <t>https://aiftponline.org/</t>
         </is>
@@ -2142,7 +2154,7 @@
           <t>International Tax</t>
         </is>
       </c>
-      <c r="D80" s="6" t="inlineStr">
+      <c r="D80" s="14" t="inlineStr">
         <is>
           <t>https://ifaindia.in/</t>
         </is>
@@ -2162,7 +2174,7 @@
           <t>GST / Tax</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="D81" s="14" t="inlineStr">
         <is>
           <t>https://gstpam.org/</t>
         </is>
@@ -2182,7 +2194,7 @@
           <t>Trade / Tax / Finance</t>
         </is>
       </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="D82" s="13" t="inlineStr">
         <is>
           <t>https://www.fieo.org/events</t>
         </is>
@@ -2202,7 +2214,7 @@
           <t>Trade / Tax / Regulatory</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D83" s="13" t="inlineStr">
         <is>
           <t>https://www.epces.in/</t>
         </is>
@@ -2222,7 +2234,7 @@
           <t>Trade / Finance / Regulation</t>
         </is>
       </c>
-      <c r="D84" s="5" t="inlineStr">
+      <c r="D84" s="13" t="inlineStr">
         <is>
           <t>https://www.chemexcil.gov.in/</t>
         </is>
@@ -2242,7 +2254,7 @@
           <t>Trade / Finance / Regulation</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D85" s="13" t="inlineStr">
         <is>
           <t>https://www.eepcindia.org/</t>
         </is>
@@ -2262,7 +2274,7 @@
           <t>Trade / Finance / Regulation</t>
         </is>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D86" s="13" t="inlineStr">
         <is>
           <t>https://servicesepc.org/</t>
         </is>
@@ -2282,7 +2294,7 @@
           <t>Trade / Finance / Regulation</t>
         </is>
       </c>
-      <c r="D87" s="6" t="inlineStr">
+      <c r="D87" s="14" t="inlineStr">
         <is>
           <t>https://www.tepc.gov.in/</t>
         </is>
@@ -2302,7 +2314,7 @@
           <t>Trade / Finance / Regulation</t>
         </is>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D88" s="13" t="inlineStr">
         <is>
           <t>https://www.escindia.in/</t>
         </is>
@@ -2322,7 +2334,7 @@
           <t>Trade / Finance / Regulation</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D89" s="13" t="inlineStr">
         <is>
           <t>https://www.leatherindia.org/</t>
         </is>
@@ -2342,7 +2354,7 @@
           <t>Trade / Finance</t>
         </is>
       </c>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D90" s="13" t="inlineStr">
         <is>
           <t>https://www.iopepc.org/</t>
         </is>
@@ -2362,7 +2374,7 @@
           <t>Trade / Finance / Regulation</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D91" s="13" t="inlineStr">
         <is>
           <t>https://www.plexconcil.org/</t>
         </is>
@@ -2382,7 +2394,7 @@
           <t>Arbitration / Commercial Law</t>
         </is>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D92" s="13" t="inlineStr">
         <is>
           <t>https://www.icaindia.co.in/</t>
         </is>
@@ -2402,7 +2414,7 @@
           <t>Arbitration / Dispute Resolution</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D93" s="13" t="inlineStr">
         <is>
           <t>https://mcia.org.in/</t>
         </is>
@@ -2422,7 +2434,7 @@
           <t>Arbitration / Mediation</t>
         </is>
       </c>
-      <c r="D94" s="5" t="inlineStr">
+      <c r="D94" s="13" t="inlineStr">
         <is>
           <t>https://www.arbitrationindia.com/</t>
         </is>
@@ -2442,7 +2454,7 @@
           <t>International Law</t>
         </is>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D95" s="13" t="inlineStr">
         <is>
           <t>https://isilindia.org/</t>
         </is>
@@ -2482,7 +2494,7 @@
           <t>Labour Law</t>
         </is>
       </c>
-      <c r="D97" s="7" t="inlineStr">
+      <c r="D97" s="15" t="inlineStr">
         <is>
           <t>https://nllaindia.com/events/</t>
         </is>
@@ -2502,7 +2514,7 @@
           <t>Legal / Corporate Law</t>
         </is>
       </c>
-      <c r="D98" s="6" t="inlineStr">
+      <c r="D98" s="14" t="inlineStr">
         <is>
           <t>https://www.silf.org.in/</t>
         </is>
@@ -2522,7 +2534,7 @@
           <t>Corporate Legal / Compliance</t>
         </is>
       </c>
-      <c r="D99" s="7" t="inlineStr">
+      <c r="D99" s="15" t="inlineStr">
         <is>
           <t>https://ccai.net.in/?page_id=1597</t>
         </is>
@@ -2542,7 +2554,7 @@
           <t>Trade Law / International Law</t>
         </is>
       </c>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="D100" s="13" t="inlineStr">
         <is>
           <t>https://ctil.org.in/</t>
         </is>
@@ -2562,7 +2574,7 @@
           <t>Insolvency / Corporate Law</t>
         </is>
       </c>
-      <c r="D101" s="7" t="inlineStr">
+      <c r="D101" s="15" t="inlineStr">
         <is>
           <t>https://aipe.org.in/events/</t>
         </is>
@@ -2582,7 +2594,7 @@
           <t>Tax / Fiscal Law / GST</t>
         </is>
       </c>
-      <c r="D102" s="5" t="inlineStr">
+      <c r="D102" s="13" t="inlineStr">
         <is>
           <t>https://www.ctconline.org/</t>
         </is>
@@ -2602,7 +2614,7 @@
           <t>Tax / Finance / Corporate Governance</t>
         </is>
       </c>
-      <c r="D103" s="5" t="inlineStr">
+      <c r="D103" s="13" t="inlineStr">
         <is>
           <t>https://www.cii.in/Events.aspx</t>
         </is>
@@ -2622,7 +2634,7 @@
           <t>Tax / Finance / Corporate Law</t>
         </is>
       </c>
-      <c r="D104" s="5" t="inlineStr">
+      <c r="D104" s="13" t="inlineStr">
         <is>
           <t>https://www.assocham.org/</t>
         </is>
@@ -2642,7 +2654,7 @@
           <t>Tax / Finance / Legal / Regulatory</t>
         </is>
       </c>
-      <c r="D105" s="5" t="inlineStr">
+      <c r="D105" s="13" t="inlineStr">
         <is>
           <t>https://ficci.in/event</t>
         </is>
@@ -2662,7 +2674,7 @@
           <t>Tax / Finance / Insolvency / Corporate Law</t>
         </is>
       </c>
-      <c r="D106" s="5" t="inlineStr">
+      <c r="D106" s="13" t="inlineStr">
         <is>
           <t>https://www.phdcci.in/events/</t>
         </is>
@@ -2682,7 +2694,7 @@
           <t>Tax / Public Finance / Fiscal Policy</t>
         </is>
       </c>
-      <c r="D107" s="5" t="inlineStr">
+      <c r="D107" s="13" t="inlineStr">
         <is>
           <t>https://www.gift.res.in/</t>
         </is>
@@ -2702,7 +2714,7 @@
           <t>Corporate Governance / Directors / Corporate Law</t>
         </is>
       </c>
-      <c r="D108" s="5" t="inlineStr">
+      <c r="D108" s="13" t="inlineStr">
         <is>
           <t>https://www.iodglobal.com/</t>
         </is>
@@ -2722,7 +2734,7 @@
           <t>Internal Audit / Risk / Governance / Finance</t>
         </is>
       </c>
-      <c r="D109" s="5" t="inlineStr">
+      <c r="D109" s="13" t="inlineStr">
         <is>
           <t>https://www.iiaindia.co.in/</t>
         </is>
@@ -2742,7 +2754,7 @@
           <t>Internal Audit / Risk / Governance</t>
         </is>
       </c>
-      <c r="D110" s="7" t="inlineStr">
+      <c r="D110" s="15" t="inlineStr">
         <is>
           <t>https://iiamadras.org/upcoming-events</t>
         </is>
@@ -2762,7 +2774,7 @@
           <t>Internal Audit / Risk / Governance</t>
         </is>
       </c>
-      <c r="D111" s="5" t="inlineStr">
+      <c r="D111" s="13" t="inlineStr">
         <is>
           <t>https://www.iiabombay.org/</t>
         </is>
@@ -2782,7 +2794,7 @@
           <t>IT Audit / Risk / Governance / Compliance</t>
         </is>
       </c>
-      <c r="D112" s="5" t="inlineStr">
+      <c r="D112" s="13" t="inlineStr">
         <is>
           <t>https://www.isacachennai.org/</t>
         </is>
@@ -2802,7 +2814,7 @@
           <t>IT Audit / Risk / Governance</t>
         </is>
       </c>
-      <c r="D113" s="5" t="inlineStr">
+      <c r="D113" s="13" t="inlineStr">
         <is>
           <t>https://isacadelhi.org/</t>
         </is>
@@ -2822,7 +2834,7 @@
           <t>Arbitration / Commercial Law / Dispute Resolution</t>
         </is>
       </c>
-      <c r="D114" s="7" t="inlineStr">
+      <c r="D114" s="15" t="inlineStr">
         <is>
           <t>https://dhcdiac.nic.in/all-events/</t>
         </is>
@@ -2842,7 +2854,7 @@
           <t>Arbitration / Insolvency / Corporate Law</t>
         </is>
       </c>
-      <c r="D115" s="5" t="inlineStr">
+      <c r="D115" s="13" t="inlineStr">
         <is>
           <t>https://www.npac.in/</t>
         </is>
@@ -2862,7 +2874,7 @@
           <t>Arbitration / ADR / Legal</t>
         </is>
       </c>
-      <c r="D116" s="7" t="inlineStr">
+      <c r="D116" s="15" t="inlineStr">
         <is>
           <t>https://arbitrationbarofindia.com/upcoming_events.php</t>
         </is>
@@ -2882,7 +2894,7 @@
           <t>Tax / Tax Practice</t>
         </is>
       </c>
-      <c r="D117" s="7" t="inlineStr">
+      <c r="D117" s="15" t="inlineStr">
         <is>
           <t>https://www.ictpi.in/event</t>
         </is>
@@ -2902,7 +2914,7 @@
           <t>Tax / Tax Practice</t>
         </is>
       </c>
-      <c r="D118" s="7" t="inlineStr">
+      <c r="D118" s="15" t="inlineStr">
         <is>
           <t>https://www.ictpi.in/</t>
         </is>
@@ -2922,7 +2934,7 @@
           <t>Professional Finance / Financial Planning</t>
         </is>
       </c>
-      <c r="D119" s="7" t="inlineStr">
+      <c r="D119" s="15" t="inlineStr">
         <is>
           <t>https://www.ifpaindia.in/events</t>
         </is>
@@ -2942,7 +2954,7 @@
           <t>Corporate Finance / CFO / Financial Management</t>
         </is>
       </c>
-      <c r="D120" s="5" t="inlineStr">
+      <c r="D120" s="13" t="inlineStr">
         <is>
           <t>https://www.cfo-india.in/</t>
         </is>
@@ -2962,7 +2974,7 @@
           <t>Internal Audit / Finance / Governance</t>
         </is>
       </c>
-      <c r="D121" s="5" t="inlineStr">
+      <c r="D121" s="13" t="inlineStr">
         <is>
           <t>https://www.iiaindia.co.in/</t>
         </is>
@@ -2982,7 +2994,7 @@
           <t>Professional Finance / Investment</t>
         </is>
       </c>
-      <c r="D122" s="5" t="inlineStr">
+      <c r="D122" s="13" t="inlineStr">
         <is>
           <t>https://cfasocietyindia.org/upcomingevents/</t>
         </is>
@@ -3002,7 +3014,7 @@
           <t>Personal Finance / Financial Planning</t>
         </is>
       </c>
-      <c r="D123" s="5" t="inlineStr">
+      <c r="D123" s="13" t="inlineStr">
         <is>
           <t>https://www.networkfp.com/</t>
         </is>
@@ -3022,7 +3034,7 @@
           <t>Corporate Treasury / Finance</t>
         </is>
       </c>
-      <c r="D124" s="7" t="inlineStr">
+      <c r="D124" s="15" t="inlineStr">
         <is>
           <t>https://ict-india.org/#events</t>
         </is>
@@ -3042,7 +3054,7 @@
           <t>Treasury / Corporate Finance</t>
         </is>
       </c>
-      <c r="D125" s="7" t="inlineStr">
+      <c r="D125" s="15" t="inlineStr">
         <is>
           <t>https://www.indiatreasurysummit.com/</t>
         </is>
@@ -3082,7 +3094,7 @@
           <t>Legal / Corporate Law</t>
         </is>
       </c>
-      <c r="D127" s="5" t="inlineStr">
+      <c r="D127" s="13" t="inlineStr">
         <is>
           <t>https://www.silf.org.in/</t>
         </is>
@@ -3102,7 +3114,7 @@
           <t>Legal / Corporate Law / Dispute Resolution</t>
         </is>
       </c>
-      <c r="D128" s="5" t="inlineStr">
+      <c r="D128" s="13" t="inlineStr">
         <is>
           <t>https://www.indianbarassociation.org/</t>
         </is>
@@ -3122,7 +3134,7 @@
           <t>Arbitration / Commercial Law</t>
         </is>
       </c>
-      <c r="D129" s="5" t="inlineStr">
+      <c r="D129" s="13" t="inlineStr">
         <is>
           <t>https://www.icdr.org/</t>
         </is>
@@ -3142,7 +3154,7 @@
           <t>Arbitration / Mediation / Dispute Resolution</t>
         </is>
       </c>
-      <c r="D130" s="5" t="inlineStr">
+      <c r="D130" s="13" t="inlineStr">
         <is>
           <t>https://indiaadrweek.com/</t>
         </is>
@@ -3162,7 +3174,7 @@
           <t>Commercial Litigation / Arbitration</t>
         </is>
       </c>
-      <c r="D131" s="5" t="inlineStr">
+      <c r="D131" s="13" t="inlineStr">
         <is>
           <t>https://www.combar.com/</t>
         </is>
@@ -3182,7 +3194,7 @@
           <t>Arbitration / Commercial Law</t>
         </is>
       </c>
-      <c r="D132" s="5" t="inlineStr">
+      <c r="D132" s="13" t="inlineStr">
         <is>
           <t>https://www.lcia.org/</t>
         </is>
@@ -3202,7 +3214,7 @@
           <t>Legal / Tax / Arbitration</t>
         </is>
       </c>
-      <c r="D133" s="5" t="inlineStr">
+      <c r="D133" s="13" t="inlineStr">
         <is>
           <t>https://www.ibanet.org/</t>
         </is>
@@ -3222,7 +3234,7 @@
           <t>International Tax / Fiscal Law</t>
         </is>
       </c>
-      <c r="D134" s="7" t="inlineStr">
+      <c r="D134" s="15" t="inlineStr">
         <is>
           <t>https://ifaindia.in/events/</t>
         </is>
@@ -3242,7 +3254,7 @@
           <t>Tax / Public Finance / Fiscal Policy</t>
         </is>
       </c>
-      <c r="D135" s="5" t="inlineStr">
+      <c r="D135" s="13" t="inlineStr">
         <is>
           <t>https://www.nipfp.org.in/event-index-page/</t>
         </is>
@@ -3262,7 +3274,7 @@
           <t>Audit / Finance / Governance / Risk</t>
         </is>
       </c>
-      <c r="D136" s="5" t="inlineStr">
+      <c r="D136" s="13" t="inlineStr">
         <is>
           <t>https://www.iiaindia.co.in/</t>
         </is>
@@ -3282,7 +3294,7 @@
           <t>Audit / Compliance / Risk / Governance</t>
         </is>
       </c>
-      <c r="D137" s="5" t="inlineStr">
+      <c r="D137" s="13" t="inlineStr">
         <is>
           <t>https://www.isaca.org/</t>
         </is>
@@ -3302,7 +3314,7 @@
           <t>Corporate Governance / Corporate Law</t>
         </is>
       </c>
-      <c r="D138" s="5" t="inlineStr">
+      <c r="D138" s="13" t="inlineStr">
         <is>
           <t>https://www.iodglobal.com/</t>
         </is>
@@ -3322,7 +3334,7 @@
           <t>International Law / Trade Law</t>
         </is>
       </c>
-      <c r="D139" s="5" t="inlineStr">
+      <c r="D139" s="13" t="inlineStr">
         <is>
           <t>https://isilindia.org/</t>
         </is>
@@ -3342,7 +3354,7 @@
           <t>Arbitration / Commercial Disputes</t>
         </is>
       </c>
-      <c r="D140" s="5" t="inlineStr">
+      <c r="D140" s="13" t="inlineStr">
         <is>
           <t>https://www.npac.in/</t>
         </is>
@@ -3362,7 +3374,7 @@
           <t>Corporate / Commercial Law</t>
         </is>
       </c>
-      <c r="D141" s="5" t="inlineStr">
+      <c r="D141" s="13" t="inlineStr">
         <is>
           <t>https://www.silf.org.in/</t>
         </is>
@@ -3382,7 +3394,7 @@
           <t>International Trade / Investment Law</t>
         </is>
       </c>
-      <c r="D142" s="5" t="inlineStr">
+      <c r="D142" s="13" t="inlineStr">
         <is>
           <t>https://ctil.org.in/</t>
         </is>
@@ -3402,7 +3414,7 @@
           <t>Tax / Regulatory / Finance</t>
         </is>
       </c>
-      <c r="D143" s="5" t="inlineStr">
+      <c r="D143" s="13" t="inlineStr">
         <is>
           <t>https://nasscom.in/</t>
         </is>
@@ -3422,7 +3434,7 @@
           <t>Tax / Public Finance / Economic Policy</t>
         </is>
       </c>
-      <c r="D144" s="5" t="inlineStr">
+      <c r="D144" s="13" t="inlineStr">
         <is>
           <t>https://icrier.org/events/</t>
         </is>
@@ -3442,7 +3454,7 @@
           <t>Direct Tax / GST / Tax Litigation</t>
         </is>
       </c>
-      <c r="D145" s="5" t="inlineStr">
+      <c r="D145" s="13" t="inlineStr">
         <is>
           <t>https://dtpa.org/</t>
         </is>
@@ -3462,7 +3474,7 @@
           <t>Direct Tax / GST / Tax Law</t>
         </is>
       </c>
-      <c r="D146" s="7" t="inlineStr">
+      <c r="D146" s="15" t="inlineStr">
         <is>
           <t>https://agftc.in/index.php</t>
         </is>
@@ -3482,7 +3494,7 @@
           <t>Corporate Law / Insolvency / Governance / Regulation</t>
         </is>
       </c>
-      <c r="D147" s="5" t="inlineStr">
+      <c r="D147" s="13" t="inlineStr">
         <is>
           <t>https://iica.nic.in/</t>
         </is>
@@ -3502,7 +3514,7 @@
           <t>Arbitration / Commercial Law / ADR</t>
         </is>
       </c>
-      <c r="D148" s="7" t="inlineStr">
+      <c r="D148" s="15" t="inlineStr">
         <is>
           <t>https://indiaiac.org/arbitration/event</t>
         </is>
@@ -3522,7 +3534,7 @@
           <t>Arbitration / Commercial Disputes</t>
         </is>
       </c>
-      <c r="D149" s="5" t="inlineStr">
+      <c r="D149" s="13" t="inlineStr">
         <is>
           <t>https://www.npac.in/</t>
         </is>
@@ -3542,7 +3554,7 @@
           <t>International Trade / Investment Law</t>
         </is>
       </c>
-      <c r="D150" s="5" t="inlineStr">
+      <c r="D150" s="13" t="inlineStr">
         <is>
           <t>https://ctil.org.in/</t>
         </is>
@@ -3562,7 +3574,7 @@
           <t>Corporate / Commercial Law</t>
         </is>
       </c>
-      <c r="D151" s="5" t="inlineStr">
+      <c r="D151" s="13" t="inlineStr">
         <is>
           <t>https://www.silf.org.in/</t>
         </is>
@@ -3582,7 +3594,7 @@
           <t>Corporate Governance / Compliance</t>
         </is>
       </c>
-      <c r="D152" s="5" t="inlineStr">
+      <c r="D152" s="13" t="inlineStr">
         <is>
           <t>https://nfcgindia.org/</t>
         </is>
@@ -3602,7 +3614,7 @@
           <t>Corporate Law / Governance / Compliance</t>
         </is>
       </c>
-      <c r="D153" s="5" t="inlineStr">
+      <c r="D153" s="13" t="inlineStr">
         <is>
           <t>https://www.icsi.edu/</t>
         </is>
@@ -3622,7 +3634,7 @@
           <t>Insolvency / Restructuring / Corporate Law</t>
         </is>
       </c>
-      <c r="D154" s="5" t="inlineStr">
+      <c r="D154" s="13" t="inlineStr">
         <is>
           <t>https://www.iiipicai.in/</t>
         </is>
@@ -3642,7 +3654,7 @@
           <t>Tax / Accounting / Finance</t>
         </is>
       </c>
-      <c r="D155" s="5" t="inlineStr">
+      <c r="D155" s="13" t="inlineStr">
         <is>
           <t>https://www.icai.org/</t>
         </is>
@@ -3662,7 +3674,7 @@
           <t>Cost Accounting / Tax / Finance</t>
         </is>
       </c>
-      <c r="D156" s="5" t="inlineStr">
+      <c r="D156" s="13" t="inlineStr">
         <is>
           <t>https://icmai.in/</t>
         </is>
@@ -3682,7 +3694,7 @@
           <t>Corporate Law / Compliance / Governance</t>
         </is>
       </c>
-      <c r="D157" s="5" t="inlineStr">
+      <c r="D157" s="13" t="inlineStr">
         <is>
           <t>https://www.icsi.edu/</t>
         </is>
@@ -3702,7 +3714,7 @@
           <t>Corporate Governance / Board Practices</t>
         </is>
       </c>
-      <c r="D158" s="5" t="inlineStr">
+      <c r="D158" s="13" t="inlineStr">
         <is>
           <t>https://iica.nic.in/</t>
         </is>
@@ -3722,7 +3734,7 @@
           <t>Public Finance / Tax Administration</t>
         </is>
       </c>
-      <c r="D159" s="5" t="inlineStr">
+      <c r="D159" s="13" t="inlineStr">
         <is>
           <t>https://iipa.org.in/</t>
         </is>
@@ -3742,7 +3754,7 @@
           <t>Labour Economics / Public Finance</t>
         </is>
       </c>
-      <c r="D160" s="7" t="inlineStr">
+      <c r="D160" s="15" t="inlineStr">
         <is>
           <t>https://www.isleijle.org/conferences/</t>
         </is>
@@ -3762,7 +3774,7 @@
           <t>Economics / Public Finance</t>
         </is>
       </c>
-      <c r="D161" s="7" t="inlineStr">
+      <c r="D161" s="15" t="inlineStr">
         <is>
           <t>https://iarniw.in/upcoming/</t>
         </is>
@@ -3782,7 +3794,7 @@
           <t>Tax Policy / Public Finance / Economic Policy</t>
         </is>
       </c>
-      <c r="D162" s="5" t="inlineStr">
+      <c r="D162" s="13" t="inlineStr">
         <is>
           <t>https://icrier.org/events/</t>
         </is>
@@ -3802,7 +3814,7 @@
           <t>International Tax / Tax Law</t>
         </is>
       </c>
-      <c r="D163" s="7" t="inlineStr">
+      <c r="D163" s="15" t="inlineStr">
         <is>
           <t>https://www.ffitindia.org/</t>
         </is>
@@ -3822,7 +3834,7 @@
           <t>Direct Tax / Tax Administration</t>
         </is>
       </c>
-      <c r="D164" s="5" t="inlineStr">
+      <c r="D164" s="13" t="inlineStr">
         <is>
           <t>https://www.nadt.gov.in/</t>
         </is>
@@ -3842,7 +3854,7 @@
           <t>Commercial Law / Arbitration / Trade</t>
         </is>
       </c>
-      <c r="D165" s="5" t="inlineStr">
+      <c r="D165" s="13" t="inlineStr">
         <is>
           <t>https://iccindiaonline.org/</t>
         </is>
@@ -3862,7 +3874,7 @@
           <t>Legal / Tax / Arbitration</t>
         </is>
       </c>
-      <c r="D166" s="5" t="inlineStr">
+      <c r="D166" s="13" t="inlineStr">
         <is>
           <t>https://www.ibanet.org/</t>
         </is>
@@ -3882,7 +3894,7 @@
           <t>Arbitration / Commercial Law</t>
         </is>
       </c>
-      <c r="D167" s="5" t="inlineStr">
+      <c r="D167" s="13" t="inlineStr">
         <is>
           <t>https://iccindiaonline.org/</t>
         </is>
@@ -3902,7 +3914,7 @@
           <t>Arbitration / Dispute Resolution</t>
         </is>
       </c>
-      <c r="D168" s="5" t="inlineStr">
+      <c r="D168" s="13" t="inlineStr">
         <is>
           <t>https://www.icdr.org/</t>
         </is>
@@ -3922,7 +3934,7 @@
           <t>Arbitration / Commercial Law</t>
         </is>
       </c>
-      <c r="D169" s="5" t="inlineStr">
+      <c r="D169" s="13" t="inlineStr">
         <is>
           <t>https://www.lcia.org/</t>
         </is>
@@ -3942,7 +3954,7 @@
           <t>Insolvency / Restructuring / Finance</t>
         </is>
       </c>
-      <c r="D170" s="5" t="inlineStr">
+      <c r="D170" s="13" t="inlineStr">
         <is>
           <t>https://iiiglobal.org/</t>
         </is>
@@ -3962,7 +3974,7 @@
           <t>Insolvency / Regulation / Finance</t>
         </is>
       </c>
-      <c r="D171" s="5" t="inlineStr">
+      <c r="D171" s="13" t="inlineStr">
         <is>
           <t>https://www.insolvencyreg.org/</t>
         </is>
@@ -3982,7 +3994,7 @@
           <t>Corporate Finance / Treasury / Financial Management</t>
         </is>
       </c>
-      <c r="D172" s="5" t="inlineStr">
+      <c r="D172" s="13" t="inlineStr">
         <is>
           <t>https://iafei.org/</t>
         </is>
@@ -4002,7 +4014,7 @@
           <t>Tax / Accounting / Finance</t>
         </is>
       </c>
-      <c r="D173" s="7" t="inlineStr">
+      <c r="D173" s="15" t="inlineStr">
         <is>
           <t>https://www.aicas.in/event.html</t>
         </is>
@@ -4022,7 +4034,7 @@
           <t>Finance / Financial Management</t>
         </is>
       </c>
-      <c r="D174" s="7" t="inlineStr">
+      <c r="D174" s="15" t="inlineStr">
         <is>
           <t>https://www.afai.in/event-conferences/#eventcalender</t>
         </is>
@@ -4042,7 +4054,7 @@
           <t>Corporate Finance / Treasury</t>
         </is>
       </c>
-      <c r="D175" s="7" t="inlineStr">
+      <c r="D175" s="15" t="inlineStr">
         <is>
           <t>https://www.treasurers.org/events</t>
         </is>
@@ -4062,7 +4074,7 @@
           <t>Accounting / Finance / Cost Management</t>
         </is>
       </c>
-      <c r="D176" s="5" t="inlineStr">
+      <c r="D176" s="13" t="inlineStr">
         <is>
           <t>https://icmai.in/</t>
         </is>
@@ -4082,7 +4094,7 @@
           <t>Finance / Financial Management</t>
         </is>
       </c>
-      <c r="D177" s="5" t="inlineStr">
+      <c r="D177" s="13" t="inlineStr">
         <is>
           <t>https://www.iifm.co.in/</t>
         </is>
@@ -4097,7 +4109,7 @@
           <t>Bombay Chartered Accountants Society</t>
         </is>
       </c>
-      <c r="D178" s="10" t="inlineStr">
+      <c r="D178" s="15" t="inlineStr">
         <is>
           <t>https://bcasonline.org/upcoming-live-events/</t>
         </is>
@@ -4117,7 +4129,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
+      <c r="D179" s="16" t="inlineStr">
         <is>
           <t>https://tpaindore.com/</t>
         </is>
@@ -4137,7 +4149,7 @@
           <t>Tax / Legal</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="D180" s="16" t="inlineStr">
         <is>
           <t>https://incometaxbar.org/</t>
         </is>
@@ -4157,7 +4169,7 @@
           <t>Tax / Legal</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
+      <c r="D181" s="16" t="inlineStr">
         <is>
           <t>https://itbaraipur.org/</t>
         </is>
@@ -4177,7 +4189,7 @@
           <t>Tax / Legal</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="D182" s="16" t="inlineStr">
         <is>
           <t>https://www.taxbarghy.org/</t>
         </is>
@@ -4197,7 +4209,7 @@
           <t>Tax / Legal</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
+      <c r="D183" s="16" t="inlineStr">
         <is>
           <t>https://taab.org.in/</t>
         </is>
@@ -4217,7 +4229,7 @@
           <t>Tax / Legal</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
+      <c r="D184" s="16" t="inlineStr">
         <is>
           <t>https://atba.in/</t>
         </is>
@@ -4237,7 +4249,7 @@
           <t>Accounting / Tax</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
+      <c r="D185" s="16" t="inlineStr">
         <is>
           <t>https://kscaa.com/kscaa-events/</t>
         </is>
@@ -4257,7 +4269,7 @@
           <t>Accounting / Tax</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
+      <c r="D186" s="16" t="inlineStr">
         <is>
           <t>https://www.caasonline.org/events</t>
         </is>
@@ -4277,7 +4289,7 @@
           <t>Accounting / Tax</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
+      <c r="D187" s="16" t="inlineStr">
         <is>
           <t>https://caa-ahm.org/Event.php</t>
         </is>
@@ -4297,7 +4309,7 @@
           <t>Accounting / Tax</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr">
+      <c r="D188" s="16" t="inlineStr">
         <is>
           <t>https://icaiahmedabad.com/past-upcoming-events.php</t>
         </is>
@@ -4317,7 +4329,7 @@
           <t>Legal (aggregator)</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr">
+      <c r="D189" s="16" t="inlineStr">
         <is>
           <t>https://www.livelaw.in/events</t>
         </is>
@@ -4337,7 +4349,7 @@
           <t>Legal (aggregator)</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
+      <c r="D190" s="16" t="inlineStr">
         <is>
           <t>https://www.conferencealerts.in/india/law</t>
         </is>
@@ -4357,7 +4369,7 @@
           <t>Finance (aggregator)</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
+      <c r="D191" s="16" t="inlineStr">
         <is>
           <t>https://conferencealerts.co.in/banking-and-finance</t>
         </is>
@@ -4377,7 +4389,7 @@
           <t>Finance (aggregator)</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr">
+      <c r="D192" s="16" t="inlineStr">
         <is>
           <t>https://10times.com/india/finance</t>
         </is>
@@ -4397,7 +4409,7 @@
           <t>Legal / Corporate</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
+      <c r="D193" s="16" t="inlineStr">
         <is>
           <t>https://www.icsi.edu/niro/home/</t>
         </is>
@@ -4417,7 +4429,7 @@
           <t>Legal / Corporate</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
+      <c r="D194" s="16" t="inlineStr">
         <is>
           <t>https://www.icsi.edu/wiro/home/</t>
         </is>
@@ -4437,7 +4449,7 @@
           <t>Accounting / Tax</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
+      <c r="D195" s="16" t="inlineStr">
         <is>
           <t>https://chandigarhicai.org/</t>
         </is>
@@ -4457,7 +4469,7 @@
           <t>Tax / Legal</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
+      <c r="D196" s="16" t="inlineStr">
         <is>
           <t>https://delhitaxbar.com/</t>
         </is>
@@ -4477,7 +4489,7 @@
           <t>Tax / Legal</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
+      <c r="D197" s="16" t="inlineStr">
         <is>
           <t>https://salestaxbar.com/</t>
         </is>
@@ -4497,7 +4509,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
+      <c r="D198" s="16" t="inlineStr">
         <is>
           <t>https://rtcaraj.com/</t>
         </is>
@@ -4517,7 +4529,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
+      <c r="D199" s="16" t="inlineStr">
         <is>
           <t>https://taxpractitioners.in/</t>
         </is>
@@ -4537,7 +4549,7 @@
           <t>Insurance / Finance</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
+      <c r="D200" s="16" t="inlineStr">
         <is>
           <t>https://ibai.glueup.com/</t>
         </is>
@@ -4557,7 +4569,7 @@
           <t>Finance / Fintech</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="D201" s="16" t="inlineStr">
         <is>
           <t>https://bharatfintechsummit.com/</t>
         </is>
@@ -4577,7 +4589,7 @@
           <t>Accounting / Tax</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
+      <c r="D202" s="16" t="inlineStr">
         <is>
           <t>https://hydicai.org/event/list</t>
         </is>
@@ -4597,7 +4609,7 @@
           <t>Accounting / Tax</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
+      <c r="D203" s="16" t="inlineStr">
         <is>
           <t>https://www.puneicai.org/</t>
         </is>
@@ -4617,7 +4629,7 @@
           <t>Legal / Corporate</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="D204" s="16" t="inlineStr">
         <is>
           <t>https://www.icsi.edu/eiro/home/</t>
         </is>
@@ -4637,7 +4649,7 @@
           <t>Legal / Corporate</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
+      <c r="D205" s="16" t="inlineStr">
         <is>
           <t>https://www.icsi.edu/siro/home/</t>
         </is>
@@ -4657,7 +4669,7 @@
           <t>Accounting (aggregator)</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
+      <c r="D206" s="16" t="inlineStr">
         <is>
           <t>https://conferencealerts.co.in/india/accounting</t>
         </is>
@@ -4677,7 +4689,7 @@
           <t>Legal (aggregator)</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
+      <c r="D207" s="16" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/d/india/legal-conferences/</t>
         </is>
@@ -4697,7 +4709,7 @@
           <t>Finance (aggregator)</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
+      <c r="D208" s="16" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/d/india--mumbai/finance-conference/</t>
         </is>
@@ -4717,7 +4729,7 @@
           <t>Tax (aggregator/publisher)</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="D209" s="16" t="inlineStr">
         <is>
           <t>https://shop.taxguru.in/taxguru-free-webinar-registration/</t>
         </is>
@@ -4737,7 +4749,7 @@
           <t>Tax (publisher)</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="D210" s="16" t="inlineStr">
         <is>
           <t>https://www.taxmann.com/webinars/</t>
         </is>
@@ -4757,7 +4769,7 @@
           <t>Tax / Legal (publisher)</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
+      <c r="D211" s="16" t="inlineStr">
         <is>
           <t>https://www.taxmann.com/learning/upcoming-events</t>
         </is>
@@ -4777,7 +4789,7 @@
           <t>Tax / GST (publisher)</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
+      <c r="D212" s="16" t="inlineStr">
         <is>
           <t>https://cleartax.in/webinars/</t>
         </is>
@@ -4797,7 +4809,7 @@
           <t>Finance / Regulator</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
+      <c r="D213" s="16" t="inlineStr">
         <is>
           <t>https://investor.sebi.gov.in/program.html?type=2</t>
         </is>
@@ -4817,7 +4829,7 @@
           <t>Finance / Regulator</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
+      <c r="D214" s="16" t="inlineStr">
         <is>
           <t>https://www.nism.ac.in/investor-education-webinars/</t>
         </is>
@@ -4837,7 +4849,7 @@
           <t>Accounting / Tax</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr">
+      <c r="D215" s="16" t="inlineStr">
         <is>
           <t>https://acachennai.in/upcoming-events.php</t>
         </is>
@@ -4857,7 +4869,7 @@
           <t>Legal (aggregator)</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr">
+      <c r="D216" s="16" t="inlineStr">
         <is>
           <t>https://www.scconline.com/blog/post/category/news/events-and-webinars/</t>
         </is>
@@ -4877,7 +4889,7 @@
           <t>Legal (aggregator)</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
+      <c r="D217" s="16" t="inlineStr">
         <is>
           <t>https://www.legallyindia.com/home/events</t>
         </is>
@@ -4897,7 +4909,7 @@
           <t>Legal (aggregator)</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
+      <c r="D218" s="16" t="inlineStr">
         <is>
           <t>https://legalbots.in/events</t>
         </is>
@@ -4917,7 +4929,7 @@
           <t>Tax / GST (aggregator)</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="D219" s="16" t="inlineStr">
         <is>
           <t>https://www.casansaar.com/events/gst.html</t>
         </is>
@@ -4937,7 +4949,7 @@
           <t>GST / Regulator</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="D220" s="16" t="inlineStr">
         <is>
           <t>https://www.gstn.org.in/events-training</t>
         </is>
@@ -4957,7 +4969,7 @@
           <t>Tax / GST (aggregator)</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="D221" s="16" t="inlineStr">
         <is>
           <t>https://www.townscript.com/in/india/gst</t>
         </is>
@@ -5080,7 +5092,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId113"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" location="events" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId119"/>
@@ -5129,11 +5141,54 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" location="eventcalender" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId165"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId167"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId212"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
@@ -5191,7 +5246,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>https://www.irs.gov/tax-professionals/irs-nationwide-tax-forum-information</t>
         </is>
@@ -5211,7 +5266,7 @@
           <t>Tax / Finance</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>https://www.aicpa-cima.com/cpe-learning/conference</t>
         </is>
@@ -5231,7 +5286,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>https://taxadmin.org/events/</t>
         </is>
@@ -5251,7 +5306,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>https://www.tei.org/events-education/events</t>
         </is>
@@ -5271,7 +5326,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>https://www.ipt.org/site/content/programs-and-schools/Programs-Calendar.aspx</t>
         </is>
@@ -5291,7 +5346,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>https://www.cost.org/events/</t>
         </is>
@@ -5311,7 +5366,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>https://www.mtc.gov/events-training/</t>
         </is>
@@ -5331,7 +5386,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>https://taxfoundation.org/events/</t>
         </is>
@@ -5351,7 +5406,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>https://ntanet.org/upcoming-events/</t>
         </is>
@@ -5371,7 +5426,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>https://www.nstp.org/events</t>
         </is>
@@ -5391,7 +5446,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>https://www.natptax.com/events-education/in-person/</t>
         </is>
@@ -5411,7 +5466,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>https://www.naea.org/calendar/</t>
         </is>
@@ -5431,7 +5486,7 @@
           <t>Tax / Finance</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>https://payroll.org/education-certification/conferences/overview</t>
         </is>
@@ -5451,7 +5506,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>https://www.appraisers.org/education/conferences-events/upcoming-conferences-events</t>
         </is>
@@ -5471,7 +5526,7 @@
           <t>Finance / Accounting</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>https://aaahq.org/Meetings/Upcoming-Meetings</t>
         </is>
@@ -5491,7 +5546,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>https://afajof.org/annual-meeting/</t>
         </is>
@@ -5511,7 +5566,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>https://www.fma.org/</t>
         </is>
@@ -5531,7 +5586,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>https://www.gfoa.org/conference</t>
         </is>
@@ -5551,7 +5606,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>https://www.agacgfm.org/events-training/</t>
         </is>
@@ -5571,7 +5626,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t>https://nast.org/conference-overview/</t>
         </is>
@@ -5591,7 +5646,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>https://www.nasact.org/eventsearch.asp</t>
         </is>
@@ -5611,7 +5666,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>https://www.cfainstitute.org/insights/events</t>
         </is>
@@ -5631,7 +5686,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="15" t="inlineStr">
         <is>
           <t>https://www.ici.org/events/events-calendar</t>
         </is>
@@ -5651,7 +5706,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="15" t="inlineStr">
         <is>
           <t>https://www.investmentadviser.org/event-calendar/</t>
         </is>
@@ -5671,7 +5726,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>https://www.managedfunds.org/events/</t>
         </is>
@@ -5691,7 +5746,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="15" t="inlineStr">
         <is>
           <t>https://www.aima.org/events.html</t>
         </is>
@@ -5711,7 +5766,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>https://www.imanet.org/continuing-education/events</t>
         </is>
@@ -5731,7 +5786,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D29" s="15" t="inlineStr">
         <is>
           <t>https://www.napfa.org/community/future-conferences</t>
         </is>
@@ -5751,7 +5806,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="D30" s="15" t="inlineStr">
         <is>
           <t>https://structuredfinance.org/industry-events/</t>
         </is>
@@ -5771,7 +5826,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D31" s="15" t="inlineStr">
         <is>
           <t>https://www.asppa-net.org/events/event-calendar/</t>
         </is>
@@ -5791,7 +5846,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D32" s="15" t="inlineStr">
         <is>
           <t>https://nysba.org/events-calendar/</t>
         </is>
@@ -5811,7 +5866,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D33" s="15" t="inlineStr">
         <is>
           <t>https://www.ncbar.org/events/</t>
         </is>
@@ -5831,7 +5886,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D34" s="15" t="inlineStr">
         <is>
           <t>https://connect.ohiobar.org/events/calendar</t>
         </is>
@@ -5851,7 +5906,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D35" s="15" t="inlineStr">
         <is>
           <t>https://www.isba.org/cle-events</t>
         </is>
@@ -5871,7 +5926,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D36" s="15" t="inlineStr">
         <is>
           <t>https://www.lsba.org/calendar/</t>
         </is>
@@ -5891,7 +5946,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D37" s="15" t="inlineStr">
         <is>
           <t>https://njsba.com/njicle/cle-programs/</t>
         </is>
@@ -5911,7 +5966,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D38" s="10" t="inlineStr">
+      <c r="D38" s="15" t="inlineStr">
         <is>
           <t>https://www.michbar.org/news/calendar</t>
         </is>
@@ -5931,7 +5986,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D39" s="15" t="inlineStr">
         <is>
           <t>https://www.sband.org/page/cle</t>
         </is>
@@ -5951,7 +6006,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D40" s="10" t="inlineStr">
+      <c r="D40" s="15" t="inlineStr">
         <is>
           <t>https://icle.gabar.org/calendar</t>
         </is>
@@ -5971,7 +6026,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D41" s="15" t="inlineStr">
         <is>
           <t>https://www.inbar.org/events/event_list.asp</t>
         </is>
@@ -5991,7 +6046,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D42" s="10" t="inlineStr">
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>https://community.nebar.com/events/calendar</t>
         </is>
@@ -6011,7 +6066,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
+      <c r="D43" s="15" t="inlineStr">
         <is>
           <t>https://www.jaxbar.org/events/event_list.asp</t>
         </is>
@@ -6031,7 +6086,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D44" s="10" t="inlineStr">
+      <c r="D44" s="15" t="inlineStr">
         <is>
           <t>https://www.browardbar.org/calendar/</t>
         </is>
@@ -6051,7 +6106,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D45" s="10" t="inlineStr">
+      <c r="D45" s="15" t="inlineStr">
         <is>
           <t>https://www.stpetebar.com/events/event_list.asp</t>
         </is>
@@ -6071,7 +6126,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D46" s="10" t="inlineStr">
+      <c r="D46" s="15" t="inlineStr">
         <is>
           <t>https://bcba-pa.org/cle-events/</t>
         </is>
@@ -6091,7 +6146,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D47" s="10" t="inlineStr">
+      <c r="D47" s="15" t="inlineStr">
         <is>
           <t>https://flagovbar.org/events</t>
         </is>
@@ -6111,7 +6166,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D48" s="10" t="inlineStr">
+      <c r="D48" s="15" t="inlineStr">
         <is>
           <t>https://www.justice.org/education/conventions</t>
         </is>
@@ -6131,7 +6186,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D49" s="10" t="inlineStr">
+      <c r="D49" s="15" t="inlineStr">
         <is>
           <t>https://www.dri.org/education-cle/seminars</t>
         </is>
@@ -6151,7 +6206,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D50" s="10" t="inlineStr">
+      <c r="D50" s="15" t="inlineStr">
         <is>
           <t>https://www.acc.com/education-events</t>
         </is>
@@ -6171,7 +6226,7 @@
           <t>Legal / Finance</t>
         </is>
       </c>
-      <c r="D51" s="10" t="inlineStr">
+      <c r="D51" s="15" t="inlineStr">
         <is>
           <t>https://www.abi.org/upcoming-events</t>
         </is>
@@ -6191,7 +6246,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D52" s="10" t="inlineStr">
+      <c r="D52" s="15" t="inlineStr">
         <is>
           <t>https://ntanet.org/upcoming-events/</t>
         </is>
@@ -6211,7 +6266,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D53" s="10" t="inlineStr">
+      <c r="D53" s="15" t="inlineStr">
         <is>
           <t>https://www.ifausa.org/news/default.asp</t>
         </is>
@@ -6231,7 +6286,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D54" s="10" t="inlineStr">
+      <c r="D54" s="15" t="inlineStr">
         <is>
           <t>https://americantaxpolicyinstitute.org/</t>
         </is>
@@ -6251,7 +6306,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D55" s="10" t="inlineStr">
+      <c r="D55" s="15" t="inlineStr">
         <is>
           <t>https://www.ipt.org/site/content/programs-and-schools/Programs-Calendar.aspx</t>
         </is>
@@ -6271,7 +6326,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D56" s="10" t="inlineStr">
+      <c r="D56" s="15" t="inlineStr">
         <is>
           <t>https://www.tei.org/events-education/events</t>
         </is>
@@ -6291,7 +6346,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D57" s="10" t="inlineStr">
+      <c r="D57" s="15" t="inlineStr">
         <is>
           <t>https://www.cost.org/events/</t>
         </is>
@@ -6311,7 +6366,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D58" s="10" t="inlineStr">
+      <c r="D58" s="15" t="inlineStr">
         <is>
           <t>https://www.mtc.gov/events-training/</t>
         </is>
@@ -6331,7 +6386,7 @@
           <t>Tax / Finance</t>
         </is>
       </c>
-      <c r="D59" s="10" t="inlineStr">
+      <c r="D59" s="15" t="inlineStr">
         <is>
           <t>https://connect.nsacct.org/events/calendar</t>
         </is>
@@ -6351,7 +6406,7 @@
           <t>Tax / Finance</t>
         </is>
       </c>
-      <c r="D60" s="10" t="inlineStr">
+      <c r="D60" s="15" t="inlineStr">
         <is>
           <t>https://payroll.org/education-certification/conferences/overview</t>
         </is>
@@ -6371,7 +6426,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D61" s="10" t="inlineStr">
+      <c r="D61" s="15" t="inlineStr">
         <is>
           <t>https://www.appraisers.org/education/conferences-events/upcoming-conferences-events</t>
         </is>
@@ -6391,7 +6446,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D62" s="10" t="inlineStr">
+      <c r="D62" s="15" t="inlineStr">
         <is>
           <t>https://aaahq.org/Meetings/Upcoming-Meetings</t>
         </is>
@@ -6411,7 +6466,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D63" s="10" t="inlineStr">
+      <c r="D63" s="15" t="inlineStr">
         <is>
           <t>https://afajof.org/conference-calendar/</t>
         </is>
@@ -6431,7 +6486,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D64" s="10" t="inlineStr">
+      <c r="D64" s="15" t="inlineStr">
         <is>
           <t>https://www.elfaonline.org/events</t>
         </is>
@@ -6451,7 +6506,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D65" s="10" t="inlineStr">
+      <c r="D65" s="15" t="inlineStr">
         <is>
           <t>https://www.sifma.org/events/</t>
         </is>
@@ -6471,7 +6526,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D66" s="10" t="inlineStr">
+      <c r="D66" s="15" t="inlineStr">
         <is>
           <t>https://www.fia.org/fia/events</t>
         </is>
@@ -6491,7 +6546,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D67" s="10" t="inlineStr">
+      <c r="D67" s="15" t="inlineStr">
         <is>
           <t>https://my.financialexecutives.org/Events/Calendar-of-Events</t>
         </is>
@@ -6511,7 +6566,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D68" s="10" t="inlineStr">
+      <c r="D68" s="15" t="inlineStr">
         <is>
           <t>https://nvca.org/events/list/</t>
         </is>
@@ -6531,7 +6586,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D69" s="10" t="inlineStr">
+      <c r="D69" s="15" t="inlineStr">
         <is>
           <t>https://www.investmentcouncil.org/the-council/events</t>
         </is>
@@ -6551,7 +6606,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D70" s="10" t="inlineStr">
+      <c r="D70" s="15" t="inlineStr">
         <is>
           <t>https://electran.org/events-upcoming/</t>
         </is>
@@ -6571,7 +6626,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D71" s="10" t="inlineStr">
+      <c r="D71" s="15" t="inlineStr">
         <is>
           <t>https://naicpe.com/events/</t>
         </is>
@@ -6591,7 +6646,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D72" s="10" t="inlineStr">
+      <c r="D72" s="15" t="inlineStr">
         <is>
           <t>https://www.nacdonline.org/nacd-events/</t>
         </is>
@@ -6611,7 +6666,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D73" s="10" t="inlineStr">
+      <c r="D73" s="15" t="inlineStr">
         <is>
           <t>https://www.nafassociation.com/events</t>
         </is>
@@ -6631,7 +6686,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D74" s="10" t="inlineStr">
+      <c r="D74" s="15" t="inlineStr">
         <is>
           <t>https://www.nafcu.org/calendar</t>
         </is>
@@ -6651,7 +6706,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D75" s="10" t="inlineStr">
+      <c r="D75" s="15" t="inlineStr">
         <is>
           <t>https://www.reit.com/events</t>
         </is>
@@ -6671,7 +6726,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D76" s="10" t="inlineStr">
+      <c r="D76" s="15" t="inlineStr">
         <is>
           <t>https://structuredfinance.org/industry-events/</t>
         </is>
@@ -6691,7 +6746,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D77" s="10" t="inlineStr">
+      <c r="D77" s="15" t="inlineStr">
         <is>
           <t>https://www.asppa-net.org/events/events/</t>
         </is>
@@ -6711,7 +6766,7 @@
           <t>Finance / Legal</t>
         </is>
       </c>
-      <c r="D78" s="10" t="inlineStr">
+      <c r="D78" s="15" t="inlineStr">
         <is>
           <t>https://ilpa.org/events/</t>
         </is>
@@ -6731,7 +6786,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D79" s="10" t="inlineStr">
+      <c r="D79" s="15" t="inlineStr">
         <is>
           <t>https://www.newyorkfed.org/outreach-and-education/upcoming-events/</t>
         </is>
@@ -6751,7 +6806,7 @@
           <t>Legal / Tax</t>
         </is>
       </c>
-      <c r="D80" s="10" t="inlineStr">
+      <c r="D80" s="15" t="inlineStr">
         <is>
           <t>https://www.actec.org/meetings/</t>
         </is>
@@ -6771,7 +6826,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D81" s="10" t="inlineStr">
+      <c r="D81" s="15" t="inlineStr">
         <is>
           <t>https://events.nationalbar.org/</t>
         </is>
@@ -6791,7 +6846,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D82" s="10" t="inlineStr">
+      <c r="D82" s="15" t="inlineStr">
         <is>
           <t>https://www.fedbar.org/events/</t>
         </is>
@@ -6811,7 +6866,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D83" s="10" t="inlineStr">
+      <c r="D83" s="15" t="inlineStr">
         <is>
           <t>https://www.aallnet.org/conference/</t>
         </is>
@@ -6831,7 +6886,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D84" s="10" t="inlineStr">
+      <c r="D84" s="15" t="inlineStr">
         <is>
           <t>https://www.aclea.org/page/future_conferences</t>
         </is>
@@ -6851,7 +6906,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D85" s="10" t="inlineStr">
+      <c r="D85" s="15" t="inlineStr">
         <is>
           <t>https://acoel.org/</t>
         </is>
@@ -6871,7 +6926,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D86" s="10" t="inlineStr">
+      <c r="D86" s="15" t="inlineStr">
         <is>
           <t>https://www.afccnet.org/Conferences-Training/AFCC-Conferences</t>
         </is>
@@ -6891,7 +6946,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D87" s="10" t="inlineStr">
+      <c r="D87" s="15" t="inlineStr">
         <is>
           <t>https://www.nals.org/events/event_list.asp</t>
         </is>
@@ -6911,7 +6966,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D88" s="10" t="inlineStr">
+      <c r="D88" s="15" t="inlineStr">
         <is>
           <t>https://www.iadclaw.org/events/cle-events/</t>
         </is>
@@ -6931,7 +6986,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D89" s="10" t="inlineStr">
+      <c r="D89" s="15" t="inlineStr">
         <is>
           <t>https://www.asil.org/annual-meeting/</t>
         </is>
@@ -6951,7 +7006,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D90" s="10" t="inlineStr">
+      <c r="D90" s="15" t="inlineStr">
         <is>
           <t>https://ascl.org/ascl-events/</t>
         </is>
@@ -6971,7 +7026,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D91" s="10" t="inlineStr">
+      <c r="D91" s="15" t="inlineStr">
         <is>
           <t>https://www.adr.org/events/</t>
         </is>
@@ -6991,7 +7046,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D92" s="10" t="inlineStr">
+      <c r="D92" s="15" t="inlineStr">
         <is>
           <t>https://www.acslaw.org/get-involved/acs-conventions/</t>
         </is>
@@ -7011,7 +7066,7 @@
           <t>Legal / Finance</t>
         </is>
       </c>
-      <c r="D93" s="10" t="inlineStr">
+      <c r="D93" s="15" t="inlineStr">
         <is>
           <t>https://accfsl.org/events/</t>
         </is>
@@ -7031,7 +7086,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D94" s="10" t="inlineStr">
+      <c r="D94" s="15" t="inlineStr">
         <is>
           <t>https://www.naag.org/events-training/event-calendar/</t>
         </is>
@@ -7051,7 +7106,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D95" s="10" t="inlineStr">
+      <c r="D95" s="15" t="inlineStr">
         <is>
           <t>https://www.ndaa.org/events/</t>
         </is>
@@ -7071,7 +7126,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D96" s="10" t="inlineStr">
+      <c r="D96" s="15" t="inlineStr">
         <is>
           <t>https://www.nela.org/programs-events/</t>
         </is>
@@ -7091,7 +7146,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D97" s="10" t="inlineStr">
+      <c r="D97" s="15" t="inlineStr">
         <is>
           <t>https://www.nacdl.org/Content/meetings</t>
         </is>
@@ -7111,7 +7166,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D98" s="10" t="inlineStr">
+      <c r="D98" s="15" t="inlineStr">
         <is>
           <t>https://www.justice.org/</t>
         </is>
@@ -7131,7 +7186,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D99" s="10" t="inlineStr">
+      <c r="D99" s="15" t="inlineStr">
         <is>
           <t>https://www.floridabar.org/news/calendars/</t>
         </is>
@@ -7151,7 +7206,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D100" s="10" t="inlineStr">
+      <c r="D100" s="15" t="inlineStr">
         <is>
           <t>https://www.texasbarcle.com/new/EventsCalendar.asp</t>
         </is>
@@ -7171,7 +7226,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D101" s="10" t="inlineStr">
+      <c r="D101" s="15" t="inlineStr">
         <is>
           <t>https://stai.org/Events</t>
         </is>
@@ -7191,7 +7246,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D102" s="10" t="inlineStr">
+      <c r="D102" s="15" t="inlineStr">
         <is>
           <t>https://www.isda.org/events</t>
         </is>
@@ -7211,7 +7266,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D103" s="10" t="inlineStr">
+      <c r="D103" s="15" t="inlineStr">
         <is>
           <t>https://www.ncsha.org/events/</t>
         </is>
@@ -7231,7 +7286,7 @@
           <t>Legal / Tax</t>
         </is>
       </c>
-      <c r="D104" s="10" t="inlineStr">
+      <c r="D104" s="15" t="inlineStr">
         <is>
           <t>https://calawyers.org/CLE-Events/Calendar-of-CLE-and-Other-Events</t>
         </is>
@@ -7251,7 +7306,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D105" s="10" t="inlineStr">
+      <c r="D105" s="15" t="inlineStr">
         <is>
           <t>https://www.nasbo.org/</t>
         </is>
@@ -7271,7 +7326,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D106" s="10" t="inlineStr">
+      <c r="D106" s="15" t="inlineStr">
         <is>
           <t>https://bpi.com/our-events/</t>
         </is>
@@ -7291,7 +7346,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D107" s="4" t="inlineStr">
+      <c r="D107" s="14" t="inlineStr">
         <is>
           <t>https://www.nfa.futures.org/</t>
         </is>
@@ -7311,7 +7366,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D108" s="4" t="inlineStr">
+      <c r="D108" s="14" t="inlineStr">
         <is>
           <t>https://www.pabar.org/site/calendar</t>
         </is>
@@ -7331,7 +7386,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr">
+      <c r="D109" s="14" t="inlineStr">
         <is>
           <t>https://www.dcbar.org/news-events</t>
         </is>
@@ -7351,7 +7406,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D110" s="4" t="inlineStr">
+      <c r="D110" s="14" t="inlineStr">
         <is>
           <t>https://capr.org/events/</t>
         </is>
@@ -7371,7 +7426,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D111" s="4" t="inlineStr">
+      <c r="D111" s="14" t="inlineStr">
         <is>
           <t>https://www.calbar.ca.gov/</t>
         </is>
@@ -7391,7 +7446,7 @@
           <t>Tax / Legal</t>
         </is>
       </c>
-      <c r="D112" s="4" t="inlineStr">
+      <c r="D112" s="14" t="inlineStr">
         <is>
           <t>https://www.actconline.org/meetings/</t>
         </is>
@@ -7411,7 +7466,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D113" s="10" t="inlineStr">
+      <c r="D113" s="15" t="inlineStr">
         <is>
           <t>https://www.ntu.org/</t>
         </is>
@@ -7431,7 +7486,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D114" s="10" t="inlineStr">
+      <c r="D114" s="15" t="inlineStr">
         <is>
           <t>https://www.natptax.com/events-education/in-person/</t>
         </is>
@@ -7471,7 +7526,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D116" s="4" t="inlineStr">
+      <c r="D116" s="14" t="inlineStr">
         <is>
           <t>https://taxadmin.org/calendar/</t>
         </is>
@@ -7491,7 +7546,7 @@
           <t>Tax / Finance</t>
         </is>
       </c>
-      <c r="D117" s="4" t="inlineStr">
+      <c r="D117" s="14" t="inlineStr">
         <is>
           <t>https://www.ncsl.org/events</t>
         </is>
@@ -7511,7 +7566,7 @@
           <t>Finance / Legal</t>
         </is>
       </c>
-      <c r="D118" s="4" t="inlineStr">
+      <c r="D118" s="14" t="inlineStr">
         <is>
           <t>https://www.csg.org/csg-events/csg-calendar/</t>
         </is>
@@ -7531,7 +7586,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D119" s="4" t="inlineStr">
+      <c r="D119" s="14" t="inlineStr">
         <is>
           <t>https://content.naic.org/events</t>
         </is>
@@ -7551,7 +7606,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr">
+      <c r="D120" s="14" t="inlineStr">
         <is>
           <t>https://www.acli.com/events</t>
         </is>
@@ -7571,7 +7626,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D121" s="10" t="inlineStr">
+      <c r="D121" s="15" t="inlineStr">
         <is>
           <t>https://events.sifma.org/eventsplus/40ca8e4e-f0da-4e72-bc08-0f8d2924f670</t>
         </is>
@@ -7631,7 +7686,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D124" s="4" t="inlineStr">
+      <c r="D124" s="14" t="inlineStr">
         <is>
           <t>https://aabd.org/upcoming-events/</t>
         </is>
@@ -7651,7 +7706,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D125" s="4" t="inlineStr">
+      <c r="D125" s="14" t="inlineStr">
         <is>
           <t>https://www.nact.org/events/</t>
         </is>
@@ -7671,7 +7726,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D126" s="4" t="inlineStr">
+      <c r="D126" s="14" t="inlineStr">
         <is>
           <t>https://www.afme.eu/events/events-calendar/</t>
         </is>
@@ -7711,7 +7766,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D128" s="4" t="inlineStr">
+      <c r="D128" s="14" t="inlineStr">
         <is>
           <t>https://www.nascus.org/events/</t>
         </is>
@@ -7731,7 +7786,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D129" s="4" t="inlineStr">
+      <c r="D129" s="14" t="inlineStr">
         <is>
           <t>https://www.csbs.org/calendar-events</t>
         </is>
@@ -7751,7 +7806,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D130" s="4" t="inlineStr">
+      <c r="D130" s="14" t="inlineStr">
         <is>
           <t>https://belong.naifa.org/events</t>
         </is>
@@ -7771,7 +7826,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D131" s="4" t="inlineStr">
+      <c r="D131" s="14" t="inlineStr">
         <is>
           <t>https://www.acec.org/events/</t>
         </is>
@@ -7791,7 +7846,7 @@
           <t>Legal / Finance</t>
         </is>
       </c>
-      <c r="D132" s="4" t="inlineStr">
+      <c r="D132" s="14" t="inlineStr">
         <is>
           <t>https://www.nabl.org/engage/events/</t>
         </is>
@@ -7811,7 +7866,7 @@
           <t>Legal / Finance</t>
         </is>
       </c>
-      <c r="D133" s="4" t="inlineStr">
+      <c r="D133" s="14" t="inlineStr">
         <is>
           <t>https://accfl.memberclicks.net/upcoming-college-non-college-events</t>
         </is>
@@ -7831,7 +7886,7 @@
           <t>Legal / Finance</t>
         </is>
       </c>
-      <c r="D134" s="4" t="inlineStr">
+      <c r="D134" s="14" t="inlineStr">
         <is>
           <t>https://www.acmaatty.org/</t>
         </is>
@@ -7851,7 +7906,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D135" s="4" t="inlineStr">
+      <c r="D135" s="14" t="inlineStr">
         <is>
           <t>https://www.acrel.org/acrel/Upcoming_Meetings.asp</t>
         </is>
@@ -7871,7 +7926,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D136" s="4" t="inlineStr">
+      <c r="D136" s="14" t="inlineStr">
         <is>
           <t>https://iapp.org/conferences</t>
         </is>
@@ -7891,7 +7946,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D137" s="4" t="inlineStr">
+      <c r="D137" s="14" t="inlineStr">
         <is>
           <t>https://www.iaj-uim.org/</t>
         </is>
@@ -7911,7 +7966,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D138" s="4" t="inlineStr">
+      <c r="D138" s="14" t="inlineStr">
         <is>
           <t>https://www.iap-association.org/en-GB/Conferences</t>
         </is>
@@ -7931,7 +7986,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D139" s="4" t="inlineStr">
+      <c r="D139" s="14" t="inlineStr">
         <is>
           <t>https://www.nawl.org/events</t>
         </is>
@@ -7951,7 +8006,7 @@
           <t>Legal / Finance</t>
         </is>
       </c>
-      <c r="D140" s="4" t="inlineStr">
+      <c r="D140" s="14" t="inlineStr">
         <is>
           <t>https://www.naepc.org/events</t>
         </is>
@@ -7971,7 +8026,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D141" s="10" t="inlineStr">
+      <c r="D141" s="15" t="inlineStr">
         <is>
           <t>https://aiolaus.com/</t>
         </is>
@@ -7991,7 +8046,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D142" s="4" t="inlineStr">
+      <c r="D142" s="14" t="inlineStr">
         <is>
           <t>https://members.aprl.net/event-calendar</t>
         </is>
@@ -8011,7 +8066,7 @@
           <t>Tax / Finance</t>
         </is>
       </c>
-      <c r="D143" s="4" t="inlineStr">
+      <c r="D143" s="14" t="inlineStr">
         <is>
           <t>https://www.iib.org/events</t>
         </is>
@@ -8031,7 +8086,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D144" s="4" t="inlineStr">
+      <c r="D144" s="14" t="inlineStr">
         <is>
           <t>https://afsaonline.org/events/</t>
         </is>
@@ -8051,7 +8106,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D145" s="4" t="inlineStr">
+      <c r="D145" s="14" t="inlineStr">
         <is>
           <t>https://www.isda.org/events/</t>
         </is>
@@ -8071,7 +8126,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D146" s="4" t="inlineStr">
+      <c r="D146" s="14" t="inlineStr">
         <is>
           <t>https://www.sfnet.com/home/events</t>
         </is>
@@ -8091,7 +8146,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D147" s="10" t="inlineStr">
+      <c r="D147" s="15" t="inlineStr">
         <is>
           <t>https://www.ncsha.org/events/future-events/</t>
         </is>
@@ -8111,7 +8166,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D148" s="10" t="inlineStr">
+      <c r="D148" s="15" t="inlineStr">
         <is>
           <t>https://www.afme.eu/events/</t>
         </is>
@@ -8131,7 +8186,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D149" s="10" t="inlineStr">
+      <c r="D149" s="15" t="inlineStr">
         <is>
           <t>https://nacfb.org/events/</t>
         </is>
@@ -8151,7 +8206,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D150" s="10" t="inlineStr">
+      <c r="D150" s="15" t="inlineStr">
         <is>
           <t>https://www.nareim.org/meetings/</t>
         </is>
@@ -8171,7 +8226,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D151" s="10" t="inlineStr">
+      <c r="D151" s="15" t="inlineStr">
         <is>
           <t>https://structuredfinance.org/industry-events/</t>
         </is>
@@ -8191,7 +8246,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D152" s="10" t="inlineStr">
+      <c r="D152" s="15" t="inlineStr">
         <is>
           <t>https://fraconference.com/</t>
         </is>
@@ -8211,7 +8266,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D153" s="10" t="inlineStr">
+      <c r="D153" s="15" t="inlineStr">
         <is>
           <t>https://www.midwestfinance.org/2026-annual-meeting</t>
         </is>
@@ -8231,7 +8286,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D154" s="10" t="inlineStr">
+      <c r="D154" s="15" t="inlineStr">
         <is>
           <t>https://easternfinance.org/2027-meeting/</t>
         </is>
@@ -8251,7 +8306,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D155" s="10" t="inlineStr">
+      <c r="D155" s="15" t="inlineStr">
         <is>
           <t>https://southernfinance.org/meeting</t>
         </is>
@@ -8271,7 +8326,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D156" s="10" t="inlineStr">
+      <c r="D156" s="15" t="inlineStr">
         <is>
           <t>https://westernfinance.org/conference/</t>
         </is>
@@ -8311,7 +8366,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D158" s="10" t="inlineStr">
+      <c r="D158" s="15" t="inlineStr">
         <is>
           <t>https://www.publicpower.org/education-and-events/calendar</t>
         </is>
@@ -8331,7 +8386,7 @@
           <t>Finance / Regulatory</t>
         </is>
       </c>
-      <c r="D159" s="4" t="inlineStr">
+      <c r="D159" s="14" t="inlineStr">
         <is>
           <t>https://www.naruc.org/events/event-list/</t>
         </is>
@@ -8351,7 +8406,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D160" s="4" t="inlineStr">
+      <c r="D160" s="14" t="inlineStr">
         <is>
           <t>https://financialservices.org/events/</t>
         </is>
@@ -8371,7 +8426,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D161" s="10" t="inlineStr">
+      <c r="D161" s="15" t="inlineStr">
         <is>
           <t>https://pestakeholder.org/news/</t>
         </is>
@@ -8391,7 +8446,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D162" s="10" t="inlineStr">
+      <c r="D162" s="15" t="inlineStr">
         <is>
           <t>https://sbia.org/events/</t>
         </is>
@@ -8411,7 +8466,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D163" s="10" t="inlineStr">
+      <c r="D163" s="15" t="inlineStr">
         <is>
           <t>https://www.nipa.org/events/event_list.asp</t>
         </is>
@@ -8431,7 +8486,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D164" s="10" t="inlineStr">
+      <c r="D164" s="15" t="inlineStr">
         <is>
           <t>https://www.napa-net.org/events/event-calendar/</t>
         </is>
@@ -8451,7 +8506,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D165" s="4" t="inlineStr">
+      <c r="D165" s="14" t="inlineStr">
         <is>
           <t>https://www.usaretirement.org/events</t>
         </is>
@@ -8471,7 +8526,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D166" s="4" t="inlineStr">
+      <c r="D166" s="14" t="inlineStr">
         <is>
           <t>https://investmentsandwealth.org/financial-advisor-conferences-events</t>
         </is>
@@ -8491,7 +8546,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D167" s="4" t="inlineStr">
+      <c r="D167" s="14" t="inlineStr">
         <is>
           <t>https://aimse.org/events-home/</t>
         </is>
@@ -8511,7 +8566,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D168" s="4" t="inlineStr">
+      <c r="D168" s="14" t="inlineStr">
         <is>
           <t>https://www.taxadmin.org/events</t>
         </is>
@@ -8531,7 +8586,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D169" s="4" t="inlineStr">
+      <c r="D169" s="14" t="inlineStr">
         <is>
           <t>https://www.csea.org/</t>
         </is>
@@ -8551,7 +8606,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D170" s="4" t="inlineStr">
+      <c r="D170" s="14" t="inlineStr">
         <is>
           <t>https://nyssea.org/events</t>
         </is>
@@ -8571,7 +8626,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D171" s="10" t="inlineStr">
+      <c r="D171" s="15" t="inlineStr">
         <is>
           <t>https://cosea.starchapter.com/meetinginfo.php?p_or_f=p</t>
         </is>
@@ -8591,7 +8646,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D172" s="10" t="inlineStr">
+      <c r="D172" s="15" t="inlineStr">
         <is>
           <t>https://txsea.org/calendar.php</t>
         </is>
@@ -8611,7 +8666,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D173" s="10" t="inlineStr">
+      <c r="D173" s="15" t="inlineStr">
         <is>
           <t>https://www.seatastates.org/</t>
         </is>
@@ -8631,7 +8686,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D174" s="10" t="inlineStr">
+      <c r="D174" s="15" t="inlineStr">
         <is>
           <t>https://ncraao.org/future-conferences/</t>
         </is>
@@ -8651,7 +8706,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D175" s="10" t="inlineStr">
+      <c r="D175" s="15" t="inlineStr">
         <is>
           <t>https://www.maa-usa.org/About-Us/Calendar-Events/Event-Calendar</t>
         </is>
@@ -8671,7 +8726,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D176" s="10" t="inlineStr">
+      <c r="D176" s="15" t="inlineStr">
         <is>
           <t>https://taptp.org/</t>
         </is>
@@ -8691,7 +8746,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D177" s="10" t="inlineStr">
+      <c r="D177" s="15" t="inlineStr">
         <is>
           <t>https://laota.wildapricot.org/events</t>
         </is>
@@ -8711,7 +8766,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D178" s="10" t="inlineStr">
+      <c r="D178" s="15" t="inlineStr">
         <is>
           <t>https://www.natptax.com/events-education/in-person/</t>
         </is>
@@ -8731,7 +8786,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D179" s="4" t="inlineStr">
+      <c r="D179" s="14" t="inlineStr">
         <is>
           <t>https://nstp.org/</t>
         </is>
@@ -8751,7 +8806,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D180" s="10" t="inlineStr">
+      <c r="D180" s="15" t="inlineStr">
         <is>
           <t>https://www.naea.org/calendar/</t>
         </is>
@@ -8771,7 +8826,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D181" s="4" t="inlineStr">
+      <c r="D181" s="14" t="inlineStr">
         <is>
           <t>https://www.irs.gov/tax-professionals/irs-nationwide-tax-forum-information</t>
         </is>
@@ -8791,7 +8846,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D182" s="4" t="inlineStr">
+      <c r="D182" s="14" t="inlineStr">
         <is>
           <t>https://www.taxpayeradvocate.irs.gov/contact-us/upcoming-events/</t>
         </is>
@@ -8811,7 +8866,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D183" s="4" t="inlineStr">
+      <c r="D183" s="14" t="inlineStr">
         <is>
           <t>https://www.iaao.org/events/</t>
         </is>
@@ -8831,7 +8886,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D184" s="4" t="inlineStr">
+      <c r="D184" s="14" t="inlineStr">
         <is>
           <t>https://www.tacaoftexas.org/</t>
         </is>
@@ -8851,7 +8906,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D185" s="4" t="inlineStr">
+      <c r="D185" s="14" t="inlineStr">
         <is>
           <t>https://ttara.org/events/</t>
         </is>
@@ -8871,7 +8926,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D186" s="4" t="inlineStr">
+      <c r="D186" s="14" t="inlineStr">
         <is>
           <t>https://ctec.org/</t>
         </is>
@@ -8891,7 +8946,7 @@
           <t>Tax / Legal</t>
         </is>
       </c>
-      <c r="D187" s="4" t="inlineStr">
+      <c r="D187" s="14" t="inlineStr">
         <is>
           <t>https://calawyers.org/section/taxation/events/</t>
         </is>
@@ -8911,7 +8966,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D188" s="4" t="inlineStr">
+      <c r="D188" s="14" t="inlineStr">
         <is>
           <t>https://thectc.org/content.aspx?page_id=4001&amp;club_id=876606</t>
         </is>
@@ -8931,7 +8986,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D189" s="10" t="inlineStr">
+      <c r="D189" s="15" t="inlineStr">
         <is>
           <t>https://www.micpa.org/cpe/store/search-results</t>
         </is>
@@ -8971,7 +9026,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D191" s="10" t="inlineStr">
+      <c r="D191" s="15" t="inlineStr">
         <is>
           <t>https://www.gfoa.org/events</t>
         </is>
@@ -8991,7 +9046,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D192" s="10" t="inlineStr">
+      <c r="D192" s="15" t="inlineStr">
         <is>
           <t>https://www.fma.org/conferences</t>
         </is>
@@ -9011,7 +9066,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D193" s="10" t="inlineStr">
+      <c r="D193" s="15" t="inlineStr">
         <is>
           <t>https://www.astps.org/schedule/</t>
         </is>
@@ -9031,7 +9086,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D194" s="10" t="inlineStr">
+      <c r="D194" s="15" t="inlineStr">
         <is>
           <t>https://www.natptax.com/events-education/</t>
         </is>
@@ -9051,7 +9106,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D195" s="10" t="inlineStr">
+      <c r="D195" s="15" t="inlineStr">
         <is>
           <t>https://www.nasact.org/Calendar_list.asp</t>
         </is>
@@ -9071,7 +9126,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D196" s="10" t="inlineStr">
+      <c r="D196" s="15" t="inlineStr">
         <is>
           <t>https://www.agacgfm.org/events-training/comprehensive-calendar/</t>
         </is>
@@ -9091,7 +9146,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D197" s="10" t="inlineStr">
+      <c r="D197" s="15" t="inlineStr">
         <is>
           <t>https://www.theiia.org/en/learning/conferences/</t>
         </is>
@@ -9111,7 +9166,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D198" s="10" t="inlineStr">
+      <c r="D198" s="15" t="inlineStr">
         <is>
           <t>https://www.acfe.com/training-events-and-products/all-events</t>
         </is>
@@ -9131,7 +9186,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D199" s="10" t="inlineStr">
+      <c r="D199" s="15" t="inlineStr">
         <is>
           <t>https://www.imanet.org/continuing-education/events</t>
         </is>
@@ -9151,7 +9206,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D200" s="10" t="inlineStr">
+      <c r="D200" s="15" t="inlineStr">
         <is>
           <t>https://www.financialprofessionals.org/events/afp-live-events</t>
         </is>
@@ -9171,7 +9226,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D201" s="10" t="inlineStr">
+      <c r="D201" s="15" t="inlineStr">
         <is>
           <t>https://nast.org/conference-overview/</t>
         </is>
@@ -9191,7 +9246,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D202" s="10" t="inlineStr">
+      <c r="D202" s="15" t="inlineStr">
         <is>
           <t>https://www.naspo.org/events-and-webinars/</t>
         </is>
@@ -9211,7 +9266,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D203" s="10" t="inlineStr">
+      <c r="D203" s="15" t="inlineStr">
         <is>
           <t>https://www.nacctfo.org/conferences</t>
         </is>
@@ -9231,7 +9286,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D204" s="10" t="inlineStr">
+      <c r="D204" s="15" t="inlineStr">
         <is>
           <t>https://www.aptusc.org/annual-conference</t>
         </is>
@@ -9251,7 +9306,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D205" s="10" t="inlineStr">
+      <c r="D205" s="15" t="inlineStr">
         <is>
           <t>https://algaonline.org/page/conference</t>
         </is>
@@ -9271,7 +9326,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D206" s="10" t="inlineStr">
+      <c r="D206" s="15" t="inlineStr">
         <is>
           <t>https://www.naggl.org/events/</t>
         </is>
@@ -9291,7 +9346,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D207" s="10" t="inlineStr">
+      <c r="D207" s="15" t="inlineStr">
         <is>
           <t>https://www.crfonline.org/events/</t>
         </is>
@@ -9311,7 +9366,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D208" s="10" t="inlineStr">
+      <c r="D208" s="15" t="inlineStr">
         <is>
           <t>https://www.nacm.org/event-calendar.html</t>
         </is>
@@ -9331,7 +9386,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D209" s="10" t="inlineStr">
+      <c r="D209" s="15" t="inlineStr">
         <is>
           <t>https://turnaround.org/events</t>
         </is>
@@ -9351,7 +9406,7 @@
           <t>Finance / Legal</t>
         </is>
       </c>
-      <c r="D210" s="10" t="inlineStr">
+      <c r="D210" s="15" t="inlineStr">
         <is>
           <t>https://www.abi.org/events</t>
         </is>
@@ -9371,7 +9426,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D211" s="10" t="inlineStr">
+      <c r="D211" s="15" t="inlineStr">
         <is>
           <t>https://www.acg.org/events</t>
         </is>
@@ -9391,7 +9446,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D212" s="10" t="inlineStr">
+      <c r="D212" s="15" t="inlineStr">
         <is>
           <t>https://www.ici.org/events</t>
         </is>
@@ -9411,7 +9466,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D213" s="10" t="inlineStr">
+      <c r="D213" s="15" t="inlineStr">
         <is>
           <t>https://www.investmentadviser.org/events-education/</t>
         </is>
@@ -9431,7 +9486,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D214" s="10" t="inlineStr">
+      <c r="D214" s="15" t="inlineStr">
         <is>
           <t>https://www.mfaalts.org/events/</t>
         </is>
@@ -9451,7 +9506,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D215" s="10" t="inlineStr">
+      <c r="D215" s="15" t="inlineStr">
         <is>
           <t>https://fundfinanceassociation.com/events/</t>
         </is>
@@ -9471,7 +9526,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D216" s="10" t="inlineStr">
+      <c r="D216" s="15" t="inlineStr">
         <is>
           <t>https://www.nacuso.org/events</t>
         </is>
@@ -9491,7 +9546,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D217" s="10" t="inlineStr">
+      <c r="D217" s="15" t="inlineStr">
         <is>
           <t>https://www.americanbar.org/events-cle/</t>
         </is>
@@ -9946,14 +10001,216 @@
     <cfRule type="duplicateValues" priority="10" dxfId="0"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId210"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10009,7 +10266,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>https://www.tax.org.uk/events</t>
         </is>
@@ -10029,7 +10286,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>https://www.att.org.uk/events</t>
         </is>
@@ -10049,7 +10306,7 @@
           <t>Tax / Payroll</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>https://www.cipp.org.uk/events.html</t>
         </is>
@@ -10069,7 +10326,7 @@
           <t>Accounting / Finance / Tax</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>https://www.icaew.com/learning-and-development/events</t>
         </is>
@@ -10089,7 +10346,7 @@
           <t>Accounting / Finance / Tax</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>https://www.accaglobal.com/learning-and-events.html</t>
         </is>
@@ -10109,7 +10366,7 @@
           <t>Accounting / Finance</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>https://www.icas.com/news-insights-events/upcoming-events</t>
         </is>
@@ -10129,7 +10386,7 @@
           <t>Accounting / Finance</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>https://www.aat.org.uk/events/search</t>
         </is>
@@ -10149,7 +10406,7 @@
           <t>Public Finance</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>https://www.cipfa.org/training/cipfa-conferences</t>
         </is>
@@ -10169,7 +10426,7 @@
           <t>Finance / Treasury</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>https://www.treasurers.org/events</t>
         </is>
@@ -10189,7 +10446,7 @@
           <t>Finance / Investment</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>https://www.cisi.org/cisiweb2/shop/events</t>
         </is>
@@ -10209,7 +10466,7 @@
           <t>Investment / Finance</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>https://www.cfauk.org/events/events-listing</t>
         </is>
@@ -10229,7 +10486,7 @@
           <t>Pensions / Finance</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>https://www.plsa.co.uk/Events</t>
         </is>
@@ -10249,7 +10506,7 @@
           <t>Investment / Finance</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>https://www.theia.org/events-training</t>
         </is>
@@ -10269,7 +10526,7 @@
           <t>Finance / ESG</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>https://uksif.org/category/events/</t>
         </is>
@@ -10289,7 +10546,7 @@
           <t>Audit / Finance</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>https://charterediia.org/events-calendar/</t>
         </is>
@@ -10309,7 +10566,7 @@
           <t>Governance / Legal / Finance</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>https://www.cgi.org.uk/events/</t>
         </is>
@@ -10329,7 +10586,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>https://irsociety.org.uk/events</t>
         </is>
@@ -10349,7 +10606,7 @@
           <t>Tax / Legal</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>https://www.step.org/events</t>
         </is>
@@ -10369,7 +10626,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>https://www.lawsociety.org.uk/events</t>
         </is>
@@ -10389,7 +10646,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>https://www.barcouncil.org.uk/training-events/calendar.html</t>
         </is>
@@ -10409,7 +10666,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>https://www.cilex.org.uk/membership/events.aspx</t>
         </is>
@@ -10429,7 +10686,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>https://www.lawscot.org.uk/news-and-events/events/</t>
         </is>
@@ -10449,7 +10706,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>https://lawsoc-ni.org/about-the-law-society/news-events/events</t>
         </is>
@@ -10469,7 +10726,7 @@
           <t>Legal / Arbitration</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>https://www.ciarb.org/events/</t>
         </is>
@@ -10489,7 +10746,7 @@
           <t>International Law</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>https://www.biicl.org/events</t>
         </is>
@@ -10509,7 +10766,7 @@
           <t>Employment Law</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>https://www.elaweb.org.uk/future-events</t>
         </is>
@@ -10529,7 +10786,7 @@
           <t>Legal / Insolvency</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>https://www.ilauk.com/news-events/upcoming-events</t>
         </is>
@@ -10549,7 +10806,7 @@
           <t>Insolvency / Finance / Legal</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>https://www.r3.org.uk/events-training/</t>
         </is>
@@ -10569,7 +10826,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>https://associationofcostslawyers.co.uk/events/</t>
         </is>
@@ -10589,7 +10846,7 @@
           <t>Legal / ADR</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>https://civilmediation.org/news-events/</t>
         </is>
@@ -10609,7 +10866,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>https://www.flba.co.uk/events/</t>
         </is>
@@ -10629,7 +10886,7 @@
           <t>Legal / Tax</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>https://www.chba.org.uk/for-members/library/seminars</t>
         </is>
@@ -10649,7 +10906,7 @@
           <t>Commercial Law</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>https://www.combar.com/news-and-events/events/</t>
         </is>
@@ -10669,7 +10926,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>https://tecbar.org/events/</t>
         </is>
@@ -10689,7 +10946,7 @@
           <t>Credit / Finance</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>https://www.cicm.com/cicm-events/</t>
         </is>
@@ -10709,7 +10966,7 @@
           <t>Legal / Corporate</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>https://www.acc.com/education-events</t>
         </is>
@@ -10729,7 +10986,7 @@
           <t>Accounting / Finance</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>https://www.aicpa-cima.com/cpe-learning/event</t>
         </is>
@@ -10749,7 +11006,7 @@
           <t>Accounting / Finance</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>https://www.ifa.org.uk/cpd</t>
         </is>
@@ -10769,7 +11026,7 @@
           <t>Management / Finance</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>https://www.managers.org.uk/community/events/</t>
         </is>
@@ -10789,7 +11046,7 @@
           <t>Pensions / Finance</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>https://www.pensions-pmi.org.uk/events/</t>
         </is>
@@ -10809,7 +11066,7 @@
           <t>Financial Planning</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>https://events.thepfs.org/</t>
         </is>
@@ -10829,7 +11086,7 @@
           <t>Pensions / Legal / Finance</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>https://the-spp.co.uk/events/upcoming-events/</t>
         </is>
@@ -10849,7 +11106,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>https://www.icaew.com/technical/tax/tax-faculty/tax-faculty-events</t>
         </is>
@@ -10869,7 +11126,7 @@
           <t>VAT / Tax</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>https://vpgweb.com/</t>
         </is>
@@ -10889,7 +11146,7 @@
           <t>Legal / Forensics</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>https://www.bafs.org.uk/events/past-events.php</t>
         </is>
@@ -10909,7 +11166,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>https://www.att.org.uk/edinburgh</t>
         </is>
@@ -10929,7 +11186,7 @@
           <t>Finance / Investment</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>https://www.cisi.org/events</t>
         </is>
@@ -10949,7 +11206,7 @@
           <t>Accounting / Tax</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="16" t="inlineStr">
         <is>
           <t>https://www.icaew.com/events-support</t>
         </is>
@@ -10984,7 +11241,7 @@
           <t>Accounting / Finance</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="16" t="inlineStr">
         <is>
           <t>https://www.aiaworldwide.com/cpd/events/</t>
         </is>
@@ -11004,7 +11261,7 @@
           <t>Finance / Leasing</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>https://fla.org.uk/events/</t>
         </is>
@@ -11024,7 +11281,7 @@
           <t>Legal Finance / Compliance</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>https://www.ilfm.org.uk/site/training-and-events/</t>
         </is>
@@ -11044,7 +11301,7 @@
           <t>Tax / Public Finance</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>https://ifs.org.uk/events</t>
         </is>
@@ -11064,7 +11321,7 @@
           <t>International Tax</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="16" t="inlineStr">
         <is>
           <t>https://ifa-uk.org/events/</t>
         </is>
@@ -11084,7 +11341,7 @@
           <t>Finance / Financial Innovation</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="16" t="inlineStr">
         <is>
           <t>https://financeinnovationlab.org/events/</t>
         </is>
@@ -11104,7 +11361,7 @@
           <t>Financial Markets</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="16" t="inlineStr">
         <is>
           <t>https://www.afme.eu/events</t>
         </is>
@@ -11139,7 +11396,7 @@
           <t>Financial Markets / Regulation</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="16" t="inlineStr">
         <is>
           <t>https://fmsb.com/events/</t>
         </is>
@@ -11159,7 +11416,7 @@
           <t>Securities / Finance</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="16" t="inlineStr">
         <is>
           <t>https://www.islaemea.org/isla-events/</t>
         </is>
@@ -11179,7 +11436,7 @@
           <t>Corporate Legal</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="16" t="inlineStr">
         <is>
           <t>https://www.acc.com/chapters-networks/chapters/europe/events-europe</t>
         </is>
@@ -11199,7 +11456,7 @@
           <t>Environmental Law</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="16" t="inlineStr">
         <is>
           <t>https://www.ukela.org/UKELA/UKELA/Events/Annual-Conference.aspx</t>
         </is>
@@ -11219,7 +11476,7 @@
           <t>Planning / Environmental Law</t>
         </is>
       </c>
-      <c r="D63" s="10" t="inlineStr">
+      <c r="D63" s="15" t="inlineStr">
         <is>
           <t>https://peba.org.uk/news-events/</t>
         </is>
@@ -11239,7 +11496,7 @@
           <t>Public / Administrative Law</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="16" t="inlineStr">
         <is>
           <t>https://adminlaw.org.uk/events/</t>
         </is>
@@ -11274,7 +11531,7 @@
           <t>Construction Law</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="16" t="inlineStr">
         <is>
           <t>https://www.scl.org.uk/events</t>
         </is>
@@ -11294,7 +11551,7 @@
           <t>Technology / Legal</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="16" t="inlineStr">
         <is>
           <t>https://www.scl.org/events/event/</t>
         </is>
@@ -11344,7 +11601,7 @@
           <t>IP / Commercial Law</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" s="16" t="inlineStr">
         <is>
           <t>https://les-bi.org/events-calendar/</t>
         </is>
@@ -11364,7 +11621,7 @@
           <t>Competition Law</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" s="16" t="inlineStr">
         <is>
           <t>https://competitionlawassociation.org.uk/events/</t>
         </is>
@@ -11384,7 +11641,7 @@
           <t>Financial Services Law</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="16" t="inlineStr">
         <is>
           <t>https://fsla.org.uk/category/events/</t>
         </is>
@@ -11404,7 +11661,7 @@
           <t>Insolvency / Finance</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" s="16" t="inlineStr">
         <is>
           <t>https://insolvency-practitioners.org.uk/calendar-of-events/</t>
         </is>
@@ -11424,7 +11681,7 @@
           <t>Restructuring / Finance</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>https://tma-uk.org/events/</t>
         </is>
@@ -11444,7 +11701,7 @@
           <t>Credit / Financial Services</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="16" t="inlineStr">
         <is>
           <t>https://www.csa-uk.com/page/events</t>
         </is>
@@ -11464,7 +11721,7 @@
           <t>Risk / Finance</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" s="16" t="inlineStr">
         <is>
           <t>https://www.theirm.org/events/</t>
         </is>
@@ -11484,7 +11741,7 @@
           <t>Compliance / Financial Crime</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" s="16" t="inlineStr">
         <is>
           <t>https://www.int-comp.org/events/</t>
         </is>
@@ -11549,7 +11806,7 @@
           <t>Accounting / Tax</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" s="16" t="inlineStr">
         <is>
           <t>https://www.charteredaccountants.ie/professional-development/cpd-courses-and-networking-events</t>
         </is>
@@ -11569,7 +11826,7 @@
           <t>Accounting / Finance</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" s="16" t="inlineStr">
         <is>
           <t>https://www.accaglobal.com/learning-and-events.html</t>
         </is>
@@ -11589,7 +11846,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" s="16" t="inlineStr">
         <is>
           <t>https://taxresearch.network/event/trn-26-london-registration/</t>
         </is>
@@ -11639,7 +11896,7 @@
           <t>Tax / Legal / Private Client</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" s="16" t="inlineStr">
         <is>
           <t>https://www.step.org/branches/step-scotland</t>
         </is>
@@ -11659,7 +11916,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" s="16" t="inlineStr">
         <is>
           <t>https://www.att.org.uk/northern-ireland</t>
         </is>
@@ -11679,7 +11936,7 @@
           <t>Business / Finance</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" s="16" t="inlineStr">
         <is>
           <t>https://www.northernirelandchamber.com/event/festival-of-business-2026/</t>
         </is>
@@ -11699,7 +11956,7 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" s="16" t="inlineStr">
         <is>
           <t>https://www.sfe.org.uk/events</t>
         </is>
@@ -11719,7 +11976,7 @@
           <t>Property / Finance / Legal</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D90" s="16" t="inlineStr">
         <is>
           <t>https://scottishpropertyfederation.org.uk/events</t>
         </is>
@@ -11739,7 +11996,7 @@
           <t>Arbitration / Legal</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D91" s="16" t="inlineStr">
         <is>
           <t>https://scottisharbitrationcentre.org/category/events-training/</t>
         </is>
@@ -11759,7 +12016,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D92" s="16" t="inlineStr">
         <is>
           <t>https://www.eventbrite.co.uk/o/scottish-young-lawyers-association-1867524801</t>
         </is>
@@ -11794,7 +12051,7 @@
           <t>Environmental Law</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D94" s="16" t="inlineStr">
         <is>
           <t>https://www.ukela.org/UKELA/UKELA/Events/Annual-Conference.aspx</t>
         </is>
@@ -11814,7 +12071,7 @@
           <t>Insurance Law</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D95" s="16" t="inlineStr">
         <is>
           <t>https://bila.org.uk/events/upcoming-events/</t>
         </is>
@@ -11834,7 +12091,7 @@
           <t>Pensions / Legal</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D96" s="16" t="inlineStr">
         <is>
           <t>http://apl-live.aptsolutions.net/calendar.php?id=5</t>
         </is>
@@ -11869,7 +12126,7 @@
           <t>Insolvency / Accounting</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D98" s="16" t="inlineStr">
         <is>
           <t>https://www.icaew.com/groups-and-networks/communities/restructuring-and-insolvency/restructuring-and-insolvency-community/events</t>
         </is>
@@ -11889,7 +12146,7 @@
           <t>Finance / Treasury</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D99" s="16" t="inlineStr">
         <is>
           <t>https://treasurers.ie/events</t>
         </is>
@@ -11909,7 +12166,7 @@
           <t>Business / Finance</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D100" s="16" t="inlineStr">
         <is>
           <t>https://www.bam.ac.uk/events-landing.html</t>
         </is>
@@ -11929,7 +12186,7 @@
           <t>Accounting / Finance</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D101" s="16" t="inlineStr">
         <is>
           <t>https://www.bafa.ac.uk/events/upcoming-events.html</t>
         </is>
@@ -11949,7 +12206,7 @@
           <t>Finance / Economics</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D102" s="16" t="inlineStr">
         <is>
           <t>https://www.efa-finance.org/efa-annual-meeting/</t>
         </is>
@@ -11969,7 +12226,7 @@
           <t>Economics / Finance</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D103" s="16" t="inlineStr">
         <is>
           <t>https://res.org.uk/event-listing/res-2026-annual-conference/</t>
         </is>
@@ -11989,7 +12246,7 @@
           <t>Economics / Finance</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D104" s="16" t="inlineStr">
         <is>
           <t>https://spe.org.uk/whats-on/events/</t>
         </is>
@@ -12009,7 +12266,7 @@
           <t>Regulation / Economics</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D105" s="16" t="inlineStr">
         <is>
           <t>https://ukrn.org.uk/events/</t>
         </is>
@@ -12029,7 +12286,7 @@
           <t>Tax / Public Finance</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D106" s="16" t="inlineStr">
         <is>
           <t>https://committees.parliament.uk/committee/158/treasury-committee/events/</t>
         </is>
@@ -12064,7 +12321,7 @@
           <t>Public Finance / Audit</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D108" s="16" t="inlineStr">
         <is>
           <t>https://committees.parliament.uk/committee/127/public-accounts-committee/events/</t>
         </is>
@@ -12084,7 +12341,7 @@
           <t>Public Policy / Finance</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D109" s="16" t="inlineStr">
         <is>
           <t>https://www.instituteforgovernment.org.uk/our-events</t>
         </is>
@@ -12104,7 +12361,7 @@
           <t>Economics / Public Finance</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D110" s="16" t="inlineStr">
         <is>
           <t>https://www.resolutionfoundation.org/events/</t>
         </is>
@@ -12139,7 +12396,7 @@
           <t>Public Finance</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D112" s="16" t="inlineStr">
         <is>
           <t>https://www.cipfa.org/training</t>
         </is>
@@ -12159,7 +12416,7 @@
           <t>Public Finance</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D113" s="16" t="inlineStr">
         <is>
           <t>https://publicfinancelive.org/</t>
         </is>
@@ -12194,7 +12451,7 @@
           <t>Tax / Public Finance</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D115" s="16" t="inlineStr">
         <is>
           <t>https://www.taxpayersalliance.com/events</t>
         </is>
@@ -12229,7 +12486,7 @@
           <t>Accounting / Finance</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D117" s="16" t="inlineStr">
         <is>
           <t>https://www.caba.org.uk/online-events-feedback-and-outcomes.html</t>
         </is>
@@ -12264,7 +12521,7 @@
           <t>Energy / Finance</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D119" s="16" t="inlineStr">
         <is>
           <t>https://www.biee.org/</t>
         </is>
@@ -12284,7 +12541,7 @@
           <t>Energy / Regulation / Finance</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D120" s="16" t="inlineStr">
         <is>
           <t>https://www.energy-uk.org.uk/events/</t>
         </is>
@@ -12304,7 +12561,7 @@
           <t>Industry / Finance / Regulation</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D121" s="16" t="inlineStr">
         <is>
           <t>https://www.makeuk.org/news-and-events/events</t>
         </is>
@@ -12324,7 +12581,7 @@
           <t>Business / Tax / Regulation</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D122" s="16" t="inlineStr">
         <is>
           <t>https://brc.org.uk/news-and-events/events/</t>
         </is>
@@ -12344,7 +12601,7 @@
           <t>Property / Finance / Tax</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D123" s="16" t="inlineStr">
         <is>
           <t>https://bpf.org.uk/events/</t>
         </is>
@@ -12379,7 +12636,7 @@
           <t>Property Finance</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D125" s="16" t="inlineStr">
         <is>
           <t>https://the-apl.com/events/</t>
         </is>
@@ -12864,7 +13121,7 @@
           <t>Finance / Mortgages</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
+      <c r="D157" s="16" t="inlineStr">
         <is>
           <t>https://www.smp.org.uk/events/</t>
         </is>
@@ -12884,7 +13141,7 @@
           <t>Property Finance / Lending</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
+      <c r="D158" s="16" t="inlineStr">
         <is>
           <t>https://www.tickettailor.com/events/bdla</t>
         </is>
@@ -12919,7 +13176,7 @@
           <t>Business Finance / Investment</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="D160" s="16" t="inlineStr">
         <is>
           <t>https://www.british-business-bank.co.uk/news-and-events/events</t>
         </is>
@@ -12939,7 +13196,7 @@
           <t>Investment / Finance</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="D161" s="16" t="inlineStr">
         <is>
           <t>https://ukbaa.org.uk/events/</t>
         </is>
@@ -12974,7 +13231,7 @@
           <t>Pensions / Finance</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D163" s="16" t="inlineStr">
         <is>
           <t>https://www.pensionsuk.org.uk/Events</t>
         </is>
@@ -12994,7 +13251,7 @@
           <t>Actuarial / Pensions / Finance</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D164" s="16" t="inlineStr">
         <is>
           <t>https://aca.org.uk/events-dates/</t>
         </is>
@@ -13014,7 +13271,7 @@
           <t>Actuarial / Finance / Risk</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
+      <c r="D165" s="16" t="inlineStr">
         <is>
           <t>https://www.actuaries.org.uk/learn-and-develop/events-calendar/events-save-date</t>
         </is>
@@ -13034,7 +13291,7 @@
           <t>Treasury / Finance</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
+      <c r="D166" s="16" t="inlineStr">
         <is>
           <t>https://www.treasurers.org/events</t>
         </is>
@@ -13054,7 +13311,7 @@
           <t>International Law</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="D167" s="16" t="inlineStr">
         <is>
           <t>https://www.biicl.org/events</t>
         </is>
@@ -13074,7 +13331,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr">
+      <c r="D168" s="16" t="inlineStr">
         <is>
           <t>https://ilpa.org.uk/training-and-events-calendar/</t>
         </is>
@@ -13094,7 +13351,7 @@
           <t>Property Law</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr">
+      <c r="D169" s="16" t="inlineStr">
         <is>
           <t>https://www.pla.org.uk/events</t>
         </is>
@@ -13129,7 +13386,7 @@
           <t>Accounting / Tax / Audit</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
+      <c r="D171" s="16" t="inlineStr">
         <is>
           <t>https://spa.org.uk/webinars/</t>
         </is>
@@ -13149,7 +13406,7 @@
           <t>Accounting / Audit</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
+      <c r="D172" s="16" t="inlineStr">
         <is>
           <t>https://www.acie.org.uk/events</t>
         </is>
@@ -13169,7 +13426,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
+      <c r="D173" s="16" t="inlineStr">
         <is>
           <t>https://www.taxadvisers.org.uk/future-events/</t>
         </is>
@@ -13189,7 +13446,7 @@
           <t>Legal Finance / Compliance / VAT</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
+      <c r="D174" s="16" t="inlineStr">
         <is>
           <t>https://alca.org.uk/events/</t>
         </is>
@@ -13209,7 +13466,7 @@
           <t>Legal Finance / Accounting</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
+      <c r="D175" s="16" t="inlineStr">
         <is>
           <t>https://www.ilfm.org.uk/site/training-and-events/</t>
         </is>
@@ -13244,7 +13501,7 @@
           <t>Fraud / Finance / Compliance</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
+      <c r="D177" s="16" t="inlineStr">
         <is>
           <t>https://acfeuk.co.uk/http-acfeuk-co-uk-events/</t>
         </is>
@@ -13264,7 +13521,7 @@
           <t>Finance / Credit / Regulation</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="D178" s="16" t="inlineStr">
         <is>
           <t>https://fla.org.uk/events-and-training/events/</t>
         </is>
@@ -13299,7 +13556,7 @@
           <t>Capital Markets / Finance</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="D180" s="16" t="inlineStr">
         <is>
           <t>https://www.afme.eu/events</t>
         </is>
@@ -13319,7 +13576,7 @@
           <t>Derivatives / Financial Regulation</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
+      <c r="D181" s="16" t="inlineStr">
         <is>
           <t>https://www.isda.org/events</t>
         </is>
@@ -13354,7 +13611,7 @@
           <t>International Legal</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
+      <c r="D183" s="16" t="inlineStr">
         <is>
           <t>https://www.ibanet.org/conferences</t>
         </is>
@@ -13374,7 +13631,7 @@
           <t>Economics / Public Finance</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
+      <c r="D184" s="16" t="inlineStr">
         <is>
           <t>https://iea.org.uk/events/</t>
         </is>
@@ -13394,7 +13651,7 @@
           <t>Tax / Public Finance</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
+      <c r="D185" s="16" t="inlineStr">
         <is>
           <t>https://ifs.org.uk/events</t>
         </is>
@@ -13454,7 +13711,135 @@
     <row r="251" ht="28.8" customHeight="1"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId129"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13511,7 +13896,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>https://sctp.org.sg/events/Tax-Professionals?utm_source=chatgpt.com</t>
         </is>
@@ -13531,7 +13916,7 @@
           <t>Accounting / Finance</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>https://www.isca.org.sg/member-support/events?utm_source=chatgpt.com</t>
         </is>
@@ -13551,7 +13936,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>https://www.taxacademy.sg/seminars-and-conferences/?utm_source=chatgpt.com</t>
         </is>
@@ -13571,7 +13956,7 @@
           <t>Accounting / Tax</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>https://icai.org.sg/events/recent-events?utm_source=chatgpt.com</t>
         </is>
@@ -13591,7 +13976,7 @@
           <t>Accounting / Finance</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>https://www.accaglobal.com/sg/en/member/cpd/events.html?utm_source=chatgpt.com</t>
         </is>
@@ -13611,7 +13996,7 @@
           <t>Legal / Tax</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>https://www.lawsociety.org.sg/cpd-events/?utm_source=chatgpt.com</t>
         </is>
@@ -13631,7 +14016,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>https://www.sal.org.sg/Events?utm_source=chatgpt.com</t>
         </is>
@@ -13651,7 +14036,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>https://www.sile.edu.sg/?utm_source=chatgpt.com</t>
         </is>
@@ -13671,7 +14056,7 @@
           <t>Legal / Arbitration</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>https://siac.org.sg/events?utm_source=chatgpt.com</t>
         </is>
@@ -13691,7 +14076,7 @@
           <t>Legal / Commercial Law</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>https://www.sicc.gov.sg/?utm_source=chatgpt.com</t>
         </is>
@@ -13711,7 +14096,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>https://www.scca.org.sg/events?utm_source=chatgpt.com</t>
         </is>
@@ -13731,7 +14116,7 @@
           <t>Governance / Finance</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>https://www.sid.org.sg/events?utm_source=chatgpt.com</t>
         </is>
@@ -13751,7 +14136,7 @@
           <t>Governance / Corporate</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>https://saicsa.org.sg/events/?utm_source=chatgpt.com</t>
         </is>
@@ -13771,7 +14156,7 @@
           <t>Finance / Investment</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>https://www.cfasocietysingapore.org/events?utm_source=chatgpt.com</t>
         </is>
@@ -13791,7 +14176,7 @@
           <t>Investment / Finance</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>https://imas.org.sg/events/?utm_source=chatgpt.com</t>
         </is>
@@ -13811,7 +14196,7 @@
           <t>Investment / Finance</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>https://sias.org.sg/events/?utm_source=chatgpt.com</t>
         </is>
@@ -13831,7 +14216,7 @@
           <t>Private Capital / Finance</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>https://svca.org.sg/events/?utm_source=chatgpt.com</t>
         </is>
@@ -13851,7 +14236,7 @@
           <t>FinTech / Finance</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>https://singaporefintech.org/events/?utm_source=chatgpt.com</t>
         </is>
@@ -13871,7 +14256,7 @@
           <t>Banking / Finance</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>https://www.abs.org.sg/events?utm_source=chatgpt.com</t>
         </is>
@@ -13891,7 +14276,7 @@
           <t>Finance / Actuarial</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>https://www.actuaries.org.sg/events/?utm_source=chatgpt.com</t>
         </is>
@@ -13911,7 +14296,7 @@
           <t>Insurance / Finance</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>https://www.sii.org.sg/events?utm_source=chatgpt.com</t>
         </is>
@@ -13931,7 +14316,7 @@
           <t>Financial Planning</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>https://www.fpas.org.sg/events/?utm_source=chatgpt.com</t>
         </is>
@@ -13951,7 +14336,7 @@
           <t>Accounting / Regulation</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>https://www.acra.gov.sg/news-events/event-highlights/?utm_source=chatgpt.com</t>
         </is>
@@ -13971,7 +14356,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>https://www.iras.gov.sg/?utm_source=chatgpt.com</t>
         </is>
@@ -13991,7 +14376,7 @@
           <t>Finance / Regulation</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>https://www.mas.gov.sg/news/events?utm_source=chatgpt.com</t>
         </is>
@@ -14011,7 +14396,7 @@
           <t>IP / Legal</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>https://www.ipos.gov.sg/events?utm_source=chatgpt.com</t>
         </is>
@@ -14031,7 +14416,7 @@
           <t>Tax / Finance / Policy</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>https://www.mof.gov.sg/news-publications/events?utm_source=chatgpt.com</t>
         </is>
@@ -14051,7 +14436,7 @@
           <t>Business / Finance</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>https://www.sbf.org.sg/events?utm_source=chatgpt.com</t>
         </is>
@@ -14071,7 +14456,7 @@
           <t>Business / Professional Services</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>https://sicc.com.sg/events/?utm_source=chatgpt.com</t>
         </is>
@@ -14091,7 +14476,7 @@
           <t>Business / Finance</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>https://www.sccci.org.sg/events/?utm_source=chatgpt.com</t>
         </is>
@@ -14111,7 +14496,7 @@
           <t>Business / Finance</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>https://asme.org.sg/events/?utm_source=chatgpt.com</t>
         </is>
@@ -14131,7 +14516,7 @@
           <t>Business / Finance</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>https://www.smfederation.org.sg/events/?utm_source=chatgpt.com</t>
         </is>
@@ -14151,7 +14536,7 @@
           <t>Business / Trade</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>https://www.sla.org.sg/events/?utm_source=chatgpt.com</t>
         </is>
@@ -14171,7 +14556,7 @@
           <t>Business / Investment</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>https://www.enterprisesg.gov.sg/events?utm_source=chatgpt.com</t>
         </is>
@@ -14191,7 +14576,7 @@
           <t>Investment / Business</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>https://www.edb.gov.sg/en/events.html?utm_source=chatgpt.com</t>
         </is>
@@ -14211,7 +14596,7 @@
           <t>Tax / Private Wealth</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>https://www.step.org/singapore/events?utm_source=chatgpt.com</t>
         </is>
@@ -14231,7 +14616,7 @@
           <t>International Tax</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>https://www.ifa.nl/events?utm_source=chatgpt.com</t>
         </is>
@@ -14251,7 +14636,7 @@
           <t>International Tax</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>https://www.taxacademy.sg/stari/?utm_source=chatgpt.com</t>
         </is>
@@ -14271,7 +14656,7 @@
           <t>Valuation / Finance</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>https://www.ivass.org.sg/events?utm_source=chatgpt.com</t>
         </is>
@@ -14291,7 +14676,7 @@
           <t>Legal / Arbitration</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>https://scma.org.sg/events/?utm_source=chatgpt.com</t>
         </is>
@@ -14311,7 +14696,7 @@
           <t>Legal / Dispute Resolution</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>https://www.smc.org.sg/events?utm_source=chatgpt.com</t>
         </is>
@@ -14331,7 +14716,7 @@
           <t>Legal / Arbitration</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>https://sicc.gov.sg/?utm_source=chatgpt.com</t>
         </is>
@@ -14351,7 +14736,7 @@
           <t>Technology / Professional</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>https://www.scs.org.sg/events?utm_source=chatgpt.com</t>
         </is>
@@ -14371,7 +14756,7 @@
           <t>Professional / Finance</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>https://www.sim.edu.sg/?utm_source=chatgpt.com</t>
         </is>
@@ -14391,7 +14776,7 @@
           <t>Professional / Employment Law</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>https://www.shri.org.sg/events?utm_source=chatgpt.com</t>
         </is>
@@ -14411,7 +14796,7 @@
           <t>Professional / Business</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>https://mis.org.sg/events/?utm_source=chatgpt.com</t>
         </is>
@@ -14431,7 +14816,7 @@
           <t>Business / Management</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>https://www.sipmm.edu.sg/events/?utm_source=chatgpt.com</t>
         </is>
@@ -14451,7 +14836,7 @@
           <t>Commercial / Legal</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="16" t="inlineStr">
         <is>
           <t>https://ccls.smu.edu.sg/events?utm_source=chatgpt.com</t>
         </is>
@@ -14471,7 +14856,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>https://law.smu.edu.sg/events?utm_source=chatgpt.com</t>
         </is>
@@ -14491,7 +14876,7 @@
           <t>Legal / Regulation / Finance</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="16" t="inlineStr">
         <is>
           <t>https://caidg.smu.edu.sg/events?utm_source=chatgpt.com</t>
         </is>
@@ -14511,7 +14896,7 @@
           <t>Treasury / Finance</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>https://act.org.sg/events/?utm_source=chatgpt.com</t>
         </is>
@@ -14531,7 +14916,7 @@
           <t>Risk Management</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>https://www.rimas.org.sg/?utm_source=chatgpt.com</t>
         </is>
@@ -14551,7 +14936,7 @@
           <t>Internal Audit / Governance</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>https://iia.org.sg/Home?utm_source=chatgpt.com</t>
         </is>
@@ -14571,7 +14956,7 @@
           <t>IT Audit / Governance / Risk</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="16" t="inlineStr">
         <is>
           <t>https://engage.isaca.org/singaporechapter/events?utm_source=chatgpt.com</t>
         </is>
@@ -14591,7 +14976,7 @@
           <t>Cybersecurity / Risk / Governance</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="16" t="inlineStr">
         <is>
           <t>https://www.isc2chapter.sg/events?utm_source=chatgpt.com</t>
         </is>
@@ -14611,7 +14996,7 @@
           <t>Legal / Arbitration</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="16" t="inlineStr">
         <is>
           <t>https://siarb.org.sg/?utm_source=chatgpt.com</t>
         </is>
@@ -14631,7 +15016,7 @@
           <t>Legal / Arbitration</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="16" t="inlineStr">
         <is>
           <t>https://ciarbsingapore.wildapricot.org/events?utm_source=chatgpt.com</t>
         </is>
@@ -14651,7 +15036,7 @@
           <t>Legal / Corporate Counsel</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="16" t="inlineStr">
         <is>
           <t>https://www.acc.com/webview/events?utm_source=chatgpt.com</t>
         </is>
@@ -14671,7 +15056,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="16" t="inlineStr">
         <is>
           <t>https://www.fwasg.org/events/Default.aspx?utm_source=chatgpt.com</t>
         </is>
@@ -14691,7 +15076,7 @@
           <t>Alternative Investments / Finance</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="16" t="inlineStr">
         <is>
           <t>https://caia.org/chapter-locations/caia-chapter-singapore/?utm_source=chatgpt.com</t>
         </is>
@@ -14711,7 +15096,7 @@
           <t>Derivatives / Finance / Legal</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="16" t="inlineStr">
         <is>
           <t>https://www.isda.org/location/singapore/?utm_source=chatgpt.com</t>
         </is>
@@ -14731,7 +15116,7 @@
           <t>Anti-Bribery / Compliance / Legal</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="16" t="inlineStr">
         <is>
           <t>https://www.traceinternational.org/events?utm_source=chatgpt.com</t>
         </is>
@@ -14751,7 +15136,7 @@
           <t>Governance / Risk / Compliance</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="16" t="inlineStr">
         <is>
           <t>https://members.agrc.org/events/event_list.asp?group=258545&amp;show=&amp;utm_source=chatgpt.com</t>
         </is>
@@ -14771,7 +15156,7 @@
           <t>Privacy / Legal / Compliance</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="16" t="inlineStr">
         <is>
           <t>https://iapp.org/events/?utm_source=chatgpt.com</t>
         </is>
@@ -14791,7 +15176,7 @@
           <t>Compliance / Financial Crime</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="16" t="inlineStr">
         <is>
           <t>https://www.int-comp.org/events/?utm_source=chatgpt.com</t>
         </is>
@@ -14811,7 +15196,7 @@
           <t>Fraud / Compliance / Finance</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="16" t="inlineStr">
         <is>
           <t>https://www.acfe.com/?utm_source=chatgpt.com</t>
         </is>
@@ -14831,7 +15216,7 @@
           <t>AML / Compliance / Finance</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" s="16" t="inlineStr">
         <is>
           <t>https://www.acams.org/en/events?utm_source=chatgpt.com</t>
         </is>
@@ -14851,7 +15236,7 @@
           <t>Corporate Governance / Investment</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="16" t="inlineStr">
         <is>
           <t>https://www.acga-asia.org/events.php?utm_source=chatgpt.com</t>
         </is>
@@ -14871,7 +15256,7 @@
           <t>Investment / Real Estate Finance</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" s="16" t="inlineStr">
         <is>
           <t>https://www.reitas.sg/events/upcoming-events/?utm_source=chatgpt.com</t>
         </is>
@@ -14891,7 +15276,7 @@
           <t>FinTech / Finance</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" s="16" t="inlineStr">
         <is>
           <t>https://singaporefintech.org/event/?utm_source=chatgpt.com</t>
         </is>
@@ -14911,7 +15296,7 @@
           <t>Banking / Finance</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="16" t="inlineStr">
         <is>
           <t>https://www.ibf.org.sg/?utm_source=chatgpt.com</t>
         </is>
@@ -14931,7 +15316,7 @@
           <t>Alternative Investments</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" s="16" t="inlineStr">
         <is>
           <t>https://www.aima.org/events/aima-conferences-information/aima-singapore-forum.html?utm_source=chatgpt.com</t>
         </is>
@@ -14951,7 +15336,7 @@
           <t>Risk Management</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>https://www.theirm.org/events/?utm_source=chatgpt.com</t>
         </is>
@@ -14971,7 +15356,7 @@
           <t>Treasury / Finance</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="16" t="inlineStr">
         <is>
           <t>https://www.treasurers.org/events-and-networking/upcoming-events/?utm_source=chatgpt.com</t>
         </is>
@@ -14991,7 +15376,7 @@
           <t>Legal / Arbitration</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" s="16" t="inlineStr">
         <is>
           <t>https://events2go.iccwbo.org/?utm_source=chatgpt.com</t>
         </is>
@@ -15011,7 +15396,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" s="16" t="inlineStr">
         <is>
           <t>https://www.ibanet.org/conferences-events?utm_source=chatgpt.com</t>
         </is>
@@ -15031,7 +15416,7 @@
           <t>International Tax</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" s="16" t="inlineStr">
         <is>
           <t>https://www.ifa.nl/events?utm_source=chatgpt.com</t>
         </is>
@@ -15051,7 +15436,7 @@
           <t>Tax / Trusts / Wealth</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" s="16" t="inlineStr">
         <is>
           <t>https://www.step.org/events?utm_source=chatgpt.com</t>
         </is>
@@ -15071,7 +15456,7 @@
           <t>International Tax</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D80" s="16" t="inlineStr">
         <is>
           <t>https://www.internationaltaxreview.com/events?utm_source=chatgpt.com</t>
         </is>
@@ -15091,7 +15476,7 @@
           <t>Tax / Legal</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" s="16" t="inlineStr">
         <is>
           <t>https://www.ibanet.org/conferences-events?utm_source=chatgpt.com</t>
         </is>
@@ -15111,7 +15496,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" s="16" t="inlineStr">
         <is>
           <t>https://www.aija.org/events/?utm_source=chatgpt.com</t>
         </is>
@@ -15131,7 +15516,7 @@
           <t>Legal / Business Law</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" s="16" t="inlineStr">
         <is>
           <t>https://www.ipba.org/events/?utm_source=chatgpt.com</t>
         </is>
@@ -15151,7 +15536,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" s="16" t="inlineStr">
         <is>
           <t>https://www.uianet.org/en/events?utm_source=chatgpt.com</t>
         </is>
@@ -15171,7 +15556,7 @@
           <t>Commercial / Legal</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" s="16" t="inlineStr">
         <is>
           <t>https://www.worldcc.com/Events?utm_source=chatgpt.com</t>
         </is>
@@ -15191,7 +15576,7 @@
           <t>Procurement / Finance</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" s="16" t="inlineStr">
         <is>
           <t>https://www.cips.org/events?utm_source=chatgpt.com</t>
         </is>
@@ -15211,7 +15596,7 @@
           <t>Procurement / Business</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" s="16" t="inlineStr">
         <is>
           <t>https://www.ismworld.org/events/?utm_source=chatgpt.com</t>
         </is>
@@ -15231,7 +15616,7 @@
           <t>Treasury / Finance</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" s="16" t="inlineStr">
         <is>
           <t>https://www.afponline.org/events?utm_source=chatgpt.com</t>
         </is>
@@ -15251,7 +15636,7 @@
           <t>Risk / Finance</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" s="16" t="inlineStr">
         <is>
           <t>https://www.garp.org/events?utm_source=chatgpt.com</t>
         </is>
@@ -15271,7 +15656,7 @@
           <t>Risk / Finance</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D90" s="16" t="inlineStr">
         <is>
           <t>https://www.prmia.org/events?utm_source=chatgpt.com</t>
         </is>
@@ -15291,7 +15676,7 @@
           <t>Compliance / Governance</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D91" s="16" t="inlineStr">
         <is>
           <t>https://www.gacp.org/events?utm_source=chatgpt.com</t>
         </is>
@@ -15311,7 +15696,7 @@
           <t>Financial Crime / Compliance</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D92" s="16" t="inlineStr">
         <is>
           <t>https://www.acfcs.org/events?utm_source=chatgpt.com</t>
         </is>
@@ -15331,7 +15716,7 @@
           <t>Insurance / Regulation</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D93" s="16" t="inlineStr">
         <is>
           <t>https://www.iais.org/activities-meetings/?utm_source=chatgpt.com</t>
         </is>
@@ -15351,7 +15736,7 @@
           <t>Securities / Regulation</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D94" s="16" t="inlineStr">
         <is>
           <t>https://www.iosco.org/events/?utm_source=chatgpt.com</t>
         </is>
@@ -15371,7 +15756,7 @@
           <t>Insurance / Finance</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D95" s="16" t="inlineStr">
         <is>
           <t>https://www.internationalinsuranceprofessionals.org/events?utm_source=chatgpt.com</t>
         </is>
@@ -15391,7 +15776,7 @@
           <t>Reporting / Finance / ESG</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D96" s="16" t="inlineStr">
         <is>
           <t>https://www.globalreporting.org/events/?utm_source=chatgpt.com</t>
         </is>
@@ -15411,7 +15796,7 @@
           <t>Reporting / Finance</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D97" s="16" t="inlineStr">
         <is>
           <t>https://www.ifrs.org/news-and-events/events/?utm_source=chatgpt.com</t>
         </is>
@@ -15431,7 +15816,7 @@
           <t>Finance / Reporting</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D98" s="16" t="inlineStr">
         <is>
           <t>https://www.ifrs.org/news-and-events/events/?utm_source=chatgpt.com</t>
         </is>
@@ -15451,7 +15836,7 @@
           <t>Economics / Finance / Business</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D99" s="16" t="inlineStr">
         <is>
           <t>https://www.weforum.org/events/?utm_source=chatgpt.com</t>
         </is>
@@ -15471,7 +15856,7 @@
           <t>International Law / Trade</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D100" s="16" t="inlineStr">
         <is>
           <t>https://uncitral.un.org/en/events?utm_source=chatgpt.com</t>
         </is>
@@ -15491,7 +15876,7 @@
           <t>Fund Finance / Legal / Finance</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D101" s="16" t="inlineStr">
         <is>
           <t>https://fundfinanceassociation.com/events/apac/11-04-26-asia-pacific-symposium/</t>
         </is>
@@ -15511,7 +15896,7 @@
           <t>Legal Finance / Litigation Finance</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D102" s="16" t="inlineStr">
         <is>
           <t>https://litfincon.com/asia/</t>
         </is>
@@ -15531,7 +15916,7 @@
           <t>Legal / Tax / Risk</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D103" s="16" t="inlineStr">
         <is>
           <t>https://www.thomsonreuters.com.sg/en-sg/events.html</t>
         </is>
@@ -15551,7 +15936,7 @@
           <t>Commercial Law</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D104" s="16" t="inlineStr">
         <is>
           <t>https://ccla.smu.edu.sg/events</t>
         </is>
@@ -15571,7 +15956,7 @@
           <t>Legal / Regulation / Governance</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D105" s="16" t="inlineStr">
         <is>
           <t>https://caidg.smu.edu.sg/events</t>
         </is>
@@ -15591,7 +15976,7 @@
           <t>Commercial Law</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D106" s="16" t="inlineStr">
         <is>
           <t>https://law.smu.edu.sg/research/centres/centre-cross-border-commercial-law-asia</t>
         </is>
@@ -15611,7 +15996,7 @@
           <t>Law / Economics</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D107" s="16" t="inlineStr">
         <is>
           <t>https://ccla.smu.edu.sg/events/past-events</t>
         </is>
@@ -15631,7 +16016,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D108" s="16" t="inlineStr">
         <is>
           <t>https://law.smu.edu.sg/events</t>
         </is>
@@ -15651,7 +16036,7 @@
           <t>AI / Legal / Regulation</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D109" s="16" t="inlineStr">
         <is>
           <t>https://caidg.smu.edu.sg/events</t>
         </is>
@@ -15671,7 +16056,7 @@
           <t>Finance / Entrepreneurship</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D110" s="16" t="inlineStr">
         <is>
           <t>https://iie.smu.edu.sg/events</t>
         </is>
@@ -15691,7 +16076,7 @@
           <t>Finance / Economics</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D111" s="16" t="inlineStr">
         <is>
           <t>https://skbi.smu.edu.sg/events</t>
         </is>
@@ -15711,7 +16096,7 @@
           <t>Sustainable Finance</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D112" s="16" t="inlineStr">
         <is>
           <t>https://business.smu.edu.sg/centres/centre-sustainable-finance</t>
         </is>
@@ -15731,7 +16116,7 @@
           <t>Banking / Finance</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D113" s="16" t="inlineStr">
         <is>
           <t>https://bschool.nus.edu.sg/cbfl/</t>
         </is>
@@ -15751,7 +16136,7 @@
           <t>International Law</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D114" s="16" t="inlineStr">
         <is>
           <t>https://cil.nus.edu.sg/events/</t>
         </is>
@@ -15771,7 +16156,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D115" s="16" t="inlineStr">
         <is>
           <t>https://law.nus.edu.sg/events/</t>
         </is>
@@ -15791,7 +16176,7 @@
           <t>Finance / Business</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D116" s="16" t="inlineStr">
         <is>
           <t>https://bschool.nus.edu.sg/events/</t>
         </is>
@@ -15811,7 +16196,7 @@
           <t>Risk / Finance</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D117" s="16" t="inlineStr">
         <is>
           <t>https://rmi.nus.edu.sg/events/</t>
         </is>
@@ -15831,7 +16216,7 @@
           <t>Real Estate / Finance</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D118" s="16" t="inlineStr">
         <is>
           <t>https://ireus.nus.edu.sg/events/</t>
         </is>
@@ -15851,7 +16236,7 @@
           <t>Sustainable Finance</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D119" s="16" t="inlineStr">
         <is>
           <t>https://sfi.nus.edu.sg/events/</t>
         </is>
@@ -15871,7 +16256,7 @@
           <t>Finance / Business</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D120" s="16" t="inlineStr">
         <is>
           <t>https://www.ntu.edu.sg/business/events</t>
         </is>
@@ -15891,7 +16276,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D121" s="16" t="inlineStr">
         <is>
           <t>https://www.ntu.edu.sg/business/research/centres/cafs</t>
         </is>
@@ -15911,7 +16296,7 @@
           <t>Banking / Finance</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D122" s="16" t="inlineStr">
         <is>
           <t>https://www.ntu.edu.sg/business/research/centres</t>
         </is>
@@ -15931,7 +16316,7 @@
           <t>Finance / Business</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D123" s="16" t="inlineStr">
         <is>
           <t>https://www.suss.edu.sg/events</t>
         </is>
@@ -15951,7 +16336,7 @@
           <t>Business / Legal</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D124" s="16" t="inlineStr">
         <is>
           <t>https://www.sutd.edu.sg/events/</t>
         </is>
@@ -15971,7 +16356,7 @@
           <t>Business / Finance</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D125" s="16" t="inlineStr">
         <is>
           <t>https://www.singaporetech.edu.sg/events</t>
         </is>
@@ -15991,7 +16376,7 @@
           <t>Governance / Regulation</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="D126" s="16" t="inlineStr">
         <is>
           <t>https://scles.nus.edu.sg/events/</t>
         </is>
@@ -16011,7 +16396,7 @@
           <t>Maritime / Commercial Law</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D127" s="16" t="inlineStr">
         <is>
           <t>https://law.nus.edu.sg/cml/</t>
         </is>
@@ -16031,7 +16416,7 @@
           <t>Commercial Law / Business</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D128" s="16" t="inlineStr">
         <is>
           <t>https://law.nus.edu.sg/ewbclb/</t>
         </is>
@@ -16051,7 +16436,7 @@
           <t>Asian / International Law</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D129" s="16" t="inlineStr">
         <is>
           <t>https://law.nus.edu.sg/asli/</t>
         </is>
@@ -16071,7 +16456,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D130" s="16" t="inlineStr">
         <is>
           <t>https://law.nus.edu.sg/cals/</t>
         </is>
@@ -16091,7 +16476,7 @@
           <t>Banking / Finance / Legal</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D131" s="16" t="inlineStr">
         <is>
           <t>https://law.nus.edu.sg/cbfl/</t>
         </is>
@@ -16111,7 +16496,7 @@
           <t>International Investment Law</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D132" s="16" t="inlineStr">
         <is>
           <t>https://cil.nus.edu.sg/events/</t>
         </is>
@@ -16131,7 +16516,7 @@
           <t>Sustainable Finance</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D133" s="16" t="inlineStr">
         <is>
           <t>https://www.singaporegreenfinance.sg/events</t>
         </is>
@@ -16151,7 +16536,7 @@
           <t>Digital Finance / FinTech</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="D134" s="16" t="inlineStr">
         <is>
           <t>https://nus.edu.sg/aidf/events</t>
         </is>
@@ -16171,7 +16556,7 @@
           <t>FinTech / Finance</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D135" s="16" t="inlineStr">
         <is>
           <t>https://fintechlab.nus.edu.sg/events/</t>
         </is>
@@ -16191,7 +16576,7 @@
           <t>Data / Finance / Risk</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="D136" s="16" t="inlineStr">
         <is>
           <t>https://www.sdsconsortium.sg/events</t>
         </is>
@@ -16211,7 +16596,7 @@
           <t>Technology / Regulation</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D137" s="16" t="inlineStr">
         <is>
           <t>https://www.weforum.org/centres/centre-for-the-fourth-industrial-revolution-singapore/</t>
         </is>
@@ -16231,7 +16616,7 @@
           <t>Energy / Finance / Policy</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="D138" s="16" t="inlineStr">
         <is>
           <t>https://www.siew.gov.sg/events</t>
         </is>
@@ -16251,7 +16636,7 @@
           <t>Infrastructure / Finance / Policy</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D139" s="16" t="inlineStr">
         <is>
           <t>https://www.sitce.org.sg/</t>
         </is>
@@ -16271,7 +16656,7 @@
           <t>Maritime / Finance / Legal</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="D140" s="16" t="inlineStr">
         <is>
           <t>https://www.smw.sg/</t>
         </is>
@@ -16291,7 +16676,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D141" s="16" t="inlineStr">
         <is>
           <t>https://www.sicc.gov.sg/</t>
         </is>
@@ -16311,7 +16696,7 @@
           <t>Maritime Arbitration / Legal</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D142" s="16" t="inlineStr">
         <is>
           <t>https://scma.org.sg/events/</t>
         </is>
@@ -16331,7 +16716,7 @@
           <t>Arbitration / Legal</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D143" s="16" t="inlineStr">
         <is>
           <t>https://siarb.org.sg/events/</t>
         </is>
@@ -16351,7 +16736,7 @@
           <t>Mediation / Legal</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="D144" s="16" t="inlineStr">
         <is>
           <t>https://simimediators.org/events/</t>
         </is>
@@ -16371,7 +16756,7 @@
           <t>Dispute Resolution / Legal</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D145" s="16" t="inlineStr">
         <is>
           <t>https://sidra.smu.edu.sg/events</t>
         </is>
@@ -16391,7 +16776,7 @@
           <t>Mediation / Legal</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="D146" s="16" t="inlineStr">
         <is>
           <t>https://www.smc.org.sg/events</t>
         </is>
@@ -16411,7 +16796,7 @@
           <t>Arbitration / Legal</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="D147" s="16" t="inlineStr">
         <is>
           <t>https://scma.org.sg/events/</t>
         </is>
@@ -16431,7 +16816,7 @@
           <t>Legal Education</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="D148" s="16" t="inlineStr">
         <is>
           <t>https://www.sile.edu.sg/</t>
         </is>
@@ -16451,7 +16836,7 @@
           <t>Corporate Legal</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="D149" s="16" t="inlineStr">
         <is>
           <t>https://www.scca.org.sg/events</t>
         </is>
@@ -16471,7 +16856,7 @@
           <t>Finance / Financial Services</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D150" s="16" t="inlineStr">
         <is>
           <t>https://www.finsia.com/events</t>
         </is>
@@ -16491,7 +16876,7 @@
           <t>Business / Finance</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D151" s="16" t="inlineStr">
         <is>
           <t>https://www.sccci.org.sg/events/</t>
         </is>
@@ -16511,7 +16896,7 @@
           <t>Business / Finance</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
+      <c r="D152" s="16" t="inlineStr">
         <is>
           <t>https://www.scal.com.sg/events/</t>
         </is>
@@ -16531,7 +16916,7 @@
           <t>Business / Trade</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
+      <c r="D153" s="16" t="inlineStr">
         <is>
           <t>https://www.singaporefurniture.com/events/</t>
         </is>
@@ -16551,7 +16936,7 @@
           <t>Business / Finance</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
+      <c r="D154" s="16" t="inlineStr">
         <is>
           <t>https://www.sra.org.sg/events/</t>
         </is>
@@ -16571,7 +16956,7 @@
           <t>Business / Finance</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
+      <c r="D155" s="16" t="inlineStr">
         <is>
           <t>https://sha.org.sg/events/</t>
         </is>
@@ -16591,7 +16976,7 @@
           <t>Maritime / Finance / Legal</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
+      <c r="D156" s="16" t="inlineStr">
         <is>
           <t>https://www.ssa.org.sg/events/</t>
         </is>
@@ -16611,7 +16996,7 @@
           <t>Maritime / Finance / Policy</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
+      <c r="D157" s="16" t="inlineStr">
         <is>
           <t>https://www.smi-ntu.sg/events/</t>
         </is>
@@ -16631,7 +17016,7 @@
           <t>Maritime / Arbitration</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
+      <c r="D158" s="16" t="inlineStr">
         <is>
           <t>https://scma.org.sg/events/</t>
         </is>
@@ -16651,7 +17036,7 @@
           <t>Maritime / Business</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="D159" s="16" t="inlineStr">
         <is>
           <t>https://www.smf.com.sg/events/</t>
         </is>
@@ -16671,7 +17056,7 @@
           <t>Maritime / Business</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="D160" s="16" t="inlineStr">
         <is>
           <t>https://www.ssa.org.sg/events/</t>
         </is>
@@ -16691,7 +17076,7 @@
           <t>International / Business</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="D161" s="16" t="inlineStr">
         <is>
           <t>https://www.sif.org.sg/events</t>
         </is>
@@ -16711,7 +17096,7 @@
           <t>International / Finance / Policy</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
+      <c r="D162" s="16" t="inlineStr">
         <is>
           <t>https://scp.gov.sg/</t>
         </is>
@@ -16731,7 +17116,7 @@
           <t>Economics / Finance</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D163" s="16" t="inlineStr">
         <is>
           <t>https://ses.org.sg/events/</t>
         </is>
@@ -16751,7 +17136,7 @@
           <t>Economics / Finance</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D164" s="16" t="inlineStr">
         <is>
           <t>https://ses.org.sg/events/</t>
         </is>
@@ -16771,7 +17156,7 @@
           <t>Statistics / Economics</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
+      <c r="D165" s="16" t="inlineStr">
         <is>
           <t>https://www.singstat.gov.sg/whats-new/events</t>
         </is>
@@ -16791,7 +17176,7 @@
           <t>Business / Employment / Policy</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
+      <c r="D166" s="16" t="inlineStr">
         <is>
           <t>https://snef.org.sg/events/</t>
         </is>
@@ -16811,7 +17196,7 @@
           <t>Employment / Business Law</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="D167" s="16" t="inlineStr">
         <is>
           <t>https://www.shri.org.sg/events</t>
         </is>
@@ -16831,7 +17216,7 @@
           <t>Employment / Legal</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr">
+      <c r="D168" s="16" t="inlineStr">
         <is>
           <t>https://www.tadm.sg/</t>
         </is>
@@ -16851,7 +17236,7 @@
           <t>Employment / Regulation</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr">
+      <c r="D169" s="16" t="inlineStr">
         <is>
           <t>https://www.tafep.sg/events</t>
         </is>
@@ -16871,7 +17256,7 @@
           <t>Employment / Legal</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr">
+      <c r="D170" s="16" t="inlineStr">
         <is>
           <t>https://www.tafep.sg/events</t>
         </is>
@@ -16891,7 +17276,7 @@
           <t>HR / Employment</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
+      <c r="D171" s="16" t="inlineStr">
         <is>
           <t>https://www.sihrp.org/events</t>
         </is>
@@ -16911,7 +17296,7 @@
           <t>Professional / Business</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
+      <c r="D172" s="16" t="inlineStr">
         <is>
           <t>https://www.spc.org.sg/events</t>
         </is>
@@ -16931,7 +17316,7 @@
           <t>Business / Professional Education</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
+      <c r="D173" s="16" t="inlineStr">
         <is>
           <t>https://www.sim.edu.sg/events</t>
         </is>
@@ -16951,7 +17336,7 @@
           <t>Business / Finance</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
+      <c r="D174" s="16" t="inlineStr">
         <is>
           <t>https://bpw-singapore.org/events/</t>
         </is>
@@ -16971,7 +17356,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
+      <c r="D175" s="16" t="inlineStr">
         <is>
           <t>https://www.fwasg.org/events/</t>
         </is>
@@ -16991,7 +17376,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
+      <c r="D176" s="16" t="inlineStr">
         <is>
           <t>https://womeninfinanceasia.com/events/</t>
         </is>
@@ -17011,7 +17396,7 @@
           <t>Payments / Finance</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
+      <c r="D177" s="16" t="inlineStr">
         <is>
           <t>https://womeninpayments.org/events/</t>
         </is>
@@ -17031,7 +17416,7 @@
           <t>Payments / Finance</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="D178" s="16" t="inlineStr">
         <is>
           <t>https://www.singaporepayments.org/events</t>
         </is>
@@ -17051,7 +17436,7 @@
           <t>Payments / FinTech</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
+      <c r="D179" s="16" t="inlineStr">
         <is>
           <t>https://emergingpayments.org/events/</t>
         </is>
@@ -17071,7 +17456,7 @@
           <t>FinTech / Finance</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="D180" s="16" t="inlineStr">
         <is>
           <t>https://www.singaporefintechfestival.com/</t>
         </is>
@@ -17091,7 +17476,7 @@
           <t>Technology / Finance</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
+      <c r="D181" s="16" t="inlineStr">
         <is>
           <t>https://www.switchsg.org/</t>
         </is>
@@ -17111,7 +17496,7 @@
           <t>Cybersecurity / Risk</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="D182" s="16" t="inlineStr">
         <is>
           <t>https://www.sicw.gov.sg/</t>
         </is>
@@ -17131,7 +17516,7 @@
           <t>Cybersecurity / Risk</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
+      <c r="D183" s="16" t="inlineStr">
         <is>
           <t>https://www.aisp.sg/events</t>
         </is>
@@ -17151,7 +17536,7 @@
           <t>Technology / Professional</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
+      <c r="D184" s="16" t="inlineStr">
         <is>
           <t>https://www.scs.org.sg/events</t>
         </is>
@@ -17171,7 +17556,7 @@
           <t>Technology / Business</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
+      <c r="D185" s="16" t="inlineStr">
         <is>
           <t>https://sitf.org.sg/events/</t>
         </is>
@@ -17191,7 +17576,7 @@
           <t>Technology / Finance</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
+      <c r="D186" s="16" t="inlineStr">
         <is>
           <t>https://www.asiacloudcomputing.org/events</t>
         </is>
@@ -17211,7 +17596,7 @@
           <t>Technology / Business</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
+      <c r="D187" s="16" t="inlineStr">
         <is>
           <t>https://www.sgtech.org.sg/events</t>
         </is>
@@ -17231,7 +17616,7 @@
           <t>Digital Business / Finance</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr">
+      <c r="D188" s="16" t="inlineStr">
         <is>
           <t>https://www.sdcc.sg/events</t>
         </is>
@@ -17251,7 +17636,7 @@
           <t>Blockchain / Finance</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr">
+      <c r="D189" s="16" t="inlineStr">
         <is>
           <t>https://www.singaporeblockchain.org/events</t>
         </is>
@@ -17271,7 +17656,7 @@
           <t>Blockchain / Finance</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
+      <c r="D190" s="16" t="inlineStr">
         <is>
           <t>https://www.bas.sg/events</t>
         </is>
@@ -17291,7 +17676,7 @@
           <t>Digital Assets / Finance</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
+      <c r="D191" s="16" t="inlineStr">
         <is>
           <t>https://www.access.org.sg/events</t>
         </is>
@@ -17311,7 +17696,7 @@
           <t>FinTech / Finance</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr">
+      <c r="D192" s="16" t="inlineStr">
         <is>
           <t>https://singaporefintech.org/events/</t>
         </is>
@@ -17331,7 +17716,7 @@
           <t>Payments / Finance</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
+      <c r="D193" s="16" t="inlineStr">
         <is>
           <t>https://singaporefintech.org/events/</t>
         </is>
@@ -17351,7 +17736,7 @@
           <t>Regulation / FinTech</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
+      <c r="D194" s="16" t="inlineStr">
         <is>
           <t>https://singaporefintech.org/events/</t>
         </is>
@@ -17371,7 +17756,7 @@
           <t>Insurance / FinTech</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
+      <c r="D195" s="16" t="inlineStr">
         <is>
           <t>https://singaporefintech.org/events/</t>
         </is>
@@ -17391,7 +17776,7 @@
           <t>Wealth / Finance</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
+      <c r="D196" s="16" t="inlineStr">
         <is>
           <t>https://singaporefintech.org/events/</t>
         </is>
@@ -17411,7 +17796,7 @@
           <t>Blockchain / Finance</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
+      <c r="D197" s="16" t="inlineStr">
         <is>
           <t>https://singaporefintech.org/events/</t>
         </is>
@@ -17431,7 +17816,7 @@
           <t>AI / Finance</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
+      <c r="D198" s="16" t="inlineStr">
         <is>
           <t>https://singaporefintech.org/events/</t>
         </is>
@@ -17451,7 +17836,7 @@
           <t>Sustainable Finance</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
+      <c r="D199" s="16" t="inlineStr">
         <is>
           <t>https://singaporefintech.org/events/</t>
         </is>
@@ -17471,7 +17856,7 @@
           <t>Cybersecurity / Finance</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
+      <c r="D200" s="16" t="inlineStr">
         <is>
           <t>https://singaporefintech.org/events/</t>
         </is>
@@ -17479,6 +17864,207 @@
     </row>
     <row r="201" ht="57.6" customHeight="1"/>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId199"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -17528,7 +18114,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>https://tax.gov.ae/en/media.centre/events.aspx</t>
         </is>
@@ -17548,7 +18134,7 @@
           <t>Tax / Compliance</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>https://taxationsociety.org/events-conferences/</t>
         </is>
@@ -17568,7 +18154,7 @@
           <t>Accounting / Tax / Finance</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>https://www.icaidubai.org/events</t>
         </is>
@@ -17588,7 +18174,7 @@
           <t>Accounting / Audit</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>https://aaa4uae.ae/site/en/training-manual</t>
         </is>
@@ -17608,7 +18194,7 @@
           <t>Accounting / Finance</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>https://picpadubai.org/events/list/</t>
         </is>
@@ -17628,7 +18214,7 @@
           <t>Accounting / Finance</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>https://imamiddleast.org/en/events/</t>
         </is>
@@ -17648,7 +18234,7 @@
           <t>Internal Audit / Risk</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>https://uaeiaa.org/events-calendar</t>
         </is>
@@ -17668,7 +18254,7 @@
           <t>Finance / Investment</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>https://www.cfasociety.org/emirates/events/calendar</t>
         </is>
@@ -17688,7 +18274,7 @@
           <t>IT Audit / Risk / Compliance</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>https://engage.isaca.org/uaechapter/events/calendar</t>
         </is>
@@ -17708,7 +18294,7 @@
           <t>Business / Finance</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>https://www.dbwc.ae/event/calendar</t>
         </is>
@@ -17728,7 +18314,7 @@
           <t>Business / Trade / Finance</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>https://www.dubaichamber.com/en/events</t>
         </is>
@@ -17748,7 +18334,7 @@
           <t>Business / Trade / Finance</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>https://www.abudhabichamber.ae/en/events</t>
         </is>
@@ -17768,7 +18354,7 @@
           <t>Business / Trade</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>https://www.sharjah.gov.ae/en/media-center/events</t>
         </is>
@@ -17788,7 +18374,7 @@
           <t>Trade / Finance / Arbitration</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>https://iccuae.ae/events-and-trainings/</t>
         </is>
@@ -17808,7 +18394,7 @@
           <t>Business / Trade / Finance</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>https://www.uaesbc.com/event-list</t>
         </is>
@@ -17828,7 +18414,7 @@
           <t>Business / Trade / Finance</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>https://www.nlbcuae.com/events</t>
         </is>
@@ -17848,7 +18434,7 @@
           <t>Business / Finance / Trade</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>https://www.fbcuae.fi/events</t>
         </is>
@@ -17868,7 +18454,7 @@
           <t>Business / Trade / Finance</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>https://austrianbc.ae/events/</t>
         </is>
@@ -17888,7 +18474,7 @@
           <t>Business / Investment / Finance</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>https://usuaebusiness.org/events_category/upcoming-events/</t>
         </is>
@@ -17908,7 +18494,7 @@
           <t>Banking / Finance</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>https://eif.gov.ae/events/</t>
         </is>
@@ -17928,7 +18514,7 @@
           <t>Banking / Finance</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>https://ubf.ae/en/events</t>
         </is>
@@ -17948,7 +18534,7 @@
           <t>Legal / Judicial</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>https://www.eall.org.ae/en/</t>
         </is>
@@ -17968,7 +18554,7 @@
           <t>Legal / Finance / Compliance</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>https://academy.difc.ae/school-of-law?category=Events</t>
         </is>
@@ -17988,7 +18574,7 @@
           <t>Arbitration / Legal</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>https://www.diac.com/en/events/</t>
         </is>
@@ -18008,7 +18594,7 @@
           <t>Finance / Legal / Regulation</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>https://www.adgm.com/events</t>
         </is>
@@ -18028,7 +18614,7 @@
           <t>Financial Regulation</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>https://www.dfsa.ae/events</t>
         </is>
@@ -18048,7 +18634,7 @@
           <t>Securities / Finance</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>https://www.sca.gov.ae/en/media-center/events.aspx</t>
         </is>
@@ -18068,7 +18654,7 @@
           <t>Tax / Finance</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>https://mof.gov.ae/en/media-center/events-and-activities/</t>
         </is>
@@ -18088,7 +18674,7 @@
           <t>Business / Finance / Trade</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>https://www.dwtc.com/en/events/</t>
         </is>
@@ -18108,7 +18694,7 @@
           <t>Business / Finance / Trade</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>https://www.investindubai.gov.ae/events-calendar</t>
         </is>
@@ -18128,7 +18714,7 @@
           <t>Business / Finance / Trade</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>https://britishchamberdubai.com/events</t>
         </is>
@@ -18148,7 +18734,7 @@
           <t>Business / Finance / Trade</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>https://www.cbc-dubai.com/upcoming-events</t>
         </is>
@@ -18168,7 +18754,7 @@
           <t>Business / Finance / Trade</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>https://www.abcduae.com/community-and-business-events</t>
         </is>
@@ -18188,7 +18774,7 @@
           <t>Business / Trade / Investment</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>https://www.spanishbusinesscouncil.ae/events/</t>
         </is>
@@ -18208,7 +18794,7 @@
           <t>Business / Finance / Trade</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>https://www.swissbcuae.com/events/</t>
         </is>
@@ -18228,7 +18814,7 @@
           <t>Business / Finance / Trade</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>https://www.bbc-uae.com/events</t>
         </is>
@@ -18248,7 +18834,7 @@
           <t>Business / Trade / Finance</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>https://sabco-uae.org/event/</t>
         </is>
@@ -18268,7 +18854,7 @@
           <t>Business / Trade / Finance</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>https://bgbc.ae/events/</t>
         </is>
@@ -18288,7 +18874,7 @@
           <t>Accounting / Finance / Tax</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>https://acamind.ae/events/</t>
         </is>
@@ -18308,7 +18894,7 @@
           <t>Treasury / Finance</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>https://www.treasurers.org/events-and-networking/upcoming-events/</t>
         </is>
@@ -18328,7 +18914,7 @@
           <t>Governance / Risk / Compliance</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>https://members.agrc.org/events/event_list.asp</t>
         </is>
@@ -18348,7 +18934,7 @@
           <t>Legal / Compliance</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>https://www.lexis.ae/training-events-2/</t>
         </is>
@@ -18368,7 +18954,7 @@
           <t>Legal / Dispute Resolution</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>https://lawhouse.ae/events/</t>
         </is>
@@ -18388,7 +18974,7 @@
           <t>Legal / Arbitration</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>https://ucl.ae/events/</t>
         </is>
@@ -18408,7 +18994,7 @@
           <t>Tax / Finance / Compliance</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>https://taxexpertsclub.ae/events/</t>
         </is>
@@ -18428,7 +19014,7 @@
           <t>Finance / Capital Markets</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>https://www.uaefma.org/events/</t>
         </is>
@@ -18448,7 +19034,7 @@
           <t>Finance / Investment</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>https://www.cfainstitute.org/societies/directory/middle-east</t>
         </is>
@@ -18468,7 +19054,7 @@
           <t>Finance / Investment</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="16" t="inlineStr">
         <is>
           <t>https://www.cisi.org/cisiweb2/events</t>
         </is>
@@ -18488,7 +19074,7 @@
           <t>Risk / Finance</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>https://www.garp.org/events</t>
         </is>
@@ -18508,7 +19094,7 @@
           <t>Risk / Compliance / Finance</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="16" t="inlineStr">
         <is>
           <t>https://www.theirm.org/events/</t>
         </is>
@@ -18528,7 +19114,7 @@
           <t>Accounting / Audit</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>https://www.aopauae.com/events?utm_source=chatgpt.com</t>
         </is>
@@ -18548,7 +19134,7 @@
           <t>Accounting / Audit</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>https://mail.aaa4uae.ae/site/en/eaaa?utm_source=chatgpt.com</t>
         </is>
@@ -18568,7 +19154,7 @@
           <t>Risk / Finance</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>https://www.garp.org/membership/chapter/united-arab-emirates?utm_source=chatgpt.com</t>
         </is>
@@ -18588,7 +19174,7 @@
           <t>Fraud / Audit / Compliance</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="16" t="inlineStr">
         <is>
           <t>https://www.acfe.com/calendar?utm_source=chatgpt.com</t>
         </is>
@@ -18608,7 +19194,7 @@
           <t>Banking / Finance</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="16" t="inlineStr">
         <is>
           <t>https://slba.ae/events/?utm_source=chatgpt.com</t>
         </is>
@@ -18628,7 +19214,7 @@
           <t>Finance / Banking / Law</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="16" t="inlineStr">
         <is>
           <t>https://academy.adgm.com/events/?utm_source=chatgpt.com</t>
         </is>
@@ -18648,7 +19234,7 @@
           <t>Business / Trade</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="16" t="inlineStr">
         <is>
           <t>https://ajmanchamber.ae/en/archives/exhibitions-conferences/?utm_source=chatgpt.com</t>
         </is>
@@ -18668,7 +19254,7 @@
           <t>Business / Trade</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="16" t="inlineStr">
         <is>
           <t>https://rakchamber.ae/?utm_source=chatgpt.com</t>
         </is>
@@ -18688,7 +19274,7 @@
           <t>Business / Trade</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="16" t="inlineStr">
         <is>
           <t>https://www.fujairahchamber.ae/?utm_source=chatgpt.com</t>
         </is>
@@ -18708,7 +19294,7 @@
           <t>Business / Trade</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="16" t="inlineStr">
         <is>
           <t>https://uaqchamber.ae/?utm_source=chatgpt.com</t>
         </is>
@@ -18728,7 +19314,7 @@
           <t>Business / Trade</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="16" t="inlineStr">
         <is>
           <t>https://www.irishbusinessnetwork.org/events/?utm_source=chatgpt.com</t>
         </is>
@@ -18748,7 +19334,7 @@
           <t>Business / Trade / Compliance</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="16" t="inlineStr">
         <is>
           <t>https://www.sbcuae.se/events?utm_source=chatgpt.com</t>
         </is>
@@ -18768,7 +19354,7 @@
           <t>Business / Trade / Finance</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="16" t="inlineStr">
         <is>
           <t>https://www.bbc-uae.com/events?utm_source=chatgpt.com</t>
         </is>
@@ -18788,7 +19374,7 @@
           <t>Business / Trade / Investment</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="16" t="inlineStr">
         <is>
           <t>https://www.sbcuae.org/events?utm_source=chatgpt.com</t>
         </is>
@@ -18808,7 +19394,7 @@
           <t>Arbitration / Legal</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="16" t="inlineStr">
         <is>
           <t>https://www.diac.com/en/events/?utm_source=chatgpt.com</t>
         </is>
@@ -18828,7 +19414,7 @@
           <t>Legal / Judicial</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="16" t="inlineStr">
         <is>
           <t>https://www.adjd.gov.ae/EN/Pages/Events.aspx?utm_source=chatgpt.com</t>
         </is>
@@ -18848,7 +19434,7 @@
           <t>Legal / Regulation</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" s="16" t="inlineStr">
         <is>
           <t>https://www.dld.gov.ae/?utm_source=chatgpt.com</t>
         </is>
@@ -18868,7 +19454,7 @@
           <t>Legal / Compliance</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="16" t="inlineStr">
         <is>
           <t>https://www.emirateslegalnetwork.com/events?utm_source=chatgpt.com</t>
         </is>
@@ -18888,7 +19474,7 @@
           <t>Legal / Tax / Compliance</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" s="16" t="inlineStr">
         <is>
           <t>https://cms.law/en/are/events?utm_source=chatgpt.com</t>
         </is>
@@ -18908,7 +19494,7 @@
           <t>Tax / Legal / Risk</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" s="16" t="inlineStr">
         <is>
           <t>https://mena.thomsonreuters.com/en/events.html?utm_source=chatgpt.com</t>
         </is>
@@ -18928,7 +19514,7 @@
           <t>Audit / Tax / Advisory</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="16" t="inlineStr">
         <is>
           <t>https://www.bakertilly.ae/events?utm_source=chatgpt.com</t>
         </is>
@@ -18948,7 +19534,7 @@
           <t>Audit / Tax / Advisory</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" s="16" t="inlineStr">
         <is>
           <t>https://www.grantthornton.ae/events/?utm_source=chatgpt.com</t>
         </is>
@@ -18968,7 +19554,7 @@
           <t>Audit / Tax / Risk / Advisory</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>https://www.crowe.com/ae/events?utm_source=chatgpt.com</t>
         </is>
@@ -18988,7 +19574,7 @@
           <t>Audit / Tax / Advisory</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="16" t="inlineStr">
         <is>
           <t>https://www.deloitte.com/middle-east/en/events.html?utm_source=chatgpt.com</t>
         </is>
@@ -19008,7 +19594,7 @@
           <t>Audit / Tax / Advisory</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" s="16" t="inlineStr">
         <is>
           <t>https://www.bdo.ae/en-gb/events?utm_source=chatgpt.com</t>
         </is>
@@ -19028,7 +19614,7 @@
           <t>Audit / Tax / Advisory</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" s="16" t="inlineStr">
         <is>
           <t>https://kpmg.com/ae/en/home/events.html?utm_source=chatgpt.com</t>
         </is>
@@ -19048,7 +19634,7 @@
           <t>Audit / Tax / Advisory</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" s="16" t="inlineStr">
         <is>
           <t>https://www.pwc.com/m1/en/events.html?utm_source=chatgpt.com</t>
         </is>
@@ -19068,7 +19654,7 @@
           <t>Audit / Tax / Advisory</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" s="16" t="inlineStr">
         <is>
           <t>https://www.ey.com/en_ae/events?utm_source=chatgpt.com</t>
         </is>
@@ -19088,7 +19674,7 @@
           <t>Internal Audit / Risk</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D80" s="16" t="inlineStr">
         <is>
           <t>https://uaeiaa.org/events-calendar?utm_source=chatgpt.com</t>
         </is>
@@ -19108,7 +19694,7 @@
           <t>Finance / Investment</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" s="16" t="inlineStr">
         <is>
           <t>https://www.cisi.org/cisiweb2/events?utm_source=chatgpt.com</t>
         </is>
@@ -19128,7 +19714,7 @@
           <t>Finance / Islamic Finance</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" s="16" t="inlineStr">
         <is>
           <t>https://www.globalethicalfinance.org/our-events/?utm_source=chatgpt.com</t>
         </is>
@@ -19148,7 +19734,7 @@
           <t>Investment / Capital Markets</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" s="16" t="inlineStr">
         <is>
           <t>https://www.dsig.ae/upcoming-events/?utm_source=chatgpt.com</t>
         </is>
@@ -19168,7 +19754,7 @@
           <t>Finance / Banking / Legal</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" s="16" t="inlineStr">
         <is>
           <t>https://academy.adgm.com/events/?utm_source=chatgpt.com</t>
         </is>
@@ -19188,7 +19774,7 @@
           <t>Business / Industry / Trade</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" s="16" t="inlineStr">
         <is>
           <t>https://moiat.gov.ae/en/media-center/events?utm_source=chatgpt.com</t>
         </is>
@@ -19208,7 +19794,7 @@
           <t>Business / Investment</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" s="16" t="inlineStr">
         <is>
           <t>https://rakchamber.ae/?utm_source=chatgpt.com</t>
         </is>
@@ -19228,7 +19814,7 @@
           <t>Accounting / Finance</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" s="16" t="inlineStr">
         <is>
           <t>https://www.aopauae.com/events?utm_source=chatgpt.com</t>
         </is>
@@ -19248,7 +19834,7 @@
           <t>Business / Tax / Trade</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" s="16" t="inlineStr">
         <is>
           <t>https://www.abudhabichamber.ae/en?utm_source=chatgpt.com</t>
         </is>
@@ -19268,7 +19854,7 @@
           <t>Business / Trade / Investment</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" s="16" t="inlineStr">
         <is>
           <t>https://ajmanchamber.ae/en/archives/exhibitions-conferences/?utm_source=chatgpt.com</t>
         </is>
@@ -19348,7 +19934,7 @@
           <t>Business / Conferences / Finance</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D94" s="16" t="inlineStr">
         <is>
           <t>https://www.adnecgroup.ae/events</t>
         </is>
@@ -19398,7 +19984,7 @@
           <t>FinTech / Finance</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D97" s="16" t="inlineStr">
         <is>
           <t>https://www.dubaifintechsummit.com/</t>
         </is>
@@ -19418,7 +20004,7 @@
           <t>Finance / Financial Services</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D98" s="16" t="inlineStr">
         <is>
           <t>https://www.dubaifuturefinanceweek.com/</t>
         </is>
@@ -19438,7 +20024,7 @@
           <t>Financial Services / Regulation</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D99" s="16" t="inlineStr">
         <is>
           <t>https://www.difc.com/whats-on/events</t>
         </is>
@@ -19458,7 +20044,7 @@
           <t>Financial Regulation</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D100" s="16" t="inlineStr">
         <is>
           <t>https://www.adgm.com/media/announcements</t>
         </is>
@@ -19478,7 +20064,7 @@
           <t>Legal / Arbitration</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D101" s="16" t="inlineStr">
         <is>
           <t>https://www.adgm.com/operating-in-adgm/courts/events</t>
         </is>
@@ -19498,7 +20084,7 @@
           <t>Legal / Arbitration</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D102" s="16" t="inlineStr">
         <is>
           <t>https://www.difccourts.ae/events</t>
         </is>
@@ -19518,7 +20104,7 @@
           <t>Arbitration / Legal</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D103" s="16" t="inlineStr">
         <is>
           <t>https://www.diac.com/en/events/</t>
         </is>
@@ -19538,7 +20124,7 @@
           <t>Arbitration / Legal</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D104" s="16" t="inlineStr">
         <is>
           <t>https://www.dubaiarbitrationweek.com/calender/</t>
         </is>
@@ -19558,7 +20144,7 @@
           <t>Legal / Business</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D105" s="16" t="inlineStr">
         <is>
           <t>https://www.dubailegalweek.com/</t>
         </is>
@@ -19578,7 +20164,7 @@
           <t>Arbitration / Legal</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D106" s="16" t="inlineStr">
         <is>
           <t>https://emac.org.ae/events/</t>
         </is>
@@ -19598,7 +20184,7 @@
           <t>Arbitration / Legal</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D107" s="16" t="inlineStr">
         <is>
           <t>https://www.diac.com/en/events/</t>
         </is>
@@ -19618,7 +20204,7 @@
           <t>Arbitration / Legal</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D108" s="16" t="inlineStr">
         <is>
           <t>https://www.ciarb.org/events/</t>
         </is>
@@ -19638,7 +20224,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D109" s="16" t="inlineStr">
         <is>
           <t>https://www.ibanet.org/events</t>
         </is>
@@ -19658,7 +20244,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D110" s="16" t="inlineStr">
         <is>
           <t>https://www.iayl.org/events/</t>
         </is>
@@ -19678,7 +20264,7 @@
           <t>Construction Law / Legal</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D111" s="16" t="inlineStr">
         <is>
           <t>https://www.scl.org.ae/events/</t>
         </is>
@@ -19698,7 +20284,7 @@
           <t>Business / Legal</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D112" s="16" t="inlineStr">
         <is>
           <t>https://www.dubaichamber.com/en/events</t>
         </is>
@@ -19718,7 +20304,7 @@
           <t>Business / Trade</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D113" s="16" t="inlineStr">
         <is>
           <t>https://nbad.ae/events/</t>
         </is>
@@ -19738,7 +20324,7 @@
           <t>Business / Trade</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D114" s="16" t="inlineStr">
         <is>
           <t>https://dba-uae.com/events/</t>
         </is>
@@ -19758,7 +20344,7 @@
           <t>Business / Trade / Investment</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D115" s="16" t="inlineStr">
         <is>
           <t>https://vae.ahk.de/en/events</t>
         </is>
@@ -19778,7 +20364,7 @@
           <t>Business / Trade / Investment</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D116" s="16" t="inlineStr">
         <is>
           <t>https://www.ccifranceuae.com/events.html</t>
         </is>
@@ -19798,7 +20384,7 @@
           <t>Business / Trade / Investment</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D117" s="16" t="inlineStr">
         <is>
           <t>https://www.iicuae.com/events/</t>
         </is>
@@ -19818,7 +20404,7 @@
           <t>Business / Trade / Investment</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D118" s="16" t="inlineStr">
         <is>
           <t>https://www.turkeybusinesscouncil.ae/events/</t>
         </is>
@@ -19838,7 +20424,7 @@
           <t>Business / Professional</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D119" s="16" t="inlineStr">
         <is>
           <t>https://ibpcdubai.com/events/</t>
         </is>
@@ -19858,7 +20444,7 @@
           <t>Business / Trade / Finance</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D120" s="16" t="inlineStr">
         <is>
           <t>https://pakistansbc.org/events/</t>
         </is>
@@ -19878,7 +20464,7 @@
           <t>Business / Trade</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D121" s="16" t="inlineStr">
         <is>
           <t>https://bbcu.ae/events/</t>
         </is>
@@ -19898,7 +20484,7 @@
           <t>Business / Trade</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D122" s="16" t="inlineStr">
         <is>
           <t>https://pbcdubai.org/events/</t>
         </is>
@@ -19918,7 +20504,7 @@
           <t>Business / Trade / Investment</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D123" s="16" t="inlineStr">
         <is>
           <t>https://www.kbcuae.com/events/</t>
         </is>
@@ -19938,7 +20524,7 @@
           <t>Business / Trade / Investment</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D124" s="16" t="inlineStr">
         <is>
           <t>https://www.jbcuae.com/events/</t>
         </is>
@@ -19958,7 +20544,7 @@
           <t>Business / Trade / Investment</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D125" s="16" t="inlineStr">
         <is>
           <t>https://www.gbcuae.com/events/</t>
         </is>
@@ -19978,7 +20564,7 @@
           <t>Business / Trade / Investment</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="D126" s="16" t="inlineStr">
         <is>
           <t>https://pbcu.ae/events/</t>
         </is>
@@ -19998,7 +20584,7 @@
           <t>Business / Trade / Investment</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D127" s="16" t="inlineStr">
         <is>
           <t>https://www.cbcuae.com/events/</t>
         </is>
@@ -20018,7 +20604,7 @@
           <t>Business / Trade / Investment</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D128" s="16" t="inlineStr">
         <is>
           <t>https://www.rbcu.ae/events/</t>
         </is>
@@ -20038,7 +20624,7 @@
           <t>Business / Trade / Investment</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D129" s="16" t="inlineStr">
         <is>
           <t>https://lbcdubai.com/events/</t>
         </is>
@@ -20058,7 +20644,7 @@
           <t>Business / Trade / Investment</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D130" s="16" t="inlineStr">
         <is>
           <t>https://ebcdubai.com/events/</t>
         </is>
@@ -20078,7 +20664,7 @@
           <t>Business / Trade / Investment</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D131" s="16" t="inlineStr">
         <is>
           <t>https://jbcuae.com/events/</t>
         </is>
@@ -20098,7 +20684,7 @@
           <t>Business / Trade / Investment</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D132" s="16" t="inlineStr">
         <is>
           <t>https://mbcuae.org/events/</t>
         </is>
@@ -20118,7 +20704,7 @@
           <t>Business / Trade / Investment</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D133" s="16" t="inlineStr">
         <is>
           <t>https://www.braziluae.com/events/</t>
         </is>
@@ -20138,7 +20724,7 @@
           <t>Business / Trade / Investment</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="D134" s="16" t="inlineStr">
         <is>
           <t>https://www.mexicanbusinesscouncil.com/events/</t>
         </is>
@@ -20158,7 +20744,7 @@
           <t>Business / Trade / Investment</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D135" s="16" t="inlineStr">
         <is>
           <t>https://nzbcuae.com/events/</t>
         </is>
@@ -20181,6 +20767,136 @@
     <row r="150" ht="72" customHeight="1"/>
     <row r="151" ht="57.6" customHeight="1"/>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId128"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -20230,7 +20946,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>https://www.taxinstitute.com.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -20250,7 +20966,7 @@
           <t>Accounting &amp; Finance</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>https://www.cpaaustralia.com.au/professional-development/conferences-and-events?utm_source=chatgpt.com</t>
         </is>
@@ -20270,7 +20986,7 @@
           <t>Accounting</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>https://www.charteredaccountants.com.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -20290,7 +21006,7 @@
           <t>Accounting</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>https://www.publicaccountants.org.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -20310,7 +21026,7 @@
           <t>Tax, Accounting &amp; Finance</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>https://ifpa.com.au/events/?utm_source=chatgpt.com</t>
         </is>
@@ -20330,7 +21046,7 @@
           <t>International Tax</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>https://ifa-australia.com.au/?utm_source=chatgpt.com</t>
         </is>
@@ -20350,7 +21066,7 @@
           <t>Tax &amp; Accounting</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>https://www.atma.com.au/?utm_source=chatgpt.com</t>
         </is>
@@ -20370,7 +21086,7 @@
           <t>Financial Advice</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>https://faaa.au/events/?utm_source=chatgpt.com</t>
         </is>
@@ -20390,7 +21106,7 @@
           <t>Superannuation &amp; Finance</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>https://www.smsfassociation.com/events?utm_source=chatgpt.com</t>
         </is>
@@ -20410,7 +21126,7 @@
           <t>Superannuation</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>https://www.aist.asn.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -20430,7 +21146,7 @@
           <t>Financial Markets</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>https://www.afma.com.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -20450,7 +21166,7 @@
           <t>Banking &amp; Finance</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>https://www.ausbanking.org.au/events/?utm_source=chatgpt.com</t>
         </is>
@@ -20470,7 +21186,7 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>https://fsc.org.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -20490,7 +21206,7 @@
           <t>Governance, Risk &amp; Compliance</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>https://www.governanceinstitute.com.au/events/?utm_source=chatgpt.com</t>
         </is>
@@ -20510,7 +21226,7 @@
           <t>Insolvency &amp; Restructuring</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>https://arita.com.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -20530,7 +21246,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>https://lawcouncil.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -20550,7 +21266,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>https://www.lawsociety.com.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -20570,7 +21286,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>https://www.liv.asn.au/Events?utm_source=chatgpt.com</t>
         </is>
@@ -20590,7 +21306,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>https://www.qls.com.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -20610,7 +21326,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>https://www.lawsocietysa.asn.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -20630,7 +21346,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>https://www.lawsocietywa.asn.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -20650,7 +21366,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>https://www.lst.org.au/events/?utm_source=chatgpt.com</t>
         </is>
@@ -20670,7 +21386,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>https://lawsocietynt.com.au/events/?utm_source=chatgpt.com</t>
         </is>
@@ -20690,7 +21406,7 @@
           <t>Commercial Law</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>https://www.cla.org.au/Home?utm_source=chatgpt.com</t>
         </is>
@@ -20710,7 +21426,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>https://www.academyoflaw.org.au/events-and-videos?utm_source=chatgpt.com</t>
         </is>
@@ -20730,7 +21446,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>https://www.aala.org.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -20750,7 +21466,7 @@
           <t>Corporate Legal</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>https://www.accaustralia.com.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -20770,7 +21486,7 @@
           <t>Corporate Governance</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>https://www.aicd.com.au/events.html?utm_source=chatgpt.com</t>
         </is>
@@ -20790,7 +21506,7 @@
           <t>Credit &amp; Finance</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>https://www.aicm.com.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -20810,7 +21526,7 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>https://www.financialcounsellingaustralia.org.au/events/?utm_source=chatgpt.com</t>
         </is>
@@ -20830,7 +21546,7 @@
           <t>Treasury &amp; Finance</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>https://www.afp.org.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -20850,7 +21566,7 @@
           <t>Risk &amp; Governance</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>https://www.arpi.org.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -20870,7 +21586,7 @@
           <t>Risk Management</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>https://www.rmia.org.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -20890,7 +21606,7 @@
           <t>Business &amp; Management</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>https://www.aim.com.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -20910,7 +21626,7 @@
           <t>Business &amp; Management</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>https://aimwa.com/events/?utm_source=chatgpt.com</t>
         </is>
@@ -20930,7 +21646,7 @@
           <t>Finance &amp; Property</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>https://www.aiqs.com.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -20950,7 +21666,7 @@
           <t>Property &amp; Finance</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>https://www.propertycouncil.com.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -20970,7 +21686,7 @@
           <t>Property &amp; Finance</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>https://www.api.org.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -20990,7 +21706,7 @@
           <t>Payroll &amp; Tax</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>https://www.australianpayrollassociation.com.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -21010,7 +21726,7 @@
           <t>Payroll &amp; Tax</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>https://taps.associationonline.com.au/events/?utm_source=chatgpt.com</t>
         </is>
@@ -21030,7 +21746,7 @@
           <t>Business &amp; Regulation</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>https://aana.com.au/events/?utm_source=chatgpt.com</t>
         </is>
@@ -21050,7 +21766,7 @@
           <t>Corporate Governance</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>https://www.aicd.com.au/events.html?utm_source=chatgpt.com</t>
         </is>
@@ -21070,7 +21786,7 @@
           <t>Business &amp; Employment Law</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>https://www.abl.com.au/events/?utm_source=chatgpt.com</t>
         </is>
@@ -21090,7 +21806,7 @@
           <t>Tax, Legal &amp; Finance</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>https://www.thomsonreuters.com.au/en-au/events.html?utm_source=chatgpt.com</t>
         </is>
@@ -21110,7 +21826,7 @@
           <t>Legal, Tax &amp; Accounting CPD</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>https://www.tved.net.au/?utm_source=chatgpt.com</t>
         </is>
@@ -21130,7 +21846,7 @@
           <t>Legal &amp; Accounting CPD</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>https://legalwiseseminars.com.au/events/?utm_source=chatgpt.com</t>
         </is>
@@ -21150,7 +21866,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>https://www.leocussen.edu.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -21170,7 +21886,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="16" t="inlineStr">
         <is>
           <t>https://www.collaw.edu.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -21190,7 +21906,7 @@
           <t>Corporate Governance</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>https://www.aicd.com.au/events.html?utm_source=chatgpt.com</t>
         </is>
@@ -21210,7 +21926,7 @@
           <t>Corporate Governance</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="16" t="inlineStr">
         <is>
           <t>https://www.aicd.com.au/events.html?utm_source=chatgpt.com</t>
         </is>
@@ -21230,7 +21946,7 @@
           <t>Corporate Tax</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>https://corptax.com.au/upcoming-events/</t>
         </is>
@@ -21250,7 +21966,7 @@
           <t>Bookkeeping &amp; Accounting</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>https://www.aubn.org.au/events/</t>
         </is>
@@ -21270,7 +21986,7 @@
           <t>Bookkeeping &amp; Accounting</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>https://www.icb.org.au/events</t>
         </is>
@@ -21290,7 +22006,7 @@
           <t>Accounting</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="16" t="inlineStr">
         <is>
           <t>https://www.aat.org.au/events</t>
         </is>
@@ -21310,7 +22026,7 @@
           <t>Professional &amp; Business</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="16" t="inlineStr">
         <is>
           <t>https://aage.com.au/events/</t>
         </is>
@@ -21330,7 +22046,7 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="16" t="inlineStr">
         <is>
           <t>https://www.afca.org.au/about-us/events</t>
         </is>
@@ -21350,7 +22066,7 @@
           <t>Financial Regulation</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="16" t="inlineStr">
         <is>
           <t>https://asic.gov.au/about-asic/news-centre/events/</t>
         </is>
@@ -21370,7 +22086,7 @@
           <t>Financial Regulation</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="16" t="inlineStr">
         <is>
           <t>https://www.apra.gov.au/events</t>
         </is>
@@ -21390,7 +22106,7 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="16" t="inlineStr">
         <is>
           <t>https://www.ato.gov.au/about-ato/learn-about-tax-and-the-ato/events</t>
         </is>
@@ -21410,7 +22126,7 @@
           <t>Accounting Standards</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="16" t="inlineStr">
         <is>
           <t>https://www.aasb.gov.au/about-aasb/events/</t>
         </is>
@@ -21430,7 +22146,7 @@
           <t>Auditing</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="16" t="inlineStr">
         <is>
           <t>https://www.auasb.gov.au/about-auasb/events/</t>
         </is>
@@ -21450,7 +22166,7 @@
           <t>Financial Reporting</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="16" t="inlineStr">
         <is>
           <t>https://www.frc.gov.au/</t>
         </is>
@@ -21470,7 +22186,7 @@
           <t>Competition &amp; Regulation</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="16" t="inlineStr">
         <is>
           <t>https://www.accc.gov.au/about-us/events</t>
         </is>
@@ -21490,7 +22206,7 @@
           <t>Competition Law</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="16" t="inlineStr">
         <is>
           <t>https://www.competitiontribunal.gov.au/</t>
         </is>
@@ -21510,7 +22226,7 @@
           <t>Governance</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="16" t="inlineStr">
         <is>
           <t>https://www.aicd.com.au/events.html</t>
         </is>
@@ -21530,7 +22246,7 @@
           <t>Compliance &amp; Risk</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="16" t="inlineStr">
         <is>
           <t>https://www.australiancomplianceinstitute.org/events/</t>
         </is>
@@ -21550,7 +22266,7 @@
           <t>Risk Management</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" s="16" t="inlineStr">
         <is>
           <t>https://www.rmia.org.au/events</t>
         </is>
@@ -21570,7 +22286,7 @@
           <t>Risk &amp; Governance</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="16" t="inlineStr">
         <is>
           <t>https://www.arpi.org.au/events/</t>
         </is>
@@ -21590,7 +22306,7 @@
           <t>Internal Audit</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" s="16" t="inlineStr">
         <is>
           <t>https://www.iia.org.au/events</t>
         </is>
@@ -21610,7 +22326,7 @@
           <t>Risk Management</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" s="16" t="inlineStr">
         <is>
           <t>https://www.irma.org.au/events</t>
         </is>
@@ -21630,7 +22346,7 @@
           <t>Credit &amp; Finance</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="16" t="inlineStr">
         <is>
           <t>https://www.aicm.com.au/events</t>
         </is>
@@ -21650,7 +22366,7 @@
           <t>Insolvency</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" s="16" t="inlineStr">
         <is>
           <t>https://arita.com.au/events</t>
         </is>
@@ -21670,7 +22386,7 @@
           <t>Credit &amp; Banking</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>https://www.aicm.com.au/events</t>
         </is>
@@ -21690,7 +22406,7 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="16" t="inlineStr">
         <is>
           <t>https://afia.asn.au/events/</t>
         </is>
@@ -21710,7 +22426,7 @@
           <t>Financial Markets</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" s="16" t="inlineStr">
         <is>
           <t>https://www.afma.com.au/events</t>
         </is>
@@ -21730,7 +22446,7 @@
           <t>Banking</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" s="16" t="inlineStr">
         <is>
           <t>https://www.ausbanking.org.au/events/</t>
         </is>
@@ -21750,7 +22466,7 @@
           <t>Banking</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" s="16" t="inlineStr">
         <is>
           <t>https://www.customerownedbanking.asn.au/</t>
         </is>
@@ -21770,7 +22486,7 @@
           <t>Capital Markets</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" s="16" t="inlineStr">
         <is>
           <t>https://www.aussecuritisation.com.au/events/</t>
         </is>
@@ -21790,7 +22506,7 @@
           <t>Private Equity &amp; Venture Capital</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D80" s="16" t="inlineStr">
         <is>
           <t>https://www.avca.asn.au/events/</t>
         </is>
@@ -21810,7 +22526,7 @@
           <t>Alternative Investments</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" s="16" t="inlineStr">
         <is>
           <t>https://www.aima.org/events.html</t>
         </is>
@@ -21830,7 +22546,7 @@
           <t>Investment &amp; Private Capital</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" s="16" t="inlineStr">
         <is>
           <t>https://investmentcouncil.org.au/events/</t>
         </is>
@@ -21850,7 +22566,7 @@
           <t>Financial Advice</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" s="16" t="inlineStr">
         <is>
           <t>https://faaa.au/events/</t>
         </is>
@@ -21870,7 +22586,7 @@
           <t>Financial Advice</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" s="16" t="inlineStr">
         <is>
           <t>https://faaa.au/events/</t>
         </is>
@@ -21890,7 +22606,7 @@
           <t>Financial Planning</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" s="16" t="inlineStr">
         <is>
           <t>https://faaa.au/events/</t>
         </is>
@@ -21910,7 +22626,7 @@
           <t>Superannuation</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" s="16" t="inlineStr">
         <is>
           <t>https://www.superannuation.asn.au/events/</t>
         </is>
@@ -21930,7 +22646,7 @@
           <t>Superannuation</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" s="16" t="inlineStr">
         <is>
           <t>https://www.aist.asn.au/events</t>
         </is>
@@ -21950,7 +22666,7 @@
           <t>Family Law</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" s="16" t="inlineStr">
         <is>
           <t>https://aiflam.org.au/events/</t>
         </is>
@@ -21970,7 +22686,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" s="16" t="inlineStr">
         <is>
           <t>https://lawyersalliance.com.au/Web/Web/Events/Upcoming-Events.aspx</t>
         </is>
@@ -21990,7 +22706,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D90" s="16" t="inlineStr">
         <is>
           <t>https://www.austbar.asn.au/events/</t>
         </is>
@@ -22010,7 +22726,7 @@
           <t>Corporate Law</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D91" s="16" t="inlineStr">
         <is>
           <t>https://www.accaustralia.com.au/events</t>
         </is>
@@ -22030,7 +22746,7 @@
           <t>Investment &amp; Finance</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D92" s="16" t="inlineStr">
         <is>
           <t>https://cfas.org.au/events/?utm_source=chatgpt.com</t>
         </is>
@@ -22050,7 +22766,7 @@
           <t>Energy &amp; Resources Law</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D93" s="16" t="inlineStr">
         <is>
           <t>https://erlaw.org.au/events/?utm_source=chatgpt.com</t>
         </is>
@@ -22070,7 +22786,7 @@
           <t>FinTech &amp; Finance</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D94" s="16" t="inlineStr">
         <is>
           <t>https://www.fintechaustralia.org.au/events/?utm_source=chatgpt.com</t>
         </is>
@@ -22090,7 +22806,7 @@
           <t>Finance &amp; Mortgage</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D95" s="15" t="inlineStr">
         <is>
           <t>https://www.mfaa.com.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -22110,7 +22826,7 @@
           <t>Banking &amp; Financial Law</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D96" s="16" t="inlineStr">
         <is>
           <t>https://shop.bfsla.org/?utm_source=chatgpt.com</t>
         </is>
@@ -22130,7 +22846,7 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D97" s="16" t="inlineStr">
         <is>
           <t>https://www.afia.asn.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -22150,7 +22866,7 @@
           <t>Local Government Finance</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D98" s="16" t="inlineStr">
         <is>
           <t>https://www.finpro.org.au/?utm_source=chatgpt.com</t>
         </is>
@@ -22170,7 +22886,7 @@
           <t>Legal Information</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D99" s="16" t="inlineStr">
         <is>
           <t>https://pecbookings.eventsair.com/alla2026/?utm_source=chatgpt.com</t>
         </is>
@@ -22190,7 +22906,7 @@
           <t>Legal Technology</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D100" s="16" t="inlineStr">
         <is>
           <t>https://www.vscl.org.au/?utm_source=chatgpt.com</t>
         </is>
@@ -22210,7 +22926,7 @@
           <t>Charity &amp; Nonprofit Law</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D101" s="16" t="inlineStr">
         <is>
           <t>https://www.claanz.org.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -22230,7 +22946,7 @@
           <t>Legal / Pro Bono</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D102" s="16" t="inlineStr">
         <is>
           <t>https://www.probonocentre.org.au/news-media-2/events-and-conferences/?utm_source=chatgpt.com</t>
         </is>
@@ -22250,7 +22966,7 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D103" s="16" t="inlineStr">
         <is>
           <t>https://www.scla.org.au/events/?utm_source=chatgpt.com</t>
         </is>
@@ -22270,7 +22986,7 @@
           <t>Legal, Tax &amp; Accounting CPD</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D104" s="16" t="inlineStr">
         <is>
           <t>https://www.tved.net.au/?utm_source=chatgpt.com</t>
         </is>
@@ -22290,7 +23006,7 @@
           <t>Tax, Accounting &amp; Finance</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D105" s="16" t="inlineStr">
         <is>
           <t>https://ifpa.com.au/events/?utm_source=chatgpt.com</t>
         </is>
@@ -22310,7 +23026,7 @@
           <t>Accounting &amp; Finance</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D106" s="16" t="inlineStr">
         <is>
           <t>https://www.afaanz.org/conference?utm_source=chatgpt.com</t>
         </is>
@@ -22330,7 +23046,7 @@
           <t>Payroll &amp; Tax</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D107" s="16" t="inlineStr">
         <is>
           <t>https://taps.associationonline.com.au/events/?utm_source=chatgpt.com</t>
         </is>
@@ -22350,7 +23066,7 @@
           <t>Property &amp; Finance</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D108" s="16" t="inlineStr">
         <is>
           <t>https://www.api.org.au/events?utm_source=chatgpt.com</t>
         </is>
@@ -22401,6 +23117,115 @@
     <row r="151" ht="57.6" customHeight="1"/>
     <row r="152" ht="57.6" customHeight="1"/>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId107"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Sources/Event_scrapper_-_Website_completed.xlsx
+++ b/Sources/Event_scrapper_-_Website_completed.xlsx
@@ -13898,7 +13898,7 @@
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>https://sctp.org.sg/events/Tax-Professionals?utm_source=chatgpt.com</t>
+          <t>https://sctp.org.sg/events/Tax-Professionals</t>
         </is>
       </c>
     </row>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>https://www.isca.org.sg/member-support/events?utm_source=chatgpt.com</t>
+          <t>https://www.isca.org.sg/member-support/events</t>
         </is>
       </c>
     </row>
@@ -13938,7 +13938,7 @@
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>https://www.taxacademy.sg/seminars-and-conferences/?utm_source=chatgpt.com</t>
+          <t>https://www.taxacademy.sg/seminars-and-conferences/</t>
         </is>
       </c>
     </row>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>https://icai.org.sg/events/recent-events?utm_source=chatgpt.com</t>
+          <t>https://icai.org.sg/events/recent-events</t>
         </is>
       </c>
     </row>
@@ -13978,7 +13978,7 @@
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>https://www.accaglobal.com/sg/en/member/cpd/events.html?utm_source=chatgpt.com</t>
+          <t>https://www.accaglobal.com/sg/en/member/cpd/events.html</t>
         </is>
       </c>
     </row>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>https://www.lawsociety.org.sg/cpd-events/?utm_source=chatgpt.com</t>
+          <t>https://www.lawsociety.org.sg/cpd-events/</t>
         </is>
       </c>
     </row>
@@ -14018,7 +14018,7 @@
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>https://www.sal.org.sg/Events?utm_source=chatgpt.com</t>
+          <t>https://www.sal.org.sg/Events</t>
         </is>
       </c>
     </row>
@@ -14038,7 +14038,7 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>https://www.sile.edu.sg/?utm_source=chatgpt.com</t>
+          <t>https://www.sile.edu.sg/</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>https://siac.org.sg/events?utm_source=chatgpt.com</t>
+          <t>https://siac.org.sg/events</t>
         </is>
       </c>
     </row>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>https://www.sicc.gov.sg/?utm_source=chatgpt.com</t>
+          <t>https://www.sicc.gov.sg/</t>
         </is>
       </c>
     </row>
@@ -14098,7 +14098,7 @@
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>https://www.scca.org.sg/events?utm_source=chatgpt.com</t>
+          <t>https://www.scca.org.sg/events</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>https://www.sid.org.sg/events?utm_source=chatgpt.com</t>
+          <t>https://www.sid.org.sg/events</t>
         </is>
       </c>
     </row>
@@ -14138,7 +14138,7 @@
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>https://saicsa.org.sg/events/?utm_source=chatgpt.com</t>
+          <t>https://saicsa.org.sg/events/</t>
         </is>
       </c>
     </row>
@@ -14158,7 +14158,7 @@
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>https://www.cfasocietysingapore.org/events?utm_source=chatgpt.com</t>
+          <t>https://www.cfasocietysingapore.org/events</t>
         </is>
       </c>
     </row>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>https://imas.org.sg/events/?utm_source=chatgpt.com</t>
+          <t>https://imas.org.sg/events/</t>
         </is>
       </c>
     </row>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>https://sias.org.sg/events/?utm_source=chatgpt.com</t>
+          <t>https://sias.org.sg/events/</t>
         </is>
       </c>
     </row>
@@ -14218,7 +14218,7 @@
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>https://svca.org.sg/events/?utm_source=chatgpt.com</t>
+          <t>https://svca.org.sg/events/</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14238,7 @@
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>https://singaporefintech.org/events/?utm_source=chatgpt.com</t>
+          <t>https://singaporefintech.org/events/</t>
         </is>
       </c>
     </row>
@@ -14258,7 +14258,7 @@
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>https://www.abs.org.sg/events?utm_source=chatgpt.com</t>
+          <t>https://www.abs.org.sg/events</t>
         </is>
       </c>
     </row>
@@ -14278,7 +14278,7 @@
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>https://www.actuaries.org.sg/events/?utm_source=chatgpt.com</t>
+          <t>https://www.actuaries.org.sg/events/</t>
         </is>
       </c>
     </row>
@@ -14298,7 +14298,7 @@
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>https://www.sii.org.sg/events?utm_source=chatgpt.com</t>
+          <t>https://www.sii.org.sg/events</t>
         </is>
       </c>
     </row>
@@ -14318,7 +14318,7 @@
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>https://www.fpas.org.sg/events/?utm_source=chatgpt.com</t>
+          <t>https://www.fpas.org.sg/events/</t>
         </is>
       </c>
     </row>
@@ -14338,7 +14338,7 @@
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>https://www.acra.gov.sg/news-events/event-highlights/?utm_source=chatgpt.com</t>
+          <t>https://www.acra.gov.sg/news-events/event-highlights/</t>
         </is>
       </c>
     </row>
@@ -14358,7 +14358,7 @@
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>https://www.iras.gov.sg/?utm_source=chatgpt.com</t>
+          <t>https://www.iras.gov.sg/</t>
         </is>
       </c>
     </row>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>https://www.mas.gov.sg/news/events?utm_source=chatgpt.com</t>
+          <t>https://www.mas.gov.sg/news/events</t>
         </is>
       </c>
     </row>
@@ -14398,7 +14398,7 @@
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>https://www.ipos.gov.sg/events?utm_source=chatgpt.com</t>
+          <t>https://www.ipos.gov.sg/events</t>
         </is>
       </c>
     </row>
@@ -14418,7 +14418,7 @@
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>https://www.mof.gov.sg/news-publications/events?utm_source=chatgpt.com</t>
+          <t>https://www.mof.gov.sg/news-publications/events</t>
         </is>
       </c>
     </row>
@@ -14438,7 +14438,7 @@
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>https://www.sbf.org.sg/events?utm_source=chatgpt.com</t>
+          <t>https://www.sbf.org.sg/events</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>https://sicc.com.sg/events/?utm_source=chatgpt.com</t>
+          <t>https://sicc.com.sg/events/</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>https://www.sccci.org.sg/events/?utm_source=chatgpt.com</t>
+          <t>https://www.sccci.org.sg/events/</t>
         </is>
       </c>
     </row>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>https://asme.org.sg/events/?utm_source=chatgpt.com</t>
+          <t>https://asme.org.sg/events/</t>
         </is>
       </c>
     </row>
@@ -14518,7 +14518,7 @@
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>https://www.smfederation.org.sg/events/?utm_source=chatgpt.com</t>
+          <t>https://www.smfederation.org.sg/events/</t>
         </is>
       </c>
     </row>
@@ -14538,7 +14538,7 @@
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>https://www.sla.org.sg/events/?utm_source=chatgpt.com</t>
+          <t>https://www.sla.org.sg/events/</t>
         </is>
       </c>
     </row>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>https://www.enterprisesg.gov.sg/events?utm_source=chatgpt.com</t>
+          <t>https://www.enterprisesg.gov.sg/events</t>
         </is>
       </c>
     </row>
@@ -14578,7 +14578,7 @@
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>https://www.edb.gov.sg/en/events.html?utm_source=chatgpt.com</t>
+          <t>https://www.edb.gov.sg/en/events.html</t>
         </is>
       </c>
     </row>
@@ -14598,7 +14598,7 @@
       </c>
       <c r="D37" s="16" t="inlineStr">
         <is>
-          <t>https://www.step.org/singapore/events?utm_source=chatgpt.com</t>
+          <t>https://www.step.org/singapore/events</t>
         </is>
       </c>
     </row>
@@ -14618,7 +14618,7 @@
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>https://www.ifa.nl/events?utm_source=chatgpt.com</t>
+          <t>https://www.ifa.nl/events</t>
         </is>
       </c>
     </row>
@@ -14638,7 +14638,7 @@
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
-          <t>https://www.taxacademy.sg/stari/?utm_source=chatgpt.com</t>
+          <t>https://www.taxacademy.sg/stari/</t>
         </is>
       </c>
     </row>
@@ -14658,7 +14658,7 @@
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>https://www.ivass.org.sg/events?utm_source=chatgpt.com</t>
+          <t>https://www.ivass.org.sg/events</t>
         </is>
       </c>
     </row>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="D41" s="16" t="inlineStr">
         <is>
-          <t>https://scma.org.sg/events/?utm_source=chatgpt.com</t>
+          <t>https://scma.org.sg/events/</t>
         </is>
       </c>
     </row>
@@ -14698,7 +14698,7 @@
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>https://www.smc.org.sg/events?utm_source=chatgpt.com</t>
+          <t>https://www.smc.org.sg/events</t>
         </is>
       </c>
     </row>
@@ -14718,7 +14718,7 @@
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>https://sicc.gov.sg/?utm_source=chatgpt.com</t>
+          <t>https://sicc.gov.sg/</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>https://www.scs.org.sg/events?utm_source=chatgpt.com</t>
+          <t>https://www.scs.org.sg/events</t>
         </is>
       </c>
     </row>
@@ -14758,7 +14758,7 @@
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>https://www.sim.edu.sg/?utm_source=chatgpt.com</t>
+          <t>https://www.sim.edu.sg/</t>
         </is>
       </c>
     </row>
@@ -14778,7 +14778,7 @@
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>https://www.shri.org.sg/events?utm_source=chatgpt.com</t>
+          <t>https://www.shri.org.sg/events</t>
         </is>
       </c>
     </row>
@@ -14798,7 +14798,7 @@
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>https://mis.org.sg/events/?utm_source=chatgpt.com</t>
+          <t>https://mis.org.sg/events/</t>
         </is>
       </c>
     </row>
@@ -14818,7 +14818,7 @@
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>https://www.sipmm.edu.sg/events/?utm_source=chatgpt.com</t>
+          <t>https://www.sipmm.edu.sg/events/</t>
         </is>
       </c>
     </row>
@@ -14838,7 +14838,7 @@
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>https://ccls.smu.edu.sg/events?utm_source=chatgpt.com</t>
+          <t>https://ccls.smu.edu.sg/events</t>
         </is>
       </c>
     </row>
@@ -14858,7 +14858,7 @@
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>https://law.smu.edu.sg/events?utm_source=chatgpt.com</t>
+          <t>https://law.smu.edu.sg/events</t>
         </is>
       </c>
     </row>
@@ -14878,7 +14878,7 @@
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>https://caidg.smu.edu.sg/events?utm_source=chatgpt.com</t>
+          <t>https://caidg.smu.edu.sg/events</t>
         </is>
       </c>
     </row>
@@ -14898,7 +14898,7 @@
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>https://act.org.sg/events/?utm_source=chatgpt.com</t>
+          <t>https://act.org.sg/events/</t>
         </is>
       </c>
     </row>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>https://www.rimas.org.sg/?utm_source=chatgpt.com</t>
+          <t>https://www.rimas.org.sg/</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>https://iia.org.sg/Home?utm_source=chatgpt.com</t>
+          <t>https://iia.org.sg/Home</t>
         </is>
       </c>
     </row>
@@ -14958,7 +14958,7 @@
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>https://engage.isaca.org/singaporechapter/events?utm_source=chatgpt.com</t>
+          <t>https://engage.isaca.org/singaporechapter/events</t>
         </is>
       </c>
     </row>
@@ -14978,7 +14978,7 @@
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>https://www.isc2chapter.sg/events?utm_source=chatgpt.com</t>
+          <t>https://www.isc2chapter.sg/events</t>
         </is>
       </c>
     </row>
@@ -14998,7 +14998,7 @@
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>https://siarb.org.sg/?utm_source=chatgpt.com</t>
+          <t>https://siarb.org.sg/</t>
         </is>
       </c>
     </row>
@@ -15018,7 +15018,7 @@
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>https://ciarbsingapore.wildapricot.org/events?utm_source=chatgpt.com</t>
+          <t>https://ciarbsingapore.wildapricot.org/events</t>
         </is>
       </c>
     </row>
@@ -15038,7 +15038,7 @@
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>https://www.acc.com/webview/events?utm_source=chatgpt.com</t>
+          <t>https://www.acc.com/webview/events</t>
         </is>
       </c>
     </row>
@@ -15058,7 +15058,7 @@
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>https://www.fwasg.org/events/Default.aspx?utm_source=chatgpt.com</t>
+          <t>https://www.fwasg.org/events/Default.aspx</t>
         </is>
       </c>
     </row>
@@ -15078,7 +15078,7 @@
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>https://caia.org/chapter-locations/caia-chapter-singapore/?utm_source=chatgpt.com</t>
+          <t>https://caia.org/chapter-locations/caia-chapter-singapore/</t>
         </is>
       </c>
     </row>
@@ -15098,7 +15098,7 @@
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>https://www.isda.org/location/singapore/?utm_source=chatgpt.com</t>
+          <t>https://www.isda.org/location/singapore/</t>
         </is>
       </c>
     </row>
@@ -15118,7 +15118,7 @@
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>https://www.traceinternational.org/events?utm_source=chatgpt.com</t>
+          <t>https://www.traceinternational.org/events</t>
         </is>
       </c>
     </row>
@@ -15138,7 +15138,7 @@
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>https://members.agrc.org/events/event_list.asp?group=258545&amp;show=&amp;utm_source=chatgpt.com</t>
+          <t>https://members.agrc.org/events/event_list.asp?group=258545</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>https://iapp.org/events/?utm_source=chatgpt.com</t>
+          <t>https://iapp.org/events/</t>
         </is>
       </c>
     </row>
@@ -15178,7 +15178,7 @@
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>https://www.int-comp.org/events/?utm_source=chatgpt.com</t>
+          <t>https://www.int-comp.org/events/</t>
         </is>
       </c>
     </row>
@@ -15198,7 +15198,7 @@
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>https://www.acfe.com/?utm_source=chatgpt.com</t>
+          <t>https://www.acfe.com/</t>
         </is>
       </c>
     </row>
@@ -15218,7 +15218,7 @@
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
-          <t>https://www.acams.org/en/events?utm_source=chatgpt.com</t>
+          <t>https://www.acams.org/en/events</t>
         </is>
       </c>
     </row>
@@ -15238,7 +15238,7 @@
       </c>
       <c r="D69" s="16" t="inlineStr">
         <is>
-          <t>https://www.acga-asia.org/events.php?utm_source=chatgpt.com</t>
+          <t>https://www.acga-asia.org/events.php</t>
         </is>
       </c>
     </row>
@@ -15258,7 +15258,7 @@
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>https://www.reitas.sg/events/upcoming-events/?utm_source=chatgpt.com</t>
+          <t>https://www.reitas.sg/events/upcoming-events/</t>
         </is>
       </c>
     </row>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="D71" s="16" t="inlineStr">
         <is>
-          <t>https://singaporefintech.org/event/?utm_source=chatgpt.com</t>
+          <t>https://singaporefintech.org/event/</t>
         </is>
       </c>
     </row>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="D72" s="16" t="inlineStr">
         <is>
-          <t>https://www.ibf.org.sg/?utm_source=chatgpt.com</t>
+          <t>https://www.ibf.org.sg/</t>
         </is>
       </c>
     </row>
@@ -15318,7 +15318,7 @@
       </c>
       <c r="D73" s="16" t="inlineStr">
         <is>
-          <t>https://www.aima.org/events/aima-conferences-information/aima-singapore-forum.html?utm_source=chatgpt.com</t>
+          <t>https://www.aima.org/events/aima-conferences-information/aima-singapore-forum.html</t>
         </is>
       </c>
     </row>
@@ -15338,7 +15338,7 @@
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>https://www.theirm.org/events/?utm_source=chatgpt.com</t>
+          <t>https://www.theirm.org/events/</t>
         </is>
       </c>
     </row>
@@ -15358,7 +15358,7 @@
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>https://www.treasurers.org/events-and-networking/upcoming-events/?utm_source=chatgpt.com</t>
+          <t>https://www.treasurers.org/events-and-networking/upcoming-events/</t>
         </is>
       </c>
     </row>
@@ -15378,7 +15378,7 @@
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>https://events2go.iccwbo.org/?utm_source=chatgpt.com</t>
+          <t>https://events2go.iccwbo.org/</t>
         </is>
       </c>
     </row>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>https://www.ibanet.org/conferences-events?utm_source=chatgpt.com</t>
+          <t>https://www.ibanet.org/conferences-events</t>
         </is>
       </c>
     </row>
@@ -15418,7 +15418,7 @@
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>https://www.ifa.nl/events?utm_source=chatgpt.com</t>
+          <t>https://www.ifa.nl/events</t>
         </is>
       </c>
     </row>
@@ -15438,7 +15438,7 @@
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>https://www.step.org/events?utm_source=chatgpt.com</t>
+          <t>https://www.step.org/events</t>
         </is>
       </c>
     </row>
@@ -15458,7 +15458,7 @@
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>https://www.internationaltaxreview.com/events?utm_source=chatgpt.com</t>
+          <t>https://www.internationaltaxreview.com/events</t>
         </is>
       </c>
     </row>
@@ -15478,7 +15478,7 @@
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>https://www.ibanet.org/conferences-events?utm_source=chatgpt.com</t>
+          <t>https://www.ibanet.org/conferences-events</t>
         </is>
       </c>
     </row>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>https://www.aija.org/events/?utm_source=chatgpt.com</t>
+          <t>https://www.aija.org/events/</t>
         </is>
       </c>
     </row>
@@ -15518,7 +15518,7 @@
       </c>
       <c r="D83" s="16" t="inlineStr">
         <is>
-          <t>https://www.ipba.org/events/?utm_source=chatgpt.com</t>
+          <t>https://www.ipba.org/events/</t>
         </is>
       </c>
     </row>
@@ -15538,7 +15538,7 @@
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>https://www.uianet.org/en/events?utm_source=chatgpt.com</t>
+          <t>https://www.uianet.org/en/events</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="D85" s="16" t="inlineStr">
         <is>
-          <t>https://www.worldcc.com/Events?utm_source=chatgpt.com</t>
+          <t>https://www.worldcc.com/Events</t>
         </is>
       </c>
     </row>
@@ -15578,7 +15578,7 @@
       </c>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>https://www.cips.org/events?utm_source=chatgpt.com</t>
+          <t>https://www.cips.org/events</t>
         </is>
       </c>
     </row>
@@ -15598,7 +15598,7 @@
       </c>
       <c r="D87" s="16" t="inlineStr">
         <is>
-          <t>https://www.ismworld.org/events/?utm_source=chatgpt.com</t>
+          <t>https://www.ismworld.org/events/</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>https://www.afponline.org/events?utm_source=chatgpt.com</t>
+          <t>https://www.afponline.org/events</t>
         </is>
       </c>
     </row>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>https://www.garp.org/events?utm_source=chatgpt.com</t>
+          <t>https://www.garp.org/events</t>
         </is>
       </c>
     </row>
@@ -15658,7 +15658,7 @@
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>https://www.prmia.org/events?utm_source=chatgpt.com</t>
+          <t>https://www.prmia.org/events</t>
         </is>
       </c>
     </row>
@@ -15678,7 +15678,7 @@
       </c>
       <c r="D91" s="16" t="inlineStr">
         <is>
-          <t>https://www.gacp.org/events?utm_source=chatgpt.com</t>
+          <t>https://www.gacp.org/events</t>
         </is>
       </c>
     </row>
@@ -15698,7 +15698,7 @@
       </c>
       <c r="D92" s="16" t="inlineStr">
         <is>
-          <t>https://www.acfcs.org/events?utm_source=chatgpt.com</t>
+          <t>https://www.acfcs.org/events</t>
         </is>
       </c>
     </row>
@@ -15718,7 +15718,7 @@
       </c>
       <c r="D93" s="16" t="inlineStr">
         <is>
-          <t>https://www.iais.org/activities-meetings/?utm_source=chatgpt.com</t>
+          <t>https://www.iais.org/activities-meetings/</t>
         </is>
       </c>
     </row>
@@ -15738,7 +15738,7 @@
       </c>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>https://www.iosco.org/events/?utm_source=chatgpt.com</t>
+          <t>https://www.iosco.org/events/</t>
         </is>
       </c>
     </row>
@@ -15758,7 +15758,7 @@
       </c>
       <c r="D95" s="16" t="inlineStr">
         <is>
-          <t>https://www.internationalinsuranceprofessionals.org/events?utm_source=chatgpt.com</t>
+          <t>https://www.internationalinsuranceprofessionals.org/events</t>
         </is>
       </c>
     </row>
@@ -15778,7 +15778,7 @@
       </c>
       <c r="D96" s="16" t="inlineStr">
         <is>
-          <t>https://www.globalreporting.org/events/?utm_source=chatgpt.com</t>
+          <t>https://www.globalreporting.org/events/</t>
         </is>
       </c>
     </row>
@@ -15798,7 +15798,7 @@
       </c>
       <c r="D97" s="16" t="inlineStr">
         <is>
-          <t>https://www.ifrs.org/news-and-events/events/?utm_source=chatgpt.com</t>
+          <t>https://www.ifrs.org/news-and-events/events/</t>
         </is>
       </c>
     </row>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="D98" s="16" t="inlineStr">
         <is>
-          <t>https://www.ifrs.org/news-and-events/events/?utm_source=chatgpt.com</t>
+          <t>https://www.ifrs.org/news-and-events/events/</t>
         </is>
       </c>
     </row>
@@ -15838,7 +15838,7 @@
       </c>
       <c r="D99" s="16" t="inlineStr">
         <is>
-          <t>https://www.weforum.org/events/?utm_source=chatgpt.com</t>
+          <t>https://www.weforum.org/events/</t>
         </is>
       </c>
     </row>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="D100" s="16" t="inlineStr">
         <is>
-          <t>https://uncitral.un.org/en/events?utm_source=chatgpt.com</t>
+          <t>https://uncitral.un.org/en/events</t>
         </is>
       </c>
     </row>
@@ -19116,7 +19116,7 @@
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>https://www.aopauae.com/events?utm_source=chatgpt.com</t>
+          <t>https://www.aopauae.com/events</t>
         </is>
       </c>
     </row>
@@ -19136,7 +19136,7 @@
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>https://mail.aaa4uae.ae/site/en/eaaa?utm_source=chatgpt.com</t>
+          <t>https://mail.aaa4uae.ae/site/en/eaaa</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>https://www.garp.org/membership/chapter/united-arab-emirates?utm_source=chatgpt.com</t>
+          <t>https://www.garp.org/membership/chapter/united-arab-emirates</t>
         </is>
       </c>
     </row>
@@ -19176,7 +19176,7 @@
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>https://www.acfe.com/calendar?utm_source=chatgpt.com</t>
+          <t>https://www.acfe.com/calendar</t>
         </is>
       </c>
     </row>
@@ -19196,7 +19196,7 @@
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>https://slba.ae/events/?utm_source=chatgpt.com</t>
+          <t>https://slba.ae/events/</t>
         </is>
       </c>
     </row>
@@ -19216,7 +19216,7 @@
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>https://academy.adgm.com/events/?utm_source=chatgpt.com</t>
+          <t>https://academy.adgm.com/events/</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>https://ajmanchamber.ae/en/archives/exhibitions-conferences/?utm_source=chatgpt.com</t>
+          <t>https://ajmanchamber.ae/en/archives/exhibitions-conferences/</t>
         </is>
       </c>
     </row>
@@ -19256,7 +19256,7 @@
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>https://rakchamber.ae/?utm_source=chatgpt.com</t>
+          <t>https://rakchamber.ae/</t>
         </is>
       </c>
     </row>
@@ -19276,7 +19276,7 @@
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>https://www.fujairahchamber.ae/?utm_source=chatgpt.com</t>
+          <t>https://www.fujairahchamber.ae/</t>
         </is>
       </c>
     </row>
@@ -19296,7 +19296,7 @@
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>https://uaqchamber.ae/?utm_source=chatgpt.com</t>
+          <t>https://uaqchamber.ae/</t>
         </is>
       </c>
     </row>
@@ -19316,7 +19316,7 @@
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>https://www.irishbusinessnetwork.org/events/?utm_source=chatgpt.com</t>
+          <t>https://www.irishbusinessnetwork.org/events/</t>
         </is>
       </c>
     </row>
@@ -19336,7 +19336,7 @@
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>https://www.sbcuae.se/events?utm_source=chatgpt.com</t>
+          <t>https://www.sbcuae.se/events</t>
         </is>
       </c>
     </row>
@@ -19356,7 +19356,7 @@
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>https://www.bbc-uae.com/events?utm_source=chatgpt.com</t>
+          <t>https://www.bbc-uae.com/events</t>
         </is>
       </c>
     </row>
@@ -19376,7 +19376,7 @@
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>https://www.sbcuae.org/events?utm_source=chatgpt.com</t>
+          <t>https://www.sbcuae.org/events</t>
         </is>
       </c>
     </row>
@@ -19396,7 +19396,7 @@
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>https://www.diac.com/en/events/?utm_source=chatgpt.com</t>
+          <t>https://www.diac.com/en/events/</t>
         </is>
       </c>
     </row>
@@ -19416,7 +19416,7 @@
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>https://www.adjd.gov.ae/EN/Pages/Events.aspx?utm_source=chatgpt.com</t>
+          <t>https://www.adjd.gov.ae/EN/Pages/Events.aspx</t>
         </is>
       </c>
     </row>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
-          <t>https://www.dld.gov.ae/?utm_source=chatgpt.com</t>
+          <t>https://www.dld.gov.ae/</t>
         </is>
       </c>
     </row>
@@ -19456,7 +19456,7 @@
       </c>
       <c r="D69" s="16" t="inlineStr">
         <is>
-          <t>https://www.emirateslegalnetwork.com/events?utm_source=chatgpt.com</t>
+          <t>https://www.emirateslegalnetwork.com/events</t>
         </is>
       </c>
     </row>
@@ -19476,7 +19476,7 @@
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>https://cms.law/en/are/events?utm_source=chatgpt.com</t>
+          <t>https://cms.law/en/are/events</t>
         </is>
       </c>
     </row>
@@ -19496,7 +19496,7 @@
       </c>
       <c r="D71" s="16" t="inlineStr">
         <is>
-          <t>https://mena.thomsonreuters.com/en/events.html?utm_source=chatgpt.com</t>
+          <t>https://mena.thomsonreuters.com/en/events.html</t>
         </is>
       </c>
     </row>
@@ -19516,7 +19516,7 @@
       </c>
       <c r="D72" s="16" t="inlineStr">
         <is>
-          <t>https://www.bakertilly.ae/events?utm_source=chatgpt.com</t>
+          <t>https://www.bakertilly.ae/events</t>
         </is>
       </c>
     </row>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="D73" s="16" t="inlineStr">
         <is>
-          <t>https://www.grantthornton.ae/events/?utm_source=chatgpt.com</t>
+          <t>https://www.grantthornton.ae/events/</t>
         </is>
       </c>
     </row>
@@ -19556,7 +19556,7 @@
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>https://www.crowe.com/ae/events?utm_source=chatgpt.com</t>
+          <t>https://www.crowe.com/ae/events</t>
         </is>
       </c>
     </row>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>https://www.deloitte.com/middle-east/en/events.html?utm_source=chatgpt.com</t>
+          <t>https://www.deloitte.com/middle-east/en/events.html</t>
         </is>
       </c>
     </row>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>https://www.bdo.ae/en-gb/events?utm_source=chatgpt.com</t>
+          <t>https://www.bdo.ae/en-gb/events</t>
         </is>
       </c>
     </row>
@@ -19616,7 +19616,7 @@
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>https://kpmg.com/ae/en/home/events.html?utm_source=chatgpt.com</t>
+          <t>https://kpmg.com/ae/en/home/events.html</t>
         </is>
       </c>
     </row>
@@ -19636,7 +19636,7 @@
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>https://www.pwc.com/m1/en/events.html?utm_source=chatgpt.com</t>
+          <t>https://www.pwc.com/m1/en/events.html</t>
         </is>
       </c>
     </row>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>https://www.ey.com/en_ae/events?utm_source=chatgpt.com</t>
+          <t>https://www.ey.com/en_ae/events</t>
         </is>
       </c>
     </row>
@@ -19676,7 +19676,7 @@
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>https://uaeiaa.org/events-calendar?utm_source=chatgpt.com</t>
+          <t>https://uaeiaa.org/events-calendar</t>
         </is>
       </c>
     </row>
@@ -19696,7 +19696,7 @@
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>https://www.cisi.org/cisiweb2/events?utm_source=chatgpt.com</t>
+          <t>https://www.cisi.org/cisiweb2/events</t>
         </is>
       </c>
     </row>
@@ -19716,7 +19716,7 @@
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>https://www.globalethicalfinance.org/our-events/?utm_source=chatgpt.com</t>
+          <t>https://www.globalethicalfinance.org/our-events/</t>
         </is>
       </c>
     </row>
@@ -19736,7 +19736,7 @@
       </c>
       <c r="D83" s="16" t="inlineStr">
         <is>
-          <t>https://www.dsig.ae/upcoming-events/?utm_source=chatgpt.com</t>
+          <t>https://www.dsig.ae/upcoming-events/</t>
         </is>
       </c>
     </row>
@@ -19756,7 +19756,7 @@
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>https://academy.adgm.com/events/?utm_source=chatgpt.com</t>
+          <t>https://academy.adgm.com/events/</t>
         </is>
       </c>
     </row>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="D85" s="16" t="inlineStr">
         <is>
-          <t>https://moiat.gov.ae/en/media-center/events?utm_source=chatgpt.com</t>
+          <t>https://moiat.gov.ae/en/media-center/events</t>
         </is>
       </c>
     </row>
@@ -19796,7 +19796,7 @@
       </c>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>https://rakchamber.ae/?utm_source=chatgpt.com</t>
+          <t>https://rakchamber.ae/</t>
         </is>
       </c>
     </row>
@@ -19816,7 +19816,7 @@
       </c>
       <c r="D87" s="16" t="inlineStr">
         <is>
-          <t>https://www.aopauae.com/events?utm_source=chatgpt.com</t>
+          <t>https://www.aopauae.com/events</t>
         </is>
       </c>
     </row>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>https://www.abudhabichamber.ae/en?utm_source=chatgpt.com</t>
+          <t>https://www.abudhabichamber.ae/en</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>https://ajmanchamber.ae/en/archives/exhibitions-conferences/?utm_source=chatgpt.com</t>
+          <t>https://ajmanchamber.ae/en/archives/exhibitions-conferences/</t>
         </is>
       </c>
     </row>
@@ -20948,7 +20948,7 @@
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>https://www.taxinstitute.com.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.taxinstitute.com.au/events</t>
         </is>
       </c>
     </row>
@@ -20968,7 +20968,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>https://www.cpaaustralia.com.au/professional-development/conferences-and-events?utm_source=chatgpt.com</t>
+          <t>https://www.cpaaustralia.com.au/professional-development/conferences-and-events</t>
         </is>
       </c>
     </row>
@@ -20988,7 +20988,7 @@
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>https://www.charteredaccountants.com.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.charteredaccountants.com.au/events</t>
         </is>
       </c>
     </row>
@@ -21008,7 +21008,7 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>https://www.publicaccountants.org.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.publicaccountants.org.au/events</t>
         </is>
       </c>
     </row>
@@ -21028,7 +21028,7 @@
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>https://ifpa.com.au/events/?utm_source=chatgpt.com</t>
+          <t>https://ifpa.com.au/events/</t>
         </is>
       </c>
     </row>
@@ -21048,7 +21048,7 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>https://ifa-australia.com.au/?utm_source=chatgpt.com</t>
+          <t>https://ifa-australia.com.au/</t>
         </is>
       </c>
     </row>
@@ -21068,7 +21068,7 @@
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>https://www.atma.com.au/?utm_source=chatgpt.com</t>
+          <t>https://www.atma.com.au/</t>
         </is>
       </c>
     </row>
@@ -21088,7 +21088,7 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>https://faaa.au/events/?utm_source=chatgpt.com</t>
+          <t>https://faaa.au/events/</t>
         </is>
       </c>
     </row>
@@ -21108,7 +21108,7 @@
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>https://www.smsfassociation.com/events?utm_source=chatgpt.com</t>
+          <t>https://www.smsfassociation.com/events</t>
         </is>
       </c>
     </row>
@@ -21128,7 +21128,7 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>https://www.aist.asn.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.aist.asn.au/events</t>
         </is>
       </c>
     </row>
@@ -21148,7 +21148,7 @@
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>https://www.afma.com.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.afma.com.au/events</t>
         </is>
       </c>
     </row>
@@ -21168,7 +21168,7 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>https://www.ausbanking.org.au/events/?utm_source=chatgpt.com</t>
+          <t>https://www.ausbanking.org.au/events/</t>
         </is>
       </c>
     </row>
@@ -21188,7 +21188,7 @@
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>https://fsc.org.au/events?utm_source=chatgpt.com</t>
+          <t>https://fsc.org.au/events</t>
         </is>
       </c>
     </row>
@@ -21208,7 +21208,7 @@
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>https://www.governanceinstitute.com.au/events/?utm_source=chatgpt.com</t>
+          <t>https://www.governanceinstitute.com.au/events/</t>
         </is>
       </c>
     </row>
@@ -21228,7 +21228,7 @@
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>https://arita.com.au/events?utm_source=chatgpt.com</t>
+          <t>https://arita.com.au/events</t>
         </is>
       </c>
     </row>
@@ -21248,7 +21248,7 @@
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>https://lawcouncil.au/events?utm_source=chatgpt.com</t>
+          <t>https://lawcouncil.au/events</t>
         </is>
       </c>
     </row>
@@ -21268,7 +21268,7 @@
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>https://www.lawsociety.com.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.lawsociety.com.au/events</t>
         </is>
       </c>
     </row>
@@ -21288,7 +21288,7 @@
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>https://www.liv.asn.au/Events?utm_source=chatgpt.com</t>
+          <t>https://www.liv.asn.au/Events</t>
         </is>
       </c>
     </row>
@@ -21308,7 +21308,7 @@
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>https://www.qls.com.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.qls.com.au/events</t>
         </is>
       </c>
     </row>
@@ -21328,7 +21328,7 @@
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>https://www.lawsocietysa.asn.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.lawsocietysa.asn.au/events</t>
         </is>
       </c>
     </row>
@@ -21348,7 +21348,7 @@
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>https://www.lawsocietywa.asn.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.lawsocietywa.asn.au/events</t>
         </is>
       </c>
     </row>
@@ -21368,7 +21368,7 @@
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>https://www.lst.org.au/events/?utm_source=chatgpt.com</t>
+          <t>https://www.lst.org.au/events/</t>
         </is>
       </c>
     </row>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>https://lawsocietynt.com.au/events/?utm_source=chatgpt.com</t>
+          <t>https://lawsocietynt.com.au/events/</t>
         </is>
       </c>
     </row>
@@ -21408,7 +21408,7 @@
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>https://www.cla.org.au/Home?utm_source=chatgpt.com</t>
+          <t>https://www.cla.org.au/Home</t>
         </is>
       </c>
     </row>
@@ -21428,7 +21428,7 @@
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>https://www.academyoflaw.org.au/events-and-videos?utm_source=chatgpt.com</t>
+          <t>https://www.academyoflaw.org.au/events-and-videos</t>
         </is>
       </c>
     </row>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>https://www.aala.org.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.aala.org.au/events</t>
         </is>
       </c>
     </row>
@@ -21468,7 +21468,7 @@
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>https://www.accaustralia.com.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.accaustralia.com.au/events</t>
         </is>
       </c>
     </row>
@@ -21488,7 +21488,7 @@
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>https://www.aicd.com.au/events.html?utm_source=chatgpt.com</t>
+          <t>https://www.aicd.com.au/events.html</t>
         </is>
       </c>
     </row>
@@ -21508,7 +21508,7 @@
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>https://www.aicm.com.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.aicm.com.au/events</t>
         </is>
       </c>
     </row>
@@ -21528,7 +21528,7 @@
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>https://www.financialcounsellingaustralia.org.au/events/?utm_source=chatgpt.com</t>
+          <t>https://www.financialcounsellingaustralia.org.au/events/</t>
         </is>
       </c>
     </row>
@@ -21548,7 +21548,7 @@
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>https://www.afp.org.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.afp.org.au/events</t>
         </is>
       </c>
     </row>
@@ -21568,7 +21568,7 @@
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>https://www.arpi.org.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.arpi.org.au/events</t>
         </is>
       </c>
     </row>
@@ -21588,7 +21588,7 @@
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>https://www.rmia.org.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.rmia.org.au/events</t>
         </is>
       </c>
     </row>
@@ -21608,7 +21608,7 @@
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>https://www.aim.com.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.aim.com.au/events</t>
         </is>
       </c>
     </row>
@@ -21628,7 +21628,7 @@
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>https://aimwa.com/events/?utm_source=chatgpt.com</t>
+          <t>https://aimwa.com/events/</t>
         </is>
       </c>
     </row>
@@ -21648,7 +21648,7 @@
       </c>
       <c r="D37" s="16" t="inlineStr">
         <is>
-          <t>https://www.aiqs.com.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.aiqs.com.au/events</t>
         </is>
       </c>
     </row>
@@ -21668,7 +21668,7 @@
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>https://www.propertycouncil.com.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.propertycouncil.com.au/events</t>
         </is>
       </c>
     </row>
@@ -21688,7 +21688,7 @@
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
-          <t>https://www.api.org.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.api.org.au/events</t>
         </is>
       </c>
     </row>
@@ -21708,7 +21708,7 @@
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>https://www.australianpayrollassociation.com.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.australianpayrollassociation.com.au/events</t>
         </is>
       </c>
     </row>
@@ -21728,7 +21728,7 @@
       </c>
       <c r="D41" s="16" t="inlineStr">
         <is>
-          <t>https://taps.associationonline.com.au/events/?utm_source=chatgpt.com</t>
+          <t>https://taps.associationonline.com.au/events/</t>
         </is>
       </c>
     </row>
@@ -21748,7 +21748,7 @@
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>https://aana.com.au/events/?utm_source=chatgpt.com</t>
+          <t>https://aana.com.au/events/</t>
         </is>
       </c>
     </row>
@@ -21768,7 +21768,7 @@
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>https://www.aicd.com.au/events.html?utm_source=chatgpt.com</t>
+          <t>https://www.aicd.com.au/events.html</t>
         </is>
       </c>
     </row>
@@ -21788,7 +21788,7 @@
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>https://www.abl.com.au/events/?utm_source=chatgpt.com</t>
+          <t>https://www.abl.com.au/events/</t>
         </is>
       </c>
     </row>
@@ -21808,7 +21808,7 @@
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>https://www.thomsonreuters.com.au/en-au/events.html?utm_source=chatgpt.com</t>
+          <t>https://www.thomsonreuters.com.au/en-au/events.html</t>
         </is>
       </c>
     </row>
@@ -21828,7 +21828,7 @@
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>https://www.tved.net.au/?utm_source=chatgpt.com</t>
+          <t>https://www.tved.net.au/</t>
         </is>
       </c>
     </row>
@@ -21848,7 +21848,7 @@
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>https://legalwiseseminars.com.au/events/?utm_source=chatgpt.com</t>
+          <t>https://legalwiseseminars.com.au/events/</t>
         </is>
       </c>
     </row>
@@ -21868,7 +21868,7 @@
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>https://www.leocussen.edu.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.leocussen.edu.au/events</t>
         </is>
       </c>
     </row>
@@ -21888,7 +21888,7 @@
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>https://www.collaw.edu.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.collaw.edu.au/events</t>
         </is>
       </c>
     </row>
@@ -21908,7 +21908,7 @@
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>https://www.aicd.com.au/events.html?utm_source=chatgpt.com</t>
+          <t>https://www.aicd.com.au/events.html</t>
         </is>
       </c>
     </row>
@@ -21928,7 +21928,7 @@
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>https://www.aicd.com.au/events.html?utm_source=chatgpt.com</t>
+          <t>https://www.aicd.com.au/events.html</t>
         </is>
       </c>
     </row>
@@ -22748,7 +22748,7 @@
       </c>
       <c r="D92" s="16" t="inlineStr">
         <is>
-          <t>https://cfas.org.au/events/?utm_source=chatgpt.com</t>
+          <t>https://cfas.org.au/events/</t>
         </is>
       </c>
     </row>
@@ -22768,7 +22768,7 @@
       </c>
       <c r="D93" s="16" t="inlineStr">
         <is>
-          <t>https://erlaw.org.au/events/?utm_source=chatgpt.com</t>
+          <t>https://erlaw.org.au/events/</t>
         </is>
       </c>
     </row>
@@ -22788,7 +22788,7 @@
       </c>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>https://www.fintechaustralia.org.au/events/?utm_source=chatgpt.com</t>
+          <t>https://www.fintechaustralia.org.au/events/</t>
         </is>
       </c>
     </row>
@@ -22808,7 +22808,7 @@
       </c>
       <c r="D95" s="15" t="inlineStr">
         <is>
-          <t>https://www.mfaa.com.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.mfaa.com.au/events</t>
         </is>
       </c>
     </row>
@@ -22828,7 +22828,7 @@
       </c>
       <c r="D96" s="16" t="inlineStr">
         <is>
-          <t>https://shop.bfsla.org/?utm_source=chatgpt.com</t>
+          <t>https://shop.bfsla.org/</t>
         </is>
       </c>
     </row>
@@ -22848,7 +22848,7 @@
       </c>
       <c r="D97" s="16" t="inlineStr">
         <is>
-          <t>https://www.afia.asn.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.afia.asn.au/events</t>
         </is>
       </c>
     </row>
@@ -22868,7 +22868,7 @@
       </c>
       <c r="D98" s="16" t="inlineStr">
         <is>
-          <t>https://www.finpro.org.au/?utm_source=chatgpt.com</t>
+          <t>https://www.finpro.org.au/</t>
         </is>
       </c>
     </row>
@@ -22888,7 +22888,7 @@
       </c>
       <c r="D99" s="16" t="inlineStr">
         <is>
-          <t>https://pecbookings.eventsair.com/alla2026/?utm_source=chatgpt.com</t>
+          <t>https://pecbookings.eventsair.com/alla2026/</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="D100" s="16" t="inlineStr">
         <is>
-          <t>https://www.vscl.org.au/?utm_source=chatgpt.com</t>
+          <t>https://www.vscl.org.au/</t>
         </is>
       </c>
     </row>
@@ -22928,7 +22928,7 @@
       </c>
       <c r="D101" s="16" t="inlineStr">
         <is>
-          <t>https://www.claanz.org.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.claanz.org.au/events</t>
         </is>
       </c>
     </row>
@@ -22948,7 +22948,7 @@
       </c>
       <c r="D102" s="16" t="inlineStr">
         <is>
-          <t>https://www.probonocentre.org.au/news-media-2/events-and-conferences/?utm_source=chatgpt.com</t>
+          <t>https://www.probonocentre.org.au/news-media-2/events-and-conferences/</t>
         </is>
       </c>
     </row>
@@ -22968,7 +22968,7 @@
       </c>
       <c r="D103" s="16" t="inlineStr">
         <is>
-          <t>https://www.scla.org.au/events/?utm_source=chatgpt.com</t>
+          <t>https://www.scla.org.au/events/</t>
         </is>
       </c>
     </row>
@@ -22988,7 +22988,7 @@
       </c>
       <c r="D104" s="16" t="inlineStr">
         <is>
-          <t>https://www.tved.net.au/?utm_source=chatgpt.com</t>
+          <t>https://www.tved.net.au/</t>
         </is>
       </c>
     </row>
@@ -23008,7 +23008,7 @@
       </c>
       <c r="D105" s="16" t="inlineStr">
         <is>
-          <t>https://ifpa.com.au/events/?utm_source=chatgpt.com</t>
+          <t>https://ifpa.com.au/events/</t>
         </is>
       </c>
     </row>
@@ -23028,7 +23028,7 @@
       </c>
       <c r="D106" s="16" t="inlineStr">
         <is>
-          <t>https://www.afaanz.org/conference?utm_source=chatgpt.com</t>
+          <t>https://www.afaanz.org/conference</t>
         </is>
       </c>
     </row>
@@ -23048,7 +23048,7 @@
       </c>
       <c r="D107" s="16" t="inlineStr">
         <is>
-          <t>https://taps.associationonline.com.au/events/?utm_source=chatgpt.com</t>
+          <t>https://taps.associationonline.com.au/events/</t>
         </is>
       </c>
     </row>
@@ -23068,7 +23068,7 @@
       </c>
       <c r="D108" s="16" t="inlineStr">
         <is>
-          <t>https://www.api.org.au/events?utm_source=chatgpt.com</t>
+          <t>https://www.api.org.au/events</t>
         </is>
       </c>
     </row>

--- a/Sources/Event_scrapper_-_Website_completed.xlsx
+++ b/Sources/Event_scrapper_-_Website_completed.xlsx
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D221"/>
+  <dimension ref="A1:D209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="4" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -581,3647 +581,3647 @@
       </c>
     </row>
     <row r="2" ht="28.8" customHeight="1">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>ICAI – CPE Directorate</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Tax, Finance, Accounting, Corporate Law</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>https://www.icai.org/committeeevents.shtml</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28.8" customHeight="1">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>ICAI – International Taxation Committee</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>International Tax</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>https://www.icai.org/category/international-taxation-committee</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>ICAI – GST &amp; Indirect Taxes Committee</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>GST / Indirect Tax</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>https://idtc.icai.org/upcoming-events.php</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28.8" customHeight="1">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>ICAI – Digital Accounting &amp; Assurance Board</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Accounting / Audit / Finance</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>https://daab.icai.org/events</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28.8" customHeight="1">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>ICAI – Placement Directorate</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Finance / Tax / Accounting</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>https://ipd.icai.org/</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28.8" customHeight="1">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>ICAI – Committee for Members in Practice</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Practice / Tax / Finance</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>https://cmp.icai.org/upcoming-events/</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28.8" customHeight="1">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>ICAI – Bengaluru Branch</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Tax / Finance / Accounting</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>https://bangaloreicai.org/member/events</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28.8" customHeight="1">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>ICAI – Nagpur Branch</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Tax / Finance / Accounting</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>https://www.nagpuricai.org/upcoming-events.php</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28.8" customHeight="1">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>ICAI – Gurugram Branch</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Tax / Finance / Accounting</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>https://icaigurugram.org/members/events</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28.8" customHeight="1">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>ICAI – Thiruvananthapuram Branch</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Tax / Finance / Accounting</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>https://thiruvananthapuramicai.org/event_type/members-event/</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28.8" customHeight="1">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>ICSI</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Corporate Law / Governance / Finance</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>https://www.icsi.edu/events/</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28.8" customHeight="1">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>ICMAI</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Cost Accounting / Finance / Tax</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>https://icmai.in/ClntAbout/Events</t>
         </is>
       </c>
     </row>
     <row r="14" ht="43.2" customHeight="1">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>ICMAI RVO</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Valuation / Insolvency / Finance</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>https://www.rvoicmai.in/upcoming-events</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28.8" customHeight="1">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>ICMAI Insolvency Professional Agency</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Insolvency / Law / Finance</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>https://www.ipaicmai.in/IPANEW/ForthcomingEvents.aspx</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28.8" customHeight="1">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Indian Institute of Corporate Affairs (IICA)</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Corporate Law / Governance / Compliance</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>https://iica.nic.in/</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28.8" customHeight="1">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>IIIPI</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Insolvency / Bankruptcy / Corporate Law</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>https://www.iiipicai.in/</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28.8" customHeight="1">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>NIPFP</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Public Finance / Tax / Economics</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>https://www.nipfp.org.in/event-index-page/</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28.8" customHeight="1">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>CFA Society India</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Investment / Finance / Capital Markets</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>https://cfasocietyindia.org/upcomingevents/</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28.8" customHeight="1">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>CAFRAL</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Banking / Finance / Financial Regulation</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>https://www.cafral.org.in/images/Upcoming-Events.aspx</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Indian Institute of Banking &amp; Finance (IIBF)</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Banking / Finance</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>https://www.iibf.org.in/training</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28.8" customHeight="1">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>AIBI – Association of Investment Bankers of India</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Investment Banking / Capital Markets</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>https://aibi.org.in/event.asp</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28.8" customHeight="1">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>NSE</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Capital Markets / Finance</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>https://www.nseindia.com/event-gallery</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28.8" customHeight="1">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>NSE Academy</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Capital Markets / Investment / Finance</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>https://www.nseacademy.com/coursedatabase/</t>
         </is>
       </c>
     </row>
     <row r="25" ht="28.8" customHeight="1">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>IIBFM</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Banking / Risk / Finance</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>https://iibfm.com/</t>
         </is>
       </c>
     </row>
     <row r="26" ht="28.8" customHeight="1">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Association of Financial Advisors of India (AFAI)</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Financial Advisory / Finance</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>https://afai.in/</t>
         </is>
       </c>
     </row>
     <row r="27" ht="28.8" customHeight="1">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>FICCI</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Banking / Capital Markets / FinTech / Finance</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>https://ficci.in/event</t>
         </is>
       </c>
     </row>
     <row r="28" ht="28.8" customHeight="1">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>CII</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Finance / Banking / Tax / Business</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>https://www.cii.in/Events.aspx</t>
         </is>
       </c>
     </row>
     <row r="29" ht="28.8" customHeight="1">
-      <c r="A29" s="1" t="n">
+      <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>ASSOCHAM</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Finance / Tax / Business / Regulatory</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>https://www.assocham.org/</t>
         </is>
       </c>
     </row>
     <row r="30" ht="28.8" customHeight="1">
-      <c r="A30" s="1" t="n">
+      <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>PHD Chamber of Commerce &amp; Industry</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Finance / Tax / Business / Law</t>
         </is>
       </c>
-      <c r="D30" s="14" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>https://www.phdcci.in/events/</t>
         </is>
       </c>
     </row>
     <row r="31" ht="28.8" customHeight="1">
-      <c r="A31" s="1" t="n">
+      <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Bombay Chamber of Commerce &amp; Industry</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Finance / Tax / Business Law</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>https://www.bombaychamber.com/events/</t>
         </is>
       </c>
     </row>
     <row r="32" ht="28.8" customHeight="1">
-      <c r="A32" s="1" t="n">
+      <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Bar Association of India</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Legal / Constitutional / Commercial Law</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>https://barindia.in/</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28.8" customHeight="1">
-      <c r="A33" s="1" t="n">
+      <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Indian National Bar Association (INBA)</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Legal / Corporate Law / Policy</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>https://www.indianbarassociation.org/</t>
         </is>
       </c>
     </row>
     <row r="34" ht="28.8" customHeight="1">
-      <c r="A34" s="1" t="n">
+      <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Indian Lawyers Association</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Legal / Law &amp; Policy</t>
         </is>
       </c>
-      <c r="D34" s="15" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>https://www.indialawyers.org/event</t>
         </is>
       </c>
     </row>
     <row r="35" ht="28.8" customHeight="1">
-      <c r="A35" s="1" t="n">
+      <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Mumbai Centre for International Arbitration (MCIA)</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Arbitration / Dispute Resolution</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>https://mcia.org.in/</t>
         </is>
       </c>
     </row>
     <row r="36" ht="43.2" customHeight="1">
-      <c r="A36" s="1" t="n">
+      <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Indian Council of Arbitration</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Arbitration / Commercial Disputes</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>https://www.icaindia.co.in/</t>
         </is>
       </c>
     </row>
     <row r="37" ht="28.8" customHeight="1">
-      <c r="A37" s="1" t="n">
+      <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Indian Institute of Arbitration &amp; Mediation</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Arbitration / Mediation</t>
         </is>
       </c>
-      <c r="D37" s="13" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>https://www.arbitrationindia.com/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Indian Society of International Law</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>International Law</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>https://isilindia.org/</t>
         </is>
       </c>
     </row>
     <row r="39" ht="28.8" customHeight="1">
-      <c r="A39" s="1" t="n">
+      <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Indian Law Firms Association</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Legal Profession / Corporate Law</t>
         </is>
       </c>
-      <c r="D39" s="15" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>https://indianlawfirmsassociation.com/events/</t>
         </is>
       </c>
     </row>
     <row r="40" ht="28.8" customHeight="1">
-      <c r="A40" s="1" t="n">
+      <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>FICL – Forum of Indian Corporate Lawyers</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Corporate Law / Compliance</t>
         </is>
       </c>
-      <c r="D40" s="15" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>https://www.ficl.org.in/ficl-events</t>
         </is>
       </c>
     </row>
     <row r="41" ht="28.8" customHeight="1">
-      <c r="A41" s="1" t="n">
+      <c r="A41" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>AIPE – Association of Insolvency Professional Entities</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Insolvency / Corporate Law</t>
         </is>
       </c>
-      <c r="D41" s="15" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>https://aipe.org.in/events/</t>
         </is>
       </c>
     </row>
     <row r="42" ht="28.8" customHeight="1">
-      <c r="A42" s="1" t="n">
+      <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Indo-French Chamber of Commerce &amp; Industry (IFCCI)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Tax / Legal / Finance / Business</t>
         </is>
       </c>
-      <c r="D42" s="14" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>https://www.ifcci.org.in/events</t>
         </is>
       </c>
     </row>
     <row r="43" ht="28.8" customHeight="1">
-      <c r="A43" s="1" t="n">
+      <c r="A43" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Indo-German Chamber of Commerce (IGCC)</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Finance / Tax / Legal / Business</t>
         </is>
       </c>
-      <c r="D43" s="14" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>https://indo-german.com/</t>
         </is>
       </c>
     </row>
     <row r="44" ht="28.8" customHeight="1">
-      <c r="A44" s="1" t="n">
+      <c r="A44" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Indo-American Chamber of Commerce (IACC)</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Finance / Tax / Business Law</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>https://www.indoamerican.org/</t>
         </is>
       </c>
     </row>
     <row r="45" ht="43.2" customHeight="1">
-      <c r="A45" s="1" t="n">
+      <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Canada India Business Council</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Finance / Business / Trade Law</t>
         </is>
       </c>
-      <c r="D45" s="15" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>https://canada-indiabusiness.com/events</t>
         </is>
       </c>
     </row>
     <row r="46" ht="43.2" customHeight="1">
-      <c r="A46" s="1" t="n">
+      <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>European Business Group</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Finance / Regulatory / Business</t>
         </is>
       </c>
-      <c r="D46" s="14" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>https://ebgfederation.in/</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28.8" customHeight="1">
-      <c r="A47" s="1" t="n">
+      <c r="A47" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>MCCIA – Mahratta Chamber of Commerce</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Finance / Business / Tax / Regulatory</t>
         </is>
       </c>
-      <c r="D47" s="14" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>https://www.mcciapune.com/events</t>
         </is>
       </c>
     </row>
     <row r="48" ht="28.8" customHeight="1">
-      <c r="A48" s="1" t="n">
+      <c r="A48" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Tamil Nadu Chamber Foundation</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Finance / Business / Tax</t>
         </is>
       </c>
-      <c r="D48" s="15" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>https://www.tamilchamber.org/upcoming-events</t>
         </is>
       </c>
     </row>
     <row r="49" ht="43.2" customHeight="1">
-      <c r="A49" s="1" t="n">
+      <c r="A49" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Bangalore Chamber of Industry &amp; Commerce</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Finance / Business / Regulation</t>
         </is>
       </c>
-      <c r="D49" s="13" t="inlineStr">
+      <c r="D49" s="16" t="inlineStr">
         <is>
           <t>https://www.bcic.in/</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28.8" customHeight="1">
-      <c r="A50" s="1" t="n">
+      <c r="A50" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Delhi Chamber of Commerce</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Finance / Business / Tax / Regulation</t>
         </is>
       </c>
-      <c r="D50" s="15" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>https://delhichamber.ca/event-calendar/</t>
         </is>
       </c>
     </row>
     <row r="51" ht="43.2" customHeight="1">
-      <c r="A51" s="1" t="n">
+      <c r="A51" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Hyderabad Management Association</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Finance / Management / Business</t>
         </is>
       </c>
-      <c r="D51" s="14" t="inlineStr">
+      <c r="D51" s="16" t="inlineStr">
         <is>
           <t>https://hyma.in/</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Indian Finance Association</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="D52" s="15" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>https://indiafa.org/conferences/</t>
         </is>
       </c>
     </row>
     <row r="53" ht="28.8" customHeight="1">
-      <c r="A53" s="1" t="n">
+      <c r="A53" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Association of National Exchanges Members of India (ANMI)</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Capital Markets</t>
         </is>
       </c>
-      <c r="D53" s="15" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>https://anmi.in/anmi_front/event_platform/public/</t>
         </is>
       </c>
     </row>
     <row r="54" ht="28.8" customHeight="1">
-      <c r="A54" s="1" t="n">
+      <c r="A54" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Association of Mutual Funds in India (AMFI)</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Investment / Finance</t>
         </is>
       </c>
-      <c r="D54" s="13" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>https://www.amfiindia.com/events</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28.8" customHeight="1">
-      <c r="A55" s="1" t="n">
+      <c r="A55" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Fixed Income Money Market and Derivatives Association of India (FIMMDA)</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Fixed Income / Finance</t>
         </is>
       </c>
-      <c r="D55" s="13" t="inlineStr">
+      <c r="D55" s="16" t="inlineStr">
         <is>
           <t>https://www.fimmda.org/</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28.8" customHeight="1">
-      <c r="A56" s="1" t="n">
+      <c r="A56" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Foreign Exchange Dealers' Association of India (FEDAI)</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Forex / Banking / Finance</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr">
+      <c r="D56" s="16" t="inlineStr">
         <is>
           <t>https://www.fedai.org.in/</t>
         </is>
       </c>
     </row>
     <row r="57" ht="28.8" customHeight="1">
-      <c r="A57" s="1" t="n">
+      <c r="A57" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Primary Dealers Association of India (PDAI)</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Debt Markets / Finance</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Financial Planning Standards Board India</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Financial Planning</t>
         </is>
       </c>
-      <c r="D58" s="13" t="inlineStr">
+      <c r="D58" s="16" t="inlineStr">
         <is>
           <t>https://www.fpsbindia.org/</t>
         </is>
       </c>
     </row>
     <row r="59" ht="28.8" customHeight="1">
-      <c r="A59" s="1" t="n">
+      <c r="A59" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Indian Association of Alternative Investment Funds (IAAIF)</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Alternative Investments</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Indian Venture Capital Association (IVCA)</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>PE / VC / Finance</t>
         </is>
       </c>
-      <c r="D60" s="13" t="inlineStr">
+      <c r="D60" s="16" t="inlineStr">
         <is>
           <t>https://ivca.in/events/</t>
         </is>
       </c>
     </row>
     <row r="61" ht="28.8" customHeight="1">
-      <c r="A61" s="1" t="n">
+      <c r="A61" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Association of Leasing &amp; Financial Services Companies</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Finance / NBFC</t>
         </is>
       </c>
-      <c r="D61" s="15" t="inlineStr">
+      <c r="D61" s="16" t="inlineStr">
         <is>
           <t>https://fla.org.uk/events-and-training/events/</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Indian Banks' Association</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Banking / Finance</t>
         </is>
       </c>
-      <c r="D62" s="13" t="inlineStr">
+      <c r="D62" s="16" t="inlineStr">
         <is>
           <t>https://www.iba.org.in/</t>
         </is>
       </c>
     </row>
     <row r="63" ht="28.8" customHeight="1">
-      <c r="A63" s="1" t="n">
+      <c r="A63" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Banking Codes and Standards Board of India</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Banking / Regulation</t>
         </is>
       </c>
-      <c r="D63" s="13" t="inlineStr">
+      <c r="D63" s="16" t="inlineStr">
         <is>
           <t>https://www.bcsbi.org.in/</t>
         </is>
       </c>
     </row>
     <row r="64" ht="28.8" customHeight="1">
-      <c r="A64" s="1" t="n">
+      <c r="A64" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>Council for Insurance Ombudsmen</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Insurance / Regulation</t>
         </is>
       </c>
-      <c r="D64" s="13" t="inlineStr">
+      <c r="D64" s="16" t="inlineStr">
         <is>
           <t>https://www.cioins.co.in/</t>
         </is>
       </c>
     </row>
     <row r="65" ht="28.8" customHeight="1">
-      <c r="A65" s="1" t="n">
+      <c r="A65" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>General Insurance Council</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Insurance / Finance</t>
         </is>
       </c>
-      <c r="D65" s="13" t="inlineStr">
+      <c r="D65" s="16" t="inlineStr">
         <is>
           <t>https://www.gicouncil.in/</t>
         </is>
       </c>
     </row>
     <row r="66" ht="28.8" customHeight="1">
-      <c r="A66" s="1" t="n">
+      <c r="A66" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>Life Insurance Council</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Insurance / Finance</t>
         </is>
       </c>
-      <c r="D66" s="13" t="inlineStr">
+      <c r="D66" s="16" t="inlineStr">
         <is>
           <t>https://www.lifeinscouncil.org/</t>
         </is>
       </c>
     </row>
     <row r="67" ht="28.8" customHeight="1">
-      <c r="A67" s="1" t="n">
+      <c r="A67" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Association of Certified Financial Crime Specialists India</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Financial Crime / Compliance</t>
         </is>
       </c>
-      <c r="D67" s="15" t="inlineStr">
+      <c r="D67" s="16" t="inlineStr">
         <is>
           <t>https://www.acfcs.org/upcoming-events</t>
         </is>
       </c>
     </row>
     <row r="68" ht="28.8" customHeight="1">
-      <c r="A68" s="1" t="n">
+      <c r="A68" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>India International Exchange</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Capital Markets / Finance</t>
         </is>
       </c>
-      <c r="D68" s="13" t="inlineStr">
+      <c r="D68" s="16" t="inlineStr">
         <is>
           <t>https://www.indiainx.com/</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>Metropolitan Stock Exchange of India</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Capital Markets</t>
         </is>
       </c>
-      <c r="D69" s="13" t="inlineStr">
+      <c r="D69" s="16" t="inlineStr">
         <is>
           <t>https://www.msei.in/</t>
         </is>
       </c>
     </row>
     <row r="70" ht="28.8" customHeight="1">
-      <c r="A70" s="1" t="n">
+      <c r="A70" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>Multi Commodity Exchange of India</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Commodities / Finance</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
+      <c r="D70" s="16" t="inlineStr">
         <is>
           <t>https://www.mcxindia.com/</t>
         </is>
       </c>
     </row>
     <row r="71" ht="28.8" customHeight="1">
-      <c r="A71" s="1" t="n">
+      <c r="A71" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>National Commodity &amp; Derivatives Exchange</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Commodities / Finance</t>
         </is>
       </c>
-      <c r="D71" s="13" t="inlineStr">
+      <c r="D71" s="16" t="inlineStr">
         <is>
           <t>https://ncdex.com/</t>
         </is>
       </c>
     </row>
     <row r="72" ht="28.8" customHeight="1">
-      <c r="A72" s="1" t="n">
+      <c r="A72" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>Bombay Stock Exchange</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Capital Markets / Finance</t>
         </is>
       </c>
-      <c r="D72" s="13" t="inlineStr">
+      <c r="D72" s="16" t="inlineStr">
         <is>
           <t>https://www.bseindia.com/</t>
         </is>
       </c>
     </row>
     <row r="73" ht="28.8" customHeight="1">
-      <c r="A73" s="1" t="n">
+      <c r="A73" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>Depositories Association of India</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Securities / Finance</t>
         </is>
       </c>
-      <c r="D73" s="8" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="74" ht="28.8" customHeight="1">
-      <c r="A74" s="1" t="n">
+      <c r="A74" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>Association of Registered Investment Advisers</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Investment Advisory</t>
         </is>
       </c>
-      <c r="D74" s="15" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>https://aria.org.in/events-upcoming-past/</t>
         </is>
       </c>
     </row>
     <row r="75" ht="28.8" customHeight="1">
-      <c r="A75" s="1" t="n">
+      <c r="A75" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>Association of Investment Managers of India</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Asset Management</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>Indian Association of Pension Funds</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Pension / Finance</t>
         </is>
       </c>
-      <c r="D76" s="8" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="77" ht="28.8" customHeight="1">
-      <c r="A77" s="1" t="n">
+      <c r="A77" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>Society of Auditors</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Audit / Tax / Accounting</t>
         </is>
       </c>
-      <c r="D77" s="14" t="inlineStr">
+      <c r="D77" s="16" t="inlineStr">
         <is>
           <t>http://www.societyofauditors.org/</t>
         </is>
       </c>
     </row>
     <row r="78" ht="28.8" customHeight="1">
-      <c r="A78" s="1" t="n">
+      <c r="A78" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>Income Tax Appellate Tribunal Bar Association</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Tax / Litigation</t>
         </is>
       </c>
-      <c r="D78" s="8" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>All India Federation of Tax Practitioners</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Tax</t>
         </is>
       </c>
-      <c r="D79" s="13" t="inlineStr">
+      <c r="D79" s="16" t="inlineStr">
         <is>
           <t>https://aiftponline.org/</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>International Fiscal Association India Branch</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>International Tax</t>
         </is>
       </c>
-      <c r="D80" s="14" t="inlineStr">
+      <c r="D80" s="16" t="inlineStr">
         <is>
           <t>https://ifaindia.in/</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>GST Practitioners Association</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>GST / Tax</t>
         </is>
       </c>
-      <c r="D81" s="14" t="inlineStr">
+      <c r="D81" s="16" t="inlineStr">
         <is>
           <t>https://gstpam.org/</t>
         </is>
       </c>
     </row>
     <row r="82" ht="28.8" customHeight="1">
-      <c r="A82" s="1" t="n">
+      <c r="A82" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>Federation of Indian Export Organisations</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Trade / Tax / Finance</t>
         </is>
       </c>
-      <c r="D82" s="13" t="inlineStr">
+      <c r="D82" s="16" t="inlineStr">
         <is>
           <t>https://www.fieo.org/events</t>
         </is>
       </c>
     </row>
     <row r="83" ht="28.8" customHeight="1">
-      <c r="A83" s="1" t="n">
+      <c r="A83" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>Export Promotion Council for EOUs &amp; SEZs</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Trade / Tax / Regulatory</t>
         </is>
       </c>
-      <c r="D83" s="13" t="inlineStr">
+      <c r="D83" s="16" t="inlineStr">
         <is>
           <t>https://www.epces.in/</t>
         </is>
       </c>
     </row>
     <row r="84" ht="28.8" customHeight="1">
-      <c r="A84" s="1" t="n">
+      <c r="A84" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>Basic Chemicals, Cosmetics &amp; Dyes Export Promotion Council</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Trade / Finance / Regulation</t>
         </is>
       </c>
-      <c r="D84" s="13" t="inlineStr">
+      <c r="D84" s="16" t="inlineStr">
         <is>
           <t>https://www.chemexcil.gov.in/</t>
         </is>
       </c>
     </row>
     <row r="85" ht="28.8" customHeight="1">
-      <c r="A85" s="1" t="n">
+      <c r="A85" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>Engineering Export Promotion Council India</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Trade / Finance / Regulation</t>
         </is>
       </c>
-      <c r="D85" s="13" t="inlineStr">
+      <c r="D85" s="16" t="inlineStr">
         <is>
           <t>https://www.eepcindia.org/</t>
         </is>
       </c>
     </row>
     <row r="86" ht="28.8" customHeight="1">
-      <c r="A86" s="1" t="n">
+      <c r="A86" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="4" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>Services Export Promotion Council</t>
         </is>
       </c>
-      <c r="C86" s="4" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Trade / Finance / Regulation</t>
         </is>
       </c>
-      <c r="D86" s="13" t="inlineStr">
+      <c r="D86" s="16" t="inlineStr">
         <is>
           <t>https://servicesepc.org/</t>
         </is>
       </c>
     </row>
     <row r="87" ht="28.8" customHeight="1">
-      <c r="A87" s="1" t="n">
+      <c r="A87" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>Telecom Equipment &amp; Services Export Promotion Council</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Trade / Finance / Regulation</t>
         </is>
       </c>
-      <c r="D87" s="14" t="inlineStr">
+      <c r="D87" s="16" t="inlineStr">
         <is>
           <t>https://www.tepc.gov.in/</t>
         </is>
       </c>
     </row>
     <row r="88" ht="28.8" customHeight="1">
-      <c r="A88" s="1" t="n">
+      <c r="A88" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="4" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>Electronics and Computer Software Export Promotion Council</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Trade / Finance / Regulation</t>
         </is>
       </c>
-      <c r="D88" s="13" t="inlineStr">
+      <c r="D88" s="16" t="inlineStr">
         <is>
           <t>https://www.escindia.in/</t>
         </is>
       </c>
     </row>
     <row r="89" ht="28.8" customHeight="1">
-      <c r="A89" s="1" t="n">
+      <c r="A89" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>Council for Leather Exports</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Trade / Finance / Regulation</t>
         </is>
       </c>
-      <c r="D89" s="13" t="inlineStr">
+      <c r="D89" s="16" t="inlineStr">
         <is>
           <t>https://www.leatherindia.org/</t>
         </is>
       </c>
     </row>
     <row r="90" ht="28.8" customHeight="1">
-      <c r="A90" s="1" t="n">
+      <c r="A90" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>Indian Oilseeds &amp; Produce Export Promotion Council</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Trade / Finance</t>
         </is>
       </c>
-      <c r="D90" s="13" t="inlineStr">
+      <c r="D90" s="16" t="inlineStr">
         <is>
           <t>https://www.iopepc.org/</t>
         </is>
       </c>
     </row>
     <row r="91" ht="28.8" customHeight="1">
-      <c r="A91" s="1" t="n">
+      <c r="A91" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>Plastics Export Promotion Council</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Trade / Finance / Regulation</t>
         </is>
       </c>
-      <c r="D91" s="13" t="inlineStr">
+      <c r="D91" s="16" t="inlineStr">
         <is>
           <t>https://www.plexconcil.org/</t>
         </is>
       </c>
     </row>
     <row r="92" ht="28.8" customHeight="1">
-      <c r="A92" s="1" t="n">
+      <c r="A92" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>Indian Council of Arbitration</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Mumbai Centre for International Arbitration</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Arbitration / Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="D92" s="16" t="inlineStr">
+        <is>
+          <t>https://mcia.org.in/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="28.8" customHeight="1">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Indian Council of Legal Aid &amp; Advice</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="28.8" customHeight="1">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Indian Association of Labour Law Practitioners</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Labour Law</t>
+        </is>
+      </c>
+      <c r="D94" s="16" t="inlineStr">
+        <is>
+          <t>https://nllaindia.com/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Society of Indian Law Firms</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Legal / Corporate Law</t>
+        </is>
+      </c>
+      <c r="D95" s="16" t="inlineStr">
+        <is>
+          <t>https://www.silf.org.in/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Indian Corporate Counsel Association</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Corporate Legal / Compliance</t>
+        </is>
+      </c>
+      <c r="D96" s="16" t="inlineStr">
+        <is>
+          <t>https://ccai.net.in/?page_id=1597</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="28.8" customHeight="1">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Centre for Trade and Investment Law</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Trade Law / International Law</t>
+        </is>
+      </c>
+      <c r="D97" s="16" t="inlineStr">
+        <is>
+          <t>https://ctil.org.in/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="28.8" customHeight="1">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Indian Insolvency Professionals Association</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Insolvency / Corporate Law</t>
+        </is>
+      </c>
+      <c r="D98" s="16" t="inlineStr">
+        <is>
+          <t>https://aipe.org.in/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="28.8" customHeight="1">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Chamber of Tax Consultants (CTC)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Tax / Fiscal Law / GST</t>
+        </is>
+      </c>
+      <c r="D99" s="16" t="inlineStr">
+        <is>
+          <t>https://www.ctconline.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="28.8" customHeight="1">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Confederation of Indian Industry (CII)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Tax / Finance / Corporate Governance</t>
+        </is>
+      </c>
+      <c r="D100" s="16" t="inlineStr">
+        <is>
+          <t>https://www.cii.in/Events.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="28.8" customHeight="1">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Federation of Indian Chambers of Commerce &amp; Industry (FICCI)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Tax / Finance / Legal / Regulatory</t>
+        </is>
+      </c>
+      <c r="D101" s="16" t="inlineStr">
+        <is>
+          <t>https://ficci.in/event</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="28.8" customHeight="1">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>PHD Chamber of Commerce and Industry (PHDCCI)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Tax / Finance / Insolvency / Corporate Law</t>
+        </is>
+      </c>
+      <c r="D102" s="16" t="inlineStr">
+        <is>
+          <t>https://www.phdcci.in/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="28.8" customHeight="1">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Gulati Institute of Finance and Taxation (GIFT)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Tax / Public Finance / Fiscal Policy</t>
+        </is>
+      </c>
+      <c r="D103" s="16" t="inlineStr">
+        <is>
+          <t>https://www.gift.res.in/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="28.8" customHeight="1">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Institute of Directors, India</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Corporate Governance / Directors / Corporate Law</t>
+        </is>
+      </c>
+      <c r="D104" s="16" t="inlineStr">
+        <is>
+          <t>https://www.iodglobal.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="28.8" customHeight="1">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Institute of Internal Auditors India</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Internal Audit / Risk / Governance / Finance</t>
+        </is>
+      </c>
+      <c r="D105" s="16" t="inlineStr">
+        <is>
+          <t>https://www.iiaindia.co.in/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="28.8" customHeight="1">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>IIA Madras Chapter</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Internal Audit / Risk / Governance</t>
+        </is>
+      </c>
+      <c r="D106" s="16" t="inlineStr">
+        <is>
+          <t>https://iiamadras.org/upcoming-events</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="28.8" customHeight="1">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>IIA Bombay Chapter</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Internal Audit / Risk / Governance</t>
+        </is>
+      </c>
+      <c r="D107" s="16" t="inlineStr">
+        <is>
+          <t>https://www.iiabombay.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="28.8" customHeight="1">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>ISACA Chennai Chapter</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>IT Audit / Risk / Governance / Compliance</t>
+        </is>
+      </c>
+      <c r="D108" s="16" t="inlineStr">
+        <is>
+          <t>https://www.isacachennai.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="28.8" customHeight="1">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ISACA New Delhi Chapter</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>IT Audit / Risk / Governance</t>
+        </is>
+      </c>
+      <c r="D109" s="16" t="inlineStr">
+        <is>
+          <t>https://isacadelhi.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="28.8" customHeight="1">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Delhi International Arbitration Centre (DIAC)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Arbitration / Commercial Law / Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="D110" s="16" t="inlineStr">
+        <is>
+          <t>https://dhcdiac.nic.in/all-events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="28.8" customHeight="1">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Nani Palkhivala Arbitration Centre (NPAC)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Arbitration / Insolvency / Corporate Law</t>
+        </is>
+      </c>
+      <c r="D111" s="16" t="inlineStr">
+        <is>
+          <t>https://www.npac.in/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="28.8" customHeight="1">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Arbitration Bar of India</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Arbitration / ADR / Legal</t>
+        </is>
+      </c>
+      <c r="D112" s="16" t="inlineStr">
+        <is>
+          <t>https://arbitrationbarofindia.com/upcoming_events.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="28.8" customHeight="1">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Institute of Chartered Tax Practitioners of India (ICTPI)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Tax / Tax Practice</t>
+        </is>
+      </c>
+      <c r="D113" s="16" t="inlineStr">
+        <is>
+          <t>https://www.ictpi.in/event</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="28.8" customHeight="1">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Federation of Tax Practitioners of India (FTPI)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Tax / Tax Practice</t>
+        </is>
+      </c>
+      <c r="D114" s="16" t="inlineStr">
+        <is>
+          <t>https://www.ictpi.in/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="28.8" customHeight="1">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Independent Financial Professionals Association (IFPA)</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Professional Finance / Financial Planning</t>
+        </is>
+      </c>
+      <c r="D115" s="16" t="inlineStr">
+        <is>
+          <t>https://www.ifpaindia.in/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="28.8" customHeight="1">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>CFO India</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Corporate Finance / CFO / Financial Management</t>
+        </is>
+      </c>
+      <c r="D116" s="16" t="inlineStr">
+        <is>
+          <t>https://www.cfo-india.in/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="28.8" customHeight="1">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Institute of Internal Auditors – India / Bombay</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Internal Audit / Finance / Governance</t>
+        </is>
+      </c>
+      <c r="D117" s="16" t="inlineStr">
+        <is>
+          <t>https://www.iiaindia.co.in/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Network FP India</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Personal Finance / Financial Planning</t>
+        </is>
+      </c>
+      <c r="D118" s="16" t="inlineStr">
+        <is>
+          <t>https://www.networkfp.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="28.8" customHeight="1">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>ICT India</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Corporate Treasury / Finance</t>
+        </is>
+      </c>
+      <c r="D119" s="16" t="inlineStr">
+        <is>
+          <t>https://ict-india.org/#events</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="28.8" customHeight="1">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>India Treasury Summit</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Treasury / Corporate Finance</t>
+        </is>
+      </c>
+      <c r="D120" s="16" t="inlineStr">
+        <is>
+          <t>https://www.indiatreasurysummit.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="28.8" customHeight="1">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Treasury India</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Treasury / Corporate Finance</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="43.2" customHeight="1">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Indian National Bar Association</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Legal / Corporate Law / Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="D122" s="16" t="inlineStr">
+        <is>
+          <t>https://www.indianbarassociation.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="28.8" customHeight="1">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>International Centre for Dispute Resolution (ICDR)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
         <is>
           <t>Arbitration / Commercial Law</t>
         </is>
       </c>
-      <c r="D92" s="13" t="inlineStr">
-        <is>
-          <t>https://www.icaindia.co.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="28.8" customHeight="1">
-      <c r="A93" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai Centre for International Arbitration</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="D123" s="16" t="inlineStr">
+        <is>
+          <t>https://www.icdr.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="28.8" customHeight="1">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>India ADR Week</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Arbitration / Mediation / Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="D124" s="16" t="inlineStr">
+        <is>
+          <t>https://indiaadrweek.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="28.8" customHeight="1">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Commercial Bar Association (COMBAR)</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Commercial Litigation / Arbitration</t>
+        </is>
+      </c>
+      <c r="D125" s="16" t="inlineStr">
+        <is>
+          <t>https://www.combar.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="28.8" customHeight="1">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>London Court of International Arbitration (LCIA)</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Arbitration / Commercial Law</t>
+        </is>
+      </c>
+      <c r="D126" s="16" t="inlineStr">
+        <is>
+          <t>https://www.lcia.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="28.8" customHeight="1">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>International Bar Association (IBA)</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Legal / Tax / Arbitration</t>
+        </is>
+      </c>
+      <c r="D127" s="16" t="inlineStr">
+        <is>
+          <t>https://www.ibanet.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="28.8" customHeight="1">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>International Fiscal Association – India Academy</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>International Tax / Fiscal Law</t>
+        </is>
+      </c>
+      <c r="D128" s="16" t="inlineStr">
+        <is>
+          <t>https://ifaindia.in/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="28.8" customHeight="1">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>National Institute of Public Finance and Policy (NIPFP)</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Tax / Public Finance / Fiscal Policy</t>
+        </is>
+      </c>
+      <c r="D129" s="16" t="inlineStr">
+        <is>
+          <t>https://www.nipfp.org.in/event-index-page/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="28.8" customHeight="1">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>ISACA India</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Audit / Compliance / Risk / Governance</t>
+        </is>
+      </c>
+      <c r="D130" s="16" t="inlineStr">
+        <is>
+          <t>https://www.isaca.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="28.8" customHeight="1">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Institute of Directors India</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Corporate Governance / Corporate Law</t>
+        </is>
+      </c>
+      <c r="D131" s="16" t="inlineStr">
+        <is>
+          <t>https://www.iodglobal.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="28.8" customHeight="1">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Nani Palkhivala Arbitration Centre</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Arbitration / Commercial Disputes</t>
+        </is>
+      </c>
+      <c r="D132" s="16" t="inlineStr">
+        <is>
+          <t>https://www.npac.in/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="28.8" customHeight="1">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>National Association of Software and Service Companies – Tax Forum</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Tax / Regulatory / Finance</t>
+        </is>
+      </c>
+      <c r="D133" s="16" t="inlineStr">
+        <is>
+          <t>https://nasscom.in/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="28.8" customHeight="1">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Indian Council for Research on International Economic Relations</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Tax / Public Finance / Economic Policy</t>
+        </is>
+      </c>
+      <c r="D134" s="16" t="inlineStr">
+        <is>
+          <t>https://icrier.org/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="28.8" customHeight="1">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Direct Taxes Professionals’ Association (DTPA), Kolkata</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Direct Tax / GST / Tax Litigation</t>
+        </is>
+      </c>
+      <c r="D135" s="16" t="inlineStr">
+        <is>
+          <t>https://dtpa.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="28.8" customHeight="1">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>All Gujarat Federation of Tax Consultants (AGFTC)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Direct Tax / GST / Tax Law</t>
+        </is>
+      </c>
+      <c r="D136" s="16" t="inlineStr">
+        <is>
+          <t>https://agftc.in/index.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="28.8" customHeight="1">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>India International Arbitration Centre (IIAC)</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Arbitration / Commercial Law / ADR</t>
+        </is>
+      </c>
+      <c r="D137" s="16" t="inlineStr">
+        <is>
+          <t>https://indiaiac.org/arbitration/event</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="28.8" customHeight="1">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Centre for Trade and Investment Law (CTIL)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>International Trade / Investment Law</t>
+        </is>
+      </c>
+      <c r="D138" s="16" t="inlineStr">
+        <is>
+          <t>https://ctil.org.in/</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="28.8" customHeight="1">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Society of Indian Law Firms (SILF)</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Corporate / Commercial Law</t>
+        </is>
+      </c>
+      <c r="D139" s="16" t="inlineStr">
+        <is>
+          <t>https://www.silf.org.in/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="43.2" customHeight="1">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>National Foundation for Corporate Governance (NFCG)</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Corporate Governance / Compliance</t>
+        </is>
+      </c>
+      <c r="D140" s="16" t="inlineStr">
+        <is>
+          <t>https://nfcgindia.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="28.8" customHeight="1">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Institute of Company Secretaries of India – Centre for Corporate Governance</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Corporate Law / Governance / Compliance</t>
+        </is>
+      </c>
+      <c r="D141" s="16" t="inlineStr">
+        <is>
+          <t>https://www.icsi.edu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="28.8" customHeight="1">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Indian Institute of Insolvency Professionals of ICAI (IIIPI)</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Insolvency / Restructuring / Corporate Law</t>
+        </is>
+      </c>
+      <c r="D142" s="16" t="inlineStr">
+        <is>
+          <t>https://www.iiipicai.in/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="28.8" customHeight="1">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>ICAI Research &amp; Publications / Tax Research</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Tax / Accounting / Finance</t>
+        </is>
+      </c>
+      <c r="D143" s="16" t="inlineStr">
+        <is>
+          <t>https://www.icai.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="28.8" customHeight="1">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Institute of Cost Accountants of India – Professional Development</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Cost Accounting / Tax / Finance</t>
+        </is>
+      </c>
+      <c r="D144" s="16" t="inlineStr">
+        <is>
+          <t>https://icmai.in/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="28.8" customHeight="1">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Institute of Company Secretaries of India – Continuing Professional Education</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Corporate Law / Compliance / Governance</t>
+        </is>
+      </c>
+      <c r="D145" s="16" t="inlineStr">
+        <is>
+          <t>https://www.icsi.edu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="28.8" customHeight="1">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>National Centre for Corporate Governance</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Corporate Governance / Board Practices</t>
+        </is>
+      </c>
+      <c r="D146" s="16" t="inlineStr">
+        <is>
+          <t>https://iica.nic.in/</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="28.8" customHeight="1">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Indian Institute of Public Administration – Financial Administration</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Public Finance / Tax Administration</t>
+        </is>
+      </c>
+      <c r="D147" s="16" t="inlineStr">
+        <is>
+          <t>https://iipa.org.in/</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="28.8" customHeight="1">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Indian Society of Labour Economics</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Labour Economics / Public Finance</t>
+        </is>
+      </c>
+      <c r="D148" s="16" t="inlineStr">
+        <is>
+          <t>https://www.isleijle.org/conferences/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="43.2" customHeight="1">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Indian Association for Research in National Income and Wealth</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Economics / Public Finance</t>
+        </is>
+      </c>
+      <c r="D149" s="16" t="inlineStr">
+        <is>
+          <t>https://iarniw.in/upcoming/</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="28.8" customHeight="1">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Indian Council for Research on International Economic Relations (ICRIER)</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Tax Policy / Public Finance / Economic Policy</t>
+        </is>
+      </c>
+      <c r="D150" s="16" t="inlineStr">
+        <is>
+          <t>https://icrier.org/events/</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="28.8" customHeight="1">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Foundation for International Taxation (FIT)</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>International Tax / Tax Law</t>
+        </is>
+      </c>
+      <c r="D151" s="16" t="inlineStr">
+        <is>
+          <t>https://www.ffitindia.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="28.8" customHeight="1">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>National Academy of Direct Taxes</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Direct Tax / Tax Administration</t>
+        </is>
+      </c>
+      <c r="D152" s="16" t="inlineStr">
+        <is>
+          <t>https://www.nadt.gov.in/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="28.8" customHeight="1">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>International Chamber of Commerce India</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Commercial Law / Arbitration / Trade</t>
+        </is>
+      </c>
+      <c r="D153" s="16" t="inlineStr">
+        <is>
+          <t>https://iccindiaonline.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="28.8" customHeight="1">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>International Bar Association</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Legal / Tax / Arbitration</t>
+        </is>
+      </c>
+      <c r="D154" s="16" t="inlineStr">
+        <is>
+          <t>https://www.ibanet.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="28.8" customHeight="1">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>International Chamber of Commerce – India Arbitration</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Arbitration / Commercial Law</t>
+        </is>
+      </c>
+      <c r="D155" s="16" t="inlineStr">
+        <is>
+          <t>https://iccindiaonline.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="28.8" customHeight="1">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>International Centre for Dispute Resolution – India</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
         <is>
           <t>Arbitration / Dispute Resolution</t>
         </is>
       </c>
-      <c r="D93" s="13" t="inlineStr">
-        <is>
-          <t>https://mcia.org.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="28.8" customHeight="1">
-      <c r="A94" s="1" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>Indian Institute of Arbitration &amp; Mediation</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>Arbitration / Mediation</t>
-        </is>
-      </c>
-      <c r="D94" s="13" t="inlineStr">
-        <is>
-          <t>https://www.arbitrationindia.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>Indian Society of International Law</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>International Law</t>
-        </is>
-      </c>
-      <c r="D95" s="13" t="inlineStr">
-        <is>
-          <t>https://isilindia.org/</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>Indian Council of Legal Aid &amp; Advice</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>Legal</t>
-        </is>
-      </c>
-      <c r="D96" s="8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="28.8" customHeight="1">
-      <c r="A97" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>Indian Association of Labour Law Practitioners</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>Labour Law</t>
-        </is>
-      </c>
-      <c r="D97" s="15" t="inlineStr">
-        <is>
-          <t>https://nllaindia.com/events/</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="28.8" customHeight="1">
-      <c r="A98" s="1" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>Society of Indian Law Firms</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>Legal / Corporate Law</t>
-        </is>
-      </c>
-      <c r="D98" s="14" t="inlineStr">
-        <is>
-          <t>https://www.silf.org.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="28.8" customHeight="1">
-      <c r="A99" s="1" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>Indian Corporate Counsel Association</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>Corporate Legal / Compliance</t>
-        </is>
-      </c>
-      <c r="D99" s="15" t="inlineStr">
-        <is>
-          <t>https://ccai.net.in/?page_id=1597</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="28.8" customHeight="1">
-      <c r="A100" s="1" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>Centre for Trade and Investment Law</t>
-        </is>
-      </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>Trade Law / International Law</t>
-        </is>
-      </c>
-      <c r="D100" s="13" t="inlineStr">
-        <is>
-          <t>https://ctil.org.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="28.8" customHeight="1">
-      <c r="A101" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>Indian Insolvency Professionals Association</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>Insolvency / Corporate Law</t>
-        </is>
-      </c>
-      <c r="D101" s="15" t="inlineStr">
-        <is>
-          <t>https://aipe.org.in/events/</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="28.8" customHeight="1">
-      <c r="A102" s="1" t="n">
-        <v>101</v>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t>Chamber of Tax Consultants (CTC)</t>
-        </is>
-      </c>
-      <c r="C102" s="4" t="inlineStr">
-        <is>
-          <t>Tax / Fiscal Law / GST</t>
-        </is>
-      </c>
-      <c r="D102" s="13" t="inlineStr">
-        <is>
-          <t>https://www.ctconline.org/</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="28.8" customHeight="1">
-      <c r="A103" s="1" t="n">
-        <v>102</v>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>Confederation of Indian Industry (CII)</t>
-        </is>
-      </c>
-      <c r="C103" s="4" t="inlineStr">
-        <is>
-          <t>Tax / Finance / Corporate Governance</t>
-        </is>
-      </c>
-      <c r="D103" s="13" t="inlineStr">
-        <is>
-          <t>https://www.cii.in/Events.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="28.8" customHeight="1">
-      <c r="A104" s="1" t="n">
-        <v>103</v>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>ASSOCHAM</t>
-        </is>
-      </c>
-      <c r="C104" s="4" t="inlineStr">
-        <is>
-          <t>Tax / Finance / Corporate Law</t>
-        </is>
-      </c>
-      <c r="D104" s="13" t="inlineStr">
-        <is>
-          <t>https://www.assocham.org/</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="28.8" customHeight="1">
-      <c r="A105" s="1" t="n">
-        <v>104</v>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>Federation of Indian Chambers of Commerce &amp; Industry (FICCI)</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>Tax / Finance / Legal / Regulatory</t>
-        </is>
-      </c>
-      <c r="D105" s="13" t="inlineStr">
-        <is>
-          <t>https://ficci.in/event</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="28.8" customHeight="1">
-      <c r="A106" s="1" t="n">
-        <v>105</v>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>PHD Chamber of Commerce and Industry (PHDCCI)</t>
-        </is>
-      </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>Tax / Finance / Insolvency / Corporate Law</t>
-        </is>
-      </c>
-      <c r="D106" s="13" t="inlineStr">
-        <is>
-          <t>https://www.phdcci.in/events/</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="28.8" customHeight="1">
-      <c r="A107" s="1" t="n">
-        <v>106</v>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>Gulati Institute of Finance and Taxation (GIFT)</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>Tax / Public Finance / Fiscal Policy</t>
-        </is>
-      </c>
-      <c r="D107" s="13" t="inlineStr">
-        <is>
-          <t>https://www.gift.res.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="28.8" customHeight="1">
-      <c r="A108" s="1" t="n">
-        <v>107</v>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>Institute of Directors, India</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="inlineStr">
-        <is>
-          <t>Corporate Governance / Directors / Corporate Law</t>
-        </is>
-      </c>
-      <c r="D108" s="13" t="inlineStr">
-        <is>
-          <t>https://www.iodglobal.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="28.8" customHeight="1">
-      <c r="A109" s="1" t="n">
-        <v>108</v>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>Institute of Internal Auditors India</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>Internal Audit / Risk / Governance / Finance</t>
-        </is>
-      </c>
-      <c r="D109" s="13" t="inlineStr">
-        <is>
-          <t>https://www.iiaindia.co.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="28.8" customHeight="1">
-      <c r="A110" s="1" t="n">
-        <v>109</v>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
-        <is>
-          <t>IIA Madras Chapter</t>
-        </is>
-      </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>Internal Audit / Risk / Governance</t>
-        </is>
-      </c>
-      <c r="D110" s="15" t="inlineStr">
-        <is>
-          <t>https://iiamadras.org/upcoming-events</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="28.8" customHeight="1">
-      <c r="A111" s="1" t="n">
-        <v>110</v>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>IIA Bombay Chapter</t>
-        </is>
-      </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>Internal Audit / Risk / Governance</t>
-        </is>
-      </c>
-      <c r="D111" s="13" t="inlineStr">
-        <is>
-          <t>https://www.iiabombay.org/</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="28.8" customHeight="1">
-      <c r="A112" s="1" t="n">
-        <v>111</v>
-      </c>
-      <c r="B112" s="4" t="inlineStr">
-        <is>
-          <t>ISACA Chennai Chapter</t>
-        </is>
-      </c>
-      <c r="C112" s="4" t="inlineStr">
-        <is>
-          <t>IT Audit / Risk / Governance / Compliance</t>
-        </is>
-      </c>
-      <c r="D112" s="13" t="inlineStr">
-        <is>
-          <t>https://www.isacachennai.org/</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="28.8" customHeight="1">
-      <c r="A113" s="1" t="n">
-        <v>112</v>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t>ISACA New Delhi Chapter</t>
-        </is>
-      </c>
-      <c r="C113" s="4" t="inlineStr">
-        <is>
-          <t>IT Audit / Risk / Governance</t>
-        </is>
-      </c>
-      <c r="D113" s="13" t="inlineStr">
-        <is>
-          <t>https://isacadelhi.org/</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="28.8" customHeight="1">
-      <c r="A114" s="1" t="n">
-        <v>113</v>
-      </c>
-      <c r="B114" s="4" t="inlineStr">
-        <is>
-          <t>Delhi International Arbitration Centre (DIAC)</t>
-        </is>
-      </c>
-      <c r="C114" s="4" t="inlineStr">
-        <is>
-          <t>Arbitration / Commercial Law / Dispute Resolution</t>
-        </is>
-      </c>
-      <c r="D114" s="15" t="inlineStr">
-        <is>
-          <t>https://dhcdiac.nic.in/all-events/</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="28.8" customHeight="1">
-      <c r="A115" s="1" t="n">
-        <v>114</v>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>Nani Palkhivala Arbitration Centre (NPAC)</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="inlineStr">
-        <is>
-          <t>Arbitration / Insolvency / Corporate Law</t>
-        </is>
-      </c>
-      <c r="D115" s="13" t="inlineStr">
-        <is>
-          <t>https://www.npac.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="28.8" customHeight="1">
-      <c r="A116" s="1" t="n">
-        <v>115</v>
-      </c>
-      <c r="B116" s="4" t="inlineStr">
-        <is>
-          <t>Arbitration Bar of India</t>
-        </is>
-      </c>
-      <c r="C116" s="4" t="inlineStr">
-        <is>
-          <t>Arbitration / ADR / Legal</t>
-        </is>
-      </c>
-      <c r="D116" s="15" t="inlineStr">
-        <is>
-          <t>https://arbitrationbarofindia.com/upcoming_events.php</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="28.8" customHeight="1">
-      <c r="A117" s="1" t="n">
-        <v>116</v>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>Institute of Chartered Tax Practitioners of India (ICTPI)</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="inlineStr">
-        <is>
-          <t>Tax / Tax Practice</t>
-        </is>
-      </c>
-      <c r="D117" s="15" t="inlineStr">
-        <is>
-          <t>https://www.ictpi.in/event</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="1" t="n">
-        <v>117</v>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>Federation of Tax Practitioners of India (FTPI)</t>
-        </is>
-      </c>
-      <c r="C118" s="4" t="inlineStr">
-        <is>
-          <t>Tax / Tax Practice</t>
-        </is>
-      </c>
-      <c r="D118" s="15" t="inlineStr">
-        <is>
-          <t>https://www.ictpi.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="28.8" customHeight="1">
-      <c r="A119" s="1" t="n">
-        <v>118</v>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>Independent Financial Professionals Association (IFPA)</t>
-        </is>
-      </c>
-      <c r="C119" s="4" t="inlineStr">
-        <is>
-          <t>Professional Finance / Financial Planning</t>
-        </is>
-      </c>
-      <c r="D119" s="15" t="inlineStr">
-        <is>
-          <t>https://www.ifpaindia.in/events</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="28.8" customHeight="1">
-      <c r="A120" s="1" t="n">
-        <v>119</v>
-      </c>
-      <c r="B120" s="4" t="inlineStr">
-        <is>
-          <t>CFO India</t>
-        </is>
-      </c>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>Corporate Finance / CFO / Financial Management</t>
-        </is>
-      </c>
-      <c r="D120" s="13" t="inlineStr">
-        <is>
-          <t>https://www.cfo-india.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="28.8" customHeight="1">
-      <c r="A121" s="1" t="n">
-        <v>120</v>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t>Institute of Internal Auditors – India / Bombay</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="inlineStr">
-        <is>
-          <t>Internal Audit / Finance / Governance</t>
-        </is>
-      </c>
-      <c r="D121" s="13" t="inlineStr">
-        <is>
-          <t>https://www.iiaindia.co.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="43.2" customHeight="1">
-      <c r="A122" s="1" t="n">
-        <v>121</v>
-      </c>
-      <c r="B122" s="4" t="inlineStr">
-        <is>
-          <t>CFA Society India</t>
-        </is>
-      </c>
-      <c r="C122" s="4" t="inlineStr">
-        <is>
-          <t>Professional Finance / Investment</t>
-        </is>
-      </c>
-      <c r="D122" s="13" t="inlineStr">
-        <is>
-          <t>https://cfasocietyindia.org/upcomingevents/</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="28.8" customHeight="1">
-      <c r="A123" s="1" t="n">
-        <v>122</v>
-      </c>
-      <c r="B123" s="4" t="inlineStr">
-        <is>
-          <t>Network FP India</t>
-        </is>
-      </c>
-      <c r="C123" s="4" t="inlineStr">
-        <is>
-          <t>Personal Finance / Financial Planning</t>
-        </is>
-      </c>
-      <c r="D123" s="13" t="inlineStr">
-        <is>
-          <t>https://www.networkfp.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="28.8" customHeight="1">
-      <c r="A124" s="1" t="n">
-        <v>123</v>
-      </c>
-      <c r="B124" s="4" t="inlineStr">
-        <is>
-          <t>ICT India</t>
-        </is>
-      </c>
-      <c r="C124" s="4" t="inlineStr">
-        <is>
-          <t>Corporate Treasury / Finance</t>
-        </is>
-      </c>
-      <c r="D124" s="15" t="inlineStr">
-        <is>
-          <t>https://ict-india.org/#events</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="28.8" customHeight="1">
-      <c r="A125" s="1" t="n">
-        <v>124</v>
-      </c>
-      <c r="B125" s="4" t="inlineStr">
-        <is>
-          <t>India Treasury Summit</t>
-        </is>
-      </c>
-      <c r="C125" s="4" t="inlineStr">
-        <is>
-          <t>Treasury / Corporate Finance</t>
-        </is>
-      </c>
-      <c r="D125" s="15" t="inlineStr">
-        <is>
-          <t>https://www.indiatreasurysummit.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="28.8" customHeight="1">
-      <c r="A126" s="1" t="n">
-        <v>125</v>
-      </c>
-      <c r="B126" s="4" t="inlineStr">
-        <is>
-          <t>Treasury India</t>
-        </is>
-      </c>
-      <c r="C126" s="4" t="inlineStr">
-        <is>
-          <t>Treasury / Corporate Finance</t>
-        </is>
-      </c>
-      <c r="D126" s="9" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="28.8" customHeight="1">
-      <c r="A127" s="1" t="n">
-        <v>126</v>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
-        <is>
-          <t>Society of Indian Law Firms</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="inlineStr">
-        <is>
-          <t>Legal / Corporate Law</t>
-        </is>
-      </c>
-      <c r="D127" s="13" t="inlineStr">
-        <is>
-          <t>https://www.silf.org.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="28.8" customHeight="1">
-      <c r="A128" s="1" t="n">
-        <v>127</v>
-      </c>
-      <c r="B128" s="4" t="inlineStr">
-        <is>
-          <t>Indian National Bar Association</t>
-        </is>
-      </c>
-      <c r="C128" s="4" t="inlineStr">
-        <is>
-          <t>Legal / Corporate Law / Dispute Resolution</t>
-        </is>
-      </c>
-      <c r="D128" s="13" t="inlineStr">
-        <is>
-          <t>https://www.indianbarassociation.org/</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="28.8" customHeight="1">
-      <c r="A129" s="1" t="n">
-        <v>128</v>
-      </c>
-      <c r="B129" s="4" t="inlineStr">
-        <is>
-          <t>International Centre for Dispute Resolution (ICDR)</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="inlineStr">
+      <c r="D156" s="16" t="inlineStr">
+        <is>
+          <t>https://www.icdr.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="28.8" customHeight="1">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>London Court of International Arbitration</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
         <is>
           <t>Arbitration / Commercial Law</t>
         </is>
       </c>
-      <c r="D129" s="13" t="inlineStr">
-        <is>
-          <t>https://www.icdr.org/</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="28.8" customHeight="1">
-      <c r="A130" s="1" t="n">
-        <v>129</v>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>India ADR Week</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>Arbitration / Mediation / Dispute Resolution</t>
-        </is>
-      </c>
-      <c r="D130" s="13" t="inlineStr">
-        <is>
-          <t>https://indiaadrweek.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="28.8" customHeight="1">
-      <c r="A131" s="1" t="n">
-        <v>130</v>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>Commercial Bar Association (COMBAR)</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="inlineStr">
-        <is>
-          <t>Commercial Litigation / Arbitration</t>
-        </is>
-      </c>
-      <c r="D131" s="13" t="inlineStr">
-        <is>
-          <t>https://www.combar.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="28.8" customHeight="1">
-      <c r="A132" s="1" t="n">
-        <v>131</v>
-      </c>
-      <c r="B132" s="4" t="inlineStr">
-        <is>
-          <t>London Court of International Arbitration (LCIA)</t>
-        </is>
-      </c>
-      <c r="C132" s="4" t="inlineStr">
-        <is>
-          <t>Arbitration / Commercial Law</t>
-        </is>
-      </c>
-      <c r="D132" s="13" t="inlineStr">
+      <c r="D157" s="16" t="inlineStr">
         <is>
           <t>https://www.lcia.org/</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="28.8" customHeight="1">
-      <c r="A133" s="1" t="n">
-        <v>132</v>
-      </c>
-      <c r="B133" s="4" t="inlineStr">
-        <is>
-          <t>International Bar Association (IBA)</t>
-        </is>
-      </c>
-      <c r="C133" s="4" t="inlineStr">
-        <is>
-          <t>Legal / Tax / Arbitration</t>
-        </is>
-      </c>
-      <c r="D133" s="13" t="inlineStr">
-        <is>
-          <t>https://www.ibanet.org/</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="28.8" customHeight="1">
-      <c r="A134" s="1" t="n">
-        <v>133</v>
-      </c>
-      <c r="B134" s="4" t="inlineStr">
-        <is>
-          <t>International Fiscal Association – India Academy</t>
-        </is>
-      </c>
-      <c r="C134" s="4" t="inlineStr">
-        <is>
-          <t>International Tax / Fiscal Law</t>
-        </is>
-      </c>
-      <c r="D134" s="15" t="inlineStr">
-        <is>
-          <t>https://ifaindia.in/events/</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="28.8" customHeight="1">
-      <c r="A135" s="1" t="n">
-        <v>134</v>
-      </c>
-      <c r="B135" s="4" t="inlineStr">
-        <is>
-          <t>National Institute of Public Finance and Policy (NIPFP)</t>
-        </is>
-      </c>
-      <c r="C135" s="4" t="inlineStr">
-        <is>
-          <t>Tax / Public Finance / Fiscal Policy</t>
-        </is>
-      </c>
-      <c r="D135" s="13" t="inlineStr">
-        <is>
-          <t>https://www.nipfp.org.in/event-index-page/</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="28.8" customHeight="1">
-      <c r="A136" s="1" t="n">
-        <v>135</v>
-      </c>
-      <c r="B136" s="4" t="inlineStr">
-        <is>
-          <t>Institute of Internal Auditors India</t>
-        </is>
-      </c>
-      <c r="C136" s="4" t="inlineStr">
-        <is>
-          <t>Audit / Finance / Governance / Risk</t>
-        </is>
-      </c>
-      <c r="D136" s="13" t="inlineStr">
-        <is>
-          <t>https://www.iiaindia.co.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="28.8" customHeight="1">
-      <c r="A137" s="1" t="n">
-        <v>136</v>
-      </c>
-      <c r="B137" s="4" t="inlineStr">
-        <is>
-          <t>ISACA India</t>
-        </is>
-      </c>
-      <c r="C137" s="4" t="inlineStr">
-        <is>
-          <t>Audit / Compliance / Risk / Governance</t>
-        </is>
-      </c>
-      <c r="D137" s="13" t="inlineStr">
-        <is>
-          <t>https://www.isaca.org/</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="28.8" customHeight="1">
-      <c r="A138" s="1" t="n">
-        <v>137</v>
-      </c>
-      <c r="B138" s="4" t="inlineStr">
-        <is>
-          <t>Institute of Directors India</t>
-        </is>
-      </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>Corporate Governance / Corporate Law</t>
-        </is>
-      </c>
-      <c r="D138" s="13" t="inlineStr">
-        <is>
-          <t>https://www.iodglobal.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="28.8" customHeight="1">
-      <c r="A139" s="1" t="n">
-        <v>138</v>
-      </c>
-      <c r="B139" s="4" t="inlineStr">
-        <is>
-          <t>Indian Society of International Law</t>
-        </is>
-      </c>
-      <c r="C139" s="4" t="inlineStr">
-        <is>
-          <t>International Law / Trade Law</t>
-        </is>
-      </c>
-      <c r="D139" s="13" t="inlineStr">
-        <is>
-          <t>https://isilindia.org/</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="43.2" customHeight="1">
-      <c r="A140" s="1" t="n">
-        <v>139</v>
-      </c>
-      <c r="B140" s="4" t="inlineStr">
-        <is>
-          <t>Nani Palkhivala Arbitration Centre</t>
-        </is>
-      </c>
-      <c r="C140" s="4" t="inlineStr">
-        <is>
-          <t>Arbitration / Commercial Disputes</t>
-        </is>
-      </c>
-      <c r="D140" s="13" t="inlineStr">
-        <is>
-          <t>https://www.npac.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="28.8" customHeight="1">
-      <c r="A141" s="1" t="n">
-        <v>140</v>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>Society of Indian Law Firms</t>
-        </is>
-      </c>
-      <c r="C141" s="4" t="inlineStr">
-        <is>
-          <t>Corporate / Commercial Law</t>
-        </is>
-      </c>
-      <c r="D141" s="13" t="inlineStr">
-        <is>
-          <t>https://www.silf.org.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="28.8" customHeight="1">
-      <c r="A142" s="1" t="n">
-        <v>141</v>
-      </c>
-      <c r="B142" s="4" t="inlineStr">
-        <is>
-          <t>Centre for Trade and Investment Law</t>
-        </is>
-      </c>
-      <c r="C142" s="4" t="inlineStr">
-        <is>
-          <t>International Trade / Investment Law</t>
-        </is>
-      </c>
-      <c r="D142" s="13" t="inlineStr">
-        <is>
-          <t>https://ctil.org.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="28.8" customHeight="1">
-      <c r="A143" s="1" t="n">
-        <v>142</v>
-      </c>
-      <c r="B143" s="4" t="inlineStr">
-        <is>
-          <t>National Association of Software and Service Companies – Tax Forum</t>
-        </is>
-      </c>
-      <c r="C143" s="4" t="inlineStr">
-        <is>
-          <t>Tax / Regulatory / Finance</t>
-        </is>
-      </c>
-      <c r="D143" s="13" t="inlineStr">
-        <is>
-          <t>https://nasscom.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="28.8" customHeight="1">
-      <c r="A144" s="1" t="n">
-        <v>143</v>
-      </c>
-      <c r="B144" s="4" t="inlineStr">
-        <is>
-          <t>Indian Council for Research on International Economic Relations</t>
-        </is>
-      </c>
-      <c r="C144" s="4" t="inlineStr">
-        <is>
-          <t>Tax / Public Finance / Economic Policy</t>
-        </is>
-      </c>
-      <c r="D144" s="13" t="inlineStr">
-        <is>
-          <t>https://icrier.org/events/</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="28.8" customHeight="1">
-      <c r="A145" s="1" t="n">
-        <v>144</v>
-      </c>
-      <c r="B145" s="4" t="inlineStr">
-        <is>
-          <t>Direct Taxes Professionals’ Association (DTPA), Kolkata</t>
-        </is>
-      </c>
-      <c r="C145" s="4" t="inlineStr">
-        <is>
-          <t>Direct Tax / GST / Tax Litigation</t>
-        </is>
-      </c>
-      <c r="D145" s="13" t="inlineStr">
-        <is>
-          <t>https://dtpa.org/</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="28.8" customHeight="1">
-      <c r="A146" s="1" t="n">
-        <v>145</v>
-      </c>
-      <c r="B146" s="4" t="inlineStr">
-        <is>
-          <t>All Gujarat Federation of Tax Consultants (AGFTC)</t>
-        </is>
-      </c>
-      <c r="C146" s="4" t="inlineStr">
-        <is>
-          <t>Direct Tax / GST / Tax Law</t>
-        </is>
-      </c>
-      <c r="D146" s="15" t="inlineStr">
-        <is>
-          <t>https://agftc.in/index.php</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="28.8" customHeight="1">
-      <c r="A147" s="1" t="n">
-        <v>146</v>
-      </c>
-      <c r="B147" s="4" t="inlineStr">
-        <is>
-          <t>Indian Institute of Corporate Affairs (IICA)</t>
-        </is>
-      </c>
-      <c r="C147" s="4" t="inlineStr">
-        <is>
-          <t>Corporate Law / Insolvency / Governance / Regulation</t>
-        </is>
-      </c>
-      <c r="D147" s="13" t="inlineStr">
-        <is>
-          <t>https://iica.nic.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="28.8" customHeight="1">
-      <c r="A148" s="1" t="n">
-        <v>147</v>
-      </c>
-      <c r="B148" s="4" t="inlineStr">
-        <is>
-          <t>India International Arbitration Centre (IIAC)</t>
-        </is>
-      </c>
-      <c r="C148" s="4" t="inlineStr">
-        <is>
-          <t>Arbitration / Commercial Law / ADR</t>
-        </is>
-      </c>
-      <c r="D148" s="15" t="inlineStr">
-        <is>
-          <t>https://indiaiac.org/arbitration/event</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="43.2" customHeight="1">
-      <c r="A149" s="1" t="n">
-        <v>148</v>
-      </c>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>Nani Palkhivala Arbitration Centre (NPAC)</t>
-        </is>
-      </c>
-      <c r="C149" s="4" t="inlineStr">
-        <is>
-          <t>Arbitration / Commercial Disputes</t>
-        </is>
-      </c>
-      <c r="D149" s="13" t="inlineStr">
-        <is>
-          <t>https://www.npac.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="28.8" customHeight="1">
-      <c r="A150" s="1" t="n">
-        <v>149</v>
-      </c>
-      <c r="B150" s="4" t="inlineStr">
-        <is>
-          <t>Centre for Trade and Investment Law (CTIL)</t>
-        </is>
-      </c>
-      <c r="C150" s="4" t="inlineStr">
-        <is>
-          <t>International Trade / Investment Law</t>
-        </is>
-      </c>
-      <c r="D150" s="13" t="inlineStr">
-        <is>
-          <t>https://ctil.org.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="28.8" customHeight="1">
-      <c r="A151" s="1" t="n">
-        <v>150</v>
-      </c>
-      <c r="B151" s="4" t="inlineStr">
-        <is>
-          <t>Society of Indian Law Firms (SILF)</t>
-        </is>
-      </c>
-      <c r="C151" s="4" t="inlineStr">
-        <is>
-          <t>Corporate / Commercial Law</t>
-        </is>
-      </c>
-      <c r="D151" s="13" t="inlineStr">
-        <is>
-          <t>https://www.silf.org.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="28.8" customHeight="1">
-      <c r="A152" s="1" t="n">
-        <v>151</v>
-      </c>
-      <c r="B152" s="4" t="inlineStr">
-        <is>
-          <t>National Foundation for Corporate Governance (NFCG)</t>
-        </is>
-      </c>
-      <c r="C152" s="4" t="inlineStr">
-        <is>
-          <t>Corporate Governance / Compliance</t>
-        </is>
-      </c>
-      <c r="D152" s="13" t="inlineStr">
-        <is>
-          <t>https://nfcgindia.org/</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="28.8" customHeight="1">
-      <c r="A153" s="1" t="n">
-        <v>152</v>
-      </c>
-      <c r="B153" s="4" t="inlineStr">
-        <is>
-          <t>Institute of Company Secretaries of India – Centre for Corporate Governance</t>
-        </is>
-      </c>
-      <c r="C153" s="4" t="inlineStr">
-        <is>
-          <t>Corporate Law / Governance / Compliance</t>
-        </is>
-      </c>
-      <c r="D153" s="13" t="inlineStr">
-        <is>
-          <t>https://www.icsi.edu/</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="28.8" customHeight="1">
-      <c r="A154" s="1" t="n">
-        <v>153</v>
-      </c>
-      <c r="B154" s="4" t="inlineStr">
-        <is>
-          <t>Indian Institute of Insolvency Professionals of ICAI (IIIPI)</t>
-        </is>
-      </c>
-      <c r="C154" s="4" t="inlineStr">
-        <is>
-          <t>Insolvency / Restructuring / Corporate Law</t>
-        </is>
-      </c>
-      <c r="D154" s="13" t="inlineStr">
-        <is>
-          <t>https://www.iiipicai.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="28.8" customHeight="1">
-      <c r="A155" s="1" t="n">
-        <v>154</v>
-      </c>
-      <c r="B155" s="4" t="inlineStr">
-        <is>
-          <t>ICAI Research &amp; Publications / Tax Research</t>
-        </is>
-      </c>
-      <c r="C155" s="4" t="inlineStr">
+    <row r="158" ht="28.8" customHeight="1">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>International Insolvency Institute</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Insolvency / Restructuring / Finance</t>
+        </is>
+      </c>
+      <c r="D158" s="16" t="inlineStr">
+        <is>
+          <t>https://iiiglobal.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="28.8" customHeight="1">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>International Association of Insolvency Regulators</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Insolvency / Regulation / Finance</t>
+        </is>
+      </c>
+      <c r="D159" s="16" t="inlineStr">
+        <is>
+          <t>https://www.insolvencyreg.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="28.8" customHeight="1">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>International Association of Financial Executives Institutes (IAFEI)</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Corporate Finance / Treasury / Financial Management</t>
+        </is>
+      </c>
+      <c r="D160" s="16" t="inlineStr">
+        <is>
+          <t>https://iafei.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="28.8" customHeight="1">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>All India Chartered Accountants Society (AICAS)</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
         <is>
           <t>Tax / Accounting / Finance</t>
         </is>
       </c>
-      <c r="D155" s="13" t="inlineStr">
-        <is>
-          <t>https://www.icai.org/</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="28.8" customHeight="1">
-      <c r="A156" s="1" t="n">
-        <v>155</v>
-      </c>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t>Institute of Cost Accountants of India – Professional Development</t>
-        </is>
-      </c>
-      <c r="C156" s="4" t="inlineStr">
-        <is>
-          <t>Cost Accounting / Tax / Finance</t>
-        </is>
-      </c>
-      <c r="D156" s="13" t="inlineStr">
+      <c r="D161" s="16" t="inlineStr">
+        <is>
+          <t>https://www.aicas.in/event.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="28.8" customHeight="1">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Association of Financial Professionals of India (AFPI)</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Finance / Financial Management</t>
+        </is>
+      </c>
+      <c r="D162" s="16" t="inlineStr">
+        <is>
+          <t>https://www.afai.in/event-conferences/#eventcalender</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="28.8" customHeight="1">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Association of Corporate Treasurers of India (ACTI)</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Corporate Finance / Treasury</t>
+        </is>
+      </c>
+      <c r="D163" s="16" t="inlineStr">
+        <is>
+          <t>https://www.treasurers.org/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="28.8" customHeight="1">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Institute of Cost and Management Accountants of India Research Foundation</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Accounting / Finance / Cost Management</t>
+        </is>
+      </c>
+      <c r="D164" s="16" t="inlineStr">
         <is>
           <t>https://icmai.in/</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="28.8" customHeight="1">
-      <c r="A157" s="1" t="n">
-        <v>156</v>
-      </c>
-      <c r="B157" s="4" t="inlineStr">
-        <is>
-          <t>Institute of Company Secretaries of India – Continuing Professional Education</t>
-        </is>
-      </c>
-      <c r="C157" s="4" t="inlineStr">
-        <is>
-          <t>Corporate Law / Compliance / Governance</t>
-        </is>
-      </c>
-      <c r="D157" s="13" t="inlineStr">
-        <is>
-          <t>https://www.icsi.edu/</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="28.8" customHeight="1">
-      <c r="A158" s="1" t="n">
-        <v>157</v>
-      </c>
-      <c r="B158" s="4" t="inlineStr">
-        <is>
-          <t>National Centre for Corporate Governance</t>
-        </is>
-      </c>
-      <c r="C158" s="4" t="inlineStr">
-        <is>
-          <t>Corporate Governance / Board Practices</t>
-        </is>
-      </c>
-      <c r="D158" s="13" t="inlineStr">
-        <is>
-          <t>https://iica.nic.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="28.8" customHeight="1">
-      <c r="A159" s="1" t="n">
-        <v>158</v>
-      </c>
-      <c r="B159" s="4" t="inlineStr">
-        <is>
-          <t>Indian Institute of Public Administration – Financial Administration</t>
-        </is>
-      </c>
-      <c r="C159" s="4" t="inlineStr">
-        <is>
-          <t>Public Finance / Tax Administration</t>
-        </is>
-      </c>
-      <c r="D159" s="13" t="inlineStr">
-        <is>
-          <t>https://iipa.org.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="28.8" customHeight="1">
-      <c r="A160" s="1" t="n">
-        <v>159</v>
-      </c>
-      <c r="B160" s="4" t="inlineStr">
-        <is>
-          <t>Indian Society of Labour Economics</t>
-        </is>
-      </c>
-      <c r="C160" s="4" t="inlineStr">
-        <is>
-          <t>Labour Economics / Public Finance</t>
-        </is>
-      </c>
-      <c r="D160" s="15" t="inlineStr">
-        <is>
-          <t>https://www.isleijle.org/conferences/</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="28.8" customHeight="1">
-      <c r="A161" s="1" t="n">
-        <v>160</v>
-      </c>
-      <c r="B161" s="4" t="inlineStr">
-        <is>
-          <t>Indian Association for Research in National Income and Wealth</t>
-        </is>
-      </c>
-      <c r="C161" s="4" t="inlineStr">
-        <is>
-          <t>Economics / Public Finance</t>
-        </is>
-      </c>
-      <c r="D161" s="15" t="inlineStr">
-        <is>
-          <t>https://iarniw.in/upcoming/</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="28.8" customHeight="1">
-      <c r="A162" s="1" t="n">
-        <v>161</v>
-      </c>
-      <c r="B162" s="4" t="inlineStr">
-        <is>
-          <t>Indian Council for Research on International Economic Relations (ICRIER)</t>
-        </is>
-      </c>
-      <c r="C162" s="4" t="inlineStr">
-        <is>
-          <t>Tax Policy / Public Finance / Economic Policy</t>
-        </is>
-      </c>
-      <c r="D162" s="13" t="inlineStr">
-        <is>
-          <t>https://icrier.org/events/</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="28.8" customHeight="1">
-      <c r="A163" s="1" t="n">
-        <v>162</v>
-      </c>
-      <c r="B163" s="4" t="inlineStr">
-        <is>
-          <t>Foundation for International Taxation (FIT)</t>
-        </is>
-      </c>
-      <c r="C163" s="4" t="inlineStr">
-        <is>
-          <t>International Tax / Tax Law</t>
-        </is>
-      </c>
-      <c r="D163" s="15" t="inlineStr">
-        <is>
-          <t>https://www.ffitindia.org/</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="28.8" customHeight="1">
-      <c r="A164" s="1" t="n">
-        <v>163</v>
-      </c>
-      <c r="B164" s="4" t="inlineStr">
-        <is>
-          <t>National Academy of Direct Taxes</t>
-        </is>
-      </c>
-      <c r="C164" s="4" t="inlineStr">
-        <is>
-          <t>Direct Tax / Tax Administration</t>
-        </is>
-      </c>
-      <c r="D164" s="13" t="inlineStr">
-        <is>
-          <t>https://www.nadt.gov.in/</t>
-        </is>
-      </c>
-    </row>
     <row r="165" ht="28.8" customHeight="1">
-      <c r="A165" s="1" t="n">
+      <c r="A165" t="n">
         <v>164</v>
       </c>
-      <c r="B165" s="4" t="inlineStr">
-        <is>
-          <t>International Chamber of Commerce India</t>
-        </is>
-      </c>
-      <c r="C165" s="4" t="inlineStr">
-        <is>
-          <t>Commercial Law / Arbitration / Trade</t>
-        </is>
-      </c>
-      <c r="D165" s="13" t="inlineStr">
-        <is>
-          <t>https://iccindiaonline.org/</t>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Indian Institute of Financial Management</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Finance / Financial Management</t>
+        </is>
+      </c>
+      <c r="D165" s="16" t="inlineStr">
+        <is>
+          <t>https://www.iifm.co.in/</t>
         </is>
       </c>
     </row>
     <row r="166" ht="28.8" customHeight="1">
-      <c r="A166" s="1" t="n">
+      <c r="A166" t="n">
         <v>165</v>
       </c>
-      <c r="B166" s="4" t="inlineStr">
-        <is>
-          <t>International Bar Association</t>
-        </is>
-      </c>
-      <c r="C166" s="4" t="inlineStr">
-        <is>
-          <t>Legal / Tax / Arbitration</t>
-        </is>
-      </c>
-      <c r="D166" s="13" t="inlineStr">
-        <is>
-          <t>https://www.ibanet.org/</t>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Bombay Chartered Accountants Society</t>
+        </is>
+      </c>
+      <c r="D166" s="16" t="inlineStr">
+        <is>
+          <t>https://bcasonline.org/upcoming-live-events/</t>
         </is>
       </c>
     </row>
     <row r="167" ht="28.8" customHeight="1">
-      <c r="A167" s="1" t="n">
+      <c r="A167" t="n">
         <v>166</v>
       </c>
-      <c r="B167" s="4" t="inlineStr">
-        <is>
-          <t>International Chamber of Commerce – India Arbitration</t>
-        </is>
-      </c>
-      <c r="C167" s="4" t="inlineStr">
-        <is>
-          <t>Arbitration / Commercial Law</t>
-        </is>
-      </c>
-      <c r="D167" s="13" t="inlineStr">
-        <is>
-          <t>https://iccindiaonline.org/</t>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Tax Practitioners Association Indore</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="D167" s="16" t="inlineStr">
+        <is>
+          <t>https://tpaindore.com/</t>
         </is>
       </c>
     </row>
     <row r="168" ht="28.8" customHeight="1">
-      <c r="A168" s="1" t="n">
+      <c r="A168" t="n">
         <v>167</v>
       </c>
-      <c r="B168" s="4" t="inlineStr">
-        <is>
-          <t>International Centre for Dispute Resolution – India</t>
-        </is>
-      </c>
-      <c r="C168" s="4" t="inlineStr">
-        <is>
-          <t>Arbitration / Dispute Resolution</t>
-        </is>
-      </c>
-      <c r="D168" s="13" t="inlineStr">
-        <is>
-          <t>https://www.icdr.org/</t>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Income Tax Bar Association Ahmedabad</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Tax / Legal</t>
+        </is>
+      </c>
+      <c r="D168" s="16" t="inlineStr">
+        <is>
+          <t>https://incometaxbar.org/</t>
         </is>
       </c>
     </row>
     <row r="169" ht="28.8" customHeight="1">
-      <c r="A169" s="1" t="n">
+      <c r="A169" t="n">
         <v>168</v>
       </c>
-      <c r="B169" s="4" t="inlineStr">
-        <is>
-          <t>London Court of International Arbitration</t>
-        </is>
-      </c>
-      <c r="C169" s="4" t="inlineStr">
-        <is>
-          <t>Arbitration / Commercial Law</t>
-        </is>
-      </c>
-      <c r="D169" s="13" t="inlineStr">
-        <is>
-          <t>https://www.lcia.org/</t>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Income Tax Bar Association Raipur</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Tax / Legal</t>
+        </is>
+      </c>
+      <c r="D169" s="16" t="inlineStr">
+        <is>
+          <t>https://itbaraipur.org/</t>
         </is>
       </c>
     </row>
     <row r="170" ht="28.8" customHeight="1">
-      <c r="A170" s="1" t="n">
+      <c r="A170" t="n">
         <v>169</v>
       </c>
-      <c r="B170" s="4" t="inlineStr">
-        <is>
-          <t>International Insolvency Institute</t>
-        </is>
-      </c>
-      <c r="C170" s="4" t="inlineStr">
-        <is>
-          <t>Insolvency / Restructuring / Finance</t>
-        </is>
-      </c>
-      <c r="D170" s="13" t="inlineStr">
-        <is>
-          <t>https://iiiglobal.org/</t>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Tax Bar Association Guwahati</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Tax / Legal</t>
+        </is>
+      </c>
+      <c r="D170" s="16" t="inlineStr">
+        <is>
+          <t>https://www.taxbarghy.org/</t>
         </is>
       </c>
     </row>
     <row r="171" ht="28.8" customHeight="1">
-      <c r="A171" s="1" t="n">
+      <c r="A171" t="n">
         <v>170</v>
       </c>
-      <c r="B171" s="4" t="inlineStr">
-        <is>
-          <t>International Association of Insolvency Regulators</t>
-        </is>
-      </c>
-      <c r="C171" s="4" t="inlineStr">
-        <is>
-          <t>Insolvency / Regulation / Finance</t>
-        </is>
-      </c>
-      <c r="D171" s="13" t="inlineStr">
-        <is>
-          <t>https://www.insolvencyreg.org/</t>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Tax Advocates Association of Bengal (TAAB)</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Tax / Legal</t>
+        </is>
+      </c>
+      <c r="D171" s="16" t="inlineStr">
+        <is>
+          <t>https://taab.org.in/</t>
         </is>
       </c>
     </row>
     <row r="172" ht="28.8" customHeight="1">
-      <c r="A172" s="1" t="n">
+      <c r="A172" t="n">
         <v>171</v>
       </c>
-      <c r="B172" s="4" t="inlineStr">
-        <is>
-          <t>International Association of Financial Executives Institutes (IAFEI)</t>
-        </is>
-      </c>
-      <c r="C172" s="4" t="inlineStr">
-        <is>
-          <t>Corporate Finance / Treasury / Financial Management</t>
-        </is>
-      </c>
-      <c r="D172" s="13" t="inlineStr">
-        <is>
-          <t>https://iafei.org/</t>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Ahmedabad Tax Bar Association (ATBA)</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Tax / Legal</t>
+        </is>
+      </c>
+      <c r="D172" s="16" t="inlineStr">
+        <is>
+          <t>https://atba.in/</t>
         </is>
       </c>
     </row>
     <row r="173" ht="28.8" customHeight="1">
-      <c r="A173" s="1" t="n">
+      <c r="A173" t="n">
         <v>172</v>
       </c>
-      <c r="B173" s="4" t="inlineStr">
-        <is>
-          <t>All India Chartered Accountants Society (AICAS)</t>
-        </is>
-      </c>
-      <c r="C173" s="4" t="inlineStr">
-        <is>
-          <t>Tax / Accounting / Finance</t>
-        </is>
-      </c>
-      <c r="D173" s="15" t="inlineStr">
-        <is>
-          <t>https://www.aicas.in/event.html</t>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Karnataka State Chartered Accountants Association (KSCAA)</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Accounting / Tax</t>
+        </is>
+      </c>
+      <c r="D173" s="16" t="inlineStr">
+        <is>
+          <t>https://kscaa.com/kscaa-events/</t>
         </is>
       </c>
     </row>
     <row r="174" ht="28.8" customHeight="1">
-      <c r="A174" s="1" t="n">
+      <c r="A174" t="n">
         <v>173</v>
       </c>
-      <c r="B174" s="4" t="inlineStr">
-        <is>
-          <t>Association of Financial Professionals of India (AFPI)</t>
-        </is>
-      </c>
-      <c r="C174" s="4" t="inlineStr">
-        <is>
-          <t>Finance / Financial Management</t>
-        </is>
-      </c>
-      <c r="D174" s="15" t="inlineStr">
-        <is>
-          <t>https://www.afai.in/event-conferences/#eventcalender</t>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Chartered Accountants Association Surat (CAAS)</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Accounting / Tax</t>
+        </is>
+      </c>
+      <c r="D174" s="16" t="inlineStr">
+        <is>
+          <t>https://www.caasonline.org/events</t>
         </is>
       </c>
     </row>
     <row r="175" ht="28.8" customHeight="1">
-      <c r="A175" s="1" t="n">
+      <c r="A175" t="n">
         <v>174</v>
       </c>
-      <c r="B175" s="4" t="inlineStr">
-        <is>
-          <t>Association of Corporate Treasurers of India (ACTI)</t>
-        </is>
-      </c>
-      <c r="C175" s="4" t="inlineStr">
-        <is>
-          <t>Corporate Finance / Treasury</t>
-        </is>
-      </c>
-      <c r="D175" s="15" t="inlineStr">
-        <is>
-          <t>https://www.treasurers.org/events</t>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Chartered Accountants Association Ahmedabad (CAA)</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Accounting / Tax</t>
+        </is>
+      </c>
+      <c r="D175" s="16" t="inlineStr">
+        <is>
+          <t>https://caa-ahm.org/Event.php</t>
         </is>
       </c>
     </row>
     <row r="176" ht="28.8" customHeight="1">
-      <c r="A176" s="1" t="n">
+      <c r="A176" t="n">
         <v>175</v>
       </c>
-      <c r="B176" s="4" t="inlineStr">
-        <is>
-          <t>Institute of Cost and Management Accountants of India Research Foundation</t>
-        </is>
-      </c>
-      <c r="C176" s="4" t="inlineStr">
-        <is>
-          <t>Accounting / Finance / Cost Management</t>
-        </is>
-      </c>
-      <c r="D176" s="13" t="inlineStr">
-        <is>
-          <t>https://icmai.in/</t>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>ICAI Ahmedabad Branch</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Accounting / Tax</t>
+        </is>
+      </c>
+      <c r="D176" s="16" t="inlineStr">
+        <is>
+          <t>https://icaiahmedabad.com/past-upcoming-events.php</t>
         </is>
       </c>
     </row>
     <row r="177" ht="43.2" customHeight="1">
-      <c r="A177" s="1" t="n">
+      <c r="A177" t="n">
         <v>176</v>
       </c>
-      <c r="B177" s="4" t="inlineStr">
-        <is>
-          <t>Indian Institute of Financial Management</t>
-        </is>
-      </c>
-      <c r="C177" s="4" t="inlineStr">
-        <is>
-          <t>Finance / Financial Management</t>
-        </is>
-      </c>
-      <c r="D177" s="13" t="inlineStr">
-        <is>
-          <t>https://www.iifm.co.in/</t>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>LiveLaw Events</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Legal (aggregator)</t>
+        </is>
+      </c>
+      <c r="D177" s="16" t="inlineStr">
+        <is>
+          <t>https://www.livelaw.in/events</t>
         </is>
       </c>
     </row>
     <row r="178" ht="28.8" customHeight="1">
-      <c r="A178" s="1" t="n">
+      <c r="A178" t="n">
         <v>177</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Bombay Chartered Accountants Society</t>
-        </is>
-      </c>
-      <c r="D178" s="15" t="inlineStr">
-        <is>
-          <t>https://bcasonline.org/upcoming-live-events/</t>
+          <t>ConferenceAlerts India - Law</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Legal (aggregator)</t>
+        </is>
+      </c>
+      <c r="D178" s="16" t="inlineStr">
+        <is>
+          <t>https://www.conferencealerts.in/india/law</t>
         </is>
       </c>
     </row>
     <row r="179" ht="28.8" customHeight="1">
       <c r="A179" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Tax Practitioners Association Indore</t>
+          <t>ConferenceAlerts India - Banking and Finance</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Finance (aggregator)</t>
         </is>
       </c>
       <c r="D179" s="16" t="inlineStr">
         <is>
-          <t>https://tpaindore.com/</t>
+          <t>https://conferencealerts.co.in/banking-and-finance</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Income Tax Bar Association Ahmedabad</t>
+          <t>10times India Finance Events</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Tax / Legal</t>
+          <t>Finance (aggregator)</t>
         </is>
       </c>
       <c r="D180" s="16" t="inlineStr">
         <is>
-          <t>https://incometaxbar.org/</t>
+          <t>https://10times.com/india/finance</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Income Tax Bar Association Raipur</t>
+          <t>ICSI Northern India Regional Council (NIRO)</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Tax / Legal</t>
+          <t>Legal / Corporate</t>
         </is>
       </c>
       <c r="D181" s="16" t="inlineStr">
         <is>
-          <t>https://itbaraipur.org/</t>
+          <t>https://www.icsi.edu/niro/home/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Tax Bar Association Guwahati</t>
+          <t>ICSI Western India Regional Council (WIRO)</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Tax / Legal</t>
+          <t>Legal / Corporate</t>
         </is>
       </c>
       <c r="D182" s="16" t="inlineStr">
         <is>
-          <t>https://www.taxbarghy.org/</t>
+          <t>https://www.icsi.edu/wiro/home/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Tax Advocates Association of Bengal (TAAB)</t>
+          <t>ICAI Chandigarh Branch</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Tax / Legal</t>
+          <t>Accounting / Tax</t>
         </is>
       </c>
       <c r="D183" s="16" t="inlineStr">
         <is>
-          <t>https://taab.org.in/</t>
+          <t>https://chandigarhicai.org/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Ahmedabad Tax Bar Association (ATBA)</t>
+          <t>Delhi Tax Bar Association</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4231,177 +4231,177 @@
       </c>
       <c r="D184" s="16" t="inlineStr">
         <is>
-          <t>https://atba.in/</t>
+          <t>https://delhitaxbar.com/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Karnataka State Chartered Accountants Association (KSCAA)</t>
+          <t>Sales Tax Bar Association Delhi</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Accounting / Tax</t>
+          <t>Tax / Legal</t>
         </is>
       </c>
       <c r="D185" s="16" t="inlineStr">
         <is>
-          <t>https://kscaa.com/kscaa-events/</t>
+          <t>https://salestaxbar.com/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Chartered Accountants Association Surat (CAAS)</t>
+          <t>Rajasthan Tax Consultants Association</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Accounting / Tax</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="D186" s="16" t="inlineStr">
         <is>
-          <t>https://www.caasonline.org/events</t>
+          <t>https://rtcaraj.com/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Chartered Accountants Association Ahmedabad (CAA)</t>
+          <t>Kerala Tax Practitioners Association</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Accounting / Tax</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="D187" s="16" t="inlineStr">
         <is>
-          <t>https://caa-ahm.org/Event.php</t>
+          <t>https://taxpractitioners.in/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ICAI Ahmedabad Branch</t>
+          <t>Insurance Brokers Association of India (IBAI)</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Accounting / Tax</t>
+          <t>Insurance / Finance</t>
         </is>
       </c>
       <c r="D188" s="16" t="inlineStr">
         <is>
-          <t>https://icaiahmedabad.com/past-upcoming-events.php</t>
+          <t>https://ibai.glueup.com/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>LiveLaw Events</t>
+          <t>Bharat Fintech Summit</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Legal (aggregator)</t>
+          <t>Finance / Fintech</t>
         </is>
       </c>
       <c r="D189" s="16" t="inlineStr">
         <is>
-          <t>https://www.livelaw.in/events</t>
+          <t>https://bharatfintechsummit.com/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ConferenceAlerts India - Law</t>
+          <t>ICAI Hyderabad Branch</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Legal (aggregator)</t>
+          <t>Accounting / Tax</t>
         </is>
       </c>
       <c r="D190" s="16" t="inlineStr">
         <is>
-          <t>https://www.conferencealerts.in/india/law</t>
+          <t>https://hydicai.org/event/list</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ConferenceAlerts India - Banking and Finance</t>
+          <t>ICAI Pune Branch</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Finance (aggregator)</t>
+          <t>Accounting / Tax</t>
         </is>
       </c>
       <c r="D191" s="16" t="inlineStr">
         <is>
-          <t>https://conferencealerts.co.in/banking-and-finance</t>
+          <t>https://www.puneicai.org/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>10times India Finance Events</t>
+          <t>ICSI Eastern India Regional Council (EIRO)</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Finance (aggregator)</t>
+          <t>Legal / Corporate</t>
         </is>
       </c>
       <c r="D192" s="16" t="inlineStr">
         <is>
-          <t>https://10times.com/india/finance</t>
+          <t>https://www.icsi.edu/eiro/home/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ICSI Northern India Regional Council (NIRO)</t>
+          <t>ICSI Southern India Regional Council (SIRO)</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4411,197 +4411,197 @@
       </c>
       <c r="D193" s="16" t="inlineStr">
         <is>
-          <t>https://www.icsi.edu/niro/home/</t>
+          <t>https://www.icsi.edu/siro/home/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ICSI Western India Regional Council (WIRO)</t>
+          <t>ConferenceAlerts India - Accounting</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Legal / Corporate</t>
+          <t>Accounting (aggregator)</t>
         </is>
       </c>
       <c r="D194" s="16" t="inlineStr">
         <is>
-          <t>https://www.icsi.edu/wiro/home/</t>
+          <t>https://conferencealerts.co.in/india/accounting</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ICAI Chandigarh Branch</t>
+          <t>Eventbrite India - Legal Conferences</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Accounting / Tax</t>
+          <t>Legal (aggregator)</t>
         </is>
       </c>
       <c r="D195" s="16" t="inlineStr">
         <is>
-          <t>https://chandigarhicai.org/</t>
+          <t>https://www.eventbrite.com/d/india/legal-conferences/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Delhi Tax Bar Association</t>
+          <t>Eventbrite Mumbai - Finance Conferences</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Tax / Legal</t>
+          <t>Finance (aggregator)</t>
         </is>
       </c>
       <c r="D196" s="16" t="inlineStr">
         <is>
-          <t>https://delhitaxbar.com/</t>
+          <t>https://www.eventbrite.com/d/india--mumbai/finance-conference/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Sales Tax Bar Association Delhi</t>
+          <t>TaxGuru Webinars</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Tax / Legal</t>
+          <t>Tax (aggregator/publisher)</t>
         </is>
       </c>
       <c r="D197" s="16" t="inlineStr">
         <is>
-          <t>https://salestaxbar.com/</t>
+          <t>https://shop.taxguru.in/taxguru-free-webinar-registration/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Rajasthan Tax Consultants Association</t>
+          <t>Taxmann Webinars</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Tax (publisher)</t>
         </is>
       </c>
       <c r="D198" s="16" t="inlineStr">
         <is>
-          <t>https://rtcaraj.com/</t>
+          <t>https://www.taxmann.com/webinars/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Kerala Tax Practitioners Association</t>
+          <t>Taxmann Learning - Upcoming Events</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Tax / Legal (publisher)</t>
         </is>
       </c>
       <c r="D199" s="16" t="inlineStr">
         <is>
-          <t>https://taxpractitioners.in/</t>
+          <t>https://www.taxmann.com/learning/upcoming-events</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Insurance Brokers Association of India (IBAI)</t>
+          <t>ClearTax Webinars</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Insurance / Finance</t>
+          <t>Tax / GST (publisher)</t>
         </is>
       </c>
       <c r="D200" s="16" t="inlineStr">
         <is>
-          <t>https://ibai.glueup.com/</t>
+          <t>https://cleartax.in/webinars/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Bharat Fintech Summit</t>
+          <t>SEBI Investor Awareness Programs</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Finance / Fintech</t>
+          <t>Finance / Regulator</t>
         </is>
       </c>
       <c r="D201" s="16" t="inlineStr">
         <is>
-          <t>https://bharatfintechsummit.com/</t>
+          <t>https://investor.sebi.gov.in/program.html?type=2</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>ICAI Hyderabad Branch</t>
+          <t>NISM Investor Education Webinars</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Accounting / Tax</t>
+          <t>Finance / Regulator</t>
         </is>
       </c>
       <c r="D202" s="16" t="inlineStr">
         <is>
-          <t>https://hydicai.org/event/list</t>
+          <t>https://www.nism.ac.in/investor-education-webinars/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ICAI Pune Branch</t>
+          <t>Association of Chartered Accountants Chennai (ACA)</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4611,365 +4611,125 @@
       </c>
       <c r="D203" s="16" t="inlineStr">
         <is>
-          <t>https://www.puneicai.org/</t>
+          <t>https://acachennai.in/upcoming-events.php</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ICSI Eastern India Regional Council (EIRO)</t>
+          <t>SCC Online Blog - Events and Webinars</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Legal / Corporate</t>
+          <t>Legal (aggregator)</t>
         </is>
       </c>
       <c r="D204" s="16" t="inlineStr">
         <is>
-          <t>https://www.icsi.edu/eiro/home/</t>
+          <t>https://www.scconline.com/blog/post/category/news/events-and-webinars/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>ICSI Southern India Regional Council (SIRO)</t>
+          <t>Legally India Events</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Legal / Corporate</t>
+          <t>Legal (aggregator)</t>
         </is>
       </c>
       <c r="D205" s="16" t="inlineStr">
         <is>
-          <t>https://www.icsi.edu/siro/home/</t>
+          <t>https://www.legallyindia.com/home/events</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ConferenceAlerts India - Accounting</t>
+          <t>LegalBots.in Events</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Accounting (aggregator)</t>
+          <t>Legal (aggregator)</t>
         </is>
       </c>
       <c r="D206" s="16" t="inlineStr">
         <is>
-          <t>https://conferencealerts.co.in/india/accounting</t>
+          <t>https://legalbots.in/events</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Eventbrite India - Legal Conferences</t>
+          <t>CA Sansaar - GST Events</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Legal (aggregator)</t>
+          <t>Tax / GST (aggregator)</t>
         </is>
       </c>
       <c r="D207" s="16" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/d/india/legal-conferences/</t>
+          <t>https://www.casansaar.com/events/gst.html</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Eventbrite Mumbai - Finance Conferences</t>
+          <t>GSTN Events and Training</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Finance (aggregator)</t>
+          <t>GST / Regulator</t>
         </is>
       </c>
       <c r="D208" s="16" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/d/india--mumbai/finance-conference/</t>
+          <t>https://www.gstn.org.in/events-training</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>TaxGuru Webinars</t>
+          <t>Townscript India - GST Events</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Tax (aggregator/publisher)</t>
+          <t>Tax / GST (aggregator)</t>
         </is>
       </c>
       <c r="D209" s="16" t="inlineStr">
-        <is>
-          <t>https://shop.taxguru.in/taxguru-free-webinar-registration/</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="n">
-        <v>210</v>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Taxmann Webinars</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Tax (publisher)</t>
-        </is>
-      </c>
-      <c r="D210" s="16" t="inlineStr">
-        <is>
-          <t>https://www.taxmann.com/webinars/</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="n">
-        <v>211</v>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Taxmann Learning - Upcoming Events</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Tax / Legal (publisher)</t>
-        </is>
-      </c>
-      <c r="D211" s="16" t="inlineStr">
-        <is>
-          <t>https://www.taxmann.com/learning/upcoming-events</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="n">
-        <v>212</v>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>ClearTax Webinars</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Tax / GST (publisher)</t>
-        </is>
-      </c>
-      <c r="D212" s="16" t="inlineStr">
-        <is>
-          <t>https://cleartax.in/webinars/</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="n">
-        <v>213</v>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>SEBI Investor Awareness Programs</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Finance / Regulator</t>
-        </is>
-      </c>
-      <c r="D213" s="16" t="inlineStr">
-        <is>
-          <t>https://investor.sebi.gov.in/program.html?type=2</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="n">
-        <v>214</v>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>NISM Investor Education Webinars</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Finance / Regulator</t>
-        </is>
-      </c>
-      <c r="D214" s="16" t="inlineStr">
-        <is>
-          <t>https://www.nism.ac.in/investor-education-webinars/</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="n">
-        <v>215</v>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Association of Chartered Accountants Chennai (ACA)</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Accounting / Tax</t>
-        </is>
-      </c>
-      <c r="D215" s="16" t="inlineStr">
-        <is>
-          <t>https://acachennai.in/upcoming-events.php</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="n">
-        <v>216</v>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>SCC Online Blog - Events and Webinars</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Legal (aggregator)</t>
-        </is>
-      </c>
-      <c r="D216" s="16" t="inlineStr">
-        <is>
-          <t>https://www.scconline.com/blog/post/category/news/events-and-webinars/</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="n">
-        <v>217</v>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Legally India Events</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Legal (aggregator)</t>
-        </is>
-      </c>
-      <c r="D217" s="16" t="inlineStr">
-        <is>
-          <t>https://www.legallyindia.com/home/events</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="n">
-        <v>218</v>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>LegalBots.in Events</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Legal (aggregator)</t>
-        </is>
-      </c>
-      <c r="D218" s="16" t="inlineStr">
-        <is>
-          <t>https://legalbots.in/events</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="n">
-        <v>219</v>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>CA Sansaar - GST Events</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Tax / GST (aggregator)</t>
-        </is>
-      </c>
-      <c r="D219" s="16" t="inlineStr">
-        <is>
-          <t>https://www.casansaar.com/events/gst.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="n">
-        <v>220</v>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>GSTN Events and Training</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>GST / Regulator</t>
-        </is>
-      </c>
-      <c r="D220" s="16" t="inlineStr">
-        <is>
-          <t>https://www.gstn.org.in/events-training</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="n">
-        <v>221</v>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Townscript India - GST Events</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Tax / GST (aggregator)</t>
-        </is>
-      </c>
-      <c r="D221" s="16" t="inlineStr">
         <is>
           <t>https://www.townscript.com/in/india/gst</t>
         </is>
@@ -5062,9 +4822,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId91"/>
@@ -5089,11 +4849,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId120"/>
@@ -5177,18 +4937,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId199"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId212"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
